--- a/reports/screener_2026-08-25.xlsx
+++ b/reports/screener_2026-08-25.xlsx
@@ -1186,10 +1186,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.868716031740068</v>
+        <v>5.86871605417369</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.88646823887783</v>
+        <v>10.88646828049219</v>
       </c>
       <c r="BZ2" t="n">
         <v>42.10015429633837</v>
@@ -1198,7 +1198,7 @@
         <v>28.26125673506212</v>
       </c>
       <c r="CB2" t="n">
-        <v>72.7865533927224</v>
+        <v>72.78655348876849</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -1504,10 +1504,10 @@
         <v>13.60999965667725</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.01575543886303</v>
+        <v>15.01575557945281</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.85422633909091</v>
+        <v>27.85422659988496</v>
       </c>
       <c r="BZ3" t="n">
         <v>38.94870312116058</v>
@@ -1516,13 +1516,13 @@
         <v>23.57226802449605</v>
       </c>
       <c r="CB3" t="n">
-        <v>74.76041635100925</v>
+        <v>74.76041608604787</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.40383479503916</v>
+        <v>48.40383469172596</v>
       </c>
       <c r="CD3" t="n">
-        <v>26.30532738193961</v>
+        <v>26.30532694818076</v>
       </c>
       <c r="CE3" t="n">
         <v>8.655042371031668</v>
@@ -1822,10 +1822,10 @@
         <v>24.54000091552734</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.25388477615138</v>
+        <v>16.25388474454687</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.1509562597608</v>
+        <v>30.15095620113445</v>
       </c>
       <c r="BZ4" t="n">
         <v>74.06720094094243</v>
@@ -1834,13 +1834,13 @@
         <v>53.70833445174577</v>
       </c>
       <c r="CB4" t="n">
-        <v>132.6406024835609</v>
+        <v>132.6406024906445</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.79451766754657</v>
+        <v>25.7945176718956</v>
       </c>
       <c r="CD4" t="n">
-        <v>65.72549926722739</v>
+        <v>65.72549933503295</v>
       </c>
       <c r="CE4" t="n">
         <v>43.53105147803891</v>
@@ -2138,10 +2138,10 @@
         <v>4.190000057220459</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.548072969479675</v>
+        <v>3.548072963759028</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.581675358384796</v>
+        <v>6.581675347772996</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.82159370858454</v>
@@ -2150,25 +2150,25 @@
         <v>8.61209444827186</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.80877192875914</v>
+        <v>24.80877193294405</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.29418312461635</v>
+        <v>11.29418312694294</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.96827545156034</v>
+        <v>10.9682754658171</v>
       </c>
       <c r="CE5" t="n">
         <v>5.153758142621466</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.238596705673224</v>
+        <v>9.238596706668487</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.790184949916098</v>
+        <v>9.790184957044481</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.811166454924487</v>
+        <v>8.811166461340033</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -2180,10 +2180,10 @@
         <v>7</v>
       </c>
       <c r="CL5" t="n">
-        <v>110.2903659807966</v>
+        <v>110.2903661339122</v>
       </c>
       <c r="CM5" t="n">
-        <v>120.4915651433637</v>
+        <v>120.491565167117</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>48.2400016784668</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.38294919383472</v>
+        <v>18.38294926403854</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.10037075456341</v>
+        <v>34.10037088479149</v>
       </c>
       <c r="BZ6" t="n">
         <v>76.54850565744731</v>
@@ -2460,23 +2460,23 @@
         <v>57.29789298233228</v>
       </c>
       <c r="CB6" t="n">
-        <v>103.9926848972992</v>
+        <v>103.9926847905225</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.49285961758768</v>
+        <v>48.49285960086324</v>
       </c>
       <c r="CD6" t="n">
-        <v>61.42668270614001</v>
+        <v>61.42668256503595</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>44.38117130585827</v>
+        <v>44.38117135178514</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.29661518607554</v>
+        <v>41.29661524282736</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.16695366746799</v>
+        <v>37.16695371854463</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -2488,10 +2488,10 @@
         <v>4.2</v>
       </c>
       <c r="CL6" t="n">
-        <v>-22.954078826124</v>
+        <v>-22.95407872024374</v>
       </c>
       <c r="CM6" t="n">
-        <v>-7.999233495738068</v>
+        <v>-7.999233400533123</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -2774,10 +2774,10 @@
         <v>4.510000228881836</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.052774384387222</v>
+        <v>3.052774388407022</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.662896483038297</v>
+        <v>5.662896490495025</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.93452446594899</v>
@@ -2786,7 +2786,7 @@
         <v>8.695832933160331</v>
       </c>
       <c r="CB7" t="n">
-        <v>23.89368935382005</v>
+        <v>23.89368936600127</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -2798,7 +2798,7 @@
         <v>5.186344183602181</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.39433293472936</v>
+        <v>11.39433293753478</v>
       </c>
       <c r="CG7" t="n">
         <v>11.57513776217851</v>
@@ -2819,7 +2819,7 @@
         <v>130.9894336423016</v>
       </c>
       <c r="CM7" t="n">
-        <v>152.6459502542943</v>
+        <v>152.6459503164988</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>-6.237000363129841</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-43.27722875916081</v>
+        <v>-43.27722523663176</v>
       </c>
       <c r="DA7" t="b">
         <v>1</v>
@@ -3102,10 +3102,10 @@
         <v>32.58000183105469</v>
       </c>
       <c r="BX8" t="n">
-        <v>24.20136284928149</v>
+        <v>24.20136285624547</v>
       </c>
       <c r="BY8" t="n">
-        <v>44.89352808541717</v>
+        <v>44.89352809833534</v>
       </c>
       <c r="BZ8" t="n">
         <v>50.78647344252641</v>
@@ -3114,25 +3114,25 @@
         <v>22.31995674309305</v>
       </c>
       <c r="CB8" t="n">
-        <v>69.38361258498088</v>
+        <v>69.38361253173336</v>
       </c>
       <c r="CC8" t="n">
-        <v>53.12760892459693</v>
+        <v>53.12760891626809</v>
       </c>
       <c r="CD8" t="n">
-        <v>28.79645703198769</v>
+        <v>28.79645699130806</v>
       </c>
       <c r="CE8" t="n">
         <v>25.44421854454374</v>
       </c>
       <c r="CF8" t="n">
-        <v>39.86915227580342</v>
+        <v>39.86915226550668</v>
       </c>
       <c r="CG8" t="n">
-        <v>36.84499255870243</v>
+        <v>36.8449925448217</v>
       </c>
       <c r="CH8" t="n">
-        <v>33.16049330283219</v>
+        <v>33.16049329033953</v>
       </c>
       <c r="CI8" t="n">
         <v>8</v>
@@ -3144,10 +3144,10 @@
         <v>3.1</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.781741679413251</v>
+        <v>1.781741641068701</v>
       </c>
       <c r="CM8" t="n">
-        <v>22.37308175287098</v>
+        <v>22.37308172126653</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
         <v>41.34999847412109</v>
       </c>
       <c r="BX9" t="n">
-        <v>121.1494722791397</v>
+        <v>121.1494724636367</v>
       </c>
       <c r="BY9" t="n">
-        <v>224.7322710778041</v>
+        <v>224.732271420046</v>
       </c>
       <c r="BZ9" t="n">
         <v>134.6160883985514</v>
@@ -3464,13 +3464,13 @@
         <v>57.31088302327341</v>
       </c>
       <c r="CF9" t="n">
-        <v>139.1218204678536</v>
+        <v>139.1218205336959</v>
       </c>
       <c r="CG9" t="n">
-        <v>122.0409500875877</v>
+        <v>122.0409501798362</v>
       </c>
       <c r="CH9" t="n">
-        <v>109.8368550788289</v>
+        <v>109.8368551618526</v>
       </c>
       <c r="CI9" t="n">
         <v>8</v>
@@ -3482,10 +3482,10 @@
         <v>5.4</v>
       </c>
       <c r="CL9" t="n">
-        <v>165.627228856055</v>
+        <v>165.6272290568378</v>
       </c>
       <c r="CM9" t="n">
-        <v>236.4493968601304</v>
+        <v>236.4493970193622</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
         <v>15.75</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.426879066780337</v>
+        <v>6.426879104229907</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.92186066887752</v>
+        <v>11.92186073834648</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.38777372262773</v>
@@ -3780,19 +3780,19 @@
         <v>18.61263551273508</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.14401442523295</v>
+        <v>35.14401436418127</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.22841486024859</v>
+        <v>12.29380744597264</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.3287793399054</v>
+        <v>20.32877926143806</v>
       </c>
       <c r="CE10" t="n">
         <v>17.80443971854372</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.20398832116729</v>
+        <v>20.21333010912071</v>
       </c>
       <c r="CG10" t="n">
         <v>18.61263551273508</v>
@@ -3813,7 +3813,7 @@
         <v>6.357917215629039</v>
       </c>
       <c r="CM10" t="n">
-        <v>28.27929092804627</v>
+        <v>28.3386038674331</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -4096,10 +4096,10 @@
         <v>32.97999954223633</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.05539027908186</v>
+        <v>46.05539021865696</v>
       </c>
       <c r="BY11" t="n">
-        <v>85.43274896769684</v>
+        <v>85.43274885560866</v>
       </c>
       <c r="BZ11" t="n">
         <v>69.25277241436312</v>
@@ -4120,7 +4120,7 @@
         <v>25.25865933859778</v>
       </c>
       <c r="CF11" t="n">
-        <v>78.35175846160264</v>
+        <v>78.35175843695791</v>
       </c>
       <c r="CG11" t="n">
         <v>69.25277241436312</v>
@@ -4141,7 +4141,7 @@
         <v>88.98573692551504</v>
       </c>
       <c r="CM11" t="n">
-        <v>137.5735583660645</v>
+        <v>137.5735582913383</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -4434,10 +4434,10 @@
         <v>45.97999954223633</v>
       </c>
       <c r="BX12" t="n">
-        <v>127.6301657283526</v>
+        <v>127.6301650560994</v>
       </c>
       <c r="BY12" t="n">
-        <v>236.753957426094</v>
+        <v>236.7539561790644</v>
       </c>
       <c r="BZ12" t="n">
         <v>134.1927299415487</v>
@@ -4458,13 +4458,13 @@
         <v>55.9815638034286</v>
       </c>
       <c r="CF12" t="n">
-        <v>141.0136557775356</v>
+        <v>141.0136555376253</v>
       </c>
       <c r="CG12" t="n">
-        <v>125.0879897431476</v>
+        <v>125.087989407021</v>
       </c>
       <c r="CH12" t="n">
-        <v>112.5791907688329</v>
+        <v>112.5791904663189</v>
       </c>
       <c r="CI12" t="n">
         <v>8</v>
@@ -4476,10 +4476,10 @@
         <v>5.4</v>
       </c>
       <c r="CL12" t="n">
-        <v>144.8438275111765</v>
+        <v>144.8438268532515</v>
       </c>
       <c r="CM12" t="n">
-        <v>206.6847698595631</v>
+        <v>206.684769337792</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>-4.327813207567233</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-13.4422178413344</v>
+        <v>-13.44221145597109</v>
       </c>
       <c r="DA12" t="b">
         <v>1</v>
@@ -4762,10 +4762,10 @@
         <v>7.449999809265137</v>
       </c>
       <c r="BX13" t="n">
-        <v>3.363729729177499</v>
+        <v>3.36372973558846</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.239718647624262</v>
+        <v>6.239718659516593</v>
       </c>
       <c r="BZ13" t="n">
         <v>21.74284085303151</v>
@@ -4774,7 +4774,7 @@
         <v>14.8939109083963</v>
       </c>
       <c r="CB13" t="n">
-        <v>34.98727166243657</v>
+        <v>34.98727168220606</v>
       </c>
       <c r="CC13" t="n">
         <v>10.95072400487419</v>
@@ -5070,10 +5070,10 @@
         <v>19.13999938964844</v>
       </c>
       <c r="BX14" t="n">
-        <v>13.15731116818023</v>
+        <v>13.15731118896105</v>
       </c>
       <c r="BY14" t="n">
-        <v>24.40681221697433</v>
+        <v>24.40681225552275</v>
       </c>
       <c r="BZ14" t="n">
         <v>20.45201547684208</v>
@@ -5082,7 +5082,7 @@
         <v>12.7798316087502</v>
       </c>
       <c r="CB14" t="n">
-        <v>34.6124474630664</v>
+        <v>34.61244748652861</v>
       </c>
       <c r="CC14" t="n">
         <v>22.8984489302328</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="CE14" t="inlineStr"/>
       <c r="CF14" t="n">
-        <v>20.22864694805736</v>
+        <v>20.22864696288967</v>
       </c>
       <c r="CG14" t="n">
         <v>21.67523220353744</v>
@@ -5113,7 +5113,7 @@
         <v>1.9211578122313</v>
       </c>
       <c r="CM14" t="n">
-        <v>5.687813966168154</v>
+        <v>5.687814043661943</v>
       </c>
       <c r="CN14" t="inlineStr">
         <is>
@@ -5396,10 +5396,10 @@
         <v>17.53000068664551</v>
       </c>
       <c r="BX15" t="n">
-        <v>10.74426543689855</v>
+        <v>10.7442654659961</v>
       </c>
       <c r="BY15" t="n">
-        <v>19.93061238544681</v>
+        <v>19.93061243942277</v>
       </c>
       <c r="BZ15" t="n">
         <v>37.89111078271664</v>
@@ -5408,25 +5408,25 @@
         <v>37.31646064248518</v>
       </c>
       <c r="CB15" t="n">
-        <v>42.403902487053</v>
+        <v>42.40390249981662</v>
       </c>
       <c r="CC15" t="n">
-        <v>34.52246248428089</v>
+        <v>34.52246247818044</v>
       </c>
       <c r="CD15" t="n">
-        <v>18.86931530664446</v>
+        <v>18.86931527289594</v>
       </c>
       <c r="CE15" t="n">
         <v>31.49264348607277</v>
       </c>
       <c r="CF15" t="n">
-        <v>31.77521536781424</v>
+        <v>31.77521537165577</v>
       </c>
       <c r="CG15" t="n">
-        <v>34.52246248428089</v>
+        <v>34.52246247818044</v>
       </c>
       <c r="CH15" t="n">
-        <v>31.0702162358528</v>
+        <v>31.07021623036239</v>
       </c>
       <c r="CI15" t="n">
         <v>7</v>
@@ -5438,10 +5438,10 @@
         <v>3.9</v>
       </c>
       <c r="CL15" t="n">
-        <v>77.24024540125849</v>
+        <v>77.24024536993845</v>
       </c>
       <c r="CM15" t="n">
-        <v>81.26191741692772</v>
+        <v>81.26191743884171</v>
       </c>
       <c r="CN15" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="BX16" t="n">
-        <v>10.37863321645883</v>
+        <v>10.37863327533605</v>
       </c>
       <c r="BY16" t="n">
-        <v>19.25236461653113</v>
+        <v>19.25236472574838</v>
       </c>
       <c r="BZ16" t="n">
         <v>25.85122324877091</v>
@@ -5736,25 +5736,25 @@
         <v>18.56165831752405</v>
       </c>
       <c r="CB16" t="n">
-        <v>39.76450202393809</v>
+        <v>39.76450197392393</v>
       </c>
       <c r="CC16" t="n">
-        <v>24.31404885344061</v>
+        <v>24.31404882939119</v>
       </c>
       <c r="CD16" t="n">
-        <v>13.00688761725288</v>
+        <v>13.00688748824112</v>
       </c>
       <c r="CE16" t="n">
         <v>10.35999965667725</v>
       </c>
       <c r="CF16" t="n">
-        <v>20.18616469382422</v>
+        <v>20.18616468945161</v>
       </c>
       <c r="CG16" t="n">
-        <v>18.90701146702759</v>
+        <v>18.90701152163621</v>
       </c>
       <c r="CH16" t="n">
-        <v>17.01631032032483</v>
+        <v>17.01631036947259</v>
       </c>
       <c r="CI16" t="n">
         <v>8</v>
@@ -5766,10 +5766,10 @@
         <v>3.8</v>
       </c>
       <c r="CL16" t="n">
-        <v>64.25010506016231</v>
+        <v>64.25010553456157</v>
       </c>
       <c r="CM16" t="n">
-        <v>94.84715601137876</v>
+        <v>94.84715596917211</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -6052,10 +6052,10 @@
         <v>11.28999996185303</v>
       </c>
       <c r="BX17" t="n">
-        <v>9.774107116375554</v>
+        <v>9.774107176349089</v>
       </c>
       <c r="BY17" t="n">
-        <v>18.13096870087665</v>
+        <v>18.13096881212756</v>
       </c>
       <c r="BZ17" t="n">
         <v>23.1209427348613</v>
@@ -6064,25 +6064,25 @@
         <v>13.6472321924953</v>
       </c>
       <c r="CB17" t="n">
-        <v>35.00095097889564</v>
+        <v>35.00095079985264</v>
       </c>
       <c r="CC17" t="n">
-        <v>25.51476119598885</v>
+        <v>25.51476115415504</v>
       </c>
       <c r="CD17" t="n">
-        <v>13.36818444215321</v>
+        <v>13.36818424804047</v>
       </c>
       <c r="CE17" t="n">
         <v>9.880299501333878</v>
       </c>
       <c r="CF17" t="n">
-        <v>18.55468085787255</v>
+        <v>18.55468082740191</v>
       </c>
       <c r="CG17" t="n">
-        <v>15.88910044668598</v>
+        <v>15.88910050231143</v>
       </c>
       <c r="CH17" t="n">
-        <v>14.30019040201738</v>
+        <v>14.30019045208029</v>
       </c>
       <c r="CI17" t="n">
         <v>8</v>
@@ -6094,10 +6094,10 @@
         <v>3.6</v>
       </c>
       <c r="CL17" t="n">
-        <v>26.66244863007323</v>
+        <v>26.66244907350024</v>
       </c>
       <c r="CM17" t="n">
-        <v>64.34615518658661</v>
+        <v>64.34615491669614</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="BX18" t="n">
-        <v>5.044350409047963</v>
+        <v>5.044350378841198</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.357270008783971</v>
+        <v>9.357269952750423</v>
       </c>
       <c r="BZ18" t="n">
         <v>8.453839145587175</v>
@@ -6700,10 +6700,10 @@
         <v>11.07999992370605</v>
       </c>
       <c r="BX19" t="n">
-        <v>3.454302384211566</v>
+        <v>3.454302382804934</v>
       </c>
       <c r="BY19" t="n">
-        <v>6.407730922712454</v>
+        <v>6.407730920103153</v>
       </c>
       <c r="BZ19" t="n">
         <v>20.4470750681205</v>
@@ -6712,13 +6712,13 @@
         <v>19.3263652032129</v>
       </c>
       <c r="CB19" t="n">
-        <v>22.0038575399476</v>
+        <v>22.00385754004261</v>
       </c>
       <c r="CC19" t="n">
-        <v>16.46863777169369</v>
+        <v>16.46863777196926</v>
       </c>
       <c r="CD19" t="n">
-        <v>13.7197938541165</v>
+        <v>13.71979385590022</v>
       </c>
       <c r="CE19" t="n">
         <v>30.3956356510297</v>
@@ -6774,7 +6774,7 @@
         <v>-18.94659940111765</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-32.89649636084019</v>
+        <v>-32.89648038436899</v>
       </c>
       <c r="DA19" t="b">
         <v>1</v>
@@ -7018,10 +7018,10 @@
         <v>27.52000045776367</v>
       </c>
       <c r="BX20" t="n">
-        <v>7.290978505888661</v>
+        <v>7.290978493448117</v>
       </c>
       <c r="BY20" t="n">
-        <v>13.52476512842347</v>
+        <v>13.52476510534626</v>
       </c>
       <c r="BZ20" t="n">
         <v>36.57372177185242</v>
@@ -7030,19 +7030,19 @@
         <v>28.87454744278962</v>
       </c>
       <c r="CB20" t="n">
-        <v>45.93352493983287</v>
+        <v>45.93352495810291</v>
       </c>
       <c r="CC20" t="n">
-        <v>26.49482250051946</v>
+        <v>26.49482250355711</v>
       </c>
       <c r="CD20" t="n">
-        <v>29.81102743456123</v>
+        <v>29.81102745702587</v>
       </c>
       <c r="CE20" t="n">
         <v>24.2620728130642</v>
       </c>
       <c r="CF20" t="n">
-        <v>29.35349743300618</v>
+        <v>29.35349743596263</v>
       </c>
       <c r="CG20" t="n">
         <v>28.87454744278962</v>
@@ -7063,7 +7063,7 @@
         <v>-5.570158916260349</v>
       </c>
       <c r="CM20" t="n">
-        <v>6.662416223635126</v>
+        <v>6.662416234378021</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>-5.331954775825187</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-21.99140136548733</v>
+        <v>-21.99140983840919</v>
       </c>
       <c r="DA20" t="b">
         <v>1</v>
@@ -7346,10 +7346,10 @@
         <v>22.06999969482422</v>
       </c>
       <c r="BX21" t="n">
-        <v>3.108072445623536</v>
+        <v>3.108072443831099</v>
       </c>
       <c r="BY21" t="n">
-        <v>5.76547438663166</v>
+        <v>5.765474383306688</v>
       </c>
       <c r="BZ21" t="n">
         <v>33.57376532220675</v>
@@ -7358,7 +7358,7 @@
         <v>28.04300293143303</v>
       </c>
       <c r="CB21" t="n">
-        <v>43.00378985776037</v>
+        <v>43.00378985487929</v>
       </c>
       <c r="CC21" t="n">
         <v>10.85340539909456</v>
@@ -7644,10 +7644,10 @@
         <v>38.90000152587891</v>
       </c>
       <c r="BX22" t="n">
-        <v>35.62892560050491</v>
+        <v>35.62892557839169</v>
       </c>
       <c r="BY22" t="n">
-        <v>51.87571567433516</v>
+        <v>51.87571564213831</v>
       </c>
       <c r="BZ22" t="n">
         <v>50.25590259243982</v>
@@ -7664,13 +7664,13 @@
       </c>
       <c r="CE22" t="inlineStr"/>
       <c r="CF22" t="n">
-        <v>49.31617721277441</v>
+        <v>49.31617719919689</v>
       </c>
       <c r="CG22" t="n">
-        <v>51.06580913338749</v>
+        <v>51.06580911728906</v>
       </c>
       <c r="CH22" t="n">
-        <v>45.95922822004874</v>
+        <v>45.95922820556016</v>
       </c>
       <c r="CI22" t="n">
         <v>4</v>
@@ -7682,10 +7682,10 @@
         <v>1.7</v>
       </c>
       <c r="CL22" t="n">
-        <v>18.14711161251128</v>
+        <v>18.14711157526556</v>
       </c>
       <c r="CM22" t="n">
-        <v>26.77680020132123</v>
+        <v>26.77680016641757</v>
       </c>
       <c r="CN22" t="inlineStr">
         <is>
@@ -7968,10 +7968,10 @@
         <v>32.75</v>
       </c>
       <c r="BX23" t="n">
-        <v>3.249356692527549</v>
+        <v>3.249356697068481</v>
       </c>
       <c r="BY23" t="n">
-        <v>6.027556664638603</v>
+        <v>6.027556673062032</v>
       </c>
       <c r="BZ23" t="n">
         <v>33.45701619121048</v>
@@ -7980,7 +7980,7 @@
         <v>23.42786572511178</v>
       </c>
       <c r="CB23" t="n">
-        <v>41.38326859640598</v>
+        <v>41.38326860130753</v>
       </c>
       <c r="CC23" t="n">
         <v>10.59424454785779</v>
@@ -8050,7 +8050,7 @@
         <v>0.738239590458023</v>
       </c>
       <c r="CZ23" t="n">
-        <v>-31.31834368818209</v>
+        <v>-31.318349352401</v>
       </c>
       <c r="DA23" t="b">
         <v>1</v>
@@ -8274,10 +8274,10 @@
         <v>14.77999973297119</v>
       </c>
       <c r="BX24" t="n">
-        <v>9.186484945828067</v>
+        <v>9.186484878581913</v>
       </c>
       <c r="BY24" t="n">
-        <v>17.04092957451106</v>
+        <v>17.04092944976945</v>
       </c>
       <c r="BZ24" t="n">
         <v>31.89495056382219</v>
@@ -8286,23 +8286,23 @@
         <v>30.33345456974609</v>
       </c>
       <c r="CB24" t="n">
-        <v>36.78693480727625</v>
+        <v>36.78693478697259</v>
       </c>
       <c r="CC24" t="n">
-        <v>25.58128744616013</v>
+        <v>25.58128745942417</v>
       </c>
       <c r="CD24" t="n">
-        <v>16.38749076540083</v>
+        <v>16.38749084901738</v>
       </c>
       <c r="CE24" t="inlineStr"/>
       <c r="CF24" t="n">
-        <v>20.92591313258036</v>
+        <v>20.92591308789943</v>
       </c>
       <c r="CG24" t="n">
-        <v>21.31110851033559</v>
+        <v>21.31110845459681</v>
       </c>
       <c r="CH24" t="n">
-        <v>19.17999765930204</v>
+        <v>19.17999760913713</v>
       </c>
       <c r="CI24" t="n">
         <v>4</v>
@@ -8314,10 +8314,10 @@
         <v>3.5</v>
       </c>
       <c r="CL24" t="n">
-        <v>29.76994591221365</v>
+        <v>29.7699455728029</v>
       </c>
       <c r="CM24" t="n">
-        <v>41.58263539003239</v>
+        <v>41.58263508772568</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>-7.171627471148123</v>
       </c>
       <c r="CZ24" t="n">
-        <v>-18.74746959920818</v>
+        <v>-18.74747840191868</v>
       </c>
       <c r="DA24" t="b">
         <v>1</v>
@@ -8580,35 +8580,35 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BX25" t="n">
-        <v>8.627042016972684</v>
+        <v>8.627042072234111</v>
       </c>
       <c r="BY25" t="n">
-        <v>14.3473090922331</v>
+        <v>14.34730902416064</v>
       </c>
       <c r="BZ25" t="n">
-        <v>19.54486218349647</v>
+        <v>19.54486196556696</v>
       </c>
       <c r="CA25" t="n">
         <v>17.74926644976348</v>
       </c>
       <c r="CB25" t="n">
-        <v>23.93539535853802</v>
+        <v>23.93539530781762</v>
       </c>
       <c r="CC25" t="n">
-        <v>17.38495031182219</v>
+        <v>17.38495029677088</v>
       </c>
       <c r="CD25" t="n">
-        <v>9.719867294471685</v>
+        <v>9.719867200323893</v>
       </c>
       <c r="CE25" t="inlineStr"/>
       <c r="CF25" t="n">
-        <v>14.97604090113111</v>
+        <v>14.97604083968315</v>
       </c>
       <c r="CG25" t="n">
-        <v>15.86612970202765</v>
+        <v>15.86612966046576</v>
       </c>
       <c r="CH25" t="n">
-        <v>14.27951673182488</v>
+        <v>14.27951669441919</v>
       </c>
       <c r="CI25" t="n">
         <v>4</v>
@@ -8620,10 +8620,10 @@
         <v>2.3</v>
       </c>
       <c r="CL25" t="n">
-        <v>11.12464052854489</v>
+        <v>11.12464023744999</v>
       </c>
       <c r="CM25" t="n">
-        <v>16.54506191865357</v>
+        <v>16.54506144045931</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -8906,10 +8906,10 @@
         <v>5.880000114440918</v>
       </c>
       <c r="BX26" t="n">
-        <v>6.975750809416621</v>
+        <v>6.975750786425684</v>
       </c>
       <c r="BY26" t="n">
-        <v>12.94001775146783</v>
+        <v>12.94001770881964</v>
       </c>
       <c r="BZ26" t="n">
         <v>5.605036080312384</v>
@@ -8930,7 +8930,7 @@
         <v>5.348622529323849</v>
       </c>
       <c r="CF26" t="n">
-        <v>7.296291364832035</v>
+        <v>7.296291356627144</v>
       </c>
       <c r="CG26" t="n">
         <v>5.869184706822859</v>
@@ -8951,7 +8951,7 @@
         <v>-10.16554195011574</v>
       </c>
       <c r="CM26" t="n">
-        <v>24.0865854222144</v>
+        <v>24.08658528267544</v>
       </c>
       <c r="CN26" t="inlineStr">
         <is>
@@ -9224,10 +9224,10 @@
         <v>39.43999862670898</v>
       </c>
       <c r="BX27" t="n">
-        <v>20.16127574530427</v>
+        <v>20.1612756175048</v>
       </c>
       <c r="BY27" t="n">
-        <v>37.39916650753941</v>
+        <v>37.3991662704714</v>
       </c>
       <c r="BZ27" t="n">
         <v>57.05021635413689</v>
@@ -9236,23 +9236,23 @@
         <v>43.06721646336476</v>
       </c>
       <c r="CB27" t="n">
-        <v>64.10972928489694</v>
+        <v>64.10972949124397</v>
       </c>
       <c r="CC27" t="n">
-        <v>45.28400689669809</v>
+        <v>45.28400693591092</v>
       </c>
       <c r="CD27" t="n">
-        <v>32.4309406972427</v>
+        <v>32.43094094972332</v>
       </c>
       <c r="CE27" t="inlineStr"/>
       <c r="CF27" t="n">
-        <v>39.97366637591966</v>
+        <v>39.973666294506</v>
       </c>
       <c r="CG27" t="n">
-        <v>41.34158670211875</v>
+        <v>41.34158660319116</v>
       </c>
       <c r="CH27" t="n">
-        <v>37.20742803190687</v>
+        <v>37.20742794287204</v>
       </c>
       <c r="CI27" t="n">
         <v>4</v>
@@ -9264,10 +9264,10 @@
         <v>2.8</v>
       </c>
       <c r="CL27" t="n">
-        <v>-5.660676147412957</v>
+        <v>-5.6606763731605</v>
       </c>
       <c r="CM27" t="n">
-        <v>1.353113001503181</v>
+        <v>1.353112795079103</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>-6.937240130506206</v>
       </c>
       <c r="CZ27" t="n">
-        <v>-19.01273240052025</v>
+        <v>-19.01272601806555</v>
       </c>
       <c r="DA27" t="b">
         <v>1</v>
@@ -9550,37 +9550,37 @@
         <v>26.45999908447266</v>
       </c>
       <c r="BX28" t="n">
-        <v>16.91893493941736</v>
+        <v>16.91893502410094</v>
       </c>
       <c r="BY28" t="n">
-        <v>28.67982834187544</v>
+        <v>28.67982835307078</v>
       </c>
       <c r="BZ28" t="n">
-        <v>49.21350852397792</v>
+        <v>49.21350829686259</v>
       </c>
       <c r="CA28" t="n">
         <v>53.99475108321082</v>
       </c>
       <c r="CB28" t="n">
-        <v>57.93925170267027</v>
+        <v>57.93925173409952</v>
       </c>
       <c r="CC28" t="n">
-        <v>43.01388446006595</v>
+        <v>43.01388444492227</v>
       </c>
       <c r="CD28" t="n">
-        <v>24.4065726658507</v>
+        <v>24.40657257113381</v>
       </c>
       <c r="CE28" t="n">
         <v>30.06721996094383</v>
       </c>
       <c r="CF28" t="n">
-        <v>38.02924395975153</v>
+        <v>38.02924393354307</v>
       </c>
       <c r="CG28" t="n">
-        <v>36.54055221050488</v>
+        <v>36.54055220293305</v>
       </c>
       <c r="CH28" t="n">
-        <v>32.8864969894544</v>
+        <v>32.88649698263975</v>
       </c>
       <c r="CI28" t="n">
         <v>8</v>
@@ -9592,10 +9592,10 @@
         <v>3.4</v>
       </c>
       <c r="CL28" t="n">
-        <v>24.28759685314186</v>
+        <v>24.2875968273873</v>
       </c>
       <c r="CM28" t="n">
-        <v>43.72352711859306</v>
+        <v>43.7235270195437</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -9878,37 +9878,37 @@
         <v>15.3100004196167</v>
       </c>
       <c r="BX29" t="n">
-        <v>5.939526977341711</v>
+        <v>5.939526957524716</v>
       </c>
       <c r="BY29" t="n">
-        <v>8.534880597078802</v>
+        <v>8.534880613439464</v>
       </c>
       <c r="BZ29" t="n">
-        <v>10.81501542279409</v>
+        <v>10.81501547960945</v>
       </c>
       <c r="CA29" t="n">
         <v>11.65944891202323</v>
       </c>
       <c r="CB29" t="n">
-        <v>9.810403792240514</v>
+        <v>9.810403824194951</v>
       </c>
       <c r="CC29" t="n">
-        <v>14.90925677619887</v>
+        <v>14.90925678315233</v>
       </c>
       <c r="CD29" t="n">
-        <v>5.384140018563597</v>
+        <v>5.384140050651277</v>
       </c>
       <c r="CE29" t="n">
         <v>10.69689722735973</v>
       </c>
       <c r="CF29" t="n">
-        <v>9.718696215450066</v>
+        <v>9.718696230994393</v>
       </c>
       <c r="CG29" t="n">
-        <v>10.25365050980012</v>
+        <v>10.25365052577734</v>
       </c>
       <c r="CH29" t="n">
-        <v>9.22828545882011</v>
+        <v>9.228285473199609</v>
       </c>
       <c r="CI29" t="n">
         <v>8</v>
@@ -9920,10 +9920,10 @@
         <v>2.8</v>
       </c>
       <c r="CL29" t="n">
-        <v>-39.72380662383321</v>
+        <v>-39.72380652991093</v>
       </c>
       <c r="CM29" t="n">
-        <v>-36.52060124702869</v>
+        <v>-36.52060114549814</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -10762,10 +10762,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.868716031740068</v>
+        <v>5.86871605417369</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.88646823887783</v>
+        <v>10.88646828049219</v>
       </c>
       <c r="BZ2" t="n">
         <v>42.10015429633837</v>
@@ -10774,7 +10774,7 @@
         <v>28.26125673506212</v>
       </c>
       <c r="CB2" t="n">
-        <v>72.7865533927224</v>
+        <v>72.78655348876849</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -11080,10 +11080,10 @@
         <v>13.60999965667725</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.01575543886303</v>
+        <v>15.01575557945281</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.85422633909091</v>
+        <v>27.85422659988496</v>
       </c>
       <c r="BZ3" t="n">
         <v>38.94870312116058</v>
@@ -11092,13 +11092,13 @@
         <v>23.57226802449605</v>
       </c>
       <c r="CB3" t="n">
-        <v>74.76041635100925</v>
+        <v>74.76041608604787</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.40383479503916</v>
+        <v>48.40383469172596</v>
       </c>
       <c r="CD3" t="n">
-        <v>26.30532738193961</v>
+        <v>26.30532694818076</v>
       </c>
       <c r="CE3" t="n">
         <v>8.655042371031668</v>
@@ -11398,10 +11398,10 @@
         <v>24.54000091552734</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.25388477615138</v>
+        <v>16.25388474454687</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.1509562597608</v>
+        <v>30.15095620113445</v>
       </c>
       <c r="BZ4" t="n">
         <v>74.06720094094243</v>
@@ -11410,13 +11410,13 @@
         <v>53.70833445174577</v>
       </c>
       <c r="CB4" t="n">
-        <v>132.6406024835609</v>
+        <v>132.6406024906445</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.79451766754657</v>
+        <v>25.7945176718956</v>
       </c>
       <c r="CD4" t="n">
-        <v>65.72549926722739</v>
+        <v>65.72549933503295</v>
       </c>
       <c r="CE4" t="n">
         <v>43.53105147803891</v>
@@ -11714,10 +11714,10 @@
         <v>4.190000057220459</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.548072969479675</v>
+        <v>3.548072963759028</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.581675358384796</v>
+        <v>6.581675347772996</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.82159370858454</v>
@@ -11726,25 +11726,25 @@
         <v>8.61209444827186</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.80877192875914</v>
+        <v>24.80877193294405</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.29418312461635</v>
+        <v>11.29418312694294</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.96827545156034</v>
+        <v>10.9682754658171</v>
       </c>
       <c r="CE5" t="n">
         <v>5.153758142621466</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.238596705673224</v>
+        <v>9.238596706668487</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.790184949916098</v>
+        <v>9.790184957044481</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.811166454924487</v>
+        <v>8.811166461340033</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -11756,10 +11756,10 @@
         <v>7</v>
       </c>
       <c r="CL5" t="n">
-        <v>110.2903659807966</v>
+        <v>110.2903661339122</v>
       </c>
       <c r="CM5" t="n">
-        <v>120.4915651433637</v>
+        <v>120.491565167117</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -12024,10 +12024,10 @@
         <v>48.2400016784668</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.38294919383472</v>
+        <v>18.38294926403854</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.10037075456341</v>
+        <v>34.10037088479149</v>
       </c>
       <c r="BZ6" t="n">
         <v>76.54850565744731</v>
@@ -12036,23 +12036,23 @@
         <v>57.29789298233228</v>
       </c>
       <c r="CB6" t="n">
-        <v>103.9926848972992</v>
+        <v>103.9926847905225</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.49285961758768</v>
+        <v>48.49285960086324</v>
       </c>
       <c r="CD6" t="n">
-        <v>61.42668270614001</v>
+        <v>61.42668256503595</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>44.38117130585827</v>
+        <v>44.38117135178514</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.29661518607554</v>
+        <v>41.29661524282736</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.16695366746799</v>
+        <v>37.16695371854463</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -12064,10 +12064,10 @@
         <v>4.2</v>
       </c>
       <c r="CL6" t="n">
-        <v>-22.954078826124</v>
+        <v>-22.95407872024374</v>
       </c>
       <c r="CM6" t="n">
-        <v>-7.999233495738068</v>
+        <v>-7.999233400533123</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -12350,10 +12350,10 @@
         <v>4.510000228881836</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.052774384387222</v>
+        <v>3.052774388407022</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.662896483038297</v>
+        <v>5.662896490495025</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.93452446594899</v>
@@ -12362,7 +12362,7 @@
         <v>8.695832933160331</v>
       </c>
       <c r="CB7" t="n">
-        <v>23.89368935382005</v>
+        <v>23.89368936600127</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -12374,7 +12374,7 @@
         <v>5.186344183602181</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.39433293472936</v>
+        <v>11.39433293753478</v>
       </c>
       <c r="CG7" t="n">
         <v>11.57513776217851</v>
@@ -12395,7 +12395,7 @@
         <v>130.9894336423016</v>
       </c>
       <c r="CM7" t="n">
-        <v>152.6459502542943</v>
+        <v>152.6459503164988</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>-6.237000363129841</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-43.27722875916081</v>
+        <v>-43.27722523663176</v>
       </c>
       <c r="DA7" t="b">
         <v>1</v>
@@ -12678,10 +12678,10 @@
         <v>32.58000183105469</v>
       </c>
       <c r="BX8" t="n">
-        <v>24.20136284928149</v>
+        <v>24.20136285624547</v>
       </c>
       <c r="BY8" t="n">
-        <v>44.89352808541717</v>
+        <v>44.89352809833534</v>
       </c>
       <c r="BZ8" t="n">
         <v>50.78647344252641</v>
@@ -12690,25 +12690,25 @@
         <v>22.31995674309305</v>
       </c>
       <c r="CB8" t="n">
-        <v>69.38361258498088</v>
+        <v>69.38361253173336</v>
       </c>
       <c r="CC8" t="n">
-        <v>53.12760892459693</v>
+        <v>53.12760891626809</v>
       </c>
       <c r="CD8" t="n">
-        <v>28.79645703198769</v>
+        <v>28.79645699130806</v>
       </c>
       <c r="CE8" t="n">
         <v>25.44421854454374</v>
       </c>
       <c r="CF8" t="n">
-        <v>39.86915227580342</v>
+        <v>39.86915226550668</v>
       </c>
       <c r="CG8" t="n">
-        <v>36.84499255870243</v>
+        <v>36.8449925448217</v>
       </c>
       <c r="CH8" t="n">
-        <v>33.16049330283219</v>
+        <v>33.16049329033953</v>
       </c>
       <c r="CI8" t="n">
         <v>8</v>
@@ -12720,10 +12720,10 @@
         <v>3.1</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.781741679413251</v>
+        <v>1.781741641068701</v>
       </c>
       <c r="CM8" t="n">
-        <v>22.37308175287098</v>
+        <v>22.37308172126653</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -13016,10 +13016,10 @@
         <v>41.34999847412109</v>
       </c>
       <c r="BX9" t="n">
-        <v>121.1494722791397</v>
+        <v>121.1494724636367</v>
       </c>
       <c r="BY9" t="n">
-        <v>224.7322710778041</v>
+        <v>224.732271420046</v>
       </c>
       <c r="BZ9" t="n">
         <v>134.6160883985514</v>
@@ -13040,13 +13040,13 @@
         <v>57.31088302327341</v>
       </c>
       <c r="CF9" t="n">
-        <v>139.1218204678536</v>
+        <v>139.1218205336959</v>
       </c>
       <c r="CG9" t="n">
-        <v>122.0409500875877</v>
+        <v>122.0409501798362</v>
       </c>
       <c r="CH9" t="n">
-        <v>109.8368550788289</v>
+        <v>109.8368551618526</v>
       </c>
       <c r="CI9" t="n">
         <v>8</v>
@@ -13058,10 +13058,10 @@
         <v>5.4</v>
       </c>
       <c r="CL9" t="n">
-        <v>165.627228856055</v>
+        <v>165.6272290568378</v>
       </c>
       <c r="CM9" t="n">
-        <v>236.4493968601304</v>
+        <v>236.4493970193622</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -13344,10 +13344,10 @@
         <v>15.75</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.426879066780337</v>
+        <v>6.426879104229907</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.92186066887752</v>
+        <v>11.92186073834648</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.38777372262773</v>
@@ -13356,19 +13356,19 @@
         <v>18.61263551273508</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.14401442523295</v>
+        <v>35.14401436418127</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.22841486024859</v>
+        <v>12.29380744597264</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.3287793399054</v>
+        <v>20.32877926143806</v>
       </c>
       <c r="CE10" t="n">
         <v>17.80443971854372</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.20398832116729</v>
+        <v>20.21333010912071</v>
       </c>
       <c r="CG10" t="n">
         <v>18.61263551273508</v>
@@ -13389,7 +13389,7 @@
         <v>6.357917215629039</v>
       </c>
       <c r="CM10" t="n">
-        <v>28.27929092804627</v>
+        <v>28.3386038674331</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -13672,10 +13672,10 @@
         <v>32.97999954223633</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.05539027908186</v>
+        <v>46.05539021865696</v>
       </c>
       <c r="BY11" t="n">
-        <v>85.43274896769684</v>
+        <v>85.43274885560866</v>
       </c>
       <c r="BZ11" t="n">
         <v>69.25277241436312</v>
@@ -13696,7 +13696,7 @@
         <v>25.25865933859778</v>
       </c>
       <c r="CF11" t="n">
-        <v>78.35175846160264</v>
+        <v>78.35175843695791</v>
       </c>
       <c r="CG11" t="n">
         <v>69.25277241436312</v>
@@ -13717,7 +13717,7 @@
         <v>88.98573692551504</v>
       </c>
       <c r="CM11" t="n">
-        <v>137.5735583660645</v>
+        <v>137.5735582913383</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -14008,10 +14008,10 @@
         <v>7.050000190734863</v>
       </c>
       <c r="BX12" t="n">
-        <v>6.617251152840846</v>
+        <v>6.617251155137779</v>
       </c>
       <c r="BY12" t="n">
-        <v>12.27500088851977</v>
+        <v>12.27500089278058</v>
       </c>
       <c r="BZ12" t="n">
         <v>41.70201005680219</v>
@@ -14020,7 +14020,7 @@
         <v>28.15049940691006</v>
       </c>
       <c r="CB12" t="n">
-        <v>88.56764241106909</v>
+        <v>88.56764242542492</v>
       </c>
       <c r="CC12" t="n">
         <v>51.88018214566937</v>
@@ -14534,10 +14534,10 @@
         <v>45.97999954223633</v>
       </c>
       <c r="BX14" t="n">
-        <v>127.6301657283526</v>
+        <v>127.6301650560994</v>
       </c>
       <c r="BY14" t="n">
-        <v>236.753957426094</v>
+        <v>236.7539561790644</v>
       </c>
       <c r="BZ14" t="n">
         <v>134.1927299415487</v>
@@ -14558,13 +14558,13 @@
         <v>55.9815638034286</v>
       </c>
       <c r="CF14" t="n">
-        <v>141.0136557775356</v>
+        <v>141.0136555376253</v>
       </c>
       <c r="CG14" t="n">
-        <v>125.0879897431476</v>
+        <v>125.087989407021</v>
       </c>
       <c r="CH14" t="n">
-        <v>112.5791907688329</v>
+        <v>112.5791904663189</v>
       </c>
       <c r="CI14" t="n">
         <v>8</v>
@@ -14576,10 +14576,10 @@
         <v>5.4</v>
       </c>
       <c r="CL14" t="n">
-        <v>144.8438275111765</v>
+        <v>144.8438268532515</v>
       </c>
       <c r="CM14" t="n">
-        <v>206.6847698595631</v>
+        <v>206.684769337792</v>
       </c>
       <c r="CN14" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>-4.327813207567233</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-13.4422178413344</v>
+        <v>-13.44221145597109</v>
       </c>
       <c r="DA14" t="b">
         <v>1</v>
@@ -15158,10 +15158,10 @@
         <v>14</v>
       </c>
       <c r="BX16" t="n">
-        <v>10.16255136782695</v>
+        <v>10.16255144218858</v>
       </c>
       <c r="BY16" t="n">
-        <v>18.85153278731899</v>
+        <v>18.85153292525982</v>
       </c>
       <c r="BZ16" t="n">
         <v>51.38504155124654</v>
@@ -15170,23 +15170,23 @@
         <v>50.44813029652846</v>
       </c>
       <c r="CB16" t="n">
-        <v>71.96961890657695</v>
+        <v>71.96961905691506</v>
       </c>
       <c r="CC16" t="n">
-        <v>33.9731973641602</v>
+        <v>33.97319735300376</v>
       </c>
       <c r="CD16" t="n">
-        <v>30.82517856960538</v>
+        <v>30.82517848283428</v>
       </c>
       <c r="CE16" t="inlineStr"/>
       <c r="CF16" t="n">
-        <v>34.73659056757524</v>
+        <v>34.7365906098367</v>
       </c>
       <c r="CG16" t="n">
-        <v>33.9731973641602</v>
+        <v>33.97319735300376</v>
       </c>
       <c r="CH16" t="n">
-        <v>30.57587762774418</v>
+        <v>30.57587761770339</v>
       </c>
       <c r="CI16" t="n">
         <v>3</v>
@@ -15198,10 +15198,10 @@
         <v>5.1</v>
       </c>
       <c r="CL16" t="n">
-        <v>118.3991259124584</v>
+        <v>118.3991258407385</v>
       </c>
       <c r="CM16" t="n">
-        <v>148.1185040541089</v>
+        <v>148.1185043559765</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -15480,10 +15480,10 @@
         <v>7.449999809265137</v>
       </c>
       <c r="BX17" t="n">
-        <v>3.363729729177499</v>
+        <v>3.36372973558846</v>
       </c>
       <c r="BY17" t="n">
-        <v>6.239718647624262</v>
+        <v>6.239718659516593</v>
       </c>
       <c r="BZ17" t="n">
         <v>21.74284085303151</v>
@@ -15492,7 +15492,7 @@
         <v>14.8939109083963</v>
       </c>
       <c r="CB17" t="n">
-        <v>34.98727166243657</v>
+        <v>34.98727168220606</v>
       </c>
       <c r="CC17" t="n">
         <v>10.95072400487419</v>
@@ -15788,10 +15788,10 @@
         <v>19.13999938964844</v>
       </c>
       <c r="BX18" t="n">
-        <v>13.15731116818023</v>
+        <v>13.15731118896105</v>
       </c>
       <c r="BY18" t="n">
-        <v>24.40681221697433</v>
+        <v>24.40681225552275</v>
       </c>
       <c r="BZ18" t="n">
         <v>20.45201547684208</v>
@@ -15800,7 +15800,7 @@
         <v>12.7798316087502</v>
       </c>
       <c r="CB18" t="n">
-        <v>34.6124474630664</v>
+        <v>34.61244748652861</v>
       </c>
       <c r="CC18" t="n">
         <v>22.8984489302328</v>
@@ -15810,7 +15810,7 @@
       </c>
       <c r="CE18" t="inlineStr"/>
       <c r="CF18" t="n">
-        <v>20.22864694805736</v>
+        <v>20.22864696288967</v>
       </c>
       <c r="CG18" t="n">
         <v>21.67523220353744</v>
@@ -15831,7 +15831,7 @@
         <v>1.9211578122313</v>
       </c>
       <c r="CM18" t="n">
-        <v>5.687813966168154</v>
+        <v>5.687814043661943</v>
       </c>
       <c r="CN18" t="inlineStr">
         <is>
@@ -16114,10 +16114,10 @@
         <v>17.53000068664551</v>
       </c>
       <c r="BX19" t="n">
-        <v>10.74426543689855</v>
+        <v>10.7442654659961</v>
       </c>
       <c r="BY19" t="n">
-        <v>19.93061238544681</v>
+        <v>19.93061243942277</v>
       </c>
       <c r="BZ19" t="n">
         <v>37.89111078271664</v>
@@ -16126,25 +16126,25 @@
         <v>37.31646064248518</v>
       </c>
       <c r="CB19" t="n">
-        <v>42.403902487053</v>
+        <v>42.40390249981662</v>
       </c>
       <c r="CC19" t="n">
-        <v>34.52246248428089</v>
+        <v>34.52246247818044</v>
       </c>
       <c r="CD19" t="n">
-        <v>18.86931530664446</v>
+        <v>18.86931527289594</v>
       </c>
       <c r="CE19" t="n">
         <v>31.49264348607277</v>
       </c>
       <c r="CF19" t="n">
-        <v>31.77521536781424</v>
+        <v>31.77521537165577</v>
       </c>
       <c r="CG19" t="n">
-        <v>34.52246248428089</v>
+        <v>34.52246247818044</v>
       </c>
       <c r="CH19" t="n">
-        <v>31.0702162358528</v>
+        <v>31.07021623036239</v>
       </c>
       <c r="CI19" t="n">
         <v>7</v>
@@ -16156,10 +16156,10 @@
         <v>3.9</v>
       </c>
       <c r="CL19" t="n">
-        <v>77.24024540125849</v>
+        <v>77.24024536993845</v>
       </c>
       <c r="CM19" t="n">
-        <v>81.26191741692772</v>
+        <v>81.26191743884171</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -16442,10 +16442,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="BX20" t="n">
-        <v>10.37863321645883</v>
+        <v>10.37863327533605</v>
       </c>
       <c r="BY20" t="n">
-        <v>19.25236461653113</v>
+        <v>19.25236472574838</v>
       </c>
       <c r="BZ20" t="n">
         <v>25.85122324877091</v>
@@ -16454,25 +16454,25 @@
         <v>18.56165831752405</v>
       </c>
       <c r="CB20" t="n">
-        <v>39.76450202393809</v>
+        <v>39.76450197392393</v>
       </c>
       <c r="CC20" t="n">
-        <v>24.31404885344061</v>
+        <v>24.31404882939119</v>
       </c>
       <c r="CD20" t="n">
-        <v>13.00688761725288</v>
+        <v>13.00688748824112</v>
       </c>
       <c r="CE20" t="n">
         <v>10.35999965667725</v>
       </c>
       <c r="CF20" t="n">
-        <v>20.18616469382422</v>
+        <v>20.18616468945161</v>
       </c>
       <c r="CG20" t="n">
-        <v>18.90701146702759</v>
+        <v>18.90701152163621</v>
       </c>
       <c r="CH20" t="n">
-        <v>17.01631032032483</v>
+        <v>17.01631036947259</v>
       </c>
       <c r="CI20" t="n">
         <v>8</v>
@@ -16484,10 +16484,10 @@
         <v>3.8</v>
       </c>
       <c r="CL20" t="n">
-        <v>64.25010506016231</v>
+        <v>64.25010553456157</v>
       </c>
       <c r="CM20" t="n">
-        <v>94.84715601137876</v>
+        <v>94.84715596917211</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -16770,10 +16770,10 @@
         <v>11.28999996185303</v>
       </c>
       <c r="BX21" t="n">
-        <v>9.774107116375554</v>
+        <v>9.774107176349089</v>
       </c>
       <c r="BY21" t="n">
-        <v>18.13096870087665</v>
+        <v>18.13096881212756</v>
       </c>
       <c r="BZ21" t="n">
         <v>23.1209427348613</v>
@@ -16782,25 +16782,25 @@
         <v>13.6472321924953</v>
       </c>
       <c r="CB21" t="n">
-        <v>35.00095097889564</v>
+        <v>35.00095079985264</v>
       </c>
       <c r="CC21" t="n">
-        <v>25.51476119598885</v>
+        <v>25.51476115415504</v>
       </c>
       <c r="CD21" t="n">
-        <v>13.36818444215321</v>
+        <v>13.36818424804047</v>
       </c>
       <c r="CE21" t="n">
         <v>9.880299501333878</v>
       </c>
       <c r="CF21" t="n">
-        <v>18.55468085787255</v>
+        <v>18.55468082740191</v>
       </c>
       <c r="CG21" t="n">
-        <v>15.88910044668598</v>
+        <v>15.88910050231143</v>
       </c>
       <c r="CH21" t="n">
-        <v>14.30019040201738</v>
+        <v>14.30019045208029</v>
       </c>
       <c r="CI21" t="n">
         <v>8</v>
@@ -16812,10 +16812,10 @@
         <v>3.6</v>
       </c>
       <c r="CL21" t="n">
-        <v>26.66244863007323</v>
+        <v>26.66244907350024</v>
       </c>
       <c r="CM21" t="n">
-        <v>64.34615518658661</v>
+        <v>64.34615491669614</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -17100,10 +17100,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="BX22" t="n">
-        <v>5.044350409047963</v>
+        <v>5.044350378841198</v>
       </c>
       <c r="BY22" t="n">
-        <v>9.357270008783971</v>
+        <v>9.357269952750423</v>
       </c>
       <c r="BZ22" t="n">
         <v>8.453839145587175</v>
@@ -17418,37 +17418,37 @@
         <v>35.20000076293945</v>
       </c>
       <c r="BX23" t="n">
-        <v>25.31139907611215</v>
+        <v>25.31139909513731</v>
       </c>
       <c r="BY23" t="n">
-        <v>31.13019017356151</v>
+        <v>31.13019014506065</v>
       </c>
       <c r="BZ23" t="n">
-        <v>34.28259768815133</v>
+        <v>34.28259763099602</v>
       </c>
       <c r="CA23" t="n">
         <v>36.6578293511453</v>
       </c>
       <c r="CB23" t="n">
-        <v>48.45443000127379</v>
+        <v>48.45442996274987</v>
       </c>
       <c r="CC23" t="n">
-        <v>48.46302885465042</v>
+        <v>48.46302884639316</v>
       </c>
       <c r="CD23" t="n">
-        <v>16.18810974135277</v>
+        <v>16.1881096985766</v>
       </c>
       <c r="CE23" t="n">
         <v>30.16806884283779</v>
       </c>
       <c r="CF23" t="n">
-        <v>33.83195671613564</v>
+        <v>33.83195669661208</v>
       </c>
       <c r="CG23" t="n">
-        <v>32.70639393085642</v>
+        <v>32.70639388802834</v>
       </c>
       <c r="CH23" t="n">
-        <v>29.43575453777078</v>
+        <v>29.4357544992255</v>
       </c>
       <c r="CI23" t="n">
         <v>8</v>
@@ -17460,10 +17460,10 @@
         <v>3</v>
       </c>
       <c r="CL23" t="n">
-        <v>-16.37569914838637</v>
+        <v>-16.37569925789</v>
       </c>
       <c r="CM23" t="n">
-        <v>-3.886488685091649</v>
+        <v>-3.886488740556293</v>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
@@ -17746,10 +17746,10 @@
         <v>11.07999992370605</v>
       </c>
       <c r="BX24" t="n">
-        <v>3.454302384211566</v>
+        <v>3.454302382804934</v>
       </c>
       <c r="BY24" t="n">
-        <v>6.407730922712454</v>
+        <v>6.407730920103153</v>
       </c>
       <c r="BZ24" t="n">
         <v>20.4470750681205</v>
@@ -17758,13 +17758,13 @@
         <v>19.3263652032129</v>
       </c>
       <c r="CB24" t="n">
-        <v>22.0038575399476</v>
+        <v>22.00385754004261</v>
       </c>
       <c r="CC24" t="n">
-        <v>16.46863777169369</v>
+        <v>16.46863777196926</v>
       </c>
       <c r="CD24" t="n">
-        <v>13.7197938541165</v>
+        <v>13.71979385590022</v>
       </c>
       <c r="CE24" t="n">
         <v>30.3956356510297</v>
@@ -17820,7 +17820,7 @@
         <v>-18.94659940111765</v>
       </c>
       <c r="CZ24" t="n">
-        <v>-32.89649636084019</v>
+        <v>-32.89648038436899</v>
       </c>
       <c r="DA24" t="b">
         <v>1</v>
@@ -18064,10 +18064,10 @@
         <v>14.13000011444092</v>
       </c>
       <c r="BX25" t="n">
-        <v>4.339755647159453</v>
+        <v>4.339755634897887</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.050246725480784</v>
+        <v>8.050246702735581</v>
       </c>
       <c r="BZ25" t="n">
         <v>24.63453967320291</v>
@@ -18076,25 +18076,25 @@
         <v>20.77142752850562</v>
       </c>
       <c r="CB25" t="n">
-        <v>30.6115073648923</v>
+        <v>30.61150737332451</v>
       </c>
       <c r="CC25" t="n">
-        <v>16.75489077569444</v>
+        <v>16.75489077818667</v>
       </c>
       <c r="CD25" t="n">
-        <v>19.18328685257559</v>
+        <v>19.18328687207345</v>
       </c>
       <c r="CE25" t="n">
         <v>14.37360703573516</v>
       </c>
       <c r="CF25" t="n">
-        <v>19.19707227944097</v>
+        <v>19.1970722805377</v>
       </c>
       <c r="CG25" t="n">
-        <v>19.18328685257559</v>
+        <v>19.18328687207345</v>
       </c>
       <c r="CH25" t="n">
-        <v>17.26495816731803</v>
+        <v>17.2649581848661</v>
       </c>
       <c r="CI25" t="n">
         <v>7</v>
@@ -18106,10 +18106,10 @@
         <v>7.1</v>
       </c>
       <c r="CL25" t="n">
-        <v>22.18653947265839</v>
+        <v>22.1865395968486</v>
       </c>
       <c r="CM25" t="n">
-        <v>35.86038304289527</v>
+        <v>35.86038305065695</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -18390,10 +18390,10 @@
         <v>8</v>
       </c>
       <c r="BX26" t="n">
-        <v>3.706794285075357</v>
+        <v>3.706794289133744</v>
       </c>
       <c r="BY26" t="n">
-        <v>6.876103398814785</v>
+        <v>6.876103406343096</v>
       </c>
       <c r="BZ26" t="n">
         <v>25.79075425790754</v>
@@ -18402,13 +18402,13 @@
         <v>23.96599241902855</v>
       </c>
       <c r="CB26" t="n">
-        <v>33.73958279737528</v>
+        <v>33.73958280279616</v>
       </c>
       <c r="CC26" t="n">
-        <v>9.621504033571808</v>
+        <v>9.621504033197077</v>
       </c>
       <c r="CD26" t="n">
-        <v>18.4709102310425</v>
+        <v>18.47091022576042</v>
       </c>
       <c r="CE26" t="inlineStr"/>
       <c r="CF26" t="inlineStr"/>
@@ -18702,10 +18702,10 @@
         <v>13.23999977111816</v>
       </c>
       <c r="BX27" t="n">
-        <v>8.302142137387513</v>
+        <v>8.302142143832688</v>
       </c>
       <c r="BY27" t="n">
-        <v>15.40047366485384</v>
+        <v>15.40047367680963</v>
       </c>
       <c r="BZ27" t="n">
         <v>14.18189142823894</v>
@@ -18726,7 +18726,7 @@
         <v>6.364116594565261</v>
       </c>
       <c r="CF27" t="n">
-        <v>11.29369907286193</v>
+        <v>11.29369907549064</v>
       </c>
       <c r="CG27" t="n">
         <v>11.52626939957729</v>
@@ -18747,7 +18747,7 @@
         <v>-21.64922478134251</v>
       </c>
       <c r="CM27" t="n">
-        <v>-14.70015658536424</v>
+        <v>-14.70015656550992</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -19030,10 +19030,10 @@
         <v>27.52000045776367</v>
       </c>
       <c r="BX28" t="n">
-        <v>7.290978505888661</v>
+        <v>7.290978493448117</v>
       </c>
       <c r="BY28" t="n">
-        <v>13.52476512842347</v>
+        <v>13.52476510534626</v>
       </c>
       <c r="BZ28" t="n">
         <v>36.57372177185242</v>
@@ -19042,19 +19042,19 @@
         <v>28.87454744278962</v>
       </c>
       <c r="CB28" t="n">
-        <v>45.93352493983287</v>
+        <v>45.93352495810291</v>
       </c>
       <c r="CC28" t="n">
-        <v>26.49482250051946</v>
+        <v>26.49482250355711</v>
       </c>
       <c r="CD28" t="n">
-        <v>29.81102743456123</v>
+        <v>29.81102745702587</v>
       </c>
       <c r="CE28" t="n">
         <v>24.2620728130642</v>
       </c>
       <c r="CF28" t="n">
-        <v>29.35349743300618</v>
+        <v>29.35349743596263</v>
       </c>
       <c r="CG28" t="n">
         <v>28.87454744278962</v>
@@ -19075,7 +19075,7 @@
         <v>-5.570158916260349</v>
       </c>
       <c r="CM28" t="n">
-        <v>6.662416223635126</v>
+        <v>6.662416234378021</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>-5.331954775825187</v>
       </c>
       <c r="CZ28" t="n">
-        <v>-21.99140136548733</v>
+        <v>-21.99140983840919</v>
       </c>
       <c r="DA28" t="b">
         <v>1</v>
@@ -19358,10 +19358,10 @@
         <v>22.06999969482422</v>
       </c>
       <c r="BX29" t="n">
-        <v>3.108072445623536</v>
+        <v>3.108072443831099</v>
       </c>
       <c r="BY29" t="n">
-        <v>5.76547438663166</v>
+        <v>5.765474383306688</v>
       </c>
       <c r="BZ29" t="n">
         <v>33.57376532220675</v>
@@ -19370,7 +19370,7 @@
         <v>28.04300293143303</v>
       </c>
       <c r="CB29" t="n">
-        <v>43.00378985776037</v>
+        <v>43.00378985487929</v>
       </c>
       <c r="CC29" t="n">
         <v>10.85340539909456</v>
@@ -19656,10 +19656,10 @@
         <v>38.90000152587891</v>
       </c>
       <c r="BX30" t="n">
-        <v>35.62892560050491</v>
+        <v>35.62892557839169</v>
       </c>
       <c r="BY30" t="n">
-        <v>51.87571567433516</v>
+        <v>51.87571564213831</v>
       </c>
       <c r="BZ30" t="n">
         <v>50.25590259243982</v>
@@ -19676,13 +19676,13 @@
       </c>
       <c r="CE30" t="inlineStr"/>
       <c r="CF30" t="n">
-        <v>49.31617721277441</v>
+        <v>49.31617719919689</v>
       </c>
       <c r="CG30" t="n">
-        <v>51.06580913338749</v>
+        <v>51.06580911728906</v>
       </c>
       <c r="CH30" t="n">
-        <v>45.95922822004874</v>
+        <v>45.95922820556016</v>
       </c>
       <c r="CI30" t="n">
         <v>4</v>
@@ -19694,10 +19694,10 @@
         <v>1.7</v>
       </c>
       <c r="CL30" t="n">
-        <v>18.14711161251128</v>
+        <v>18.14711157526556</v>
       </c>
       <c r="CM30" t="n">
-        <v>26.77680020132123</v>
+        <v>26.77680016641757</v>
       </c>
       <c r="CN30" t="inlineStr">
         <is>
@@ -19980,10 +19980,10 @@
         <v>24.72999954223633</v>
       </c>
       <c r="BX31" t="n">
-        <v>12.83053367469218</v>
+        <v>12.83053369544166</v>
       </c>
       <c r="BY31" t="n">
-        <v>23.80063996655399</v>
+        <v>23.80064000504428</v>
       </c>
       <c r="BZ31" t="n">
         <v>61.59257404786302</v>
@@ -19992,13 +19992,13 @@
         <v>51.63850781741169</v>
       </c>
       <c r="CB31" t="n">
-        <v>85.84612579802551</v>
+        <v>85.84612579958544</v>
       </c>
       <c r="CC31" t="n">
-        <v>33.66425527526015</v>
+        <v>33.66425527180574</v>
       </c>
       <c r="CD31" t="n">
-        <v>45.15510821049845</v>
+        <v>45.15510817715654</v>
       </c>
       <c r="CE31" t="n">
         <v>5.142038558436727</v>
@@ -20294,10 +20294,10 @@
         <v>12.02999973297119</v>
       </c>
       <c r="BX32" t="n">
-        <v>2.080017508669553</v>
+        <v>2.08001751083452</v>
       </c>
       <c r="BY32" t="n">
-        <v>3.858432478582021</v>
+        <v>3.858432482598035</v>
       </c>
       <c r="BZ32" t="n">
         <v>28.61714478669089</v>
@@ -20306,7 +20306,7 @@
         <v>24.30030260991828</v>
       </c>
       <c r="CB32" t="n">
-        <v>37.6248188718028</v>
+        <v>37.62481887724437</v>
       </c>
       <c r="CC32" t="n">
         <v>9.158754146</v>
@@ -20608,10 +20608,10 @@
         <v>33.43000030517578</v>
       </c>
       <c r="BX33" t="n">
-        <v>7.930922177531123</v>
+        <v>7.930922164176469</v>
       </c>
       <c r="BY33" t="n">
-        <v>14.71186063932023</v>
+        <v>14.71186061454735</v>
       </c>
       <c r="BZ33" t="n">
         <v>67.41971142215816</v>
@@ -20620,7 +20620,7 @@
         <v>39.36375120302754</v>
       </c>
       <c r="CB33" t="n">
-        <v>93.22418798524696</v>
+        <v>93.22418795678955</v>
       </c>
       <c r="CC33" t="n">
         <v>22.51480113099953</v>
@@ -20908,35 +20908,35 @@
         <v>23.04999923706055</v>
       </c>
       <c r="BX34" t="n">
-        <v>16.54376616781284</v>
+        <v>16.5437661860459</v>
       </c>
       <c r="BY34" t="n">
-        <v>30.07147189300477</v>
+        <v>30.07147189023322</v>
       </c>
       <c r="BZ34" t="n">
-        <v>51.50946629191572</v>
+        <v>51.50946623039919</v>
       </c>
       <c r="CA34" t="n">
         <v>50.09186275696137</v>
       </c>
       <c r="CB34" t="n">
-        <v>63.06344045567126</v>
+        <v>63.06344046374193</v>
       </c>
       <c r="CC34" t="n">
-        <v>45.81097523940456</v>
+        <v>45.81097523549202</v>
       </c>
       <c r="CD34" t="n">
-        <v>25.18054540458671</v>
+        <v>25.18054538204336</v>
       </c>
       <c r="CE34" t="inlineStr"/>
       <c r="CF34" t="n">
-        <v>35.98391989803447</v>
+        <v>35.98391988554259</v>
       </c>
       <c r="CG34" t="n">
-        <v>37.94122356620466</v>
+        <v>37.94122356286262</v>
       </c>
       <c r="CH34" t="n">
-        <v>34.1471012095842</v>
+        <v>34.14710120657637</v>
       </c>
       <c r="CI34" t="n">
         <v>4</v>
@@ -20948,10 +20948,10 @@
         <v>3.1</v>
       </c>
       <c r="CL34" t="n">
-        <v>48.14361101878637</v>
+        <v>48.14361100573718</v>
       </c>
       <c r="CM34" t="n">
-        <v>56.11245591790885</v>
+        <v>56.11245586371414</v>
       </c>
       <c r="CN34" t="inlineStr">
         <is>
@@ -21230,10 +21230,10 @@
         <v>32.75</v>
       </c>
       <c r="BX35" t="n">
-        <v>3.249356692527549</v>
+        <v>3.249356697068481</v>
       </c>
       <c r="BY35" t="n">
-        <v>6.027556664638603</v>
+        <v>6.027556673062032</v>
       </c>
       <c r="BZ35" t="n">
         <v>33.45701619121048</v>
@@ -21242,7 +21242,7 @@
         <v>23.42786572511178</v>
       </c>
       <c r="CB35" t="n">
-        <v>41.38326859640598</v>
+        <v>41.38326860130753</v>
       </c>
       <c r="CC35" t="n">
         <v>10.59424454785779</v>
@@ -21312,7 +21312,7 @@
         <v>0.738239590458023</v>
       </c>
       <c r="CZ35" t="n">
-        <v>-31.31834368818209</v>
+        <v>-31.318349352401</v>
       </c>
       <c r="DA35" t="b">
         <v>1</v>
@@ -21556,10 +21556,10 @@
         <v>33.65000152587891</v>
       </c>
       <c r="BX36" t="n">
-        <v>15.24688680176719</v>
+        <v>15.2468868650438</v>
       </c>
       <c r="BY36" t="n">
-        <v>28.28297501727814</v>
+        <v>28.28297513465624</v>
       </c>
       <c r="BZ36" t="n">
         <v>20.22969692458691</v>
@@ -21568,7 +21568,7 @@
         <v>37.31912959637818</v>
       </c>
       <c r="CB36" t="n">
-        <v>27.24280547968912</v>
+        <v>27.24280551988296</v>
       </c>
       <c r="CC36" t="n">
         <v>15.03391666666667</v>
@@ -21580,7 +21580,7 @@
         <v>77.67169119949854</v>
       </c>
       <c r="CF36" t="n">
-        <v>22.6386327600837</v>
+        <v>22.63863279163349</v>
       </c>
       <c r="CG36" t="n">
         <v>20.22969692458691</v>
@@ -21601,7 +21601,7 @@
         <v>-45.89382940108894</v>
       </c>
       <c r="CM36" t="n">
-        <v>-32.72323407571555</v>
+        <v>-32.72323398195689</v>
       </c>
       <c r="CN36" t="inlineStr">
         <is>
@@ -21860,10 +21860,10 @@
         <v>14.77999973297119</v>
       </c>
       <c r="BX37" t="n">
-        <v>9.186484945828067</v>
+        <v>9.186484878581913</v>
       </c>
       <c r="BY37" t="n">
-        <v>17.04092957451106</v>
+        <v>17.04092944976945</v>
       </c>
       <c r="BZ37" t="n">
         <v>31.89495056382219</v>
@@ -21872,23 +21872,23 @@
         <v>30.33345456974609</v>
       </c>
       <c r="CB37" t="n">
-        <v>36.78693480727625</v>
+        <v>36.78693478697259</v>
       </c>
       <c r="CC37" t="n">
-        <v>25.58128744616013</v>
+        <v>25.58128745942417</v>
       </c>
       <c r="CD37" t="n">
-        <v>16.38749076540083</v>
+        <v>16.38749084901738</v>
       </c>
       <c r="CE37" t="inlineStr"/>
       <c r="CF37" t="n">
-        <v>20.92591313258036</v>
+        <v>20.92591308789943</v>
       </c>
       <c r="CG37" t="n">
-        <v>21.31110851033559</v>
+        <v>21.31110845459681</v>
       </c>
       <c r="CH37" t="n">
-        <v>19.17999765930204</v>
+        <v>19.17999760913713</v>
       </c>
       <c r="CI37" t="n">
         <v>4</v>
@@ -21900,10 +21900,10 @@
         <v>3.5</v>
       </c>
       <c r="CL37" t="n">
-        <v>29.76994591221365</v>
+        <v>29.7699455728029</v>
       </c>
       <c r="CM37" t="n">
-        <v>41.58263539003239</v>
+        <v>41.58263508772568</v>
       </c>
       <c r="CN37" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>-7.171627471148123</v>
       </c>
       <c r="CZ37" t="n">
-        <v>-18.74746959920818</v>
+        <v>-18.74747840191868</v>
       </c>
       <c r="DA37" t="b">
         <v>1</v>
@@ -22166,35 +22166,35 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BX38" t="n">
-        <v>8.627042016972684</v>
+        <v>8.627042072234111</v>
       </c>
       <c r="BY38" t="n">
-        <v>14.3473090922331</v>
+        <v>14.34730902416064</v>
       </c>
       <c r="BZ38" t="n">
-        <v>19.54486218349647</v>
+        <v>19.54486196556696</v>
       </c>
       <c r="CA38" t="n">
         <v>17.74926644976348</v>
       </c>
       <c r="CB38" t="n">
-        <v>23.93539535853802</v>
+        <v>23.93539530781762</v>
       </c>
       <c r="CC38" t="n">
-        <v>17.38495031182219</v>
+        <v>17.38495029677088</v>
       </c>
       <c r="CD38" t="n">
-        <v>9.719867294471685</v>
+        <v>9.719867200323893</v>
       </c>
       <c r="CE38" t="inlineStr"/>
       <c r="CF38" t="n">
-        <v>14.97604090113111</v>
+        <v>14.97604083968315</v>
       </c>
       <c r="CG38" t="n">
-        <v>15.86612970202765</v>
+        <v>15.86612966046576</v>
       </c>
       <c r="CH38" t="n">
-        <v>14.27951673182488</v>
+        <v>14.27951669441919</v>
       </c>
       <c r="CI38" t="n">
         <v>4</v>
@@ -22206,10 +22206,10 @@
         <v>2.3</v>
       </c>
       <c r="CL38" t="n">
-        <v>11.12464052854489</v>
+        <v>11.12464023744999</v>
       </c>
       <c r="CM38" t="n">
-        <v>16.54506191865357</v>
+        <v>16.54506144045931</v>
       </c>
       <c r="CN38" t="inlineStr">
         <is>
@@ -22492,10 +22492,10 @@
         <v>5.880000114440918</v>
       </c>
       <c r="BX39" t="n">
-        <v>6.975750809416621</v>
+        <v>6.975750786425684</v>
       </c>
       <c r="BY39" t="n">
-        <v>12.94001775146783</v>
+        <v>12.94001770881964</v>
       </c>
       <c r="BZ39" t="n">
         <v>5.605036080312384</v>
@@ -22516,7 +22516,7 @@
         <v>5.348622529323849</v>
       </c>
       <c r="CF39" t="n">
-        <v>7.296291364832035</v>
+        <v>7.296291356627144</v>
       </c>
       <c r="CG39" t="n">
         <v>5.869184706822859</v>
@@ -22537,7 +22537,7 @@
         <v>-10.16554195011574</v>
       </c>
       <c r="CM39" t="n">
-        <v>24.0865854222144</v>
+        <v>24.08658528267544</v>
       </c>
       <c r="CN39" t="inlineStr">
         <is>
@@ -22810,10 +22810,10 @@
         <v>39.43999862670898</v>
       </c>
       <c r="BX40" t="n">
-        <v>20.16127574530427</v>
+        <v>20.1612756175048</v>
       </c>
       <c r="BY40" t="n">
-        <v>37.39916650753941</v>
+        <v>37.3991662704714</v>
       </c>
       <c r="BZ40" t="n">
         <v>57.05021635413689</v>
@@ -22822,23 +22822,23 @@
         <v>43.06721646336476</v>
       </c>
       <c r="CB40" t="n">
-        <v>64.10972928489694</v>
+        <v>64.10972949124397</v>
       </c>
       <c r="CC40" t="n">
-        <v>45.28400689669809</v>
+        <v>45.28400693591092</v>
       </c>
       <c r="CD40" t="n">
-        <v>32.4309406972427</v>
+        <v>32.43094094972332</v>
       </c>
       <c r="CE40" t="inlineStr"/>
       <c r="CF40" t="n">
-        <v>39.97366637591966</v>
+        <v>39.973666294506</v>
       </c>
       <c r="CG40" t="n">
-        <v>41.34158670211875</v>
+        <v>41.34158660319116</v>
       </c>
       <c r="CH40" t="n">
-        <v>37.20742803190687</v>
+        <v>37.20742794287204</v>
       </c>
       <c r="CI40" t="n">
         <v>4</v>
@@ -22850,10 +22850,10 @@
         <v>2.8</v>
       </c>
       <c r="CL40" t="n">
-        <v>-5.660676147412957</v>
+        <v>-5.6606763731605</v>
       </c>
       <c r="CM40" t="n">
-        <v>1.353113001503181</v>
+        <v>1.353112795079103</v>
       </c>
       <c r="CN40" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>-6.937240130506206</v>
       </c>
       <c r="CZ40" t="n">
-        <v>-19.01273240052025</v>
+        <v>-19.01272601806555</v>
       </c>
       <c r="DA40" t="b">
         <v>1</v>
@@ -23136,37 +23136,37 @@
         <v>26.45999908447266</v>
       </c>
       <c r="BX41" t="n">
-        <v>16.91893493941736</v>
+        <v>16.91893502410094</v>
       </c>
       <c r="BY41" t="n">
-        <v>28.67982834187544</v>
+        <v>28.67982835307078</v>
       </c>
       <c r="BZ41" t="n">
-        <v>49.21350852397792</v>
+        <v>49.21350829686259</v>
       </c>
       <c r="CA41" t="n">
         <v>53.99475108321082</v>
       </c>
       <c r="CB41" t="n">
-        <v>57.93925170267027</v>
+        <v>57.93925173409952</v>
       </c>
       <c r="CC41" t="n">
-        <v>43.01388446006595</v>
+        <v>43.01388444492227</v>
       </c>
       <c r="CD41" t="n">
-        <v>24.4065726658507</v>
+        <v>24.40657257113381</v>
       </c>
       <c r="CE41" t="n">
         <v>30.06721996094383</v>
       </c>
       <c r="CF41" t="n">
-        <v>38.02924395975153</v>
+        <v>38.02924393354307</v>
       </c>
       <c r="CG41" t="n">
-        <v>36.54055221050488</v>
+        <v>36.54055220293305</v>
       </c>
       <c r="CH41" t="n">
-        <v>32.8864969894544</v>
+        <v>32.88649698263975</v>
       </c>
       <c r="CI41" t="n">
         <v>8</v>
@@ -23178,10 +23178,10 @@
         <v>3.4</v>
       </c>
       <c r="CL41" t="n">
-        <v>24.28759685314186</v>
+        <v>24.2875968273873</v>
       </c>
       <c r="CM41" t="n">
-        <v>43.72352711859306</v>
+        <v>43.7235270195437</v>
       </c>
       <c r="CN41" t="inlineStr">
         <is>
@@ -23464,10 +23464,10 @@
         <v>11.76000022888184</v>
       </c>
       <c r="BX42" t="n">
-        <v>4.779815381815517</v>
+        <v>4.779815359277475</v>
       </c>
       <c r="BY42" t="n">
-        <v>8.866557533267784</v>
+        <v>8.866557491459718</v>
       </c>
       <c r="BZ42" t="n">
         <v>27.09913096220597</v>
@@ -23476,25 +23476,25 @@
         <v>30.54574135914352</v>
       </c>
       <c r="CB42" t="n">
-        <v>25.60465063262587</v>
+        <v>25.60465060977719</v>
       </c>
       <c r="CC42" t="n">
-        <v>14.19260756846341</v>
+        <v>14.19260757054379</v>
       </c>
       <c r="CD42" t="n">
-        <v>14.24280839169414</v>
+        <v>14.24280841182511</v>
       </c>
       <c r="CE42" t="n">
         <v>5.07221344413531</v>
       </c>
       <c r="CF42" t="n">
-        <v>20.09191607456678</v>
+        <v>20.09191606749255</v>
       </c>
       <c r="CG42" t="n">
-        <v>19.92372951216</v>
+        <v>19.92372951080115</v>
       </c>
       <c r="CH42" t="n">
-        <v>17.931356560944</v>
+        <v>17.93135655972104</v>
       </c>
       <c r="CI42" t="n">
         <v>6</v>
@@ -23506,10 +23506,10 @@
         <v>6.4</v>
       </c>
       <c r="CL42" t="n">
-        <v>52.47751880910425</v>
+        <v>52.47751879870488</v>
       </c>
       <c r="CM42" t="n">
-        <v>70.8496231592094</v>
+        <v>70.8496230990544</v>
       </c>
       <c r="CN42" t="inlineStr">
         <is>
@@ -23792,37 +23792,37 @@
         <v>15.3100004196167</v>
       </c>
       <c r="BX43" t="n">
-        <v>5.939526977341711</v>
+        <v>5.939526957524716</v>
       </c>
       <c r="BY43" t="n">
-        <v>8.534880597078802</v>
+        <v>8.534880613439464</v>
       </c>
       <c r="BZ43" t="n">
-        <v>10.81501542279409</v>
+        <v>10.81501547960945</v>
       </c>
       <c r="CA43" t="n">
         <v>11.65944891202323</v>
       </c>
       <c r="CB43" t="n">
-        <v>9.810403792240514</v>
+        <v>9.810403824194951</v>
       </c>
       <c r="CC43" t="n">
-        <v>14.90925677619887</v>
+        <v>14.90925678315233</v>
       </c>
       <c r="CD43" t="n">
-        <v>5.384140018563597</v>
+        <v>5.384140050651277</v>
       </c>
       <c r="CE43" t="n">
         <v>10.69689722735973</v>
       </c>
       <c r="CF43" t="n">
-        <v>9.718696215450066</v>
+        <v>9.718696230994393</v>
       </c>
       <c r="CG43" t="n">
-        <v>10.25365050980012</v>
+        <v>10.25365052577734</v>
       </c>
       <c r="CH43" t="n">
-        <v>9.22828545882011</v>
+        <v>9.228285473199609</v>
       </c>
       <c r="CI43" t="n">
         <v>8</v>
@@ -23834,10 +23834,10 @@
         <v>2.8</v>
       </c>
       <c r="CL43" t="n">
-        <v>-39.72380662383321</v>
+        <v>-39.72380652991093</v>
       </c>
       <c r="CM43" t="n">
-        <v>-36.52060124702869</v>
+        <v>-36.52060114549814</v>
       </c>
       <c r="CN43" t="inlineStr">
         <is>
@@ -24120,10 +24120,10 @@
         <v>9.25</v>
       </c>
       <c r="BX44" t="n">
-        <v>2.521670917965907</v>
+        <v>2.521670910160942</v>
       </c>
       <c r="BY44" t="n">
-        <v>4.677699552826757</v>
+        <v>4.677699538348548</v>
       </c>
       <c r="BZ44" t="n">
         <v>13.66360089186176</v>
@@ -24132,19 +24132,19 @@
         <v>15.44242552617786</v>
       </c>
       <c r="CB44" t="n">
-        <v>10.73109422262332</v>
+        <v>10.73109422139046</v>
       </c>
       <c r="CC44" t="n">
-        <v>7.312738777796768</v>
+        <v>7.312738778525191</v>
       </c>
       <c r="CD44" t="n">
-        <v>7.026196818471051</v>
+        <v>7.026196825353156</v>
       </c>
       <c r="CE44" t="n">
         <v>10.33342380121613</v>
       </c>
       <c r="CF44" t="n">
-        <v>9.88388279871052</v>
+        <v>9.883882797553301</v>
       </c>
       <c r="CG44" t="n">
         <v>10.33342380121613</v>
@@ -24165,7 +24165,7 @@
         <v>0.5414207685893846</v>
       </c>
       <c r="CM44" t="n">
-        <v>6.852787013086692</v>
+        <v>6.852787000576233</v>
       </c>
       <c r="CN44" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>-0.5376364484882101</v>
       </c>
       <c r="CZ44" t="n">
-        <v>-35.23798556234104</v>
+        <v>-35.23799006988425</v>
       </c>
       <c r="DA44" t="b">
         <v>0</v>
@@ -24446,10 +24446,10 @@
         <v>6.400000095367432</v>
       </c>
       <c r="BX45" t="n">
-        <v>7.596590938149569</v>
+        <v>7.59659094360428</v>
       </c>
       <c r="BY45" t="n">
-        <v>11.06063640594577</v>
+        <v>11.06063641388783</v>
       </c>
       <c r="BZ45" t="n">
         <v>8.29925199399268</v>
@@ -24468,7 +24468,7 @@
         <v>5.369614780864673</v>
       </c>
       <c r="CF45" t="n">
-        <v>8.371703267309314</v>
+        <v>8.37170326954211</v>
       </c>
       <c r="CG45" t="n">
         <v>8.587865965618855</v>
@@ -24489,7 +24489,7 @@
         <v>20.76686334194866</v>
       </c>
       <c r="CM45" t="n">
-        <v>30.807861602519</v>
+        <v>30.80786163740643</v>
       </c>
       <c r="CN45" t="inlineStr">
         <is>
@@ -24772,37 +24772,37 @@
         <v>38.86000061035156</v>
       </c>
       <c r="BX46" t="n">
-        <v>30.97422558314344</v>
+        <v>30.97422553314541</v>
       </c>
       <c r="BY46" t="n">
-        <v>37.33904008942356</v>
+        <v>37.33904013124479</v>
       </c>
       <c r="BZ46" t="n">
-        <v>41.77389235468468</v>
+        <v>41.77389246890377</v>
       </c>
       <c r="CA46" t="n">
         <v>51.32924379406393</v>
       </c>
       <c r="CB46" t="n">
-        <v>64.51021342797708</v>
+        <v>64.51021348156419</v>
       </c>
       <c r="CC46" t="n">
-        <v>16.342100463568</v>
+        <v>16.34210046821733</v>
       </c>
       <c r="CD46" t="n">
-        <v>19.48042941943218</v>
+        <v>19.48042950804467</v>
       </c>
       <c r="CE46" t="n">
         <v>27.99121924833823</v>
       </c>
       <c r="CF46" t="n">
-        <v>36.21754554757889</v>
+        <v>36.21754557919029</v>
       </c>
       <c r="CG46" t="n">
-        <v>34.1566328362835</v>
+        <v>34.1566328321951</v>
       </c>
       <c r="CH46" t="n">
-        <v>30.74096955265515</v>
+        <v>30.74096954897559</v>
       </c>
       <c r="CI46" t="n">
         <v>8</v>
@@ -24814,10 +24814,10 @@
         <v>3.9</v>
       </c>
       <c r="CL46" t="n">
-        <v>-20.89302864172796</v>
+        <v>-20.89302865119672</v>
       </c>
       <c r="CM46" t="n">
-        <v>-6.799935721227901</v>
+        <v>-6.799935639881016</v>
       </c>
       <c r="CN46" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>-1.436158705057633</v>
       </c>
       <c r="CZ46" t="n">
-        <v>-11.3028015909127</v>
+        <v>-11.30279367757439</v>
       </c>
       <c r="DA46" t="b">
         <v>0</v>
@@ -25078,35 +25078,35 @@
         <v>16.78000068664551</v>
       </c>
       <c r="BX47" t="n">
-        <v>9.985664099891691</v>
+        <v>9.985664037482243</v>
       </c>
       <c r="BY47" t="n">
-        <v>18.36675920024908</v>
+        <v>18.36675921097795</v>
       </c>
       <c r="BZ47" t="n">
-        <v>31.67453719910337</v>
+        <v>31.67453741556876</v>
       </c>
       <c r="CA47" t="n">
         <v>30.47653407949944</v>
       </c>
       <c r="CB47" t="n">
-        <v>34.39875972310931</v>
+        <v>34.39875972103142</v>
       </c>
       <c r="CC47" t="n">
-        <v>27.99338996709194</v>
+        <v>27.99338998062349</v>
       </c>
       <c r="CD47" t="n">
-        <v>15.43712483677016</v>
+        <v>15.43712491437256</v>
       </c>
       <c r="CE47" t="inlineStr"/>
       <c r="CF47" t="n">
-        <v>22.00508761658402</v>
+        <v>22.00508766116311</v>
       </c>
       <c r="CG47" t="n">
-        <v>23.18007458367051</v>
+        <v>23.18007459580072</v>
       </c>
       <c r="CH47" t="n">
-        <v>20.86206712530346</v>
+        <v>20.86206713622065</v>
       </c>
       <c r="CI47" t="n">
         <v>4</v>
@@ -25118,10 +25118,10 @@
         <v>3.2</v>
       </c>
       <c r="CL47" t="n">
-        <v>24.3269742051125</v>
+        <v>24.32697427017321</v>
       </c>
       <c r="CM47" t="n">
-        <v>31.13877661576581</v>
+        <v>31.13877688143378</v>
       </c>
       <c r="CN47" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>-7.744448996751174</v>
       </c>
       <c r="CZ47" t="n">
-        <v>-20.99429475986069</v>
+        <v>-20.99430199889827</v>
       </c>
       <c r="DA47" t="b">
         <v>0</v>
@@ -25400,10 +25400,10 @@
         <v>34.09000015258789</v>
       </c>
       <c r="BX48" t="n">
-        <v>14.76402962612475</v>
+        <v>14.76402953259265</v>
       </c>
       <c r="BY48" t="n">
-        <v>27.38727495646141</v>
+        <v>27.38727478295937</v>
       </c>
       <c r="BZ48" t="n">
         <v>56.25062291678574</v>
@@ -25412,25 +25412,25 @@
         <v>43.51071962247149</v>
       </c>
       <c r="CB48" t="n">
-        <v>72.55360772024832</v>
+        <v>72.55360783857934</v>
       </c>
       <c r="CC48" t="n">
-        <v>38.45081140628864</v>
+        <v>38.45081142924435</v>
       </c>
       <c r="CD48" t="n">
-        <v>40.76646229951829</v>
+        <v>40.76646247639871</v>
       </c>
       <c r="CE48" t="n">
         <v>21.06667845031192</v>
       </c>
       <c r="CF48" t="n">
-        <v>42.85516819601226</v>
+        <v>42.85516821667871</v>
       </c>
       <c r="CG48" t="n">
-        <v>40.76646229951829</v>
+        <v>40.76646247639871</v>
       </c>
       <c r="CH48" t="n">
-        <v>36.68981606956646</v>
+        <v>36.68981622875884</v>
       </c>
       <c r="CI48" t="n">
         <v>7</v>
@@ -25442,10 +25442,10 @@
         <v>4.9</v>
       </c>
       <c r="CL48" t="n">
-        <v>7.626330024469685</v>
+        <v>7.626330491446454</v>
       </c>
       <c r="CM48" t="n">
-        <v>25.71184512816429</v>
+        <v>25.71184518878749</v>
       </c>
       <c r="CN48" t="inlineStr">
         <is>
@@ -25724,37 +25724,37 @@
         <v>44.2400016784668</v>
       </c>
       <c r="BX49" t="n">
-        <v>32.08407763132491</v>
+        <v>32.08407771579532</v>
       </c>
       <c r="BY49" t="n">
-        <v>48.69139716298315</v>
+        <v>48.69139697039319</v>
       </c>
       <c r="BZ49" t="n">
-        <v>58.34154951601694</v>
+        <v>58.3415491316569</v>
       </c>
       <c r="CA49" t="n">
         <v>49.68675315451532</v>
       </c>
       <c r="CB49" t="n">
-        <v>78.1730471894993</v>
+        <v>78.17304702080875</v>
       </c>
       <c r="CC49" t="n">
-        <v>59.71139343337703</v>
+        <v>60.40706011937741</v>
       </c>
       <c r="CD49" t="n">
-        <v>29.16704240610924</v>
+        <v>29.16704220964456</v>
       </c>
       <c r="CE49" t="n">
         <v>77.58261943552711</v>
       </c>
       <c r="CF49" t="n">
-        <v>54.17973499116913</v>
+        <v>54.26669321971482</v>
       </c>
       <c r="CG49" t="n">
-        <v>54.01415133526613</v>
+        <v>54.01415114308611</v>
       </c>
       <c r="CH49" t="n">
-        <v>48.61273620173952</v>
+        <v>48.6127360287775</v>
       </c>
       <c r="CI49" t="n">
         <v>8</v>
@@ -25766,10 +25766,10 @@
         <v>2.7</v>
       </c>
       <c r="CL49" t="n">
-        <v>9.884119252647071</v>
+        <v>9.884118861684099</v>
       </c>
       <c r="CM49" t="n">
-        <v>22.46775075856373</v>
+        <v>22.66431094221315</v>
       </c>
       <c r="CN49" t="inlineStr">
         <is>
@@ -26048,10 +26048,10 @@
         <v>32.65999984741211</v>
       </c>
       <c r="BX50" t="n">
-        <v>11.09799944154755</v>
+        <v>11.0979993579001</v>
       </c>
       <c r="BY50" t="n">
-        <v>20.58678896407071</v>
+        <v>20.58678880890468</v>
       </c>
       <c r="BZ50" t="n">
         <v>56.94013131292242</v>
@@ -26060,19 +26060,19 @@
         <v>53.82541566292831</v>
       </c>
       <c r="CB50" t="n">
-        <v>59.89734831209908</v>
+        <v>59.89734832641072</v>
       </c>
       <c r="CC50" t="n">
-        <v>28.27275389182588</v>
+        <v>28.27275368887696</v>
       </c>
       <c r="CD50" t="n">
-        <v>36.27955938165171</v>
+        <v>36.27955948750253</v>
       </c>
       <c r="CE50" t="n">
         <v>53.57698797570033</v>
       </c>
       <c r="CF50" t="n">
-        <v>44.19699792874263</v>
+        <v>44.19699789474942</v>
       </c>
       <c r="CG50" t="n">
         <v>53.57698797570033</v>
@@ -26093,7 +26093,7 @@
         <v>47.64020025539306</v>
       </c>
       <c r="CM50" t="n">
-        <v>35.32455032220303</v>
+        <v>35.32455021812093</v>
       </c>
       <c r="CN50" t="inlineStr">
         <is>
@@ -26372,10 +26372,10 @@
         <v>12.96000003814697</v>
       </c>
       <c r="BX51" t="n">
-        <v>1.595679016573354</v>
+        <v>1.595679011519226</v>
       </c>
       <c r="BY51" t="n">
-        <v>2.959984575743571</v>
+        <v>2.959984566368163</v>
       </c>
       <c r="BZ51" t="n">
         <v>13.02883160132378</v>
@@ -26384,7 +26384,7 @@
         <v>9.525658668173282</v>
       </c>
       <c r="CB51" t="n">
-        <v>16.44457563006309</v>
+        <v>16.44457562469452</v>
       </c>
       <c r="CC51" t="n">
         <v>6.104046666666666</v>
@@ -26686,37 +26686,37 @@
         <v>10.59000015258789</v>
       </c>
       <c r="BX52" t="n">
-        <v>8.101227362482744</v>
+        <v>8.101227378904682</v>
       </c>
       <c r="BY52" t="n">
-        <v>11.55102778545224</v>
+        <v>11.55102779006567</v>
       </c>
       <c r="BZ52" t="n">
-        <v>17.45216310705328</v>
+        <v>17.45216307864644</v>
       </c>
       <c r="CA52" t="n">
         <v>24.15149214812595</v>
       </c>
       <c r="CB52" t="n">
-        <v>24.87656900340325</v>
+        <v>24.87656901471751</v>
       </c>
       <c r="CC52" t="n">
-        <v>21.04926982811537</v>
+        <v>21.04926982505205</v>
       </c>
       <c r="CD52" t="n">
-        <v>8.678711550277338</v>
+        <v>8.678711534005169</v>
       </c>
       <c r="CE52" t="n">
         <v>10.2336008131</v>
       </c>
       <c r="CF52" t="n">
-        <v>15.76175769975127</v>
+        <v>15.76175769782718</v>
       </c>
       <c r="CG52" t="n">
-        <v>14.50159544625276</v>
+        <v>14.50159543435606</v>
       </c>
       <c r="CH52" t="n">
-        <v>13.05143590162749</v>
+        <v>13.05143589092045</v>
       </c>
       <c r="CI52" t="n">
         <v>8</v>
@@ -26728,10 +26728,10 @@
         <v>3.1</v>
       </c>
       <c r="CL52" t="n">
-        <v>23.24301901391468</v>
+        <v>23.24301891280951</v>
       </c>
       <c r="CM52" t="n">
-        <v>48.836236757745</v>
+        <v>48.83623673957609</v>
       </c>
       <c r="CN52" t="inlineStr">
         <is>
@@ -26996,10 +26996,10 @@
         <v>54.20000076293945</v>
       </c>
       <c r="BX53" t="n">
-        <v>10.59687584109176</v>
+        <v>10.59687587099957</v>
       </c>
       <c r="BY53" t="n">
-        <v>19.6572046852252</v>
+        <v>19.65720474070419</v>
       </c>
       <c r="BZ53" t="n">
         <v>63.89234965382096</v>
@@ -27008,7 +27008,7 @@
         <v>47.83445546432147</v>
       </c>
       <c r="CB53" t="n">
-        <v>85.52991754620786</v>
+        <v>85.52991758345958</v>
       </c>
       <c r="CC53" t="n">
         <v>11.76833333333333</v>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="CE53" t="inlineStr"/>
       <c r="CF53" t="n">
-        <v>14.0074712865501</v>
+        <v>14.00747131501237</v>
       </c>
       <c r="CG53" t="n">
         <v>11.76833333333333</v>
@@ -27039,7 +27039,7 @@
         <v>-80.45848735994448</v>
       </c>
       <c r="CM53" t="n">
-        <v>-74.15595739967583</v>
+        <v>-74.15595734716243</v>
       </c>
       <c r="CN53" t="inlineStr">
         <is>
@@ -27316,10 +27316,10 @@
         <v>4.639999866485596</v>
       </c>
       <c r="BX54" t="n">
-        <v>1.073494104114275</v>
+        <v>1.073494102797005</v>
       </c>
       <c r="BY54" t="n">
-        <v>1.99133156313198</v>
+        <v>1.991331560688444</v>
       </c>
       <c r="BZ54" t="n">
         <v>10.07868823457937</v>
@@ -27328,13 +27328,13 @@
         <v>9.446029690082037</v>
       </c>
       <c r="CB54" t="n">
-        <v>11.32627913908613</v>
+        <v>11.32627913874063</v>
       </c>
       <c r="CC54" t="n">
-        <v>4.230026072002111</v>
+        <v>4.230026072135482</v>
       </c>
       <c r="CD54" t="n">
-        <v>7.602765638944097</v>
+        <v>7.602765640627252</v>
       </c>
       <c r="CE54" t="n">
         <v>7.2410239750103</v>
@@ -27390,7 +27390,7 @@
         <v>7.906968852776419</v>
       </c>
       <c r="CZ54" t="n">
-        <v>-35.92779681249883</v>
+        <v>-35.92780109506861</v>
       </c>
       <c r="DA54" t="b">
         <v>0</v>
@@ -27632,10 +27632,10 @@
         <v>10.51000022888184</v>
       </c>
       <c r="BX55" t="n">
-        <v>13.08696656590138</v>
+        <v>13.086966536379</v>
       </c>
       <c r="BY55" t="n">
-        <v>19.0546233199524</v>
+        <v>19.05462327696782</v>
       </c>
       <c r="BZ55" t="n">
         <v>17.18616389628476</v>
@@ -27654,7 +27654,7 @@
         <v>14.72238167572673</v>
       </c>
       <c r="CF55" t="n">
-        <v>16.32432247877803</v>
+        <v>16.32432246669353</v>
       </c>
       <c r="CG55" t="n">
         <v>15.95427278600574</v>
@@ -27675,7 +27675,7 @@
         <v>36.62079157664122</v>
       </c>
       <c r="CM55" t="n">
-        <v>55.32180897502015</v>
+        <v>55.32180886003925</v>
       </c>
       <c r="CN55" t="inlineStr">
         <is>
@@ -27936,10 +27936,10 @@
         <v>29.69000053405762</v>
       </c>
       <c r="BX56" t="n">
-        <v>15.52022464046681</v>
+        <v>15.52022464562511</v>
       </c>
       <c r="BY56" t="n">
-        <v>28.79001670806593</v>
+        <v>28.79001671763458</v>
       </c>
       <c r="BZ56" t="n">
         <v>54.8664584485723</v>
@@ -27948,23 +27948,23 @@
         <v>49.47692096413685</v>
       </c>
       <c r="CB56" t="n">
-        <v>61.18292634636837</v>
+        <v>61.18292634510964</v>
       </c>
       <c r="CC56" t="n">
-        <v>36.64283818246783</v>
+        <v>36.64283818153474</v>
       </c>
       <c r="CD56" t="n">
-        <v>30.47133159014448</v>
+        <v>30.47133158302231</v>
       </c>
       <c r="CE56" t="inlineStr"/>
       <c r="CF56" t="n">
-        <v>33.95488449489322</v>
+        <v>33.95488449834168</v>
       </c>
       <c r="CG56" t="n">
-        <v>32.71642744526688</v>
+        <v>32.71642744958466</v>
       </c>
       <c r="CH56" t="n">
-        <v>29.44478470074019</v>
+        <v>29.44478470462619</v>
       </c>
       <c r="CI56" t="n">
         <v>4</v>
@@ -27976,10 +27976,10 @@
         <v>3.5</v>
       </c>
       <c r="CL56" t="n">
-        <v>-0.8259206093180649</v>
+        <v>-0.8259205962294902</v>
       </c>
       <c r="CM56" t="n">
-        <v>14.3647150020874</v>
+        <v>14.36471501370227</v>
       </c>
       <c r="CN56" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>-0.8018702595090188</v>
       </c>
       <c r="CZ56" t="n">
-        <v>-18.56622956112421</v>
+        <v>-18.56623828442452</v>
       </c>
       <c r="DA56" t="b">
         <v>0</v>
@@ -28262,37 +28262,37 @@
         <v>23.78000068664551</v>
       </c>
       <c r="BX57" t="n">
-        <v>10.50498165533896</v>
+        <v>10.50498165492592</v>
       </c>
       <c r="BY57" t="n">
-        <v>15.2215972950233</v>
+        <v>15.22159729527519</v>
       </c>
       <c r="BZ57" t="n">
-        <v>19.84847166416833</v>
+        <v>19.8484716652772</v>
       </c>
       <c r="CA57" t="n">
         <v>22.05215577512442</v>
       </c>
       <c r="CB57" t="n">
-        <v>19.44680932736826</v>
+        <v>19.44680932788322</v>
       </c>
       <c r="CC57" t="n">
-        <v>22.99285751133411</v>
+        <v>23.36371005195449</v>
       </c>
       <c r="CD57" t="n">
-        <v>9.891671195536906</v>
+        <v>9.891671196153721</v>
       </c>
       <c r="CE57" t="n">
         <v>19.45038570269356</v>
       </c>
       <c r="CF57" t="n">
-        <v>17.42611626582348</v>
+        <v>17.47247283366097</v>
       </c>
       <c r="CG57" t="n">
-        <v>19.44859751503091</v>
+        <v>19.44859751528839</v>
       </c>
       <c r="CH57" t="n">
-        <v>17.50373776352782</v>
+        <v>17.50373776375955</v>
       </c>
       <c r="CI57" t="n">
         <v>8</v>
@@ -28301,13 +28301,13 @@
         <v>1</v>
       </c>
       <c r="CK57" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="CL57" t="n">
-        <v>-26.39303087422678</v>
+        <v>-26.3930308732523</v>
       </c>
       <c r="CM57" t="n">
-        <v>-26.71944590981561</v>
+        <v>-26.52450660578305</v>
       </c>
       <c r="CN57" t="inlineStr">
         <is>
@@ -28586,10 +28586,10 @@
         <v>24.32999992370605</v>
       </c>
       <c r="BX58" t="n">
-        <v>4.265826969219717</v>
+        <v>4.265826982686783</v>
       </c>
       <c r="BY58" t="n">
-        <v>7.913109027902573</v>
+        <v>7.913109052883983</v>
       </c>
       <c r="BZ58" t="n">
         <v>29.33325741484123</v>
@@ -28598,13 +28598,13 @@
         <v>29.21395447941907</v>
       </c>
       <c r="CB58" t="n">
-        <v>26.33700607878938</v>
+        <v>26.33700607156679</v>
       </c>
       <c r="CC58" t="n">
-        <v>2.973172390416636</v>
+        <v>2.973172390117484</v>
       </c>
       <c r="CD58" t="n">
-        <v>19.05301343059025</v>
+        <v>19.05301341526689</v>
       </c>
       <c r="CE58" t="n">
         <v>18.00727121747286</v>
@@ -28900,10 +28900,10 @@
         <v>49.58000183105469</v>
       </c>
       <c r="BX59" t="n">
-        <v>8.252002701618549</v>
+        <v>8.25200272869739</v>
       </c>
       <c r="BY59" t="n">
-        <v>15.30746501150241</v>
+        <v>15.30746506173366</v>
       </c>
       <c r="BZ59" t="n">
         <v>19.94943893900621</v>
@@ -28912,25 +28912,25 @@
         <v>12.40196818721602</v>
       </c>
       <c r="CB59" t="n">
-        <v>15.12548809804349</v>
+        <v>15.12548798384509</v>
       </c>
       <c r="CC59" t="n">
-        <v>20.74522888508173</v>
+        <v>20.74522886900135</v>
       </c>
       <c r="CD59" t="n">
-        <v>11.32438891728228</v>
+        <v>11.32438883826405</v>
       </c>
       <c r="CE59" t="n">
         <v>12.98629942513824</v>
       </c>
       <c r="CF59" t="n">
-        <v>14.51153502061111</v>
+        <v>14.51153500411275</v>
       </c>
       <c r="CG59" t="n">
-        <v>14.05589376159087</v>
+        <v>14.05589370449167</v>
       </c>
       <c r="CH59" t="n">
-        <v>12.65030438543178</v>
+        <v>12.6503043340425</v>
       </c>
       <c r="CI59" t="n">
         <v>8</v>
@@ -28942,10 +28942,10 @@
         <v>2.5</v>
       </c>
       <c r="CL59" t="n">
-        <v>-74.48506672400283</v>
+        <v>-74.48506682765203</v>
       </c>
       <c r="CM59" t="n">
-        <v>-70.73107203573812</v>
+        <v>-70.73107206901437</v>
       </c>
       <c r="CN59" t="inlineStr">
         <is>
@@ -29240,10 +29240,10 @@
         <v>33.61999893188477</v>
       </c>
       <c r="BX60" t="n">
-        <v>11.88440177907633</v>
+        <v>11.88440173407689</v>
       </c>
       <c r="BY60" t="n">
-        <v>22.0455653001866</v>
+        <v>22.04556521671263</v>
       </c>
       <c r="BZ60" t="n">
         <v>39.73817893376209</v>
@@ -29252,25 +29252,25 @@
         <v>32.40852551699374</v>
       </c>
       <c r="CB60" t="n">
-        <v>40.5466134182216</v>
+        <v>40.54661348329596</v>
       </c>
       <c r="CC60" t="n">
-        <v>23.78010069884006</v>
+        <v>23.78010070769682</v>
       </c>
       <c r="CD60" t="n">
-        <v>24.16893068275144</v>
+        <v>24.16893075898049</v>
       </c>
       <c r="CE60" t="n">
         <v>25.56648631344748</v>
       </c>
       <c r="CF60" t="n">
-        <v>27.51735033040992</v>
+        <v>27.51735033312076</v>
       </c>
       <c r="CG60" t="n">
-        <v>24.86770849809946</v>
+        <v>24.86770853621398</v>
       </c>
       <c r="CH60" t="n">
-        <v>22.38093764828951</v>
+        <v>22.38093768259258</v>
       </c>
       <c r="CI60" t="n">
         <v>8</v>
@@ -29282,10 +29282,10 @@
         <v>3.4</v>
       </c>
       <c r="CL60" t="n">
-        <v>-33.42968959150166</v>
+        <v>-33.42968948946992</v>
       </c>
       <c r="CM60" t="n">
-        <v>-18.15184055727966</v>
+        <v>-18.15184054921647</v>
       </c>
       <c r="CN60" t="inlineStr">
         <is>
@@ -29564,10 +29564,10 @@
         <v>4.519999980926514</v>
       </c>
       <c r="BX61" t="n">
-        <v>2.935043321212322</v>
+        <v>2.935043319749744</v>
       </c>
       <c r="BY61" t="n">
-        <v>5.444505360848858</v>
+        <v>5.444505358135775</v>
       </c>
       <c r="BZ61" t="n">
         <v>13.76781603385662</v>
@@ -29576,13 +29576,13 @@
         <v>15.32423511716514</v>
       </c>
       <c r="CB61" t="n">
-        <v>15.90374916955883</v>
+        <v>15.90374916695663</v>
       </c>
       <c r="CC61" t="n">
-        <v>9.471435211183172</v>
+        <v>9.471435211363815</v>
       </c>
       <c r="CD61" t="n">
-        <v>6.834912648998449</v>
+        <v>6.834912650321556</v>
       </c>
       <c r="CE61" t="n">
         <v>1.44645468896914</v>
@@ -29878,37 +29878,37 @@
         <v>30</v>
       </c>
       <c r="BX62" t="n">
-        <v>13.81421965444975</v>
+        <v>13.81421961956552</v>
       </c>
       <c r="BY62" t="n">
-        <v>14.6766781942743</v>
+        <v>14.67667818667521</v>
       </c>
       <c r="BZ62" t="n">
-        <v>15.82099669036707</v>
+        <v>15.82099672212732</v>
       </c>
       <c r="CA62" t="n">
         <v>31.15287379381833</v>
       </c>
       <c r="CB62" t="n">
-        <v>14.95526752313823</v>
+        <v>14.95526753828155</v>
       </c>
       <c r="CC62" t="n">
-        <v>30.37744171199433</v>
+        <v>30.52562436162667</v>
       </c>
       <c r="CD62" t="n">
-        <v>6.52190794977579</v>
+        <v>6.521907980627405</v>
       </c>
       <c r="CE62" t="n">
         <v>38.80831925964276</v>
       </c>
       <c r="CF62" t="n">
-        <v>18.18848364540254</v>
+        <v>18.20965260038886</v>
       </c>
       <c r="CG62" t="n">
-        <v>14.95526752313823</v>
+        <v>14.95526753828155</v>
       </c>
       <c r="CH62" t="n">
-        <v>13.4597407708244</v>
+        <v>13.45974078445339</v>
       </c>
       <c r="CI62" t="n">
         <v>7</v>
@@ -29920,10 +29920,10 @@
         <v>6</v>
       </c>
       <c r="CL62" t="n">
-        <v>-55.13419743058532</v>
+        <v>-55.13419738515536</v>
       </c>
       <c r="CM62" t="n">
-        <v>-39.37172118199154</v>
+        <v>-39.30115799870381</v>
       </c>
       <c r="CN62" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>-5.213268999738752</v>
       </c>
       <c r="CZ62" t="n">
-        <v>-27.23200907385727</v>
+        <v>-27.23199551707314</v>
       </c>
       <c r="DA62" t="b">
         <v>0</v>
@@ -30202,35 +30202,35 @@
         <v>3.509999990463257</v>
       </c>
       <c r="BX63" t="n">
-        <v>2.694277162698206</v>
+        <v>2.694277181360765</v>
       </c>
       <c r="BY63" t="n">
-        <v>3.2213095997089</v>
+        <v>3.221309606253355</v>
       </c>
       <c r="BZ63" t="n">
-        <v>4.095040444629302</v>
+        <v>4.095040424583558</v>
       </c>
       <c r="CA63" t="n">
         <v>7.355188608855169</v>
       </c>
       <c r="CB63" t="n">
-        <v>6.136182372263043</v>
+        <v>6.136182382847855</v>
       </c>
       <c r="CC63" t="n">
-        <v>8.504201678697649</v>
+        <v>8.504201674334045</v>
       </c>
       <c r="CD63" t="n">
-        <v>1.898979087535158</v>
+        <v>1.898979071752606</v>
       </c>
       <c r="CE63" t="inlineStr"/>
       <c r="CF63" t="n">
-        <v>4.843596993483919</v>
+        <v>4.843596992855336</v>
       </c>
       <c r="CG63" t="n">
-        <v>4.095040444629302</v>
+        <v>4.095040424583558</v>
       </c>
       <c r="CH63" t="n">
-        <v>3.685536400166372</v>
+        <v>3.685536382125202</v>
       </c>
       <c r="CI63" t="n">
         <v>7</v>
@@ -30242,10 +30242,10 @@
         <v>4.5</v>
       </c>
       <c r="CL63" t="n">
-        <v>5.001037327066982</v>
+        <v>5.001036813073534</v>
       </c>
       <c r="CM63" t="n">
-        <v>37.99421671350635</v>
+        <v>37.99421669559801</v>
       </c>
       <c r="CN63" t="inlineStr">
         <is>
@@ -30524,37 +30524,37 @@
         <v>18.63999938964844</v>
       </c>
       <c r="BX64" t="n">
-        <v>8.745140380649891</v>
+        <v>8.74514038693229</v>
       </c>
       <c r="BY64" t="n">
-        <v>9.25302284189222</v>
+        <v>9.253022841577703</v>
       </c>
       <c r="BZ64" t="n">
-        <v>9.762664751133441</v>
+        <v>9.762664743788223</v>
       </c>
       <c r="CA64" t="n">
         <v>16.97559723955254</v>
       </c>
       <c r="CB64" t="n">
-        <v>9.361180431993921</v>
+        <v>9.361180426655146</v>
       </c>
       <c r="CC64" t="n">
-        <v>17.55266733914102</v>
+        <v>17.55266733759782</v>
       </c>
       <c r="CD64" t="n">
-        <v>4.001855352208201</v>
+        <v>4.001855345021139</v>
       </c>
       <c r="CE64" t="n">
         <v>16.08382941914014</v>
       </c>
       <c r="CF64" t="n">
-        <v>11.46699471946392</v>
+        <v>11.46699471753313</v>
       </c>
       <c r="CG64" t="n">
-        <v>9.561922591563681</v>
+        <v>9.561922585221684</v>
       </c>
       <c r="CH64" t="n">
-        <v>8.605730332407314</v>
+        <v>8.605730326699515</v>
       </c>
       <c r="CI64" t="n">
         <v>8</v>
@@ -30566,10 +30566,10 @@
         <v>4.4</v>
       </c>
       <c r="CL64" t="n">
-        <v>-53.8319173058212</v>
+        <v>-53.83191733644244</v>
       </c>
       <c r="CM64" t="n">
-        <v>-38.48178597134494</v>
+        <v>-38.48178598170329</v>
       </c>
       <c r="CN64" t="inlineStr">
         <is>
@@ -31164,10 +31164,10 @@
         <v>36.06999969482422</v>
       </c>
       <c r="BX66" t="n">
-        <v>10.32734667443655</v>
+        <v>10.32734671252357</v>
       </c>
       <c r="BY66" t="n">
-        <v>19.1572280810798</v>
+        <v>19.15722815173122</v>
       </c>
       <c r="BZ66" t="n">
         <v>29.79597855089906</v>
@@ -31176,25 +31176,25 @@
         <v>22.11977982655244</v>
       </c>
       <c r="CB66" t="n">
-        <v>27.689918959173</v>
+        <v>27.68991886838946</v>
       </c>
       <c r="CC66" t="n">
-        <v>22.95497934994834</v>
+        <v>22.9549793382587</v>
       </c>
       <c r="CD66" t="n">
-        <v>17.74659921277622</v>
+        <v>17.74659913481667</v>
       </c>
       <c r="CE66" t="n">
         <v>27.14442054393252</v>
       </c>
       <c r="CF66" t="n">
-        <v>22.11703139984974</v>
+        <v>22.11703139088795</v>
       </c>
       <c r="CG66" t="n">
-        <v>22.53737958825039</v>
+        <v>22.53737958240557</v>
       </c>
       <c r="CH66" t="n">
-        <v>20.28364162942535</v>
+        <v>20.28364162416501</v>
       </c>
       <c r="CI66" t="n">
         <v>8</v>
@@ -31206,10 +31206,10 @@
         <v>2.9</v>
       </c>
       <c r="CL66" t="n">
-        <v>-43.76589464641469</v>
+        <v>-43.76589466099838</v>
       </c>
       <c r="CM66" t="n">
-        <v>-38.68302859169867</v>
+        <v>-38.68302861654422</v>
       </c>
       <c r="CN66" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>4.42964313474894</v>
       </c>
       <c r="CZ66" t="n">
-        <v>-19.75885395890232</v>
+        <v>-19.75884710571682</v>
       </c>
       <c r="DA66" t="b">
         <v>0</v>
@@ -31492,10 +31492,10 @@
         <v>8.960000038146973</v>
       </c>
       <c r="BX67" t="n">
-        <v>0.5329077799188203</v>
+        <v>0.5329077806602136</v>
       </c>
       <c r="BY67" t="n">
-        <v>0.9885439317494117</v>
+        <v>0.9885439331246964</v>
       </c>
       <c r="BZ67" t="n">
         <v>10.18181822516701</v>
@@ -31504,13 +31504,13 @@
         <v>9.355421567964147</v>
       </c>
       <c r="CB67" t="n">
-        <v>11.19304002413374</v>
+        <v>11.1930400234452</v>
       </c>
       <c r="CC67" t="n">
-        <v>0.7359287832457172</v>
+        <v>0.7359287832324234</v>
       </c>
       <c r="CD67" t="n">
-        <v>8.686260804563911</v>
+        <v>8.686260803571571</v>
       </c>
       <c r="CE67" t="inlineStr"/>
       <c r="CF67" t="inlineStr"/>
@@ -31808,10 +31808,10 @@
         <v>8.510000228881836</v>
       </c>
       <c r="BX68" t="n">
-        <v>1.637947945349258</v>
+        <v>1.637947944173167</v>
       </c>
       <c r="BY68" t="n">
-        <v>3.038393438622874</v>
+        <v>3.038393436441224</v>
       </c>
       <c r="BZ68" t="n">
         <v>25.00166364361071</v>
@@ -31820,13 +31820,13 @@
         <v>24.7460880607331</v>
       </c>
       <c r="CB68" t="n">
-        <v>26.7494403277319</v>
+        <v>26.74944032623308</v>
       </c>
       <c r="CC68" t="n">
-        <v>6.71096436840774</v>
+        <v>6.710964368476396</v>
       </c>
       <c r="CD68" t="n">
-        <v>18.6587046154605</v>
+        <v>18.65870461681319</v>
       </c>
       <c r="CE68" t="n">
         <v>14.23395771137433</v>
@@ -32122,10 +32122,10 @@
         <v>21.79999923706055</v>
       </c>
       <c r="BX69" t="n">
-        <v>6.028554345793752</v>
+        <v>6.028554346258669</v>
       </c>
       <c r="BY69" t="n">
-        <v>11.18296831144741</v>
+        <v>11.18296831230983</v>
       </c>
       <c r="BZ69" t="n">
         <v>33.43171179294585</v>
@@ -32134,25 +32134,25 @@
         <v>34.49643348400799</v>
       </c>
       <c r="CB69" t="n">
-        <v>30.08621130044126</v>
+        <v>30.08621130040702</v>
       </c>
       <c r="CC69" t="n">
-        <v>25.30591858361604</v>
+        <v>25.30591858354294</v>
       </c>
       <c r="CD69" t="n">
-        <v>19.51154839334841</v>
+        <v>19.51154839285337</v>
       </c>
       <c r="CE69" t="n">
         <v>13.40148489337126</v>
       </c>
       <c r="CF69" t="n">
-        <v>23.91661096559688</v>
+        <v>23.91661096563404</v>
       </c>
       <c r="CG69" t="n">
-        <v>25.30591858361604</v>
+        <v>25.30591858354294</v>
       </c>
       <c r="CH69" t="n">
-        <v>22.77532672525444</v>
+        <v>22.77532672518865</v>
       </c>
       <c r="CI69" t="n">
         <v>7</v>
@@ -32164,10 +32164,10 @@
         <v>5.7</v>
       </c>
       <c r="CL69" t="n">
-        <v>4.473979460218547</v>
+        <v>4.473979459916766</v>
       </c>
       <c r="CM69" t="n">
-        <v>9.709228452348029</v>
+        <v>9.70922845251847</v>
       </c>
       <c r="CN69" t="inlineStr">
         <is>
@@ -32450,10 +32450,10 @@
         <v>24.69000053405762</v>
       </c>
       <c r="BX70" t="n">
-        <v>4.528795217843462</v>
+        <v>4.528795221897692</v>
       </c>
       <c r="BY70" t="n">
-        <v>8.400915129099621</v>
+        <v>8.400915136620219</v>
       </c>
       <c r="BZ70" t="n">
         <v>31.27557429027375</v>
@@ -32462,13 +32462,13 @@
         <v>26.55156008995373</v>
       </c>
       <c r="CB70" t="n">
-        <v>36.79121579285436</v>
+        <v>36.79121578817753</v>
       </c>
       <c r="CC70" t="n">
-        <v>11.80687700268151</v>
+        <v>11.80687700223436</v>
       </c>
       <c r="CD70" t="n">
-        <v>25.62152608874692</v>
+        <v>25.62152608239638</v>
       </c>
       <c r="CE70" t="n">
         <v>25.17925941757476</v>
@@ -32764,25 +32764,25 @@
         <v>17.30999946594238</v>
       </c>
       <c r="BX71" t="n">
-        <v>4.028449975644791</v>
+        <v>4.028449978070674</v>
       </c>
       <c r="BY71" t="n">
-        <v>6.922307408476789</v>
+        <v>6.922307411470418</v>
       </c>
       <c r="BZ71" t="n">
-        <v>23.65950143892474</v>
+        <v>23.65950143490909</v>
       </c>
       <c r="CA71" t="n">
         <v>32.98569202610356</v>
       </c>
       <c r="CB71" t="n">
-        <v>16.71223336934571</v>
+        <v>16.71223337052959</v>
       </c>
       <c r="CC71" t="n">
-        <v>20.3004620853361</v>
+        <v>20.30046208507653</v>
       </c>
       <c r="CD71" t="n">
-        <v>11.70662164179114</v>
+        <v>11.70662164015804</v>
       </c>
       <c r="CE71" t="n">
         <v>21.93193610654263</v>
@@ -32834,7 +32834,7 @@
         <v>-1.364797304640797</v>
       </c>
       <c r="CZ71" t="n">
-        <v>-40.04429185860444</v>
+        <v>-40.04429587939873</v>
       </c>
       <c r="DA71" t="b">
         <v>0</v>
@@ -33078,35 +33078,35 @@
         <v>23.89999961853027</v>
       </c>
       <c r="BX72" t="n">
-        <v>22.96133601733414</v>
+        <v>22.96133611046082</v>
       </c>
       <c r="BY72" t="n">
-        <v>29.32452635976519</v>
+        <v>29.32452638621756</v>
       </c>
       <c r="BZ72" t="n">
-        <v>39.49704754384081</v>
+        <v>39.49704741927707</v>
       </c>
       <c r="CA72" t="n">
         <v>62.81937459029582</v>
       </c>
       <c r="CB72" t="n">
-        <v>70.08903035270892</v>
+        <v>70.08903045030866</v>
       </c>
       <c r="CC72" t="n">
-        <v>41.76900676852177</v>
+        <v>41.76900675550808</v>
       </c>
       <c r="CD72" t="n">
-        <v>19.01744470510681</v>
+        <v>19.01744461799239</v>
       </c>
       <c r="CE72" t="inlineStr"/>
       <c r="CF72" t="n">
-        <v>40.78253804822477</v>
+        <v>40.78253804715148</v>
       </c>
       <c r="CG72" t="n">
-        <v>39.49704754384081</v>
+        <v>39.49704741927707</v>
       </c>
       <c r="CH72" t="n">
-        <v>35.54734278945673</v>
+        <v>35.54734267734936</v>
       </c>
       <c r="CI72" t="n">
         <v>7</v>
@@ -33118,10 +33118,10 @@
         <v>3.7</v>
       </c>
       <c r="CL72" t="n">
-        <v>48.7336542126803</v>
+        <v>48.73365374361182</v>
       </c>
       <c r="CM72" t="n">
-        <v>70.63823723497067</v>
+        <v>70.63823723047993</v>
       </c>
       <c r="CN72" t="inlineStr">
         <is>
@@ -33400,10 +33400,10 @@
         <v>4.050000190734863</v>
       </c>
       <c r="BX73" t="n">
-        <v>0.9834174969746797</v>
+        <v>0.9834174955160336</v>
       </c>
       <c r="BY73" t="n">
-        <v>1.824239456888031</v>
+        <v>1.824239454182242</v>
       </c>
       <c r="BZ73" t="n">
         <v>6.261668906328697</v>
@@ -33412,7 +33412,7 @@
         <v>4.158686841231277</v>
       </c>
       <c r="CB73" t="n">
-        <v>8.695198111863299</v>
+        <v>8.695198109480446</v>
       </c>
       <c r="CC73" t="n">
         <v>3.760485277130923</v>
@@ -33470,7 +33470,7 @@
         <v>1.50376393620828</v>
       </c>
       <c r="CZ73" t="n">
-        <v>-44.63291810308804</v>
+        <v>-44.6329217901767</v>
       </c>
       <c r="DA73" t="b">
         <v>0</v>
@@ -33714,10 +33714,10 @@
         <v>12.53999996185303</v>
       </c>
       <c r="BX74" t="n">
-        <v>2.073799231394308</v>
+        <v>2.073799234551615</v>
       </c>
       <c r="BY74" t="n">
-        <v>3.846897574236441</v>
+        <v>3.846897580093246</v>
       </c>
       <c r="BZ74" t="n">
         <v>16.58233527889746</v>
@@ -33726,7 +33726,7 @@
         <v>13.15648423765553</v>
       </c>
       <c r="CB74" t="n">
-        <v>21.66997890891374</v>
+        <v>21.66997891332515</v>
       </c>
       <c r="CC74" t="n">
         <v>9.294207014285712</v>
@@ -34030,10 +34030,10 @@
         <v>55.5</v>
       </c>
       <c r="BX75" t="n">
-        <v>40.36268322071383</v>
+        <v>40.36268322185821</v>
       </c>
       <c r="BY75" t="n">
-        <v>58.76806676935935</v>
+        <v>58.76806677102556</v>
       </c>
       <c r="BZ75" t="n">
         <v>35.98503740648379</v>
@@ -34052,13 +34052,13 @@
         <v>47.31284142717968</v>
       </c>
       <c r="CF75" t="n">
-        <v>43.20016088954765</v>
+        <v>43.20016089001607</v>
       </c>
       <c r="CG75" t="n">
-        <v>41.66677586240407</v>
+        <v>41.66677586297625</v>
       </c>
       <c r="CH75" t="n">
-        <v>37.50009827616366</v>
+        <v>37.50009827667863</v>
       </c>
       <c r="CI75" t="n">
         <v>6</v>
@@ -34070,10 +34070,10 @@
         <v>6.4</v>
       </c>
       <c r="CL75" t="n">
-        <v>-32.43225535826367</v>
+        <v>-32.43225535733581</v>
       </c>
       <c r="CM75" t="n">
-        <v>-22.16187227108533</v>
+        <v>-22.16187227024131</v>
       </c>
       <c r="CN75" t="inlineStr">
         <is>
@@ -34332,35 +34332,35 @@
         <v>12.85999965667725</v>
       </c>
       <c r="BX76" t="n">
-        <v>10.87454812872476</v>
+        <v>10.87454816796245</v>
       </c>
       <c r="BY76" t="n">
-        <v>11.49697211879848</v>
+        <v>11.49697209321865</v>
       </c>
       <c r="BZ76" t="n">
-        <v>11.90131694288041</v>
+        <v>11.90131687345846</v>
       </c>
       <c r="CA76" t="n">
         <v>16.82961568340781</v>
       </c>
       <c r="CB76" t="n">
-        <v>19.71212212356147</v>
+        <v>19.71212208266349</v>
       </c>
       <c r="CC76" t="n">
-        <v>7.38241558969151</v>
+        <v>7.382415584655944</v>
       </c>
       <c r="CD76" t="n">
-        <v>4.873141834292192</v>
+        <v>4.873141766269742</v>
       </c>
       <c r="CE76" t="inlineStr"/>
       <c r="CF76" t="n">
-        <v>10.41381319502379</v>
+        <v>10.41381317982388</v>
       </c>
       <c r="CG76" t="n">
-        <v>11.18576012376162</v>
+        <v>11.18576013059055</v>
       </c>
       <c r="CH76" t="n">
-        <v>10.06718411138546</v>
+        <v>10.06718411753149</v>
       </c>
       <c r="CI76" t="n">
         <v>4</v>
@@ -34372,10 +34372,10 @@
         <v>1.6</v>
       </c>
       <c r="CL76" t="n">
-        <v>-21.71707324923359</v>
+        <v>-21.71707320144173</v>
       </c>
       <c r="CM76" t="n">
-        <v>-19.02166817231081</v>
+        <v>-19.02166829050611</v>
       </c>
       <c r="CN76" t="inlineStr">
         <is>
@@ -34654,10 +34654,10 @@
         <v>28.85000038146973</v>
       </c>
       <c r="BX77" t="n">
-        <v>13.47679398648694</v>
+        <v>13.47679399227867</v>
       </c>
       <c r="BY77" t="n">
-        <v>24.99945284493327</v>
+        <v>24.99945285567694</v>
       </c>
       <c r="BZ77" t="n">
         <v>38.1119147611639</v>
@@ -34666,25 +34666,25 @@
         <v>26.54383559620355</v>
       </c>
       <c r="CB77" t="n">
-        <v>44.90735160876068</v>
+        <v>44.90735159546294</v>
       </c>
       <c r="CC77" t="n">
-        <v>42.35229042998681</v>
+        <v>42.35229042710036</v>
       </c>
       <c r="CD77" t="n">
-        <v>24.08739123719862</v>
+        <v>24.08739122375856</v>
       </c>
       <c r="CE77" t="n">
         <v>24.8974245271389</v>
       </c>
       <c r="CF77" t="n">
-        <v>29.92205687398408</v>
+        <v>29.92205687234797</v>
       </c>
       <c r="CG77" t="n">
-        <v>25.77164422056841</v>
+        <v>25.77164422594024</v>
       </c>
       <c r="CH77" t="n">
-        <v>23.19447979851157</v>
+        <v>23.19447980334622</v>
       </c>
       <c r="CI77" t="n">
         <v>8</v>
@@ -34696,10 +34696,10 @@
         <v>3.3</v>
       </c>
       <c r="CL77" t="n">
-        <v>-19.60319066959416</v>
+        <v>-19.60319065283629</v>
       </c>
       <c r="CM77" t="n">
-        <v>3.715966995975961</v>
+        <v>3.715966990304875</v>
       </c>
       <c r="CN77" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>-2.337816543811788</v>
       </c>
       <c r="CZ77" t="n">
-        <v>-24.19493858539801</v>
+        <v>-24.19493061245316</v>
       </c>
       <c r="DA77" t="b">
         <v>0</v>
@@ -34986,10 +34986,10 @@
         <v>15.11999988555908</v>
       </c>
       <c r="BX78" t="n">
-        <v>2.439882942804438</v>
+        <v>2.439882943900921</v>
       </c>
       <c r="BY78" t="n">
-        <v>4.525982858902231</v>
+        <v>4.525982860936208</v>
       </c>
       <c r="BZ78" t="n">
         <v>26.57029157608194</v>
@@ -34998,7 +34998,7 @@
         <v>20.33365271794082</v>
       </c>
       <c r="CB78" t="n">
-        <v>34.60986200035124</v>
+        <v>34.60986200238716</v>
       </c>
       <c r="CC78" t="n">
         <v>10.38593205872702</v>
@@ -35304,10 +35304,10 @@
         <v>14.64999961853027</v>
       </c>
       <c r="BX79" t="n">
-        <v>9.578902374596568</v>
+        <v>9.578902405897873</v>
       </c>
       <c r="BY79" t="n">
-        <v>17.76886390487664</v>
+        <v>17.76886396294055</v>
       </c>
       <c r="BZ79" t="n">
         <v>14.2102851351044</v>
@@ -35328,7 +35328,7 @@
         <v>12.06136669897467</v>
       </c>
       <c r="CF79" t="n">
-        <v>15.18293135971039</v>
+        <v>15.18293137088104</v>
       </c>
       <c r="CG79" t="n">
         <v>13.55468557413323</v>
@@ -35349,7 +35349,7 @@
         <v>-16.72889191553597</v>
       </c>
       <c r="CM79" t="n">
-        <v>3.637759420184783</v>
+        <v>3.637759496434967</v>
       </c>
       <c r="CN79" t="inlineStr">
         <is>
@@ -35628,25 +35628,25 @@
         <v>26.55999946594238</v>
       </c>
       <c r="BX80" t="n">
-        <v>12.09583913639073</v>
+        <v>12.09583914676028</v>
       </c>
       <c r="BY80" t="n">
-        <v>12.89484428908725</v>
+        <v>12.89484429399581</v>
       </c>
       <c r="BZ80" t="n">
-        <v>14.4152591724424</v>
+        <v>14.41525916557178</v>
       </c>
       <c r="CA80" t="n">
         <v>33.30354002524292</v>
       </c>
       <c r="CB80" t="n">
-        <v>13.5215665468583</v>
+        <v>13.52156654665155</v>
       </c>
       <c r="CC80" t="n">
-        <v>24.69737288532047</v>
+        <v>24.69737288395405</v>
       </c>
       <c r="CD80" t="n">
-        <v>5.969673610448125</v>
+        <v>5.969673603814106</v>
       </c>
       <c r="CE80" t="n">
         <v>64.9533816160684</v>
@@ -35942,35 +35942,35 @@
         <v>2.740000009536743</v>
       </c>
       <c r="BX81" t="n">
-        <v>1.25964964149074</v>
+        <v>1.259649643459965</v>
       </c>
       <c r="BY81" t="n">
-        <v>1.768404342102879</v>
+        <v>1.7684043440741</v>
       </c>
       <c r="BZ81" t="n">
-        <v>4.169355427420831</v>
+        <v>4.169355425550364</v>
       </c>
       <c r="CA81" t="n">
         <v>7.812220106719857</v>
       </c>
       <c r="CB81" t="n">
-        <v>4.198816918476743</v>
+        <v>4.198816920906828</v>
       </c>
       <c r="CC81" t="n">
-        <v>1.40930818809145</v>
+        <v>1.343758969986019</v>
       </c>
       <c r="CD81" t="n">
-        <v>2.06790543313807</v>
+        <v>2.067905432035935</v>
       </c>
       <c r="CE81" t="inlineStr"/>
       <c r="CF81" t="n">
-        <v>2.478906658453452</v>
+        <v>2.467981789335535</v>
       </c>
       <c r="CG81" t="n">
-        <v>1.918154887620474</v>
+        <v>1.918154888055017</v>
       </c>
       <c r="CH81" t="n">
-        <v>1.726339398858427</v>
+        <v>1.726339399249516</v>
       </c>
       <c r="CI81" t="n">
         <v>6</v>
@@ -35982,10 +35982,10 @@
         <v>6.2</v>
       </c>
       <c r="CL81" t="n">
-        <v>-36.99491266971556</v>
+        <v>-36.99491265544225</v>
       </c>
       <c r="CM81" t="n">
-        <v>-9.528954385932087</v>
+        <v>-9.92767223556319</v>
       </c>
       <c r="CN81" t="inlineStr">
         <is>
@@ -36264,10 +36264,10 @@
         <v>6.949999809265137</v>
       </c>
       <c r="BX82" t="n">
-        <v>1.251744408842757</v>
+        <v>1.251744408289311</v>
       </c>
       <c r="BY82" t="n">
-        <v>2.321985878403313</v>
+        <v>2.321985877376673</v>
       </c>
       <c r="BZ82" t="n">
         <v>10.83382323208977</v>
@@ -36276,13 +36276,13 @@
         <v>10.63720103437324</v>
       </c>
       <c r="CB82" t="n">
-        <v>10.59280611164891</v>
+        <v>10.59280611176632</v>
       </c>
       <c r="CC82" t="n">
-        <v>1.875514633765064</v>
+        <v>1.875514633786436</v>
       </c>
       <c r="CD82" t="n">
-        <v>7.546697301247287</v>
+        <v>7.546697301894066</v>
       </c>
       <c r="CE82" t="n">
         <v>10.17050614593439</v>
@@ -36578,10 +36578,10 @@
         <v>9.840000152587891</v>
       </c>
       <c r="BX83" t="n">
-        <v>6.031752834367726</v>
+        <v>6.03175285881263</v>
       </c>
       <c r="BY83" t="n">
-        <v>11.18890150775213</v>
+        <v>11.18890155309743</v>
       </c>
       <c r="BZ83" t="n">
         <v>8.033271843609951</v>
@@ -36602,7 +36602,7 @@
         <v>40.23059672158782</v>
       </c>
       <c r="CF83" t="n">
-        <v>10.14916135501505</v>
+        <v>10.14916136498508</v>
       </c>
       <c r="CG83" t="n">
         <v>8.033271843609951</v>
@@ -36623,7 +36623,7 @@
         <v>-26.52495378927914</v>
       </c>
       <c r="CM83" t="n">
-        <v>3.141882089766579</v>
+        <v>3.141882191087997</v>
       </c>
       <c r="CN83" t="inlineStr">
         <is>
@@ -36900,10 +36900,10 @@
         <v>5.159999847412109</v>
       </c>
       <c r="BX84" t="n">
-        <v>3.051395861962572</v>
+        <v>3.051395882818362</v>
       </c>
       <c r="BY84" t="n">
-        <v>4.442832375017505</v>
+        <v>4.442832405383536</v>
       </c>
       <c r="BZ84" t="n">
         <v>4.377161371377319</v>
@@ -37188,10 +37188,10 @@
         <v>52.93999862670898</v>
       </c>
       <c r="BX85" t="n">
-        <v>11.11616390180424</v>
+        <v>11.11616392129055</v>
       </c>
       <c r="BY85" t="n">
-        <v>16.18513464102698</v>
+        <v>16.18513466939904</v>
       </c>
       <c r="BZ85" t="inlineStr"/>
       <c r="CA85" t="inlineStr"/>
@@ -37202,13 +37202,13 @@
       <c r="CD85" t="inlineStr"/>
       <c r="CE85" t="inlineStr"/>
       <c r="CF85" t="n">
-        <v>17.87633284761041</v>
+        <v>17.8763328635632</v>
       </c>
       <c r="CG85" t="n">
-        <v>16.18513464102698</v>
+        <v>16.18513466939904</v>
       </c>
       <c r="CH85" t="n">
-        <v>14.56662117692428</v>
+        <v>14.56662120245913</v>
       </c>
       <c r="CI85" t="n">
         <v>3</v>
@@ -37220,10 +37220,10 @@
         <v>2.4</v>
       </c>
       <c r="CL85" t="n">
-        <v>-72.48465894448435</v>
+        <v>-72.48465889625078</v>
       </c>
       <c r="CM85" t="n">
-        <v>-66.23284225286787</v>
+        <v>-66.23284222273415</v>
       </c>
       <c r="CN85" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>22.45000076293945</v>
       </c>
       <c r="BX86" t="n">
-        <v>11.31405136287344</v>
+        <v>11.31405128315595</v>
       </c>
       <c r="BY86" t="n">
-        <v>20.98756527813023</v>
+        <v>20.98756513025429</v>
       </c>
       <c r="BZ86" t="n">
         <v>15.19216088401163</v>
@@ -37538,13 +37538,13 @@
         <v>23.03202693646428</v>
       </c>
       <c r="CF86" t="n">
-        <v>19.65754613362034</v>
+        <v>19.65754610517116</v>
       </c>
       <c r="CG86" t="n">
-        <v>18.08986308107093</v>
+        <v>18.08986300713296</v>
       </c>
       <c r="CH86" t="n">
-        <v>16.28087677296384</v>
+        <v>16.28087670641966</v>
       </c>
       <c r="CI86" t="n">
         <v>8</v>
@@ -37556,10 +37556,10 @@
         <v>3</v>
       </c>
       <c r="CL86" t="n">
-        <v>-27.47939323084402</v>
+        <v>-27.47939352725459</v>
       </c>
       <c r="CM86" t="n">
-        <v>-12.43855026467929</v>
+        <v>-12.43855039140169</v>
       </c>
       <c r="CN86" t="inlineStr">
         <is>
@@ -38150,10 +38150,10 @@
         <v>18.45999908447266</v>
       </c>
       <c r="BX88" t="n">
-        <v>4.484582525127631</v>
+        <v>4.484582523342956</v>
       </c>
       <c r="BY88" t="n">
-        <v>8.318900584111756</v>
+        <v>8.318900580801182</v>
       </c>
       <c r="BZ88" t="n">
         <v>31.00063217607892</v>
@@ -38162,13 +38162,13 @@
         <v>33.42141293239761</v>
       </c>
       <c r="CB88" t="n">
-        <v>26.78755093170726</v>
+        <v>26.78755093128893</v>
       </c>
       <c r="CC88" t="n">
-        <v>11.12047331862219</v>
+        <v>11.12047331874309</v>
       </c>
       <c r="CD88" t="n">
-        <v>18.08633564144353</v>
+        <v>18.08633564317109</v>
       </c>
       <c r="CE88" t="n">
         <v>39.71865914645217</v>
@@ -38468,25 +38468,25 @@
         <v>1.690000057220459</v>
       </c>
       <c r="BX89" t="n">
-        <v>0.1506862968400711</v>
+        <v>0.1506862966979866</v>
       </c>
       <c r="BY89" t="n">
-        <v>0.171696878037741</v>
+        <v>0.1716968778821741</v>
       </c>
       <c r="BZ89" t="n">
-        <v>0.774905894763351</v>
+        <v>0.7749058947919139</v>
       </c>
       <c r="CA89" t="n">
         <v>3.21621281095181</v>
       </c>
       <c r="CB89" t="n">
-        <v>0.2641169346773998</v>
+        <v>0.2641169346043211</v>
       </c>
       <c r="CC89" t="n">
-        <v>0.5414796436172654</v>
+        <v>0.5414796436194493</v>
       </c>
       <c r="CD89" t="n">
-        <v>0.3456600223982224</v>
+        <v>0.3456600224227291</v>
       </c>
       <c r="CE89" t="inlineStr"/>
       <c r="CF89" t="inlineStr"/>
@@ -38782,10 +38782,10 @@
         <v>13.89999961853027</v>
       </c>
       <c r="BX90" t="n">
-        <v>6.000512463883257</v>
+        <v>6.000512473969495</v>
       </c>
       <c r="BY90" t="n">
-        <v>8.736746147414022</v>
+        <v>8.736746162099585</v>
       </c>
       <c r="BZ90" t="n">
         <v>3.740232756344498</v>
@@ -39094,10 +39094,10 @@
         <v>7.420000076293945</v>
       </c>
       <c r="BX91" t="n">
-        <v>3.087450361173849</v>
+        <v>3.087450359731478</v>
       </c>
       <c r="BY91" t="n">
-        <v>5.727220419977489</v>
+        <v>5.727220417301892</v>
       </c>
       <c r="BZ91" t="n">
         <v>15.03287477230807</v>
@@ -39106,23 +39106,23 @@
         <v>16.21959651842132</v>
       </c>
       <c r="CB91" t="n">
-        <v>14.39085493579771</v>
+        <v>14.39085493494747</v>
       </c>
       <c r="CC91" t="n">
-        <v>14.99868039719251</v>
+        <v>14.99868039746931</v>
       </c>
       <c r="CD91" t="n">
-        <v>7.922199668215433</v>
+        <v>7.922199669621802</v>
       </c>
       <c r="CE91" t="inlineStr"/>
       <c r="CF91" t="n">
-        <v>13.71284125838701</v>
+        <v>13.71284125855359</v>
       </c>
       <c r="CG91" t="n">
-        <v>14.99868039719251</v>
+        <v>14.99868039746931</v>
       </c>
       <c r="CH91" t="n">
-        <v>13.49881235747326</v>
+        <v>13.49881235772238</v>
       </c>
       <c r="CI91" t="n">
         <v>5</v>
@@ -39134,10 +39134,10 @@
         <v>5.3</v>
       </c>
       <c r="CL91" t="n">
-        <v>81.92469297406649</v>
+        <v>81.92469297742389</v>
       </c>
       <c r="CM91" t="n">
-        <v>84.80917947963333</v>
+        <v>84.8091794818784</v>
       </c>
       <c r="CN91" t="inlineStr">
         <is>
@@ -39418,10 +39418,10 @@
         <v>3.690000057220459</v>
       </c>
       <c r="BX92" t="n">
-        <v>33.80143549133481</v>
+        <v>33.80143550034843</v>
       </c>
       <c r="BY92" t="n">
-        <v>62.70166283642606</v>
+        <v>62.70166285314632</v>
       </c>
       <c r="BZ92" t="n">
         <v>4.860089538585594</v>
@@ -39714,35 +39714,35 @@
         <v>19.56999969482422</v>
       </c>
       <c r="BX93" t="n">
-        <v>11.66679782333251</v>
+        <v>11.66679780424779</v>
       </c>
       <c r="BY93" t="n">
-        <v>15.4210879871201</v>
+        <v>15.42108797443522</v>
       </c>
       <c r="BZ93" t="n">
-        <v>25.10431132229267</v>
+        <v>25.10431134270869</v>
       </c>
       <c r="CA93" t="n">
         <v>44.54686696093374</v>
       </c>
       <c r="CB93" t="n">
-        <v>30.38694754833936</v>
+        <v>30.38694753338507</v>
       </c>
       <c r="CC93" t="n">
-        <v>15.82484537310268</v>
+        <v>15.82484537433523</v>
       </c>
       <c r="CD93" t="n">
-        <v>12.25417619917221</v>
+        <v>12.25417621259106</v>
       </c>
       <c r="CE93" t="inlineStr"/>
       <c r="CF93" t="n">
-        <v>17.00426062646199</v>
+        <v>17.00426062393174</v>
       </c>
       <c r="CG93" t="n">
-        <v>15.62296668011139</v>
+        <v>15.62296667438523</v>
       </c>
       <c r="CH93" t="n">
-        <v>14.06067001210025</v>
+        <v>14.06067000694671</v>
       </c>
       <c r="CI93" t="n">
         <v>4</v>
@@ -39754,10 +39754,10 @@
         <v>2.2</v>
       </c>
       <c r="CL93" t="n">
-        <v>-28.15191501602857</v>
+        <v>-28.15191504236249</v>
       </c>
       <c r="CM93" t="n">
-        <v>-13.11057285831641</v>
+        <v>-13.11057287124566</v>
       </c>
       <c r="CN93" t="inlineStr">
         <is>
@@ -40046,10 +40046,10 @@
         <v>78.69999694824219</v>
       </c>
       <c r="BX94" t="n">
-        <v>58.83949685793001</v>
+        <v>58.83949676437168</v>
       </c>
       <c r="BY94" t="n">
-        <v>85.67030742514611</v>
+        <v>85.67030728892516</v>
       </c>
       <c r="BZ94" t="n">
         <v>24.78740061361959</v>
@@ -40362,10 +40362,10 @@
         <v>35.65000152587891</v>
       </c>
       <c r="BX95" t="n">
-        <v>8.823433614410847</v>
+        <v>8.823433620759227</v>
       </c>
       <c r="BY95" t="n">
-        <v>16.36746935473212</v>
+        <v>16.36746936650837</v>
       </c>
       <c r="BZ95" t="n">
         <v>42.70908862729615</v>
@@ -40374,19 +40374,19 @@
         <v>42.97434148367212</v>
       </c>
       <c r="CB95" t="n">
-        <v>36.27793360466261</v>
+        <v>36.27793360147332</v>
       </c>
       <c r="CC95" t="n">
-        <v>50.14199040583466</v>
+        <v>50.14199040421468</v>
       </c>
       <c r="CD95" t="n">
-        <v>24.39370807057</v>
+        <v>24.39370806351415</v>
       </c>
       <c r="CE95" t="n">
         <v>54.38971422125846</v>
       </c>
       <c r="CF95" t="n">
-        <v>38.17917796686088</v>
+        <v>38.17917796684818</v>
       </c>
       <c r="CG95" t="n">
         <v>42.70908862729615</v>
@@ -40407,7 +40407,7 @@
         <v>7.820976491862575</v>
       </c>
       <c r="CM95" t="n">
-        <v>7.094463766420889</v>
+        <v>7.094463766385273</v>
       </c>
       <c r="CN95" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>19.59000015258789</v>
       </c>
       <c r="BX96" t="n">
-        <v>2.021554711969168</v>
+        <v>2.021554705666515</v>
       </c>
       <c r="BY96" t="n">
-        <v>3.749983990702806</v>
+        <v>3.749983979011385</v>
       </c>
       <c r="BZ96" t="n">
         <v>10.85148419823535</v>
@@ -40706,19 +40706,19 @@
         <v>9.057717523549277</v>
       </c>
       <c r="CB96" t="n">
-        <v>11.05024976734021</v>
+        <v>11.05024977989582</v>
       </c>
       <c r="CC96" t="n">
-        <v>7.567164101673733</v>
+        <v>7.567164103013291</v>
       </c>
       <c r="CD96" t="n">
-        <v>8.390001911784012</v>
+        <v>8.390001921994815</v>
       </c>
       <c r="CE96" t="n">
         <v>14.26878965170031</v>
       </c>
       <c r="CF96" t="n">
-        <v>9.27648444928367</v>
+        <v>9.276484451057177</v>
       </c>
       <c r="CG96" t="n">
         <v>9.057717523549277</v>
@@ -40739,7 +40739,7 @@
         <v>-58.38720925115738</v>
       </c>
       <c r="CM96" t="n">
-        <v>-52.64683830000776</v>
+        <v>-52.64683829095463</v>
       </c>
       <c r="CN96" t="inlineStr">
         <is>
@@ -41020,10 +41020,10 @@
         <v>7.78000020980835</v>
       </c>
       <c r="BX97" t="n">
-        <v>5.007638628799211</v>
+        <v>5.007638608110152</v>
       </c>
       <c r="BY97" t="n">
-        <v>7.291121843531651</v>
+        <v>7.291121813408381</v>
       </c>
       <c r="BZ97" t="n">
         <v>5.804304317217133</v>
@@ -41042,13 +41042,13 @@
         <v>7.482269761699905</v>
       </c>
       <c r="CF97" t="n">
-        <v>6.550785520086774</v>
+        <v>6.550785511618052</v>
       </c>
       <c r="CG97" t="n">
-        <v>6.547713080374391</v>
+        <v>6.547713065312757</v>
       </c>
       <c r="CH97" t="n">
-        <v>5.892941772336952</v>
+        <v>5.892941758781482</v>
       </c>
       <c r="CI97" t="n">
         <v>6</v>
@@ -41060,10 +41060,10 @@
         <v>5.9</v>
       </c>
       <c r="CL97" t="n">
-        <v>-24.25524918485681</v>
+        <v>-24.25524935909164</v>
       </c>
       <c r="CM97" t="n">
-        <v>-15.79967424900437</v>
+        <v>-15.79967435785683</v>
       </c>
       <c r="CN97" t="inlineStr">
         <is>
@@ -41342,10 +41342,10 @@
         <v>15.90999984741211</v>
       </c>
       <c r="BX98" t="n">
-        <v>8.011259043519965</v>
+        <v>8.011259054289059</v>
       </c>
       <c r="BY98" t="n">
-        <v>14.86088552572954</v>
+        <v>14.8608855457062</v>
       </c>
       <c r="BZ98" t="n">
         <v>10.43085096379072</v>
@@ -41366,7 +41366,7 @@
         <v>8.936869495263364</v>
       </c>
       <c r="CF98" t="n">
-        <v>12.31270293006664</v>
+        <v>12.31270293390986</v>
       </c>
       <c r="CG98" t="n">
         <v>9.978191393663952</v>
@@ -41387,7 +41387,7 @@
         <v>-43.55517070757051</v>
       </c>
       <c r="CM98" t="n">
-        <v>-22.61028882367082</v>
+        <v>-22.61028879951482</v>
       </c>
       <c r="CN98" t="inlineStr">
         <is>
@@ -41666,10 +41666,10 @@
         <v>6.96999979019165</v>
       </c>
       <c r="BX99" t="n">
-        <v>3.118821959530353</v>
+        <v>3.118821969423426</v>
       </c>
       <c r="BY99" t="n">
-        <v>5.785414734928805</v>
+        <v>5.785414753280454</v>
       </c>
       <c r="BZ99" t="inlineStr"/>
       <c r="CA99" t="inlineStr"/>
@@ -41680,13 +41680,13 @@
         <v>9.526511531301223</v>
       </c>
       <c r="CF99" t="n">
-        <v>6.143582741920127</v>
+        <v>6.143582751335035</v>
       </c>
       <c r="CG99" t="n">
-        <v>5.785414734928805</v>
+        <v>5.785414753280454</v>
       </c>
       <c r="CH99" t="n">
-        <v>5.206873261435925</v>
+        <v>5.206873277952409</v>
       </c>
       <c r="CI99" t="n">
         <v>3</v>
@@ -41698,10 +41698,10 @@
         <v>3.1</v>
       </c>
       <c r="CL99" t="n">
-        <v>-25.29593374216221</v>
+        <v>-25.29593350519687</v>
       </c>
       <c r="CM99" t="n">
-        <v>-11.85677292895297</v>
+        <v>-11.85677279387539</v>
       </c>
       <c r="CN99" t="inlineStr">
         <is>
@@ -41980,25 +41980,25 @@
         <v>47.2400016784668</v>
       </c>
       <c r="BX100" t="n">
-        <v>18.15640581790407</v>
+        <v>18.15640576604682</v>
       </c>
       <c r="BY100" t="n">
-        <v>20.57934591739978</v>
+        <v>20.57934589188578</v>
       </c>
       <c r="BZ100" t="n">
-        <v>25.36192495986403</v>
+        <v>25.36192500085788</v>
       </c>
       <c r="CA100" t="n">
         <v>53.3467002990466</v>
       </c>
       <c r="CB100" t="n">
-        <v>21.45195355960631</v>
+        <v>21.45195356794589</v>
       </c>
       <c r="CC100" t="n">
-        <v>23.33743286253424</v>
+        <v>23.33743286668126</v>
       </c>
       <c r="CD100" t="n">
-        <v>11.25742189836525</v>
+        <v>11.2574219338688</v>
       </c>
       <c r="CE100" t="n">
         <v>121.096867054075</v>
@@ -42294,37 +42294,37 @@
         <v>23.35000038146973</v>
       </c>
       <c r="BX101" t="n">
-        <v>5.114427474428636</v>
+        <v>5.114427492218534</v>
       </c>
       <c r="BY101" t="n">
-        <v>7.202559906409332</v>
+        <v>7.202559910278175</v>
       </c>
       <c r="BZ101" t="n">
-        <v>10.55646946245659</v>
+        <v>10.55646943140762</v>
       </c>
       <c r="CA101" t="n">
         <v>14.59026773421743</v>
       </c>
       <c r="CB101" t="n">
-        <v>7.092388219416534</v>
+        <v>7.092388201669571</v>
       </c>
       <c r="CC101" t="n">
-        <v>8.429566139486898</v>
+        <v>8.429566137245022</v>
       </c>
       <c r="CD101" t="n">
-        <v>5.238787039419317</v>
+        <v>5.238787021228078</v>
       </c>
       <c r="CE101" t="n">
         <v>10.33412711493239</v>
       </c>
       <c r="CF101" t="n">
-        <v>8.56982413634589</v>
+        <v>8.569824130399603</v>
       </c>
       <c r="CG101" t="n">
-        <v>7.816063022948115</v>
+        <v>7.816063023761599</v>
       </c>
       <c r="CH101" t="n">
-        <v>7.034456720653304</v>
+        <v>7.034456721385439</v>
       </c>
       <c r="CI101" t="n">
         <v>8</v>
@@ -42336,10 +42336,10 @@
         <v>2.9</v>
       </c>
       <c r="CL101" t="n">
-        <v>-69.87384751292869</v>
+        <v>-69.87384750979319</v>
       </c>
       <c r="CM101" t="n">
-        <v>-63.29839830261075</v>
+        <v>-63.29839832807664</v>
       </c>
       <c r="CN101" t="inlineStr">
         <is>
@@ -42622,10 +42622,10 @@
         <v>12.18000030517578</v>
       </c>
       <c r="BX102" t="n">
-        <v>2.166666235469671</v>
+        <v>2.166666232411048</v>
       </c>
       <c r="BY102" t="n">
-        <v>4.019165866796238</v>
+        <v>4.019165861122495</v>
       </c>
       <c r="BZ102" t="n">
         <v>12.84912452576267</v>
@@ -42634,25 +42634,25 @@
         <v>14.24321699181254</v>
       </c>
       <c r="CB102" t="n">
-        <v>9.379078960379072</v>
+        <v>9.379078961444545</v>
       </c>
       <c r="CC102" t="n">
-        <v>5.744344356450679</v>
+        <v>5.744344356697985</v>
       </c>
       <c r="CD102" t="n">
-        <v>6.967979814243</v>
+        <v>6.967979817055708</v>
       </c>
       <c r="CE102" t="n">
         <v>12.18000030517578</v>
       </c>
       <c r="CF102" t="n">
-        <v>9.340415831517138</v>
+        <v>9.34041583129596</v>
       </c>
       <c r="CG102" t="n">
-        <v>9.379078960379072</v>
+        <v>9.379078961444545</v>
       </c>
       <c r="CH102" t="n">
-        <v>8.441171064341166</v>
+        <v>8.441171065300091</v>
       </c>
       <c r="CI102" t="n">
         <v>7</v>
@@ -42664,10 +42664,10 @@
         <v>6.6</v>
       </c>
       <c r="CL102" t="n">
-        <v>-30.69646262033207</v>
+        <v>-30.69646261245912</v>
       </c>
       <c r="CM102" t="n">
-        <v>-23.31350084163781</v>
+        <v>-23.31350084345372</v>
       </c>
       <c r="CN102" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>-2.090026398533917</v>
       </c>
       <c r="CZ102" t="n">
-        <v>-25.25441878355007</v>
+        <v>-25.25442765560502</v>
       </c>
       <c r="DA102" t="b">
         <v>0</v>
@@ -42950,10 +42950,10 @@
         <v>46.34000015258789</v>
       </c>
       <c r="BX103" t="n">
-        <v>10.13865032644999</v>
+        <v>10.13865028202517</v>
       </c>
       <c r="BY103" t="n">
-        <v>18.80719635556474</v>
+        <v>18.8071962731567</v>
       </c>
       <c r="BZ103" t="n">
         <v>85.63528619550759</v>
@@ -42962,13 +42962,13 @@
         <v>75.5695277891077</v>
       </c>
       <c r="CB103" t="n">
-        <v>102.7137955298205</v>
+        <v>102.7137955453257</v>
       </c>
       <c r="CC103" t="n">
-        <v>15.99814152097135</v>
+        <v>15.99814152321454</v>
       </c>
       <c r="CD103" t="n">
-        <v>69.38497637216281</v>
+        <v>69.38497643643309</v>
       </c>
       <c r="CE103" t="n">
         <v>21.49551710110895</v>
@@ -43268,37 +43268,37 @@
         <v>53.65000152587891</v>
       </c>
       <c r="BX104" t="n">
-        <v>16.38838747429374</v>
+        <v>16.38838750787029</v>
       </c>
       <c r="BY104" t="n">
-        <v>25.10603631579315</v>
+        <v>25.10603633543943</v>
       </c>
       <c r="BZ104" t="n">
-        <v>45.79263210481762</v>
+        <v>45.79263204683181</v>
       </c>
       <c r="CA104" t="n">
         <v>63.31865958566679</v>
       </c>
       <c r="CB104" t="n">
-        <v>36.53709861108386</v>
+        <v>36.53709860140184</v>
       </c>
       <c r="CC104" t="n">
-        <v>26.77810746320801</v>
+        <v>26.7781074603687</v>
       </c>
       <c r="CD104" t="n">
-        <v>22.89631177369578</v>
+        <v>22.89631174456208</v>
       </c>
       <c r="CE104" t="n">
         <v>21.28296611184845</v>
       </c>
       <c r="CF104" t="n">
-        <v>32.26252493005092</v>
+        <v>32.26252492424867</v>
       </c>
       <c r="CG104" t="n">
-        <v>25.94207188950058</v>
+        <v>25.94207189790406</v>
       </c>
       <c r="CH104" t="n">
-        <v>23.34786470055052</v>
+        <v>23.34786470811366</v>
       </c>
       <c r="CI104" t="n">
         <v>8</v>
@@ -43310,10 +43310,10 @@
         <v>3.9</v>
       </c>
       <c r="CL104" t="n">
-        <v>-56.48114811462155</v>
+        <v>-56.48114810052437</v>
       </c>
       <c r="CM104" t="n">
-        <v>-39.86482010724902</v>
+        <v>-39.86482011806402</v>
       </c>
       <c r="CN104" t="inlineStr">
         <is>
@@ -43608,10 +43608,10 @@
         <v>3.009999990463257</v>
       </c>
       <c r="BX105" t="n">
-        <v>0.6298002101346222</v>
+        <v>0.6298002122623935</v>
       </c>
       <c r="BY105" t="n">
-        <v>1.168279389799724</v>
+        <v>1.16827939374674</v>
       </c>
       <c r="BZ105" t="n">
         <v>3.655591189151068</v>
@@ -43620,13 +43620,13 @@
         <v>4.238661238286214</v>
       </c>
       <c r="CB105" t="n">
-        <v>2.604672399874839</v>
+        <v>2.604672399754464</v>
       </c>
       <c r="CC105" t="n">
-        <v>2.640588270642566</v>
+        <v>2.640588270386397</v>
       </c>
       <c r="CD105" t="n">
-        <v>1.86625639336077</v>
+        <v>1.866256391568846</v>
       </c>
       <c r="CE105" t="n">
         <v>9.198296956105558</v>
@@ -43922,25 +43922,25 @@
         <v>14.64000034332275</v>
       </c>
       <c r="BX106" t="n">
-        <v>3.69513882932004</v>
+        <v>3.695138816303984</v>
       </c>
       <c r="BY106" t="n">
-        <v>4.706896839291422</v>
+        <v>4.706896824861083</v>
       </c>
       <c r="BZ106" t="n">
-        <v>14.38487143497322</v>
+        <v>14.38487144154272</v>
       </c>
       <c r="CA106" t="n">
         <v>37.51681749325965</v>
       </c>
       <c r="CB106" t="n">
-        <v>9.873209691295827</v>
+        <v>9.873209678960782</v>
       </c>
       <c r="CC106" t="n">
-        <v>48.41659564291383</v>
+        <v>48.41659564510339</v>
       </c>
       <c r="CD106" t="n">
-        <v>6.917949864180472</v>
+        <v>6.917949868796486</v>
       </c>
       <c r="CE106" t="n">
         <v>21.52179483859446</v>
@@ -44536,10 +44536,10 @@
         <v>58.11999893188477</v>
       </c>
       <c r="BX108" t="n">
-        <v>65.75643252560363</v>
+        <v>65.75643233938598</v>
       </c>
       <c r="BY108" t="n">
-        <v>95.74136575727888</v>
+        <v>95.74136548614599</v>
       </c>
       <c r="BZ108" t="n">
         <v>24.17791955566406</v>
@@ -44846,10 +44846,10 @@
         <v>6.420000076293945</v>
       </c>
       <c r="BX109" t="n">
-        <v>0.0613760399881119</v>
+        <v>0.06137604026835535</v>
       </c>
       <c r="BY109" t="n">
-        <v>0.1138525541779476</v>
+        <v>0.1138525546977992</v>
       </c>
       <c r="BZ109" t="inlineStr"/>
       <c r="CA109" t="inlineStr"/>
@@ -45454,10 +45454,10 @@
         <v>96.33999633789062</v>
       </c>
       <c r="BX111" t="n">
-        <v>4.919793622499637</v>
+        <v>4.919793614619158</v>
       </c>
       <c r="BY111" t="n">
-        <v>9.126217169736826</v>
+        <v>9.126217155118537</v>
       </c>
       <c r="BZ111" t="n">
         <v>40.88741036121239</v>
@@ -45466,13 +45466,13 @@
         <v>40.58994084391919</v>
       </c>
       <c r="CB111" t="n">
-        <v>33.39208158819415</v>
+        <v>33.39208159901381</v>
       </c>
       <c r="CC111" t="n">
-        <v>17.63215568083535</v>
+        <v>17.63215568158022</v>
       </c>
       <c r="CD111" t="n">
-        <v>27.84617053161724</v>
+        <v>27.84617054063945</v>
       </c>
       <c r="CE111" t="n">
         <v>40.97990082873793</v>
@@ -45768,10 +45768,10 @@
         <v>17.45000076293945</v>
       </c>
       <c r="BX112" t="n">
-        <v>3.276083597558068</v>
+        <v>3.276083604449043</v>
       </c>
       <c r="BY112" t="n">
-        <v>6.077135073470215</v>
+        <v>6.077135086252974</v>
       </c>
       <c r="BZ112" t="n">
         <v>14.63370317145239</v>
@@ -45780,23 +45780,23 @@
         <v>15.60803264394471</v>
       </c>
       <c r="CB112" t="n">
-        <v>10.20015846936116</v>
+        <v>10.20015846456556</v>
       </c>
       <c r="CC112" t="n">
-        <v>13.00594068610181</v>
+        <v>13.0059406848976</v>
       </c>
       <c r="CD112" t="n">
-        <v>7.537281025744835</v>
+        <v>7.537281018892449</v>
       </c>
       <c r="CE112" t="inlineStr"/>
       <c r="CF112" t="n">
-        <v>11.17704184501252</v>
+        <v>11.17704184500095</v>
       </c>
       <c r="CG112" t="n">
-        <v>11.60304957773149</v>
+        <v>11.60304957473158</v>
       </c>
       <c r="CH112" t="n">
-        <v>10.44274461995834</v>
+        <v>10.44274461725842</v>
       </c>
       <c r="CI112" t="n">
         <v>6</v>
@@ -45808,10 +45808,10 @@
         <v>4.8</v>
       </c>
       <c r="CL112" t="n">
-        <v>-40.15619390609552</v>
+        <v>-40.15619392156782</v>
       </c>
       <c r="CM112" t="n">
-        <v>-35.94818706970791</v>
+        <v>-35.94818706977423</v>
       </c>
       <c r="CN112" t="inlineStr">
         <is>
@@ -46090,10 +46090,10 @@
         <v>14.52999973297119</v>
       </c>
       <c r="BX113" t="n">
-        <v>1.359804410024615</v>
+        <v>1.359804413051002</v>
       </c>
       <c r="BY113" t="n">
-        <v>2.522437180595661</v>
+        <v>2.522437186209608</v>
       </c>
       <c r="BZ113" t="n">
         <v>8.9254750330027</v>
@@ -46102,13 +46102,13 @@
         <v>10.96999041107547</v>
       </c>
       <c r="CB113" t="n">
-        <v>4.980524742014525</v>
+        <v>4.980524740385874</v>
       </c>
       <c r="CC113" t="n">
-        <v>7.696681032002975</v>
+        <v>7.696681031615996</v>
       </c>
       <c r="CD113" t="n">
-        <v>4.375380393166168</v>
+        <v>4.375380390907757</v>
       </c>
       <c r="CE113" t="n">
         <v>11.24969464648006</v>
@@ -46408,10 +46408,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX114" t="n">
-        <v>11.98290320900679</v>
+        <v>11.98290318703899</v>
       </c>
       <c r="BY114" t="n">
-        <v>14.95257922167369</v>
+        <v>14.9525791942617</v>
       </c>
       <c r="BZ114" t="inlineStr"/>
       <c r="CA114" t="inlineStr"/>
@@ -46714,10 +46714,10 @@
         <v>11.18000030517578</v>
       </c>
       <c r="BX115" t="n">
-        <v>2.429612152842727</v>
+        <v>2.429612152241572</v>
       </c>
       <c r="BY115" t="n">
-        <v>4.506930543523258</v>
+        <v>4.506930542408115</v>
       </c>
       <c r="BZ115" t="n">
         <v>12.21228392774766</v>
@@ -46726,13 +46726,13 @@
         <v>12.73311481937156</v>
       </c>
       <c r="CB115" t="n">
-        <v>9.672110407786137</v>
+        <v>9.672110408086258</v>
       </c>
       <c r="CC115" t="n">
-        <v>0.7924908650655506</v>
+        <v>0.7924908650735042</v>
       </c>
       <c r="CD115" t="n">
-        <v>6.779198843199116</v>
+        <v>6.779198843823884</v>
       </c>
       <c r="CE115" t="n">
         <v>7.307661395663775</v>
@@ -47028,10 +47028,10 @@
         <v>3.430000066757202</v>
       </c>
       <c r="BX116" t="n">
-        <v>1.689358882511283</v>
+        <v>1.689358881558354</v>
       </c>
       <c r="BY116" t="n">
-        <v>3.13376072705843</v>
+        <v>3.133760725290748</v>
       </c>
       <c r="BZ116" t="n">
         <v>1.168015956939936</v>
@@ -47040,7 +47040,7 @@
         <v>4.684615221800192</v>
       </c>
       <c r="CB116" t="n">
-        <v>1.621588926313693</v>
+        <v>1.621588925970825</v>
       </c>
       <c r="CC116" t="n">
         <v>0.7445919647652398</v>
@@ -47342,10 +47342,10 @@
         <v>4.809999942779541</v>
       </c>
       <c r="BX117" t="n">
-        <v>1.47941850270575</v>
+        <v>1.479418497515615</v>
       </c>
       <c r="BY117" t="n">
-        <v>1.541882839486659</v>
+        <v>1.541882834077386</v>
       </c>
       <c r="BZ117" t="inlineStr"/>
       <c r="CA117" t="inlineStr"/>
@@ -47646,25 +47646,25 @@
         <v>8.739999771118164</v>
       </c>
       <c r="BX118" t="n">
-        <v>2.24763468242547</v>
+        <v>2.247634684342729</v>
       </c>
       <c r="BY118" t="n">
-        <v>2.42101175664966</v>
+        <v>2.421011758180439</v>
       </c>
       <c r="BZ118" t="n">
-        <v>3.136387960401557</v>
+        <v>3.136387959709285</v>
       </c>
       <c r="CA118" t="n">
         <v>9.827685355919407</v>
       </c>
       <c r="CB118" t="n">
-        <v>1.829365608276007</v>
+        <v>1.829365608483809</v>
       </c>
       <c r="CC118" t="n">
-        <v>5.905845202217133</v>
+        <v>5.905845202067193</v>
       </c>
       <c r="CD118" t="n">
-        <v>1.316356165410622</v>
+        <v>1.316356164754305</v>
       </c>
       <c r="CE118" t="n">
         <v>12.81521599596358</v>
@@ -47960,10 +47960,10 @@
         <v>6.559999942779541</v>
       </c>
       <c r="BX119" t="n">
-        <v>1.053466681675942</v>
+        <v>1.053466679878761</v>
       </c>
       <c r="BY119" t="n">
-        <v>1.954180694508872</v>
+        <v>1.954180691175101</v>
       </c>
       <c r="BZ119" t="inlineStr"/>
       <c r="CA119" t="inlineStr"/>
@@ -48264,25 +48264,25 @@
         <v>3.700000047683716</v>
       </c>
       <c r="BX120" t="n">
-        <v>1.267030924928017</v>
+        <v>1.267030928589983</v>
       </c>
       <c r="BY120" t="n">
-        <v>1.302892958092053</v>
+        <v>1.30289296055145</v>
       </c>
       <c r="BZ120" t="n">
-        <v>1.408844264028967</v>
+        <v>1.408844262616528</v>
       </c>
       <c r="CA120" t="n">
         <v>4.28417545380731</v>
       </c>
       <c r="CB120" t="n">
-        <v>0.9846225508301961</v>
+        <v>0.9846225511757564</v>
       </c>
       <c r="CC120" t="n">
-        <v>2.173299921083388</v>
+        <v>2.173299920822292</v>
       </c>
       <c r="CD120" t="n">
-        <v>0.5532971898125109</v>
+        <v>0.5532971883591499</v>
       </c>
       <c r="CE120" t="n">
         <v>5.184427633155422</v>
@@ -48582,10 +48582,10 @@
         <v>5.510000228881836</v>
       </c>
       <c r="BX121" t="n">
-        <v>5.460017777761098</v>
+        <v>5.460017772915138</v>
       </c>
       <c r="BY121" t="n">
-        <v>7.94978588442016</v>
+        <v>7.949785877364442</v>
       </c>
       <c r="BZ121" t="inlineStr"/>
       <c r="CA121" t="inlineStr"/>
@@ -48594,13 +48594,13 @@
       <c r="CD121" t="inlineStr"/>
       <c r="CE121" t="inlineStr"/>
       <c r="CF121" t="n">
-        <v>6.704901831090629</v>
+        <v>6.70490182513979</v>
       </c>
       <c r="CG121" t="n">
-        <v>6.704901831090629</v>
+        <v>6.70490182513979</v>
       </c>
       <c r="CH121" t="n">
-        <v>6.034411647981566</v>
+        <v>6.034411642625811</v>
       </c>
       <c r="CI121" t="n">
         <v>2</v>
@@ -48612,10 +48612,10 @@
         <v>1.5</v>
       </c>
       <c r="CL121" t="n">
-        <v>9.517448227150993</v>
+        <v>9.517448129950367</v>
       </c>
       <c r="CM121" t="n">
-        <v>21.68605358572333</v>
+        <v>21.68605347772263</v>
       </c>
       <c r="CN121" t="inlineStr">
         <is>
@@ -48894,10 +48894,10 @@
         <v>5.079999923706055</v>
       </c>
       <c r="BX122" t="n">
-        <v>5.591984093976706</v>
+        <v>5.591984110918216</v>
       </c>
       <c r="BY122" t="n">
-        <v>9.969901279839434</v>
+        <v>9.969901310044307</v>
       </c>
       <c r="BZ122" t="inlineStr"/>
       <c r="CA122" t="inlineStr"/>
@@ -48906,13 +48906,13 @@
       <c r="CD122" t="inlineStr"/>
       <c r="CE122" t="inlineStr"/>
       <c r="CF122" t="n">
-        <v>7.78094268690807</v>
+        <v>7.780942710481261</v>
       </c>
       <c r="CG122" t="n">
-        <v>7.78094268690807</v>
+        <v>7.780942710481261</v>
       </c>
       <c r="CH122" t="n">
-        <v>7.002848418217263</v>
+        <v>7.002848439433135</v>
       </c>
       <c r="CI122" t="n">
         <v>2</v>
@@ -48924,10 +48924,10 @@
         <v>1.8</v>
       </c>
       <c r="CL122" t="n">
-        <v>37.85134888561998</v>
+        <v>37.85134930325529</v>
       </c>
       <c r="CM122" t="n">
-        <v>53.16816542846665</v>
+        <v>53.16816589250586</v>
       </c>
       <c r="CN122" t="inlineStr">
         <is>
@@ -49192,10 +49192,10 @@
         <v>21.88999938964844</v>
       </c>
       <c r="BX123" t="n">
-        <v>37.94222278195326</v>
+        <v>37.94222254853295</v>
       </c>
       <c r="BY123" t="n">
-        <v>70.38282326052328</v>
+        <v>70.38282282752863</v>
       </c>
       <c r="BZ123" t="n">
         <v>20.07214476905479</v>
@@ -49214,7 +49214,7 @@
       </c>
       <c r="CE123" t="inlineStr"/>
       <c r="CF123" t="n">
-        <v>26.06992677873426</v>
+        <v>26.06992673983088</v>
       </c>
       <c r="CG123" t="n">
         <v>23.36448533113464</v>
@@ -49235,7 +49235,7 @@
         <v>-3.937700391325161</v>
       </c>
       <c r="CM123" t="n">
-        <v>19.0951462112076</v>
+        <v>19.09514603348546</v>
       </c>
       <c r="CN123" t="inlineStr">
         <is>
@@ -49514,25 +49514,25 @@
         <v>9.210000038146973</v>
       </c>
       <c r="BX124" t="n">
-        <v>3.562432709206973</v>
+        <v>3.562432704321006</v>
       </c>
       <c r="BY124" t="n">
-        <v>3.67092490614029</v>
+        <v>3.670924901888007</v>
       </c>
       <c r="BZ124" t="n">
-        <v>4.387649661101686</v>
+        <v>4.387649662036944</v>
       </c>
       <c r="CA124" t="n">
         <v>19.06106624245507</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.445242683846772</v>
+        <v>3.445242680944758</v>
       </c>
       <c r="CC124" t="n">
-        <v>7.613744425285681</v>
+        <v>7.613744425479803</v>
       </c>
       <c r="CD124" t="n">
-        <v>1.728975898974595</v>
+        <v>1.728975899933417</v>
       </c>
       <c r="CE124" t="n">
         <v>20.19385877757074</v>
@@ -49828,10 +49828,10 @@
         <v>11.46000003814697</v>
       </c>
       <c r="BX125" t="n">
-        <v>0.7792719065467144</v>
+        <v>0.7792719061356694</v>
       </c>
       <c r="BY125" t="n">
-        <v>1.445549386644155</v>
+        <v>1.445549385881667</v>
       </c>
       <c r="BZ125" t="n">
         <v>16.15372345802631</v>
@@ -49840,13 +49840,13 @@
         <v>16.82869587224833</v>
       </c>
       <c r="CB125" t="n">
-        <v>14.21481600330217</v>
+        <v>14.21481600336672</v>
       </c>
       <c r="CC125" t="n">
-        <v>1.741983299182193</v>
+        <v>1.741983299190928</v>
       </c>
       <c r="CD125" t="n">
-        <v>11.46236536727429</v>
+        <v>11.46236536769968</v>
       </c>
       <c r="CE125" t="inlineStr"/>
       <c r="CF125" t="inlineStr"/>
@@ -50434,25 +50434,25 @@
         <v>19</v>
       </c>
       <c r="BX127" t="n">
-        <v>0.5916775938260741</v>
+        <v>0.5916775938526385</v>
       </c>
       <c r="BY127" t="n">
-        <v>0.7950536082095966</v>
+        <v>0.7950536082428489</v>
       </c>
       <c r="BZ127" t="n">
-        <v>4.662824168707756</v>
+        <v>4.662824168693428</v>
       </c>
       <c r="CA127" t="n">
         <v>11.65078630453671</v>
       </c>
       <c r="CB127" t="n">
-        <v>1.78742957707428</v>
+        <v>1.787429577069247</v>
       </c>
       <c r="CC127" t="n">
-        <v>0.6882468011065569</v>
+        <v>0.6882468011063573</v>
       </c>
       <c r="CD127" t="n">
-        <v>2.288200648579334</v>
+        <v>2.288200648570193</v>
       </c>
       <c r="CE127" t="n">
         <v>19</v>
@@ -50752,10 +50752,10 @@
         <v>5.150000095367432</v>
       </c>
       <c r="BX128" t="n">
-        <v>1.268396225248033</v>
+        <v>1.268396230781867</v>
       </c>
       <c r="BY128" t="n">
-        <v>2.122834046074209</v>
+        <v>2.122834055335833</v>
       </c>
       <c r="BZ128" t="inlineStr"/>
       <c r="CA128" t="inlineStr"/>
@@ -50766,13 +50766,13 @@
         <v>5.988941589713868</v>
       </c>
       <c r="CF128" t="n">
-        <v>1.695615135661121</v>
+        <v>1.69561514305885</v>
       </c>
       <c r="CG128" t="n">
-        <v>1.695615135661121</v>
+        <v>1.69561514305885</v>
       </c>
       <c r="CH128" t="n">
-        <v>1.526053622095009</v>
+        <v>1.526053628752965</v>
       </c>
       <c r="CI128" t="n">
         <v>2</v>
@@ -50784,10 +50784,10 @@
         <v>4.7</v>
       </c>
       <c r="CL128" t="n">
-        <v>-70.36789138183246</v>
+        <v>-70.36789125255176</v>
       </c>
       <c r="CM128" t="n">
-        <v>-67.07543486870274</v>
+        <v>-67.07543472505752</v>
       </c>
       <c r="CN128" t="inlineStr">
         <is>
@@ -51070,37 +51070,37 @@
         <v>17.20999908447266</v>
       </c>
       <c r="BX129" t="n">
-        <v>2.072597792683087</v>
+        <v>2.072597801662844</v>
       </c>
       <c r="BY129" t="n">
-        <v>3.775021099287439</v>
+        <v>3.775021108484919</v>
       </c>
       <c r="BZ129" t="n">
-        <v>10.46758217569889</v>
+        <v>10.46758215585021</v>
       </c>
       <c r="CA129" t="n">
         <v>12.60778163571021</v>
       </c>
       <c r="CB129" t="n">
-        <v>6.073750646234867</v>
+        <v>6.07375064058401</v>
       </c>
       <c r="CC129" t="n">
-        <v>5.548158130330276</v>
+        <v>5.548158129579353</v>
       </c>
       <c r="CD129" t="n">
-        <v>5.114486573641898</v>
+        <v>5.114486566395594</v>
       </c>
       <c r="CE129" t="n">
         <v>15.99015396619785</v>
       </c>
       <c r="CF129" t="n">
-        <v>7.264463376817262</v>
+        <v>7.264463372767382</v>
       </c>
       <c r="CG129" t="n">
-        <v>5.810954388282571</v>
+        <v>5.810954385081681</v>
       </c>
       <c r="CH129" t="n">
-        <v>5.229858949454314</v>
+        <v>5.229858946573513</v>
       </c>
       <c r="CI129" t="n">
         <v>6</v>
@@ -51112,10 +51112,10 @@
         <v>7.7</v>
       </c>
       <c r="CL129" t="n">
-        <v>-69.61150942667487</v>
+        <v>-69.61150944341399</v>
       </c>
       <c r="CM129" t="n">
-        <v>-57.7892866747944</v>
+        <v>-57.78928669832653</v>
       </c>
       <c r="CN129" t="inlineStr">
         <is>
@@ -51688,10 +51688,10 @@
         <v>4.110000133514404</v>
       </c>
       <c r="BX131" t="n">
-        <v>2.868183345405823</v>
+        <v>2.868183362782094</v>
       </c>
       <c r="BY131" t="n">
-        <v>5.320480105727802</v>
+        <v>5.320480137960785</v>
       </c>
       <c r="BZ131" t="inlineStr"/>
       <c r="CA131" t="inlineStr"/>
@@ -51700,13 +51700,13 @@
       <c r="CD131" t="inlineStr"/>
       <c r="CE131" t="inlineStr"/>
       <c r="CF131" t="n">
-        <v>4.094331725566812</v>
+        <v>4.09433175037144</v>
       </c>
       <c r="CG131" t="n">
-        <v>4.094331725566812</v>
+        <v>4.09433175037144</v>
       </c>
       <c r="CH131" t="n">
-        <v>3.684898553010131</v>
+        <v>3.684898575334296</v>
       </c>
       <c r="CI131" t="n">
         <v>2</v>
@@ -51718,10 +51718,10 @@
         <v>1.9</v>
       </c>
       <c r="CL131" t="n">
-        <v>-10.34310381252408</v>
+        <v>-10.34310326935707</v>
       </c>
       <c r="CM131" t="n">
-        <v>-0.3812264583600955</v>
+        <v>-0.3812258548411829</v>
       </c>
       <c r="CN131" t="inlineStr">
         <is>
@@ -51992,10 +51992,10 @@
         <v>4.21999979019165</v>
       </c>
       <c r="BX132" t="n">
-        <v>0.8881979183719727</v>
+        <v>0.8881979179583234</v>
       </c>
       <c r="BY132" t="n">
-        <v>0.9831240708979773</v>
+        <v>0.9831240704401192</v>
       </c>
       <c r="BZ132" t="inlineStr"/>
       <c r="CA132" t="inlineStr"/>
@@ -52004,13 +52004,13 @@
       <c r="CD132" t="inlineStr"/>
       <c r="CE132" t="inlineStr"/>
       <c r="CF132" t="n">
-        <v>0.935660994634975</v>
+        <v>0.9356609941992213</v>
       </c>
       <c r="CG132" t="n">
-        <v>0.935660994634975</v>
+        <v>0.9356609941992213</v>
       </c>
       <c r="CH132" t="n">
-        <v>0.8420948951714775</v>
+        <v>0.8420948947792992</v>
       </c>
       <c r="CI132" t="n">
         <v>2</v>
@@ -52022,10 +52022,10 @@
         <v>1.1</v>
       </c>
       <c r="CL132" t="n">
-        <v>-80.04514367207507</v>
+        <v>-80.04514368136839</v>
       </c>
       <c r="CM132" t="n">
-        <v>-77.82793741341673</v>
+        <v>-77.82793742374265</v>
       </c>
       <c r="CN132" t="inlineStr">
         <is>
@@ -52306,10 +52306,10 @@
         <v>1.220000028610229</v>
       </c>
       <c r="BX133" t="n">
-        <v>0.3579768030146158</v>
+        <v>0.3579768036191621</v>
       </c>
       <c r="BY133" t="n">
-        <v>0.6640469695921123</v>
+        <v>0.6640469707135457</v>
       </c>
       <c r="BZ133" t="inlineStr"/>
       <c r="CA133" t="inlineStr"/>
@@ -52318,13 +52318,13 @@
       <c r="CD133" t="inlineStr"/>
       <c r="CE133" t="inlineStr"/>
       <c r="CF133" t="n">
-        <v>0.511011886303364</v>
+        <v>0.5110118871663539</v>
       </c>
       <c r="CG133" t="n">
-        <v>0.511011886303364</v>
+        <v>0.5110118871663539</v>
       </c>
       <c r="CH133" t="n">
-        <v>0.4599106976730276</v>
+        <v>0.4599106984497185</v>
       </c>
       <c r="CI133" t="n">
         <v>2</v>
@@ -52336,10 +52336,10 @@
         <v>1.9</v>
       </c>
       <c r="CL133" t="n">
-        <v>-62.30240271412634</v>
+        <v>-62.30240265046316</v>
       </c>
       <c r="CM133" t="n">
-        <v>-58.11378079347372</v>
+        <v>-58.11378072273685</v>
       </c>
       <c r="CN133" t="inlineStr">
         <is>
@@ -52926,10 +52926,10 @@
         <v>5.460000038146973</v>
       </c>
       <c r="BX135" t="n">
-        <v>1.040556585576844</v>
+        <v>1.04055658505233</v>
       </c>
       <c r="BY135" t="n">
-        <v>1.930232466245046</v>
+        <v>1.930232465272072</v>
       </c>
       <c r="BZ135" t="inlineStr"/>
       <c r="CA135" t="inlineStr"/>
@@ -52940,13 +52940,13 @@
         <v>2.857508361672422</v>
       </c>
       <c r="CF135" t="n">
-        <v>1.942765804498104</v>
+        <v>1.942765803998941</v>
       </c>
       <c r="CG135" t="n">
-        <v>1.930232466245046</v>
+        <v>1.930232465272072</v>
       </c>
       <c r="CH135" t="n">
-        <v>1.737209219620541</v>
+        <v>1.737209218744865</v>
       </c>
       <c r="CI135" t="n">
         <v>3</v>
@@ -52958,10 +52958,10 @@
         <v>2.7</v>
       </c>
       <c r="CL135" t="n">
-        <v>-68.18298154792468</v>
+        <v>-68.18298156396271</v>
       </c>
       <c r="CM135" t="n">
-        <v>-64.41820895742256</v>
+        <v>-64.41820896656473</v>
       </c>
       <c r="CN135" t="inlineStr">
         <is>
@@ -53238,10 +53238,10 @@
         <v>37.15000152587891</v>
       </c>
       <c r="BX136" t="n">
-        <v>8.367448545783304</v>
+        <v>8.367448543929402</v>
       </c>
       <c r="BY136" t="n">
-        <v>12.18300508266049</v>
+        <v>12.18300507996121</v>
       </c>
       <c r="BZ136" t="n">
         <v>8.093004102830763</v>
@@ -53550,25 +53550,25 @@
         <v>4.840000152587891</v>
       </c>
       <c r="BX137" t="n">
-        <v>1.502502732634856</v>
+        <v>1.502502730193916</v>
       </c>
       <c r="BY137" t="n">
-        <v>1.672911394183507</v>
+        <v>1.672911392047966</v>
       </c>
       <c r="BZ137" t="n">
-        <v>2.547478597131607</v>
+        <v>2.547478598018235</v>
       </c>
       <c r="CA137" t="n">
         <v>7.892423639597566</v>
       </c>
       <c r="CB137" t="n">
-        <v>1.797906282228001</v>
+        <v>1.797906281227365</v>
       </c>
       <c r="CC137" t="n">
-        <v>1.843026215514787</v>
+        <v>1.843026215586434</v>
       </c>
       <c r="CD137" t="n">
-        <v>1.110767096442591</v>
+        <v>1.110767097235213</v>
       </c>
       <c r="CE137" t="n">
         <v>0.03519118999648198</v>
@@ -53862,10 +53862,10 @@
         <v>1.990000009536743</v>
       </c>
       <c r="BX138" t="n">
-        <v>0.5586583805852912</v>
+        <v>0.5586583815869235</v>
       </c>
       <c r="BY138" t="n">
-        <v>0.8134066021321841</v>
+        <v>0.8134066035905607</v>
       </c>
       <c r="BZ138" t="n">
         <v>0.3613128508935427</v>
@@ -53928,7 +53928,7 @@
         <v>-0.9950239314132636</v>
       </c>
       <c r="CZ138" t="n">
-        <v>-53.22525700906506</v>
+        <v>-53.22526227613638</v>
       </c>
       <c r="DA138" t="b">
         <v>0</v>
@@ -54170,10 +54170,10 @@
         <v>6.889999866485596</v>
       </c>
       <c r="BX139" t="n">
-        <v>1.890787841641169</v>
+        <v>1.890787837944808</v>
       </c>
       <c r="BY139" t="n">
-        <v>2.752987097429541</v>
+        <v>2.75298709204764</v>
       </c>
       <c r="BZ139" t="n">
         <v>1.758861036118071</v>
@@ -54183,7 +54183,7 @@
       </c>
       <c r="CB139" t="inlineStr"/>
       <c r="CC139" t="n">
-        <v>1.015942276303052</v>
+        <v>1.052225929028161</v>
       </c>
       <c r="CD139" t="n">
         <v>0.4517953485632956</v>
@@ -55342,25 +55342,25 @@
         <v>4.539999961853027</v>
       </c>
       <c r="BX143" t="n">
-        <v>0.7601321063839337</v>
+        <v>0.7601321081395994</v>
       </c>
       <c r="BY143" t="n">
-        <v>0.7672875997377082</v>
+        <v>0.7672876014117518</v>
       </c>
       <c r="BZ143" t="n">
-        <v>0.897555170667815</v>
+        <v>0.8975551705530024</v>
       </c>
       <c r="CA143" t="n">
         <v>6.621863553251451</v>
       </c>
       <c r="CB143" t="n">
-        <v>0.3060705861614106</v>
+        <v>0.306070586641194</v>
       </c>
       <c r="CC143" t="n">
-        <v>0.4177451123125095</v>
+        <v>0.4177451123060008</v>
       </c>
       <c r="CD143" t="n">
-        <v>0.3415268767031632</v>
+        <v>0.3415268765811094</v>
       </c>
       <c r="CE143" t="inlineStr"/>
       <c r="CF143" t="inlineStr"/>
@@ -55656,10 +55656,10 @@
         <v>18.30999946594238</v>
       </c>
       <c r="BX144" t="n">
-        <v>27.85107494017667</v>
+        <v>27.8510749884693</v>
       </c>
       <c r="BY144" t="n">
-        <v>37.2585491421919</v>
+        <v>37.25854920679671</v>
       </c>
       <c r="BZ144" t="n">
         <v>2.504827732555547</v>
@@ -55668,7 +55668,7 @@
         <v>6.943403056792157</v>
       </c>
       <c r="CB144" t="n">
-        <v>6.421002826821604</v>
+        <v>6.421002836500871</v>
       </c>
       <c r="CC144" t="n">
         <v>3.046690502845772</v>
@@ -55970,10 +55970,10 @@
         <v>3.75</v>
       </c>
       <c r="BX145" t="n">
-        <v>0.6782855607317353</v>
+        <v>0.6782855629857154</v>
       </c>
       <c r="BY145" t="n">
-        <v>1.258219715157369</v>
+        <v>1.258219719338502</v>
       </c>
       <c r="BZ145" t="inlineStr"/>
       <c r="CA145" t="inlineStr"/>
@@ -55984,13 +55984,13 @@
         <v>3.40392002364466</v>
       </c>
       <c r="CF145" t="n">
-        <v>0.9682526379445521</v>
+        <v>0.9682526411621087</v>
       </c>
       <c r="CG145" t="n">
-        <v>0.9682526379445521</v>
+        <v>0.9682526411621087</v>
       </c>
       <c r="CH145" t="n">
-        <v>0.8714273741500969</v>
+        <v>0.8714273770458979</v>
       </c>
       <c r="CI145" t="n">
         <v>2</v>
@@ -56002,10 +56002,10 @@
         <v>5</v>
       </c>
       <c r="CL145" t="n">
-        <v>-76.76193668933075</v>
+        <v>-76.76193661210939</v>
       </c>
       <c r="CM145" t="n">
-        <v>-74.17992965481194</v>
+        <v>-74.17992956901043</v>
       </c>
       <c r="CN145" t="inlineStr">
         <is>
@@ -56282,10 +56282,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX146" t="n">
-        <v>9.49803044110058</v>
+        <v>9.498030414271254</v>
       </c>
       <c r="BY146" t="n">
-        <v>13.82913232224245</v>
+        <v>13.82913228317895</v>
       </c>
       <c r="BZ146" t="n">
         <v>4.692896643862964</v>
@@ -57218,10 +57218,10 @@
         <v>10.71000003814697</v>
       </c>
       <c r="BX149" t="n">
-        <v>5.722370910474035</v>
+        <v>5.722370889056207</v>
       </c>
       <c r="BY149" t="n">
-        <v>10.47405816280099</v>
+        <v>10.47405812359843</v>
       </c>
       <c r="BZ149" t="inlineStr"/>
       <c r="CA149" t="inlineStr"/>
@@ -57232,13 +57232,13 @@
         <v>2.986819537882496</v>
       </c>
       <c r="CF149" t="n">
-        <v>6.394416203719175</v>
+        <v>6.394416183512379</v>
       </c>
       <c r="CG149" t="n">
-        <v>5.722370910474035</v>
+        <v>5.722370889056207</v>
       </c>
       <c r="CH149" t="n">
-        <v>5.150133819426631</v>
+        <v>5.150133800150586</v>
       </c>
       <c r="CI149" t="n">
         <v>3</v>
@@ -57250,10 +57250,10 @@
         <v>3.5</v>
       </c>
       <c r="CL149" t="n">
-        <v>-51.91284966309208</v>
+        <v>-51.91284984307381</v>
       </c>
       <c r="CM149" t="n">
-        <v>-40.29490027130264</v>
+        <v>-40.29490045997487</v>
       </c>
       <c r="CN149" t="inlineStr">
         <is>
@@ -57850,10 +57850,10 @@
         <v>15.35000038146973</v>
       </c>
       <c r="BX151" t="n">
-        <v>3.926670161373388</v>
+        <v>3.926670156039753</v>
       </c>
       <c r="BY151" t="n">
-        <v>5.717231754959653</v>
+        <v>5.717231747193881</v>
       </c>
       <c r="BZ151" t="inlineStr"/>
       <c r="CA151" t="inlineStr"/>
@@ -57864,7 +57864,7 @@
         <v>5.079183152512682</v>
       </c>
       <c r="CF151" t="n">
-        <v>4.907695022948574</v>
+        <v>4.907695018582105</v>
       </c>
       <c r="CG151" t="n">
         <v>5.079183152512682</v>
@@ -57885,7 +57885,7 @@
         <v>-70.21977378723865</v>
       </c>
       <c r="CM151" t="n">
-        <v>-68.02804624765309</v>
+        <v>-68.02804627609915</v>
       </c>
       <c r="CN151" t="inlineStr">
         <is>

--- a/reports/screener_2026-08-25.xlsx
+++ b/reports/screener_2026-08-25.xlsx
@@ -1186,10 +1186,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.86871605417369</v>
+        <v>5.868716018802491</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.88646828049219</v>
+        <v>10.88646821487862</v>
       </c>
       <c r="BZ2" t="n">
         <v>42.10015429633837</v>
@@ -1198,7 +1198,7 @@
         <v>28.26125673506212</v>
       </c>
       <c r="CB2" t="n">
-        <v>72.78655348876849</v>
+        <v>72.78655333733215</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -1260,7 +1260,7 @@
         <v>-4.94053016263244</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-26.59161854099229</v>
+        <v>-26.59161348668701</v>
       </c>
       <c r="DA2" t="b">
         <v>1</v>
@@ -1504,10 +1504,10 @@
         <v>13.60999965667725</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.01575557945281</v>
+        <v>15.0157554397903</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.85422659988496</v>
+        <v>27.85422634081101</v>
       </c>
       <c r="BZ3" t="n">
         <v>38.94870312116058</v>
@@ -1516,13 +1516,13 @@
         <v>23.57226802449605</v>
       </c>
       <c r="CB3" t="n">
-        <v>74.76041608604787</v>
+        <v>74.76041634926167</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.40383469172596</v>
+        <v>48.40383479435776</v>
       </c>
       <c r="CD3" t="n">
-        <v>26.30532694818076</v>
+        <v>26.30532737907871</v>
       </c>
       <c r="CE3" t="n">
         <v>8.655042371031668</v>
@@ -1822,10 +1822,10 @@
         <v>24.54000091552734</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.25388474454687</v>
+        <v>16.25388475294957</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.15095620113445</v>
+        <v>30.15095621672145</v>
       </c>
       <c r="BZ4" t="n">
         <v>74.06720094094243</v>
@@ -1834,13 +1834,13 @@
         <v>53.70833445174577</v>
       </c>
       <c r="CB4" t="n">
-        <v>132.6406024906445</v>
+        <v>132.6406024887612</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.7945176718956</v>
+        <v>25.79451767073932</v>
       </c>
       <c r="CD4" t="n">
-        <v>65.72549933503295</v>
+        <v>65.72549931700549</v>
       </c>
       <c r="CE4" t="n">
         <v>43.53105147803891</v>
@@ -2138,10 +2138,10 @@
         <v>4.190000057220459</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.548072963759028</v>
+        <v>3.548072995676882</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.581675347772996</v>
+        <v>6.581675406980615</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.82159370858454</v>
@@ -2150,25 +2150,25 @@
         <v>8.61209444827186</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.80877193294405</v>
+        <v>24.80877190959474</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.29418312694294</v>
+        <v>11.29418311396195</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.9682754658171</v>
+        <v>10.9682753862727</v>
       </c>
       <c r="CE5" t="n">
         <v>5.153758142621466</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.238596706668487</v>
+        <v>9.238596701115524</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.790184957044481</v>
+        <v>9.790184917272281</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.811166461340033</v>
+        <v>8.811166425545053</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -2180,10 +2180,10 @@
         <v>7</v>
       </c>
       <c r="CL5" t="n">
-        <v>110.2903661339122</v>
+        <v>110.2903652796167</v>
       </c>
       <c r="CM5" t="n">
-        <v>120.491565167117</v>
+        <v>120.491565034588</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>48.2400016784668</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.38294926403854</v>
+        <v>18.38294924500586</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.10037088479149</v>
+        <v>34.10037084948588</v>
       </c>
       <c r="BZ6" t="n">
         <v>76.54850565744731</v>
@@ -2460,23 +2460,23 @@
         <v>57.29789298233228</v>
       </c>
       <c r="CB6" t="n">
-        <v>103.9926847905225</v>
+        <v>103.9926848194703</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.49285960086324</v>
+        <v>48.49285960539734</v>
       </c>
       <c r="CD6" t="n">
-        <v>61.42668256503595</v>
+        <v>61.4266826032901</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>44.38117135178514</v>
+        <v>44.3811713393341</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.29661524282736</v>
+        <v>41.29661522744161</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.16695371854463</v>
+        <v>37.16695370469745</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -2488,10 +2488,10 @@
         <v>4.2</v>
       </c>
       <c r="CL6" t="n">
-        <v>-22.95407872024374</v>
+        <v>-22.9540787489485</v>
       </c>
       <c r="CM6" t="n">
-        <v>-7.999233400533123</v>
+        <v>-7.999233426343744</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -2774,10 +2774,10 @@
         <v>4.510000228881836</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.052774388407022</v>
+        <v>3.052774365013348</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.662896490495025</v>
+        <v>5.662896447099761</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.93452446594899</v>
@@ -2786,7 +2786,7 @@
         <v>8.695832933160331</v>
       </c>
       <c r="CB7" t="n">
-        <v>23.89368936600127</v>
+        <v>23.89368929511135</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -2798,7 +2798,7 @@
         <v>5.186344183602181</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.39433293753478</v>
+        <v>11.39433292120833</v>
       </c>
       <c r="CG7" t="n">
         <v>11.57513776217851</v>
@@ -2819,7 +2819,7 @@
         <v>130.9894336423016</v>
       </c>
       <c r="CM7" t="n">
-        <v>152.6459503164988</v>
+        <v>152.6459499544931</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>-6.237000363129841</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-43.27722523663176</v>
+        <v>-43.27722875916081</v>
       </c>
       <c r="DA7" t="b">
         <v>1</v>
@@ -3102,10 +3102,10 @@
         <v>32.58000183105469</v>
       </c>
       <c r="BX8" t="n">
-        <v>24.20136285624547</v>
+        <v>24.20136286831822</v>
       </c>
       <c r="BY8" t="n">
-        <v>44.89352809833534</v>
+        <v>44.89352812073029</v>
       </c>
       <c r="BZ8" t="n">
         <v>50.78647344252641</v>
@@ -3114,25 +3114,25 @@
         <v>22.31995674309305</v>
       </c>
       <c r="CB8" t="n">
-        <v>69.38361253173336</v>
+        <v>69.38361243942339</v>
       </c>
       <c r="CC8" t="n">
-        <v>53.12760891626809</v>
+        <v>53.12760890182916</v>
       </c>
       <c r="CD8" t="n">
-        <v>28.79645699130806</v>
+        <v>28.79645692078581</v>
       </c>
       <c r="CE8" t="n">
         <v>25.44421854454374</v>
       </c>
       <c r="CF8" t="n">
-        <v>39.86915226550668</v>
+        <v>39.86915224765626</v>
       </c>
       <c r="CG8" t="n">
-        <v>36.8449925448217</v>
+        <v>36.84499252075805</v>
       </c>
       <c r="CH8" t="n">
-        <v>33.16049329033953</v>
+        <v>33.16049326868225</v>
       </c>
       <c r="CI8" t="n">
         <v>8</v>
@@ -3144,10 +3144,10 @@
         <v>3.1</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.781741641068701</v>
+        <v>1.78174157459452</v>
       </c>
       <c r="CM8" t="n">
-        <v>22.37308172126653</v>
+        <v>22.37308166647702</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
         <v>41.34999847412109</v>
       </c>
       <c r="BX9" t="n">
-        <v>121.1494724636367</v>
+        <v>121.1494712699134</v>
       </c>
       <c r="BY9" t="n">
-        <v>224.732271420046</v>
+        <v>224.7322692056893</v>
       </c>
       <c r="BZ9" t="n">
         <v>134.6160883985514</v>
@@ -3464,13 +3464,13 @@
         <v>57.31088302327341</v>
       </c>
       <c r="CF9" t="n">
-        <v>139.1218205336959</v>
+        <v>139.1218201076859</v>
       </c>
       <c r="CG9" t="n">
-        <v>122.0409501798362</v>
+        <v>122.0409495829745</v>
       </c>
       <c r="CH9" t="n">
-        <v>109.8368551618526</v>
+        <v>109.8368546246771</v>
       </c>
       <c r="CI9" t="n">
         <v>8</v>
@@ -3482,10 +3482,10 @@
         <v>5.4</v>
       </c>
       <c r="CL9" t="n">
-        <v>165.6272290568378</v>
+        <v>165.6272277577434</v>
       </c>
       <c r="CM9" t="n">
-        <v>236.4493970193622</v>
+        <v>236.4493959891083</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
         <v>15.75</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.426879104229907</v>
+        <v>6.426879088895687</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.92186073834648</v>
+        <v>11.9218607099015</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.38777372262773</v>
@@ -3780,19 +3780,19 @@
         <v>18.61263551273508</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.14401436418127</v>
+        <v>35.14401438917969</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.29380744597264</v>
+        <v>12.29380744888454</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.32877926143806</v>
+        <v>20.32877929356755</v>
       </c>
       <c r="CE10" t="n">
         <v>17.80443971854372</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.21333010912071</v>
+        <v>20.21333011363426</v>
       </c>
       <c r="CG10" t="n">
         <v>18.61263551273508</v>
@@ -3813,7 +3813,7 @@
         <v>6.357917215629039</v>
       </c>
       <c r="CM10" t="n">
-        <v>28.3386038674331</v>
+        <v>28.33860389609053</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -4096,10 +4096,10 @@
         <v>32.97999954223633</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.05539021865696</v>
+        <v>46.05539014609449</v>
       </c>
       <c r="BY11" t="n">
-        <v>85.43274885560866</v>
+        <v>85.43274872100527</v>
       </c>
       <c r="BZ11" t="n">
         <v>69.25277241436312</v>
@@ -4120,7 +4120,7 @@
         <v>25.25865933859778</v>
       </c>
       <c r="CF11" t="n">
-        <v>78.35175843695791</v>
+        <v>78.35175840736279</v>
       </c>
       <c r="CG11" t="n">
         <v>69.25277241436312</v>
@@ -4141,7 +4141,7 @@
         <v>88.98573692551504</v>
       </c>
       <c r="CM11" t="n">
-        <v>137.5735582913383</v>
+        <v>137.5735582016017</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -4434,10 +4434,10 @@
         <v>45.97999954223633</v>
       </c>
       <c r="BX12" t="n">
-        <v>127.6301650560994</v>
+        <v>127.6301646824178</v>
       </c>
       <c r="BY12" t="n">
-        <v>236.7539561790644</v>
+        <v>236.753955485885</v>
       </c>
       <c r="BZ12" t="n">
         <v>134.1927299415487</v>
@@ -4458,13 +4458,13 @@
         <v>55.9815638034286</v>
       </c>
       <c r="CF12" t="n">
-        <v>141.0136555376253</v>
+        <v>141.0136554042676</v>
       </c>
       <c r="CG12" t="n">
-        <v>125.087989407021</v>
+        <v>125.0879892201802</v>
       </c>
       <c r="CH12" t="n">
-        <v>112.5791904663189</v>
+        <v>112.5791902981622</v>
       </c>
       <c r="CI12" t="n">
         <v>8</v>
@@ -4476,10 +4476,10 @@
         <v>5.4</v>
       </c>
       <c r="CL12" t="n">
-        <v>144.8438268532515</v>
+        <v>144.8438264875344</v>
       </c>
       <c r="CM12" t="n">
-        <v>206.684769337792</v>
+        <v>206.6847690477579</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -4762,10 +4762,10 @@
         <v>7.449999809265137</v>
       </c>
       <c r="BX13" t="n">
-        <v>3.36372973558846</v>
+        <v>3.363729728852422</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.239718659516593</v>
+        <v>6.239718647021244</v>
       </c>
       <c r="BZ13" t="n">
         <v>21.74284085303151</v>
@@ -4774,7 +4774,7 @@
         <v>14.8939109083963</v>
       </c>
       <c r="CB13" t="n">
-        <v>34.98727168220606</v>
+        <v>34.98727166143413</v>
       </c>
       <c r="CC13" t="n">
         <v>10.95072400487419</v>
@@ -5070,10 +5070,10 @@
         <v>19.13999938964844</v>
       </c>
       <c r="BX14" t="n">
-        <v>13.15731118896105</v>
+        <v>13.15731116173671</v>
       </c>
       <c r="BY14" t="n">
-        <v>24.40681225552275</v>
+        <v>24.40681220502159</v>
       </c>
       <c r="BZ14" t="n">
         <v>20.45201547684208</v>
@@ -5082,7 +5082,7 @@
         <v>12.7798316087502</v>
       </c>
       <c r="CB14" t="n">
-        <v>34.61244748652861</v>
+        <v>34.61244745579145</v>
       </c>
       <c r="CC14" t="n">
         <v>22.8984489302328</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="CE14" t="inlineStr"/>
       <c r="CF14" t="n">
-        <v>20.22864696288967</v>
+        <v>20.22864694345829</v>
       </c>
       <c r="CG14" t="n">
         <v>21.67523220353744</v>
@@ -5113,7 +5113,7 @@
         <v>1.9211578122313</v>
       </c>
       <c r="CM14" t="n">
-        <v>5.687814043661943</v>
+        <v>5.687813942139597</v>
       </c>
       <c r="CN14" t="inlineStr">
         <is>
@@ -5396,10 +5396,10 @@
         <v>17.53000068664551</v>
       </c>
       <c r="BX15" t="n">
-        <v>10.7442654659961</v>
+        <v>10.74426551276496</v>
       </c>
       <c r="BY15" t="n">
-        <v>19.93061243942277</v>
+        <v>19.930612526179</v>
       </c>
       <c r="BZ15" t="n">
         <v>37.89111078271664</v>
@@ -5408,25 +5408,25 @@
         <v>37.31646064248518</v>
       </c>
       <c r="CB15" t="n">
-        <v>42.40390249981662</v>
+        <v>42.40390252033178</v>
       </c>
       <c r="CC15" t="n">
-        <v>34.52246247818044</v>
+        <v>34.52246246837511</v>
       </c>
       <c r="CD15" t="n">
-        <v>18.86931527289594</v>
+        <v>18.86931521865155</v>
       </c>
       <c r="CE15" t="n">
         <v>31.49264348607277</v>
       </c>
       <c r="CF15" t="n">
-        <v>31.77521537165577</v>
+        <v>31.77521537783029</v>
       </c>
       <c r="CG15" t="n">
-        <v>34.52246247818044</v>
+        <v>34.52246246837511</v>
       </c>
       <c r="CH15" t="n">
-        <v>31.07021623036239</v>
+        <v>31.0702162215376</v>
       </c>
       <c r="CI15" t="n">
         <v>7</v>
@@ -5438,10 +5438,10 @@
         <v>3.9</v>
       </c>
       <c r="CL15" t="n">
-        <v>77.24024536993845</v>
+        <v>77.24024531959736</v>
       </c>
       <c r="CM15" t="n">
-        <v>81.26191743884171</v>
+        <v>81.26191747406433</v>
       </c>
       <c r="CN15" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>-5.040678244190966</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-23.22124503926587</v>
+        <v>-23.2212515115939</v>
       </c>
       <c r="DA15" t="b">
         <v>1</v>
@@ -5724,10 +5724,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="BX16" t="n">
-        <v>10.37863327533605</v>
+        <v>10.37863322903966</v>
       </c>
       <c r="BY16" t="n">
-        <v>19.25236472574838</v>
+        <v>19.25236463986857</v>
       </c>
       <c r="BZ16" t="n">
         <v>25.85122324877091</v>
@@ -5736,25 +5736,25 @@
         <v>18.56165831752405</v>
       </c>
       <c r="CB16" t="n">
-        <v>39.76450197392393</v>
+        <v>39.76450201325112</v>
       </c>
       <c r="CC16" t="n">
-        <v>24.31404882939119</v>
+        <v>24.31404884830175</v>
       </c>
       <c r="CD16" t="n">
-        <v>13.00688748824112</v>
+        <v>13.00688758968578</v>
       </c>
       <c r="CE16" t="n">
         <v>10.35999965667725</v>
       </c>
       <c r="CF16" t="n">
-        <v>20.18616468945161</v>
+        <v>20.18616469288988</v>
       </c>
       <c r="CG16" t="n">
-        <v>18.90701152163621</v>
+        <v>18.9070114786963</v>
       </c>
       <c r="CH16" t="n">
-        <v>17.01631036947259</v>
+        <v>17.01631033082667</v>
       </c>
       <c r="CI16" t="n">
         <v>8</v>
@@ -5766,10 +5766,10 @@
         <v>3.8</v>
       </c>
       <c r="CL16" t="n">
-        <v>64.25010553456157</v>
+        <v>64.25010516153145</v>
       </c>
       <c r="CM16" t="n">
-        <v>94.84715596917211</v>
+        <v>94.84715600236007</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -6052,10 +6052,10 @@
         <v>11.28999996185303</v>
       </c>
       <c r="BX17" t="n">
-        <v>9.774107176349089</v>
+        <v>9.774107152415171</v>
       </c>
       <c r="BY17" t="n">
-        <v>18.13096881212756</v>
+        <v>18.13096876773014</v>
       </c>
       <c r="BZ17" t="n">
         <v>23.1209427348613</v>
@@ -6064,25 +6064,25 @@
         <v>13.6472321924953</v>
       </c>
       <c r="CB17" t="n">
-        <v>35.00095079985264</v>
+        <v>35.00095087130416</v>
       </c>
       <c r="CC17" t="n">
-        <v>25.51476115415504</v>
+        <v>25.51476117084985</v>
       </c>
       <c r="CD17" t="n">
-        <v>13.36818424804047</v>
+        <v>13.36818432550593</v>
       </c>
       <c r="CE17" t="n">
         <v>9.880299501333878</v>
       </c>
       <c r="CF17" t="n">
-        <v>18.55468082740191</v>
+        <v>18.55468083956197</v>
       </c>
       <c r="CG17" t="n">
-        <v>15.88910050231143</v>
+        <v>15.88910048011272</v>
       </c>
       <c r="CH17" t="n">
-        <v>14.30019045208029</v>
+        <v>14.30019043210145</v>
       </c>
       <c r="CI17" t="n">
         <v>8</v>
@@ -6094,10 +6094,10 @@
         <v>3.6</v>
       </c>
       <c r="CL17" t="n">
-        <v>26.66244907350024</v>
+        <v>26.66244889653975</v>
       </c>
       <c r="CM17" t="n">
-        <v>64.34615491669614</v>
+        <v>64.34615502440258</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="BX18" t="n">
-        <v>5.044350378841198</v>
+        <v>5.044350332854253</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.357269952750423</v>
+        <v>9.357269867444639</v>
       </c>
       <c r="BZ18" t="n">
         <v>8.453839145587175</v>
@@ -6456,7 +6456,7 @@
         <v>-2.887864672525231</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-28.51676265378231</v>
+        <v>-28.51675560376472</v>
       </c>
       <c r="DA18" t="b">
         <v>1</v>
@@ -6700,10 +6700,10 @@
         <v>11.07999992370605</v>
       </c>
       <c r="BX19" t="n">
-        <v>3.454302382804934</v>
+        <v>3.454302376618553</v>
       </c>
       <c r="BY19" t="n">
-        <v>6.407730920103153</v>
+        <v>6.407730908627417</v>
       </c>
       <c r="BZ19" t="n">
         <v>20.4470750681205</v>
@@ -6712,13 +6712,13 @@
         <v>19.3263652032129</v>
       </c>
       <c r="CB19" t="n">
-        <v>22.00385754004261</v>
+        <v>22.00385754046043</v>
       </c>
       <c r="CC19" t="n">
-        <v>16.46863777196926</v>
+        <v>16.46863777318124</v>
       </c>
       <c r="CD19" t="n">
-        <v>13.71979385590022</v>
+        <v>13.71979386374505</v>
       </c>
       <c r="CE19" t="n">
         <v>30.3956356510297</v>
@@ -6774,7 +6774,7 @@
         <v>-18.94659940111765</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-32.89648038436899</v>
+        <v>-32.89648837260555</v>
       </c>
       <c r="DA19" t="b">
         <v>1</v>
@@ -7018,10 +7018,10 @@
         <v>27.52000045776367</v>
       </c>
       <c r="BX20" t="n">
-        <v>7.290978493448117</v>
+        <v>7.290978511925755</v>
       </c>
       <c r="BY20" t="n">
-        <v>13.52476510534626</v>
+        <v>13.52476513962228</v>
       </c>
       <c r="BZ20" t="n">
         <v>36.57372177185242</v>
@@ -7030,19 +7030,19 @@
         <v>28.87454744278962</v>
       </c>
       <c r="CB20" t="n">
-        <v>45.93352495810291</v>
+        <v>45.93352493096688</v>
       </c>
       <c r="CC20" t="n">
-        <v>26.49482250355711</v>
+        <v>26.49482249904537</v>
       </c>
       <c r="CD20" t="n">
-        <v>29.81102745702587</v>
+        <v>29.81102742365968</v>
       </c>
       <c r="CE20" t="n">
         <v>24.2620728130642</v>
       </c>
       <c r="CF20" t="n">
-        <v>29.35349743596263</v>
+        <v>29.35349743157149</v>
       </c>
       <c r="CG20" t="n">
         <v>28.87454744278962</v>
@@ -7063,7 +7063,7 @@
         <v>-5.570158916260349</v>
       </c>
       <c r="CM20" t="n">
-        <v>6.662416234378021</v>
+        <v>6.662416218421874</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -7346,10 +7346,10 @@
         <v>22.06999969482422</v>
       </c>
       <c r="BX21" t="n">
-        <v>3.108072443831099</v>
+        <v>3.108072450041836</v>
       </c>
       <c r="BY21" t="n">
-        <v>5.765474383306688</v>
+        <v>5.765474394827605</v>
       </c>
       <c r="BZ21" t="n">
         <v>33.57376532220675</v>
@@ -7358,7 +7358,7 @@
         <v>28.04300293143303</v>
       </c>
       <c r="CB21" t="n">
-        <v>43.00378985487929</v>
+        <v>43.00378986486211</v>
       </c>
       <c r="CC21" t="n">
         <v>10.85340539909456</v>
@@ -7644,10 +7644,10 @@
         <v>38.90000152587891</v>
       </c>
       <c r="BX22" t="n">
-        <v>35.62892557839169</v>
+        <v>35.62892548976458</v>
       </c>
       <c r="BY22" t="n">
-        <v>51.87571564213831</v>
+        <v>51.87571551309724</v>
       </c>
       <c r="BZ22" t="n">
         <v>50.25590259243982</v>
@@ -7664,13 +7664,13 @@
       </c>
       <c r="CE22" t="inlineStr"/>
       <c r="CF22" t="n">
-        <v>49.31617719919689</v>
+        <v>49.31617714477984</v>
       </c>
       <c r="CG22" t="n">
-        <v>51.06580911728906</v>
+        <v>51.06580905276853</v>
       </c>
       <c r="CH22" t="n">
-        <v>45.95922820556016</v>
+        <v>45.95922814749168</v>
       </c>
       <c r="CI22" t="n">
         <v>4</v>
@@ -7682,10 +7682,10 @@
         <v>1.7</v>
       </c>
       <c r="CL22" t="n">
-        <v>18.14711157526556</v>
+        <v>18.14711142598928</v>
       </c>
       <c r="CM22" t="n">
-        <v>26.77680016641757</v>
+        <v>26.776800026528</v>
       </c>
       <c r="CN22" t="inlineStr">
         <is>
@@ -7968,10 +7968,10 @@
         <v>32.75</v>
       </c>
       <c r="BX23" t="n">
-        <v>3.249356697068481</v>
+        <v>3.249356690606488</v>
       </c>
       <c r="BY23" t="n">
-        <v>6.027556673062032</v>
+        <v>6.027556661075034</v>
       </c>
       <c r="BZ23" t="n">
         <v>33.45701619121048</v>
@@ -7980,7 +7980,7 @@
         <v>23.42786572511178</v>
       </c>
       <c r="CB23" t="n">
-        <v>41.38326860130753</v>
+        <v>41.38326859433236</v>
       </c>
       <c r="CC23" t="n">
         <v>10.59424454785779</v>
@@ -8274,10 +8274,10 @@
         <v>14.77999973297119</v>
       </c>
       <c r="BX24" t="n">
-        <v>9.186484878581913</v>
+        <v>9.186484929091723</v>
       </c>
       <c r="BY24" t="n">
-        <v>17.04092944976945</v>
+        <v>17.04092954346514</v>
       </c>
       <c r="BZ24" t="n">
         <v>31.89495056382219</v>
@@ -8286,23 +8286,23 @@
         <v>30.33345456974609</v>
       </c>
       <c r="CB24" t="n">
-        <v>36.78693478697259</v>
+        <v>36.78693480222304</v>
       </c>
       <c r="CC24" t="n">
-        <v>25.58128745942417</v>
+        <v>25.58128744946131</v>
       </c>
       <c r="CD24" t="n">
-        <v>16.38749084901738</v>
+        <v>16.38749078621147</v>
       </c>
       <c r="CE24" t="inlineStr"/>
       <c r="CF24" t="n">
-        <v>20.92591308789943</v>
+        <v>20.92591312146009</v>
       </c>
       <c r="CG24" t="n">
-        <v>21.31110845459681</v>
+        <v>21.31110849646323</v>
       </c>
       <c r="CH24" t="n">
-        <v>19.17999760913713</v>
+        <v>19.1799976468169</v>
       </c>
       <c r="CI24" t="n">
         <v>4</v>
@@ -8314,10 +8314,10 @@
         <v>3.5</v>
       </c>
       <c r="CL24" t="n">
-        <v>29.7699455728029</v>
+        <v>29.76994582774049</v>
       </c>
       <c r="CM24" t="n">
-        <v>41.58263508772568</v>
+        <v>41.58263531479373</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -8580,35 +8580,35 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BX25" t="n">
-        <v>8.627042072234111</v>
+        <v>8.627042103431171</v>
       </c>
       <c r="BY25" t="n">
-        <v>14.34730902416064</v>
+        <v>14.3473089857313</v>
       </c>
       <c r="BZ25" t="n">
-        <v>19.54486196556696</v>
+        <v>19.54486184253791</v>
       </c>
       <c r="CA25" t="n">
         <v>17.74926644976348</v>
       </c>
       <c r="CB25" t="n">
-        <v>23.93539530781762</v>
+        <v>23.93539527918414</v>
       </c>
       <c r="CC25" t="n">
-        <v>17.38495029677088</v>
+        <v>17.38495028827388</v>
       </c>
       <c r="CD25" t="n">
-        <v>9.719867200323893</v>
+        <v>9.719867147174087</v>
       </c>
       <c r="CE25" t="inlineStr"/>
       <c r="CF25" t="n">
-        <v>14.97604083968315</v>
+        <v>14.97604080499356</v>
       </c>
       <c r="CG25" t="n">
-        <v>15.86612966046576</v>
+        <v>15.86612963700259</v>
       </c>
       <c r="CH25" t="n">
-        <v>14.27951669441919</v>
+        <v>14.27951667330233</v>
       </c>
       <c r="CI25" t="n">
         <v>4</v>
@@ -8620,10 +8620,10 @@
         <v>2.3</v>
       </c>
       <c r="CL25" t="n">
-        <v>11.12464023744999</v>
+        <v>11.12464007311649</v>
       </c>
       <c r="CM25" t="n">
-        <v>16.54506144045931</v>
+        <v>16.54506117050147</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -8906,10 +8906,10 @@
         <v>5.880000114440918</v>
       </c>
       <c r="BX26" t="n">
-        <v>6.975750786425684</v>
+        <v>6.975750828113066</v>
       </c>
       <c r="BY26" t="n">
-        <v>12.94001770881964</v>
+        <v>12.94001778614973</v>
       </c>
       <c r="BZ26" t="n">
         <v>5.605036080312384</v>
@@ -8930,7 +8930,7 @@
         <v>5.348622529323849</v>
       </c>
       <c r="CF26" t="n">
-        <v>7.296291356627144</v>
+        <v>7.296291371504328</v>
       </c>
       <c r="CG26" t="n">
         <v>5.869184706822859</v>
@@ -8951,7 +8951,7 @@
         <v>-10.16554195011574</v>
       </c>
       <c r="CM26" t="n">
-        <v>24.08658528267544</v>
+        <v>24.08658553568879</v>
       </c>
       <c r="CN26" t="inlineStr">
         <is>
@@ -8968,16 +8968,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="CQ26" t="inlineStr">
-        <is>
-          <t>A CSN Mineração (CMIN3) apresenta uma notável eficiência operacional, com um ROE de 31,8% e um ROIC de 20,3% que se posicionam muito acima dos pares do setor de materiais (8,4% e 8,7%, respectivamente), sugerindo uma forte capacidade de geração de valor sobre o capital empregado. No entanto, essa elevada qualidade operacional convive com múltiplos de preço esticados, visto que o P/L de 13,9 e o P/VP de 4,42 indicam que o mercado já cobra um prêmio considerável pelo papel, embora o PEG de 0,15 aponte que esse preço está desalinhado positivamente com o crescimento projetado. No âmbito financeiro, a excelente rentabilidade é acompanhada por um endividamento sob controle, evidenciado pela relação Dívida Líquida/EBITDA de apenas 0,2, patamar substancialmente abaixo da média do setor de 2,17, o que confere segurança financeira mesmo com uma relação Dívida/Patrimônio de 1,24. Essa estrutura de capital robusta e a forte geração de caixa dão sustentabilidade ao expressivo dividend yield de 18,25%, o qual se mostra coerente com o lucro e com a saúde do balanço, posicionando a empresa como uma forte pagadora de proventos. O crescimento histórico da companhia também é um destaque, com um CAGR de receita nos últimos cinco anos de 90,7%, superando com folga a média setorial de 17,7%, o que se reflete no checklist de critérios fundamentalistas, onde a empresa atende a expressivos 7 de 8 requisitos analisados. Sob a ótica do valuation, os métodos de preço-teto revelam uma dispersão acentuada entre as premissas, variando desde os conservadores R$ 3,56 de Graham e R$ 5,61 do fluxo de caixa descontado até os otimistas R$ 12,94 de Gordon e R$ 12,69 de Lynch. Essa disparidade resulta em uma média de R$ 7,30 e uma mediana de R$ 5,87, sendo que o preço-teto ajustado com margem de segurança fica em R$ 5,28, o que gera um upside negativo de 10,2% em relação à cotação atual de R$ 5,88. Em suma, os principais prós do ativo residem em sua rentabilidade excepcional, endividamento muito abaixo dos pares, forte crescimento histórico e proventos altamente atrativos, enquanto os contras concentram-se no valuation esticado frente ao preço-teto ajustado, na margem líquida abaixo de 15% e em uma tendência gráfica lateralizada que exige cautela do investidor.</t>
-        </is>
-      </c>
-      <c r="CR26" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
+      <c r="CQ26" t="inlineStr"/>
+      <c r="CR26" t="inlineStr"/>
       <c r="CS26" t="b">
         <v>0</v>
       </c>
@@ -9004,14 +8996,14 @@
         <v>1</v>
       </c>
       <c r="DB26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD26" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$4.78 (candidato)</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -9224,10 +9216,10 @@
         <v>39.43999862670898</v>
       </c>
       <c r="BX27" t="n">
-        <v>20.1612756175048</v>
+        <v>20.16127568549079</v>
       </c>
       <c r="BY27" t="n">
-        <v>37.3991662704714</v>
+        <v>37.39916639658541</v>
       </c>
       <c r="BZ27" t="n">
         <v>57.05021635413689</v>
@@ -9236,23 +9228,23 @@
         <v>43.06721646336476</v>
       </c>
       <c r="CB27" t="n">
-        <v>64.10972949124397</v>
+        <v>64.10972938147273</v>
       </c>
       <c r="CC27" t="n">
-        <v>45.28400693591092</v>
+        <v>45.28400691505072</v>
       </c>
       <c r="CD27" t="n">
-        <v>32.43094094972332</v>
+        <v>32.43094081541021</v>
       </c>
       <c r="CE27" t="inlineStr"/>
       <c r="CF27" t="n">
-        <v>39.973666294506</v>
+        <v>39.97366633781595</v>
       </c>
       <c r="CG27" t="n">
-        <v>41.34158660319116</v>
+        <v>41.34158665581806</v>
       </c>
       <c r="CH27" t="n">
-        <v>37.20742794287204</v>
+        <v>37.20742799023625</v>
       </c>
       <c r="CI27" t="n">
         <v>4</v>
@@ -9264,10 +9256,10 @@
         <v>2.8</v>
       </c>
       <c r="CL27" t="n">
-        <v>-5.6606763731605</v>
+        <v>-5.660676253068686</v>
       </c>
       <c r="CM27" t="n">
-        <v>1.353112795079103</v>
+        <v>1.353112904891329</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -9550,37 +9542,37 @@
         <v>26.45999908447266</v>
       </c>
       <c r="BX28" t="n">
-        <v>16.91893502410094</v>
+        <v>16.9189349966709</v>
       </c>
       <c r="BY28" t="n">
-        <v>28.67982835307078</v>
+        <v>28.67982834944448</v>
       </c>
       <c r="BZ28" t="n">
-        <v>49.21350829686259</v>
+        <v>49.213508370428</v>
       </c>
       <c r="CA28" t="n">
         <v>53.99475108321082</v>
       </c>
       <c r="CB28" t="n">
-        <v>57.93925173409952</v>
+        <v>57.93925172391921</v>
       </c>
       <c r="CC28" t="n">
-        <v>43.01388444492227</v>
+        <v>43.01388444982749</v>
       </c>
       <c r="CD28" t="n">
-        <v>24.40657257113381</v>
+        <v>24.40657260181376</v>
       </c>
       <c r="CE28" t="n">
         <v>30.06721996094383</v>
       </c>
       <c r="CF28" t="n">
-        <v>38.02924393354307</v>
+        <v>38.02924394203231</v>
       </c>
       <c r="CG28" t="n">
-        <v>36.54055220293305</v>
+        <v>36.54055220538566</v>
       </c>
       <c r="CH28" t="n">
-        <v>32.88649698263975</v>
+        <v>32.88649698484709</v>
       </c>
       <c r="CI28" t="n">
         <v>8</v>
@@ -9592,10 +9584,10 @@
         <v>3.4</v>
       </c>
       <c r="CL28" t="n">
-        <v>24.2875968273873</v>
+        <v>24.2875968357295</v>
       </c>
       <c r="CM28" t="n">
-        <v>43.7235270195437</v>
+        <v>43.72352705162699</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -9878,37 +9870,37 @@
         <v>15.3100004196167</v>
       </c>
       <c r="BX29" t="n">
-        <v>5.939526957524716</v>
+        <v>5.939526977006997</v>
       </c>
       <c r="BY29" t="n">
-        <v>8.534880613439464</v>
+        <v>8.534880597355141</v>
       </c>
       <c r="BZ29" t="n">
-        <v>10.81501547960945</v>
+        <v>10.81501542375372</v>
       </c>
       <c r="CA29" t="n">
         <v>11.65944891202323</v>
       </c>
       <c r="CB29" t="n">
-        <v>9.810403824194951</v>
+        <v>9.810403792780233</v>
       </c>
       <c r="CC29" t="n">
-        <v>14.90925678315233</v>
+        <v>14.90925677631631</v>
       </c>
       <c r="CD29" t="n">
-        <v>5.384140050651277</v>
+        <v>5.384140019105566</v>
       </c>
       <c r="CE29" t="n">
         <v>10.69689722735973</v>
       </c>
       <c r="CF29" t="n">
-        <v>9.718696230994393</v>
+        <v>9.718696215712617</v>
       </c>
       <c r="CG29" t="n">
-        <v>10.25365052577734</v>
+        <v>10.25365051006998</v>
       </c>
       <c r="CH29" t="n">
-        <v>9.228285473199609</v>
+        <v>9.228285459062983</v>
       </c>
       <c r="CI29" t="n">
         <v>8</v>
@@ -9920,10 +9912,10 @@
         <v>2.8</v>
       </c>
       <c r="CL29" t="n">
-        <v>-39.72380652991093</v>
+        <v>-39.72380662224684</v>
       </c>
       <c r="CM29" t="n">
-        <v>-36.52060114549814</v>
+        <v>-36.52060124531379</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -10762,10 +10754,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.86871605417369</v>
+        <v>5.868716018802491</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.88646828049219</v>
+        <v>10.88646821487862</v>
       </c>
       <c r="BZ2" t="n">
         <v>42.10015429633837</v>
@@ -10774,7 +10766,7 @@
         <v>28.26125673506212</v>
       </c>
       <c r="CB2" t="n">
-        <v>72.78655348876849</v>
+        <v>72.78655333733215</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -10836,7 +10828,7 @@
         <v>-4.94053016263244</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-26.59161854099229</v>
+        <v>-26.59161348668701</v>
       </c>
       <c r="DA2" t="b">
         <v>1</v>
@@ -11080,10 +11072,10 @@
         <v>13.60999965667725</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.01575557945281</v>
+        <v>15.0157554397903</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.85422659988496</v>
+        <v>27.85422634081101</v>
       </c>
       <c r="BZ3" t="n">
         <v>38.94870312116058</v>
@@ -11092,13 +11084,13 @@
         <v>23.57226802449605</v>
       </c>
       <c r="CB3" t="n">
-        <v>74.76041608604787</v>
+        <v>74.76041634926167</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.40383469172596</v>
+        <v>48.40383479435776</v>
       </c>
       <c r="CD3" t="n">
-        <v>26.30532694818076</v>
+        <v>26.30532737907871</v>
       </c>
       <c r="CE3" t="n">
         <v>8.655042371031668</v>
@@ -11398,10 +11390,10 @@
         <v>24.54000091552734</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.25388474454687</v>
+        <v>16.25388475294957</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.15095620113445</v>
+        <v>30.15095621672145</v>
       </c>
       <c r="BZ4" t="n">
         <v>74.06720094094243</v>
@@ -11410,13 +11402,13 @@
         <v>53.70833445174577</v>
       </c>
       <c r="CB4" t="n">
-        <v>132.6406024906445</v>
+        <v>132.6406024887612</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.7945176718956</v>
+        <v>25.79451767073932</v>
       </c>
       <c r="CD4" t="n">
-        <v>65.72549933503295</v>
+        <v>65.72549931700549</v>
       </c>
       <c r="CE4" t="n">
         <v>43.53105147803891</v>
@@ -11714,10 +11706,10 @@
         <v>4.190000057220459</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.548072963759028</v>
+        <v>3.548072995676882</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.581675347772996</v>
+        <v>6.581675406980615</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.82159370858454</v>
@@ -11726,25 +11718,25 @@
         <v>8.61209444827186</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.80877193294405</v>
+        <v>24.80877190959474</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.29418312694294</v>
+        <v>11.29418311396195</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.9682754658171</v>
+        <v>10.9682753862727</v>
       </c>
       <c r="CE5" t="n">
         <v>5.153758142621466</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.238596706668487</v>
+        <v>9.238596701115524</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.790184957044481</v>
+        <v>9.790184917272281</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.811166461340033</v>
+        <v>8.811166425545053</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -11756,10 +11748,10 @@
         <v>7</v>
       </c>
       <c r="CL5" t="n">
-        <v>110.2903661339122</v>
+        <v>110.2903652796167</v>
       </c>
       <c r="CM5" t="n">
-        <v>120.491565167117</v>
+        <v>120.491565034588</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -12024,10 +12016,10 @@
         <v>48.2400016784668</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.38294926403854</v>
+        <v>18.38294924500586</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.10037088479149</v>
+        <v>34.10037084948588</v>
       </c>
       <c r="BZ6" t="n">
         <v>76.54850565744731</v>
@@ -12036,23 +12028,23 @@
         <v>57.29789298233228</v>
       </c>
       <c r="CB6" t="n">
-        <v>103.9926847905225</v>
+        <v>103.9926848194703</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.49285960086324</v>
+        <v>48.49285960539734</v>
       </c>
       <c r="CD6" t="n">
-        <v>61.42668256503595</v>
+        <v>61.4266826032901</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>44.38117135178514</v>
+        <v>44.3811713393341</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.29661524282736</v>
+        <v>41.29661522744161</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.16695371854463</v>
+        <v>37.16695370469745</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -12064,10 +12056,10 @@
         <v>4.2</v>
       </c>
       <c r="CL6" t="n">
-        <v>-22.95407872024374</v>
+        <v>-22.9540787489485</v>
       </c>
       <c r="CM6" t="n">
-        <v>-7.999233400533123</v>
+        <v>-7.999233426343744</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -12350,10 +12342,10 @@
         <v>4.510000228881836</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.052774388407022</v>
+        <v>3.052774365013348</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.662896490495025</v>
+        <v>5.662896447099761</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.93452446594899</v>
@@ -12362,7 +12354,7 @@
         <v>8.695832933160331</v>
       </c>
       <c r="CB7" t="n">
-        <v>23.89368936600127</v>
+        <v>23.89368929511135</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -12374,7 +12366,7 @@
         <v>5.186344183602181</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.39433293753478</v>
+        <v>11.39433292120833</v>
       </c>
       <c r="CG7" t="n">
         <v>11.57513776217851</v>
@@ -12395,7 +12387,7 @@
         <v>130.9894336423016</v>
       </c>
       <c r="CM7" t="n">
-        <v>152.6459503164988</v>
+        <v>152.6459499544931</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -12434,7 +12426,7 @@
         <v>-6.237000363129841</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-43.27722523663176</v>
+        <v>-43.27722875916081</v>
       </c>
       <c r="DA7" t="b">
         <v>1</v>
@@ -12678,10 +12670,10 @@
         <v>32.58000183105469</v>
       </c>
       <c r="BX8" t="n">
-        <v>24.20136285624547</v>
+        <v>24.20136286831822</v>
       </c>
       <c r="BY8" t="n">
-        <v>44.89352809833534</v>
+        <v>44.89352812073029</v>
       </c>
       <c r="BZ8" t="n">
         <v>50.78647344252641</v>
@@ -12690,25 +12682,25 @@
         <v>22.31995674309305</v>
       </c>
       <c r="CB8" t="n">
-        <v>69.38361253173336</v>
+        <v>69.38361243942339</v>
       </c>
       <c r="CC8" t="n">
-        <v>53.12760891626809</v>
+        <v>53.12760890182916</v>
       </c>
       <c r="CD8" t="n">
-        <v>28.79645699130806</v>
+        <v>28.79645692078581</v>
       </c>
       <c r="CE8" t="n">
         <v>25.44421854454374</v>
       </c>
       <c r="CF8" t="n">
-        <v>39.86915226550668</v>
+        <v>39.86915224765626</v>
       </c>
       <c r="CG8" t="n">
-        <v>36.8449925448217</v>
+        <v>36.84499252075805</v>
       </c>
       <c r="CH8" t="n">
-        <v>33.16049329033953</v>
+        <v>33.16049326868225</v>
       </c>
       <c r="CI8" t="n">
         <v>8</v>
@@ -12720,10 +12712,10 @@
         <v>3.1</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.781741641068701</v>
+        <v>1.78174157459452</v>
       </c>
       <c r="CM8" t="n">
-        <v>22.37308172126653</v>
+        <v>22.37308166647702</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -13016,10 +13008,10 @@
         <v>41.34999847412109</v>
       </c>
       <c r="BX9" t="n">
-        <v>121.1494724636367</v>
+        <v>121.1494712699134</v>
       </c>
       <c r="BY9" t="n">
-        <v>224.732271420046</v>
+        <v>224.7322692056893</v>
       </c>
       <c r="BZ9" t="n">
         <v>134.6160883985514</v>
@@ -13040,13 +13032,13 @@
         <v>57.31088302327341</v>
       </c>
       <c r="CF9" t="n">
-        <v>139.1218205336959</v>
+        <v>139.1218201076859</v>
       </c>
       <c r="CG9" t="n">
-        <v>122.0409501798362</v>
+        <v>122.0409495829745</v>
       </c>
       <c r="CH9" t="n">
-        <v>109.8368551618526</v>
+        <v>109.8368546246771</v>
       </c>
       <c r="CI9" t="n">
         <v>8</v>
@@ -13058,10 +13050,10 @@
         <v>5.4</v>
       </c>
       <c r="CL9" t="n">
-        <v>165.6272290568378</v>
+        <v>165.6272277577434</v>
       </c>
       <c r="CM9" t="n">
-        <v>236.4493970193622</v>
+        <v>236.4493959891083</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -13344,10 +13336,10 @@
         <v>15.75</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.426879104229907</v>
+        <v>6.426879088895687</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.92186073834648</v>
+        <v>11.9218607099015</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.38777372262773</v>
@@ -13356,19 +13348,19 @@
         <v>18.61263551273508</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.14401436418127</v>
+        <v>35.14401438917969</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.29380744597264</v>
+        <v>12.29380744888454</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.32877926143806</v>
+        <v>20.32877929356755</v>
       </c>
       <c r="CE10" t="n">
         <v>17.80443971854372</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.21333010912071</v>
+        <v>20.21333011363426</v>
       </c>
       <c r="CG10" t="n">
         <v>18.61263551273508</v>
@@ -13389,7 +13381,7 @@
         <v>6.357917215629039</v>
       </c>
       <c r="CM10" t="n">
-        <v>28.3386038674331</v>
+        <v>28.33860389609053</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -13672,10 +13664,10 @@
         <v>32.97999954223633</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.05539021865696</v>
+        <v>46.05539014609449</v>
       </c>
       <c r="BY11" t="n">
-        <v>85.43274885560866</v>
+        <v>85.43274872100527</v>
       </c>
       <c r="BZ11" t="n">
         <v>69.25277241436312</v>
@@ -13696,7 +13688,7 @@
         <v>25.25865933859778</v>
       </c>
       <c r="CF11" t="n">
-        <v>78.35175843695791</v>
+        <v>78.35175840736279</v>
       </c>
       <c r="CG11" t="n">
         <v>69.25277241436312</v>
@@ -13717,7 +13709,7 @@
         <v>88.98573692551504</v>
       </c>
       <c r="CM11" t="n">
-        <v>137.5735582913383</v>
+        <v>137.5735582016017</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -14008,10 +14000,10 @@
         <v>7.050000190734863</v>
       </c>
       <c r="BX12" t="n">
-        <v>6.617251155137779</v>
+        <v>6.617251157636814</v>
       </c>
       <c r="BY12" t="n">
-        <v>12.27500089278058</v>
+        <v>12.27500089741629</v>
       </c>
       <c r="BZ12" t="n">
         <v>41.70201005680219</v>
@@ -14020,7 +14012,7 @@
         <v>28.15049940691006</v>
       </c>
       <c r="CB12" t="n">
-        <v>88.56764242542492</v>
+        <v>88.5676424410439</v>
       </c>
       <c r="CC12" t="n">
         <v>51.88018214566937</v>
@@ -14534,10 +14526,10 @@
         <v>45.97999954223633</v>
       </c>
       <c r="BX14" t="n">
-        <v>127.6301650560994</v>
+        <v>127.6301646824178</v>
       </c>
       <c r="BY14" t="n">
-        <v>236.7539561790644</v>
+        <v>236.753955485885</v>
       </c>
       <c r="BZ14" t="n">
         <v>134.1927299415487</v>
@@ -14558,13 +14550,13 @@
         <v>55.9815638034286</v>
       </c>
       <c r="CF14" t="n">
-        <v>141.0136555376253</v>
+        <v>141.0136554042676</v>
       </c>
       <c r="CG14" t="n">
-        <v>125.087989407021</v>
+        <v>125.0879892201802</v>
       </c>
       <c r="CH14" t="n">
-        <v>112.5791904663189</v>
+        <v>112.5791902981622</v>
       </c>
       <c r="CI14" t="n">
         <v>8</v>
@@ -14576,10 +14568,10 @@
         <v>5.4</v>
       </c>
       <c r="CL14" t="n">
-        <v>144.8438268532515</v>
+        <v>144.8438264875344</v>
       </c>
       <c r="CM14" t="n">
-        <v>206.684769337792</v>
+        <v>206.6847690477579</v>
       </c>
       <c r="CN14" t="inlineStr">
         <is>
@@ -15158,10 +15150,10 @@
         <v>14</v>
       </c>
       <c r="BX16" t="n">
-        <v>10.16255144218858</v>
+        <v>10.16255144346047</v>
       </c>
       <c r="BY16" t="n">
-        <v>18.85153292525982</v>
+        <v>18.85153292761918</v>
       </c>
       <c r="BZ16" t="n">
         <v>51.38504155124654</v>
@@ -15170,23 +15162,23 @@
         <v>50.44813029652846</v>
       </c>
       <c r="CB16" t="n">
-        <v>71.96961905691506</v>
+        <v>71.96961905948648</v>
       </c>
       <c r="CC16" t="n">
-        <v>33.97319735300376</v>
+        <v>33.97319735281295</v>
       </c>
       <c r="CD16" t="n">
-        <v>30.82517848283428</v>
+        <v>30.82517848135013</v>
       </c>
       <c r="CE16" t="inlineStr"/>
       <c r="CF16" t="n">
-        <v>34.7365906098367</v>
+        <v>34.73659061055955</v>
       </c>
       <c r="CG16" t="n">
-        <v>33.97319735300376</v>
+        <v>33.97319735281295</v>
       </c>
       <c r="CH16" t="n">
-        <v>30.57587761770339</v>
+        <v>30.57587761753165</v>
       </c>
       <c r="CI16" t="n">
         <v>3</v>
@@ -15198,10 +15190,10 @@
         <v>5.1</v>
       </c>
       <c r="CL16" t="n">
-        <v>118.3991258407385</v>
+        <v>118.3991258395118</v>
       </c>
       <c r="CM16" t="n">
-        <v>148.1185043559765</v>
+        <v>148.1185043611397</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -15480,10 +15472,10 @@
         <v>7.449999809265137</v>
       </c>
       <c r="BX17" t="n">
-        <v>3.36372973558846</v>
+        <v>3.363729728852422</v>
       </c>
       <c r="BY17" t="n">
-        <v>6.239718659516593</v>
+        <v>6.239718647021244</v>
       </c>
       <c r="BZ17" t="n">
         <v>21.74284085303151</v>
@@ -15492,7 +15484,7 @@
         <v>14.8939109083963</v>
       </c>
       <c r="CB17" t="n">
-        <v>34.98727168220606</v>
+        <v>34.98727166143413</v>
       </c>
       <c r="CC17" t="n">
         <v>10.95072400487419</v>
@@ -15788,10 +15780,10 @@
         <v>19.13999938964844</v>
       </c>
       <c r="BX18" t="n">
-        <v>13.15731118896105</v>
+        <v>13.15731116173671</v>
       </c>
       <c r="BY18" t="n">
-        <v>24.40681225552275</v>
+        <v>24.40681220502159</v>
       </c>
       <c r="BZ18" t="n">
         <v>20.45201547684208</v>
@@ -15800,7 +15792,7 @@
         <v>12.7798316087502</v>
       </c>
       <c r="CB18" t="n">
-        <v>34.61244748652861</v>
+        <v>34.61244745579145</v>
       </c>
       <c r="CC18" t="n">
         <v>22.8984489302328</v>
@@ -15810,7 +15802,7 @@
       </c>
       <c r="CE18" t="inlineStr"/>
       <c r="CF18" t="n">
-        <v>20.22864696288967</v>
+        <v>20.22864694345829</v>
       </c>
       <c r="CG18" t="n">
         <v>21.67523220353744</v>
@@ -15831,7 +15823,7 @@
         <v>1.9211578122313</v>
       </c>
       <c r="CM18" t="n">
-        <v>5.687814043661943</v>
+        <v>5.687813942139597</v>
       </c>
       <c r="CN18" t="inlineStr">
         <is>
@@ -16114,10 +16106,10 @@
         <v>17.53000068664551</v>
       </c>
       <c r="BX19" t="n">
-        <v>10.7442654659961</v>
+        <v>10.74426551276496</v>
       </c>
       <c r="BY19" t="n">
-        <v>19.93061243942277</v>
+        <v>19.930612526179</v>
       </c>
       <c r="BZ19" t="n">
         <v>37.89111078271664</v>
@@ -16126,25 +16118,25 @@
         <v>37.31646064248518</v>
       </c>
       <c r="CB19" t="n">
-        <v>42.40390249981662</v>
+        <v>42.40390252033178</v>
       </c>
       <c r="CC19" t="n">
-        <v>34.52246247818044</v>
+        <v>34.52246246837511</v>
       </c>
       <c r="CD19" t="n">
-        <v>18.86931527289594</v>
+        <v>18.86931521865155</v>
       </c>
       <c r="CE19" t="n">
         <v>31.49264348607277</v>
       </c>
       <c r="CF19" t="n">
-        <v>31.77521537165577</v>
+        <v>31.77521537783029</v>
       </c>
       <c r="CG19" t="n">
-        <v>34.52246247818044</v>
+        <v>34.52246246837511</v>
       </c>
       <c r="CH19" t="n">
-        <v>31.07021623036239</v>
+        <v>31.0702162215376</v>
       </c>
       <c r="CI19" t="n">
         <v>7</v>
@@ -16156,10 +16148,10 @@
         <v>3.9</v>
       </c>
       <c r="CL19" t="n">
-        <v>77.24024536993845</v>
+        <v>77.24024531959736</v>
       </c>
       <c r="CM19" t="n">
-        <v>81.26191743884171</v>
+        <v>81.26191747406433</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -16198,7 +16190,7 @@
         <v>-5.040678244190966</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-23.22124503926587</v>
+        <v>-23.2212515115939</v>
       </c>
       <c r="DA19" t="b">
         <v>1</v>
@@ -16442,10 +16434,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="BX20" t="n">
-        <v>10.37863327533605</v>
+        <v>10.37863322903966</v>
       </c>
       <c r="BY20" t="n">
-        <v>19.25236472574838</v>
+        <v>19.25236463986857</v>
       </c>
       <c r="BZ20" t="n">
         <v>25.85122324877091</v>
@@ -16454,25 +16446,25 @@
         <v>18.56165831752405</v>
       </c>
       <c r="CB20" t="n">
-        <v>39.76450197392393</v>
+        <v>39.76450201325112</v>
       </c>
       <c r="CC20" t="n">
-        <v>24.31404882939119</v>
+        <v>24.31404884830175</v>
       </c>
       <c r="CD20" t="n">
-        <v>13.00688748824112</v>
+        <v>13.00688758968578</v>
       </c>
       <c r="CE20" t="n">
         <v>10.35999965667725</v>
       </c>
       <c r="CF20" t="n">
-        <v>20.18616468945161</v>
+        <v>20.18616469288988</v>
       </c>
       <c r="CG20" t="n">
-        <v>18.90701152163621</v>
+        <v>18.9070114786963</v>
       </c>
       <c r="CH20" t="n">
-        <v>17.01631036947259</v>
+        <v>17.01631033082667</v>
       </c>
       <c r="CI20" t="n">
         <v>8</v>
@@ -16484,10 +16476,10 @@
         <v>3.8</v>
       </c>
       <c r="CL20" t="n">
-        <v>64.25010553456157</v>
+        <v>64.25010516153145</v>
       </c>
       <c r="CM20" t="n">
-        <v>94.84715596917211</v>
+        <v>94.84715600236007</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -16770,10 +16762,10 @@
         <v>11.28999996185303</v>
       </c>
       <c r="BX21" t="n">
-        <v>9.774107176349089</v>
+        <v>9.774107152415171</v>
       </c>
       <c r="BY21" t="n">
-        <v>18.13096881212756</v>
+        <v>18.13096876773014</v>
       </c>
       <c r="BZ21" t="n">
         <v>23.1209427348613</v>
@@ -16782,25 +16774,25 @@
         <v>13.6472321924953</v>
       </c>
       <c r="CB21" t="n">
-        <v>35.00095079985264</v>
+        <v>35.00095087130416</v>
       </c>
       <c r="CC21" t="n">
-        <v>25.51476115415504</v>
+        <v>25.51476117084985</v>
       </c>
       <c r="CD21" t="n">
-        <v>13.36818424804047</v>
+        <v>13.36818432550593</v>
       </c>
       <c r="CE21" t="n">
         <v>9.880299501333878</v>
       </c>
       <c r="CF21" t="n">
-        <v>18.55468082740191</v>
+        <v>18.55468083956197</v>
       </c>
       <c r="CG21" t="n">
-        <v>15.88910050231143</v>
+        <v>15.88910048011272</v>
       </c>
       <c r="CH21" t="n">
-        <v>14.30019045208029</v>
+        <v>14.30019043210145</v>
       </c>
       <c r="CI21" t="n">
         <v>8</v>
@@ -16812,10 +16804,10 @@
         <v>3.6</v>
       </c>
       <c r="CL21" t="n">
-        <v>26.66244907350024</v>
+        <v>26.66244889653975</v>
       </c>
       <c r="CM21" t="n">
-        <v>64.34615491669614</v>
+        <v>64.34615502440258</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -17100,10 +17092,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="BX22" t="n">
-        <v>5.044350378841198</v>
+        <v>5.044350332854253</v>
       </c>
       <c r="BY22" t="n">
-        <v>9.357269952750423</v>
+        <v>9.357269867444639</v>
       </c>
       <c r="BZ22" t="n">
         <v>8.453839145587175</v>
@@ -17174,7 +17166,7 @@
         <v>-2.887864672525231</v>
       </c>
       <c r="CZ22" t="n">
-        <v>-28.51676265378231</v>
+        <v>-28.51675560376472</v>
       </c>
       <c r="DA22" t="b">
         <v>1</v>
@@ -17418,37 +17410,37 @@
         <v>35.20000076293945</v>
       </c>
       <c r="BX23" t="n">
-        <v>25.31139909513731</v>
+        <v>25.31139904667668</v>
       </c>
       <c r="BY23" t="n">
-        <v>31.13019014506065</v>
+        <v>31.13019021765763</v>
       </c>
       <c r="BZ23" t="n">
-        <v>34.28259763099602</v>
+        <v>34.28259777658124</v>
       </c>
       <c r="CA23" t="n">
         <v>36.6578293511453</v>
       </c>
       <c r="CB23" t="n">
-        <v>48.45442996274987</v>
+        <v>48.45443006087749</v>
       </c>
       <c r="CC23" t="n">
-        <v>48.46302884639316</v>
+        <v>48.46302886742595</v>
       </c>
       <c r="CD23" t="n">
-        <v>16.1881096985766</v>
+        <v>16.18810980753548</v>
       </c>
       <c r="CE23" t="n">
         <v>30.16806884283779</v>
       </c>
       <c r="CF23" t="n">
-        <v>33.83195669661208</v>
+        <v>33.83195674634219</v>
       </c>
       <c r="CG23" t="n">
-        <v>32.70639388802834</v>
+        <v>32.70639399711943</v>
       </c>
       <c r="CH23" t="n">
-        <v>29.4357544992255</v>
+        <v>29.43575459740749</v>
       </c>
       <c r="CI23" t="n">
         <v>8</v>
@@ -17460,10 +17452,10 @@
         <v>3</v>
       </c>
       <c r="CL23" t="n">
-        <v>-16.37569925789</v>
+        <v>-16.3756989789639</v>
       </c>
       <c r="CM23" t="n">
-        <v>-3.886488740556293</v>
+        <v>-3.886488599277571</v>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
@@ -17746,10 +17738,10 @@
         <v>11.07999992370605</v>
       </c>
       <c r="BX24" t="n">
-        <v>3.454302382804934</v>
+        <v>3.454302376618553</v>
       </c>
       <c r="BY24" t="n">
-        <v>6.407730920103153</v>
+        <v>6.407730908627417</v>
       </c>
       <c r="BZ24" t="n">
         <v>20.4470750681205</v>
@@ -17758,13 +17750,13 @@
         <v>19.3263652032129</v>
       </c>
       <c r="CB24" t="n">
-        <v>22.00385754004261</v>
+        <v>22.00385754046043</v>
       </c>
       <c r="CC24" t="n">
-        <v>16.46863777196926</v>
+        <v>16.46863777318124</v>
       </c>
       <c r="CD24" t="n">
-        <v>13.71979385590022</v>
+        <v>13.71979386374505</v>
       </c>
       <c r="CE24" t="n">
         <v>30.3956356510297</v>
@@ -17820,7 +17812,7 @@
         <v>-18.94659940111765</v>
       </c>
       <c r="CZ24" t="n">
-        <v>-32.89648038436899</v>
+        <v>-32.89648837260555</v>
       </c>
       <c r="DA24" t="b">
         <v>1</v>
@@ -18064,10 +18056,10 @@
         <v>14.13000011444092</v>
       </c>
       <c r="BX25" t="n">
-        <v>4.339755634897887</v>
+        <v>4.339755630381581</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.050246702735581</v>
+        <v>8.050246694357833</v>
       </c>
       <c r="BZ25" t="n">
         <v>24.63453967320291</v>
@@ -18076,25 +18068,25 @@
         <v>20.77142752850562</v>
       </c>
       <c r="CB25" t="n">
-        <v>30.61150737332451</v>
+        <v>30.61150737643035</v>
       </c>
       <c r="CC25" t="n">
-        <v>16.75489077818667</v>
+        <v>16.75489077910463</v>
       </c>
       <c r="CD25" t="n">
-        <v>19.18328687207345</v>
+        <v>19.18328687925509</v>
       </c>
       <c r="CE25" t="n">
         <v>14.37360703573516</v>
       </c>
       <c r="CF25" t="n">
-        <v>19.1970722805377</v>
+        <v>19.19707228094165</v>
       </c>
       <c r="CG25" t="n">
-        <v>19.18328687207345</v>
+        <v>19.18328687925509</v>
       </c>
       <c r="CH25" t="n">
-        <v>17.2649581848661</v>
+        <v>17.26495819132958</v>
       </c>
       <c r="CI25" t="n">
         <v>7</v>
@@ -18106,10 +18098,10 @@
         <v>7.1</v>
       </c>
       <c r="CL25" t="n">
-        <v>22.1865395968486</v>
+        <v>22.18653964259154</v>
       </c>
       <c r="CM25" t="n">
-        <v>35.86038305065695</v>
+        <v>35.86038305351582</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -18702,10 +18694,10 @@
         <v>13.23999977111816</v>
       </c>
       <c r="BX27" t="n">
-        <v>8.302142143832688</v>
+        <v>8.302142152710502</v>
       </c>
       <c r="BY27" t="n">
-        <v>15.40047367680963</v>
+        <v>15.40047369327798</v>
       </c>
       <c r="BZ27" t="n">
         <v>14.18189142823894</v>
@@ -18726,7 +18718,7 @@
         <v>6.364116594565261</v>
       </c>
       <c r="CF27" t="n">
-        <v>11.29369907549064</v>
+        <v>11.29369907911152</v>
       </c>
       <c r="CG27" t="n">
         <v>11.52626939957729</v>
@@ -18747,7 +18739,7 @@
         <v>-21.64922478134251</v>
       </c>
       <c r="CM27" t="n">
-        <v>-14.70015656550992</v>
+        <v>-14.70015653816189</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -19030,10 +19022,10 @@
         <v>27.52000045776367</v>
       </c>
       <c r="BX28" t="n">
-        <v>7.290978493448117</v>
+        <v>7.290978511925755</v>
       </c>
       <c r="BY28" t="n">
-        <v>13.52476510534626</v>
+        <v>13.52476513962228</v>
       </c>
       <c r="BZ28" t="n">
         <v>36.57372177185242</v>
@@ -19042,19 +19034,19 @@
         <v>28.87454744278962</v>
       </c>
       <c r="CB28" t="n">
-        <v>45.93352495810291</v>
+        <v>45.93352493096688</v>
       </c>
       <c r="CC28" t="n">
-        <v>26.49482250355711</v>
+        <v>26.49482249904537</v>
       </c>
       <c r="CD28" t="n">
-        <v>29.81102745702587</v>
+        <v>29.81102742365968</v>
       </c>
       <c r="CE28" t="n">
         <v>24.2620728130642</v>
       </c>
       <c r="CF28" t="n">
-        <v>29.35349743596263</v>
+        <v>29.35349743157149</v>
       </c>
       <c r="CG28" t="n">
         <v>28.87454744278962</v>
@@ -19075,7 +19067,7 @@
         <v>-5.570158916260349</v>
       </c>
       <c r="CM28" t="n">
-        <v>6.662416234378021</v>
+        <v>6.662416218421874</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -19358,10 +19350,10 @@
         <v>22.06999969482422</v>
       </c>
       <c r="BX29" t="n">
-        <v>3.108072443831099</v>
+        <v>3.108072450041836</v>
       </c>
       <c r="BY29" t="n">
-        <v>5.765474383306688</v>
+        <v>5.765474394827605</v>
       </c>
       <c r="BZ29" t="n">
         <v>33.57376532220675</v>
@@ -19370,7 +19362,7 @@
         <v>28.04300293143303</v>
       </c>
       <c r="CB29" t="n">
-        <v>43.00378985487929</v>
+        <v>43.00378986486211</v>
       </c>
       <c r="CC29" t="n">
         <v>10.85340539909456</v>
@@ -19656,10 +19648,10 @@
         <v>38.90000152587891</v>
       </c>
       <c r="BX30" t="n">
-        <v>35.62892557839169</v>
+        <v>35.62892548976458</v>
       </c>
       <c r="BY30" t="n">
-        <v>51.87571564213831</v>
+        <v>51.87571551309724</v>
       </c>
       <c r="BZ30" t="n">
         <v>50.25590259243982</v>
@@ -19676,13 +19668,13 @@
       </c>
       <c r="CE30" t="inlineStr"/>
       <c r="CF30" t="n">
-        <v>49.31617719919689</v>
+        <v>49.31617714477984</v>
       </c>
       <c r="CG30" t="n">
-        <v>51.06580911728906</v>
+        <v>51.06580905276853</v>
       </c>
       <c r="CH30" t="n">
-        <v>45.95922820556016</v>
+        <v>45.95922814749168</v>
       </c>
       <c r="CI30" t="n">
         <v>4</v>
@@ -19694,10 +19686,10 @@
         <v>1.7</v>
       </c>
       <c r="CL30" t="n">
-        <v>18.14711157526556</v>
+        <v>18.14711142598928</v>
       </c>
       <c r="CM30" t="n">
-        <v>26.77680016641757</v>
+        <v>26.776800026528</v>
       </c>
       <c r="CN30" t="inlineStr">
         <is>
@@ -19980,10 +19972,10 @@
         <v>24.72999954223633</v>
       </c>
       <c r="BX31" t="n">
-        <v>12.83053369544166</v>
+        <v>12.8305336720007</v>
       </c>
       <c r="BY31" t="n">
-        <v>23.80064000504428</v>
+        <v>23.80063996156129</v>
       </c>
       <c r="BZ31" t="n">
         <v>61.59257404786302</v>
@@ -19992,13 +19984,13 @@
         <v>51.63850781741169</v>
       </c>
       <c r="CB31" t="n">
-        <v>85.84612579958544</v>
+        <v>85.84612579782318</v>
       </c>
       <c r="CC31" t="n">
-        <v>33.66425527180574</v>
+        <v>33.66425527570821</v>
       </c>
       <c r="CD31" t="n">
-        <v>45.15510817715654</v>
+        <v>45.15510821482336</v>
       </c>
       <c r="CE31" t="n">
         <v>5.142038558436727</v>
@@ -20294,10 +20286,10 @@
         <v>12.02999973297119</v>
       </c>
       <c r="BX32" t="n">
-        <v>2.08001751083452</v>
+        <v>2.080017508669553</v>
       </c>
       <c r="BY32" t="n">
-        <v>3.858432482598035</v>
+        <v>3.858432478582021</v>
       </c>
       <c r="BZ32" t="n">
         <v>28.61714478669089</v>
@@ -20306,7 +20298,7 @@
         <v>24.30030260991828</v>
       </c>
       <c r="CB32" t="n">
-        <v>37.62481887724437</v>
+        <v>37.6248188718028</v>
       </c>
       <c r="CC32" t="n">
         <v>9.158754146</v>
@@ -20608,10 +20600,10 @@
         <v>33.43000030517578</v>
       </c>
       <c r="BX33" t="n">
-        <v>7.930922164176469</v>
+        <v>7.930922167268104</v>
       </c>
       <c r="BY33" t="n">
-        <v>14.71186061454735</v>
+        <v>14.71186062028233</v>
       </c>
       <c r="BZ33" t="n">
         <v>67.41971142215816</v>
@@ -20620,7 +20612,7 @@
         <v>39.36375120302754</v>
       </c>
       <c r="CB33" t="n">
-        <v>93.22418795678955</v>
+        <v>93.2241879633775</v>
       </c>
       <c r="CC33" t="n">
         <v>22.51480113099953</v>
@@ -20908,35 +20900,35 @@
         <v>23.04999923706055</v>
       </c>
       <c r="BX34" t="n">
-        <v>16.5437661860459</v>
+        <v>16.54376621964911</v>
       </c>
       <c r="BY34" t="n">
-        <v>30.07147189023322</v>
+        <v>30.07147188512531</v>
       </c>
       <c r="BZ34" t="n">
-        <v>51.50946623039919</v>
+        <v>51.50946611702533</v>
       </c>
       <c r="CA34" t="n">
         <v>50.09186275696137</v>
       </c>
       <c r="CB34" t="n">
-        <v>63.06344046374193</v>
+        <v>63.063440478616</v>
       </c>
       <c r="CC34" t="n">
-        <v>45.81097523549202</v>
+        <v>45.81097522828131</v>
       </c>
       <c r="CD34" t="n">
-        <v>25.18054538204336</v>
+        <v>25.18054534049634</v>
       </c>
       <c r="CE34" t="inlineStr"/>
       <c r="CF34" t="n">
-        <v>35.98391988554259</v>
+        <v>35.98391986252027</v>
       </c>
       <c r="CG34" t="n">
-        <v>37.94122356286262</v>
+        <v>37.94122355670331</v>
       </c>
       <c r="CH34" t="n">
-        <v>34.14710120657637</v>
+        <v>34.14710120103297</v>
       </c>
       <c r="CI34" t="n">
         <v>4</v>
@@ -20948,10 +20940,10 @@
         <v>3.1</v>
       </c>
       <c r="CL34" t="n">
-        <v>48.14361100573718</v>
+        <v>48.14361098168776</v>
       </c>
       <c r="CM34" t="n">
-        <v>56.11245586371414</v>
+        <v>56.11245576383419</v>
       </c>
       <c r="CN34" t="inlineStr">
         <is>
@@ -21230,10 +21222,10 @@
         <v>32.75</v>
       </c>
       <c r="BX35" t="n">
-        <v>3.249356697068481</v>
+        <v>3.249356690606488</v>
       </c>
       <c r="BY35" t="n">
-        <v>6.027556673062032</v>
+        <v>6.027556661075034</v>
       </c>
       <c r="BZ35" t="n">
         <v>33.45701619121048</v>
@@ -21242,7 +21234,7 @@
         <v>23.42786572511178</v>
       </c>
       <c r="CB35" t="n">
-        <v>41.38326860130753</v>
+        <v>41.38326859433236</v>
       </c>
       <c r="CC35" t="n">
         <v>10.59424454785779</v>
@@ -21556,10 +21548,10 @@
         <v>33.65000152587891</v>
       </c>
       <c r="BX36" t="n">
-        <v>15.2468868650438</v>
+        <v>15.24688680545705</v>
       </c>
       <c r="BY36" t="n">
-        <v>28.28297513465624</v>
+        <v>28.28297502412283</v>
       </c>
       <c r="BZ36" t="n">
         <v>20.22969692458691</v>
@@ -21568,7 +21560,7 @@
         <v>37.31912959637818</v>
       </c>
       <c r="CB36" t="n">
-        <v>27.24280551988296</v>
+        <v>27.24280548203295</v>
       </c>
       <c r="CC36" t="n">
         <v>15.03391666666667</v>
@@ -21580,7 +21572,7 @@
         <v>77.67169119949854</v>
       </c>
       <c r="CF36" t="n">
-        <v>22.63863279163349</v>
+        <v>22.63863276192346</v>
       </c>
       <c r="CG36" t="n">
         <v>20.22969692458691</v>
@@ -21601,7 +21593,7 @@
         <v>-45.89382940108894</v>
       </c>
       <c r="CM36" t="n">
-        <v>-32.72323398195689</v>
+        <v>-32.72323407024821</v>
       </c>
       <c r="CN36" t="inlineStr">
         <is>
@@ -21860,10 +21852,10 @@
         <v>14.77999973297119</v>
       </c>
       <c r="BX37" t="n">
-        <v>9.186484878581913</v>
+        <v>9.186484929091723</v>
       </c>
       <c r="BY37" t="n">
-        <v>17.04092944976945</v>
+        <v>17.04092954346514</v>
       </c>
       <c r="BZ37" t="n">
         <v>31.89495056382219</v>
@@ -21872,23 +21864,23 @@
         <v>30.33345456974609</v>
       </c>
       <c r="CB37" t="n">
-        <v>36.78693478697259</v>
+        <v>36.78693480222304</v>
       </c>
       <c r="CC37" t="n">
-        <v>25.58128745942417</v>
+        <v>25.58128744946131</v>
       </c>
       <c r="CD37" t="n">
-        <v>16.38749084901738</v>
+        <v>16.38749078621147</v>
       </c>
       <c r="CE37" t="inlineStr"/>
       <c r="CF37" t="n">
-        <v>20.92591308789943</v>
+        <v>20.92591312146009</v>
       </c>
       <c r="CG37" t="n">
-        <v>21.31110845459681</v>
+        <v>21.31110849646323</v>
       </c>
       <c r="CH37" t="n">
-        <v>19.17999760913713</v>
+        <v>19.1799976468169</v>
       </c>
       <c r="CI37" t="n">
         <v>4</v>
@@ -21900,10 +21892,10 @@
         <v>3.5</v>
       </c>
       <c r="CL37" t="n">
-        <v>29.7699455728029</v>
+        <v>29.76994582774049</v>
       </c>
       <c r="CM37" t="n">
-        <v>41.58263508772568</v>
+        <v>41.58263531479373</v>
       </c>
       <c r="CN37" t="inlineStr">
         <is>
@@ -22166,35 +22158,35 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BX38" t="n">
-        <v>8.627042072234111</v>
+        <v>8.627042103431171</v>
       </c>
       <c r="BY38" t="n">
-        <v>14.34730902416064</v>
+        <v>14.3473089857313</v>
       </c>
       <c r="BZ38" t="n">
-        <v>19.54486196556696</v>
+        <v>19.54486184253791</v>
       </c>
       <c r="CA38" t="n">
         <v>17.74926644976348</v>
       </c>
       <c r="CB38" t="n">
-        <v>23.93539530781762</v>
+        <v>23.93539527918414</v>
       </c>
       <c r="CC38" t="n">
-        <v>17.38495029677088</v>
+        <v>17.38495028827388</v>
       </c>
       <c r="CD38" t="n">
-        <v>9.719867200323893</v>
+        <v>9.719867147174087</v>
       </c>
       <c r="CE38" t="inlineStr"/>
       <c r="CF38" t="n">
-        <v>14.97604083968315</v>
+        <v>14.97604080499356</v>
       </c>
       <c r="CG38" t="n">
-        <v>15.86612966046576</v>
+        <v>15.86612963700259</v>
       </c>
       <c r="CH38" t="n">
-        <v>14.27951669441919</v>
+        <v>14.27951667330233</v>
       </c>
       <c r="CI38" t="n">
         <v>4</v>
@@ -22206,10 +22198,10 @@
         <v>2.3</v>
       </c>
       <c r="CL38" t="n">
-        <v>11.12464023744999</v>
+        <v>11.12464007311649</v>
       </c>
       <c r="CM38" t="n">
-        <v>16.54506144045931</v>
+        <v>16.54506117050147</v>
       </c>
       <c r="CN38" t="inlineStr">
         <is>
@@ -22321,7 +22313,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -22492,10 +22484,10 @@
         <v>5.880000114440918</v>
       </c>
       <c r="BX39" t="n">
-        <v>6.975750786425684</v>
+        <v>6.975750828113066</v>
       </c>
       <c r="BY39" t="n">
-        <v>12.94001770881964</v>
+        <v>12.94001778614973</v>
       </c>
       <c r="BZ39" t="n">
         <v>5.605036080312384</v>
@@ -22516,7 +22508,7 @@
         <v>5.348622529323849</v>
       </c>
       <c r="CF39" t="n">
-        <v>7.296291356627144</v>
+        <v>7.296291371504328</v>
       </c>
       <c r="CG39" t="n">
         <v>5.869184706822859</v>
@@ -22537,7 +22529,7 @@
         <v>-10.16554195011574</v>
       </c>
       <c r="CM39" t="n">
-        <v>24.08658528267544</v>
+        <v>24.08658553568879</v>
       </c>
       <c r="CN39" t="inlineStr">
         <is>
@@ -22554,16 +22546,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="CQ39" t="inlineStr">
-        <is>
-          <t>A CSN Mineração (CMIN3) apresenta uma notável eficiência operacional, com um ROE de 31,8% e um ROIC de 20,3% que se posicionam muito acima dos pares do setor de materiais (8,4% e 8,7%, respectivamente), sugerindo uma forte capacidade de geração de valor sobre o capital empregado. No entanto, essa elevada qualidade operacional convive com múltiplos de preço esticados, visto que o P/L de 13,9 e o P/VP de 4,42 indicam que o mercado já cobra um prêmio considerável pelo papel, embora o PEG de 0,15 aponte que esse preço está desalinhado positivamente com o crescimento projetado. No âmbito financeiro, a excelente rentabilidade é acompanhada por um endividamento sob controle, evidenciado pela relação Dívida Líquida/EBITDA de apenas 0,2, patamar substancialmente abaixo da média do setor de 2,17, o que confere segurança financeira mesmo com uma relação Dívida/Patrimônio de 1,24. Essa estrutura de capital robusta e a forte geração de caixa dão sustentabilidade ao expressivo dividend yield de 18,25%, o qual se mostra coerente com o lucro e com a saúde do balanço, posicionando a empresa como uma forte pagadora de proventos. O crescimento histórico da companhia também é um destaque, com um CAGR de receita nos últimos cinco anos de 90,7%, superando com folga a média setorial de 17,7%, o que se reflete no checklist de critérios fundamentalistas, onde a empresa atende a expressivos 7 de 8 requisitos analisados. Sob a ótica do valuation, os métodos de preço-teto revelam uma dispersão acentuada entre as premissas, variando desde os conservadores R$ 3,56 de Graham e R$ 5,61 do fluxo de caixa descontado até os otimistas R$ 12,94 de Gordon e R$ 12,69 de Lynch. Essa disparidade resulta em uma média de R$ 7,30 e uma mediana de R$ 5,87, sendo que o preço-teto ajustado com margem de segurança fica em R$ 5,28, o que gera um upside negativo de 10,2% em relação à cotação atual de R$ 5,88. Em suma, os principais prós do ativo residem em sua rentabilidade excepcional, endividamento muito abaixo dos pares, forte crescimento histórico e proventos altamente atrativos, enquanto os contras concentram-se no valuation esticado frente ao preço-teto ajustado, na margem líquida abaixo de 15% e em uma tendência gráfica lateralizada que exige cautela do investidor.</t>
-        </is>
-      </c>
-      <c r="CR39" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
+      <c r="CQ39" t="inlineStr"/>
+      <c r="CR39" t="inlineStr"/>
       <c r="CS39" t="b">
         <v>0</v>
       </c>
@@ -22590,14 +22574,14 @@
         <v>1</v>
       </c>
       <c r="DB39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD39" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$4.78 (candidato)</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -22810,10 +22794,10 @@
         <v>39.43999862670898</v>
       </c>
       <c r="BX40" t="n">
-        <v>20.1612756175048</v>
+        <v>20.16127568549079</v>
       </c>
       <c r="BY40" t="n">
-        <v>37.3991662704714</v>
+        <v>37.39916639658541</v>
       </c>
       <c r="BZ40" t="n">
         <v>57.05021635413689</v>
@@ -22822,23 +22806,23 @@
         <v>43.06721646336476</v>
       </c>
       <c r="CB40" t="n">
-        <v>64.10972949124397</v>
+        <v>64.10972938147273</v>
       </c>
       <c r="CC40" t="n">
-        <v>45.28400693591092</v>
+        <v>45.28400691505072</v>
       </c>
       <c r="CD40" t="n">
-        <v>32.43094094972332</v>
+        <v>32.43094081541021</v>
       </c>
       <c r="CE40" t="inlineStr"/>
       <c r="CF40" t="n">
-        <v>39.973666294506</v>
+        <v>39.97366633781595</v>
       </c>
       <c r="CG40" t="n">
-        <v>41.34158660319116</v>
+        <v>41.34158665581806</v>
       </c>
       <c r="CH40" t="n">
-        <v>37.20742794287204</v>
+        <v>37.20742799023625</v>
       </c>
       <c r="CI40" t="n">
         <v>4</v>
@@ -22850,10 +22834,10 @@
         <v>2.8</v>
       </c>
       <c r="CL40" t="n">
-        <v>-5.6606763731605</v>
+        <v>-5.660676253068686</v>
       </c>
       <c r="CM40" t="n">
-        <v>1.353112795079103</v>
+        <v>1.353112904891329</v>
       </c>
       <c r="CN40" t="inlineStr">
         <is>
@@ -23136,37 +23120,37 @@
         <v>26.45999908447266</v>
       </c>
       <c r="BX41" t="n">
-        <v>16.91893502410094</v>
+        <v>16.9189349966709</v>
       </c>
       <c r="BY41" t="n">
-        <v>28.67982835307078</v>
+        <v>28.67982834944448</v>
       </c>
       <c r="BZ41" t="n">
-        <v>49.21350829686259</v>
+        <v>49.213508370428</v>
       </c>
       <c r="CA41" t="n">
         <v>53.99475108321082</v>
       </c>
       <c r="CB41" t="n">
-        <v>57.93925173409952</v>
+        <v>57.93925172391921</v>
       </c>
       <c r="CC41" t="n">
-        <v>43.01388444492227</v>
+        <v>43.01388444982749</v>
       </c>
       <c r="CD41" t="n">
-        <v>24.40657257113381</v>
+        <v>24.40657260181376</v>
       </c>
       <c r="CE41" t="n">
         <v>30.06721996094383</v>
       </c>
       <c r="CF41" t="n">
-        <v>38.02924393354307</v>
+        <v>38.02924394203231</v>
       </c>
       <c r="CG41" t="n">
-        <v>36.54055220293305</v>
+        <v>36.54055220538566</v>
       </c>
       <c r="CH41" t="n">
-        <v>32.88649698263975</v>
+        <v>32.88649698484709</v>
       </c>
       <c r="CI41" t="n">
         <v>8</v>
@@ -23178,10 +23162,10 @@
         <v>3.4</v>
       </c>
       <c r="CL41" t="n">
-        <v>24.2875968273873</v>
+        <v>24.2875968357295</v>
       </c>
       <c r="CM41" t="n">
-        <v>43.7235270195437</v>
+        <v>43.72352705162699</v>
       </c>
       <c r="CN41" t="inlineStr">
         <is>
@@ -23464,10 +23448,10 @@
         <v>11.76000022888184</v>
       </c>
       <c r="BX42" t="n">
-        <v>4.779815359277475</v>
+        <v>4.779815379034154</v>
       </c>
       <c r="BY42" t="n">
-        <v>8.866557491459718</v>
+        <v>8.866557528108356</v>
       </c>
       <c r="BZ42" t="n">
         <v>27.09913096220597</v>
@@ -23476,25 +23460,25 @@
         <v>30.54574135914352</v>
       </c>
       <c r="CB42" t="n">
-        <v>25.60465060977719</v>
+        <v>25.60465062980617</v>
       </c>
       <c r="CC42" t="n">
-        <v>14.19260757054379</v>
+        <v>14.19260756872015</v>
       </c>
       <c r="CD42" t="n">
-        <v>14.24280841182511</v>
+        <v>14.24280839417845</v>
       </c>
       <c r="CE42" t="n">
         <v>5.07221344413531</v>
       </c>
       <c r="CF42" t="n">
-        <v>20.09191606749255</v>
+        <v>20.09191607369377</v>
       </c>
       <c r="CG42" t="n">
-        <v>19.92372951080115</v>
+        <v>19.92372951199231</v>
       </c>
       <c r="CH42" t="n">
-        <v>17.93135655972104</v>
+        <v>17.93135656079308</v>
       </c>
       <c r="CI42" t="n">
         <v>6</v>
@@ -23506,10 +23490,10 @@
         <v>6.4</v>
       </c>
       <c r="CL42" t="n">
-        <v>52.47751879870488</v>
+        <v>52.47751880782088</v>
       </c>
       <c r="CM42" t="n">
-        <v>70.8496230990544</v>
+        <v>70.84962315178585</v>
       </c>
       <c r="CN42" t="inlineStr">
         <is>
@@ -23548,7 +23532,7 @@
         <v>4.347823879462331</v>
       </c>
       <c r="CZ42" t="n">
-        <v>-28.48248018644097</v>
+        <v>-28.48247563627588</v>
       </c>
       <c r="DA42" t="b">
         <v>0</v>
@@ -23792,37 +23776,37 @@
         <v>15.3100004196167</v>
       </c>
       <c r="BX43" t="n">
-        <v>5.939526957524716</v>
+        <v>5.939526977006997</v>
       </c>
       <c r="BY43" t="n">
-        <v>8.534880613439464</v>
+        <v>8.534880597355141</v>
       </c>
       <c r="BZ43" t="n">
-        <v>10.81501547960945</v>
+        <v>10.81501542375372</v>
       </c>
       <c r="CA43" t="n">
         <v>11.65944891202323</v>
       </c>
       <c r="CB43" t="n">
-        <v>9.810403824194951</v>
+        <v>9.810403792780233</v>
       </c>
       <c r="CC43" t="n">
-        <v>14.90925678315233</v>
+        <v>14.90925677631631</v>
       </c>
       <c r="CD43" t="n">
-        <v>5.384140050651277</v>
+        <v>5.384140019105566</v>
       </c>
       <c r="CE43" t="n">
         <v>10.69689722735973</v>
       </c>
       <c r="CF43" t="n">
-        <v>9.718696230994393</v>
+        <v>9.718696215712617</v>
       </c>
       <c r="CG43" t="n">
-        <v>10.25365052577734</v>
+        <v>10.25365051006998</v>
       </c>
       <c r="CH43" t="n">
-        <v>9.228285473199609</v>
+        <v>9.228285459062983</v>
       </c>
       <c r="CI43" t="n">
         <v>8</v>
@@ -23834,10 +23818,10 @@
         <v>2.8</v>
       </c>
       <c r="CL43" t="n">
-        <v>-39.72380652991093</v>
+        <v>-39.72380662224684</v>
       </c>
       <c r="CM43" t="n">
-        <v>-36.52060114549814</v>
+        <v>-36.52060124531379</v>
       </c>
       <c r="CN43" t="inlineStr">
         <is>
@@ -24120,10 +24104,10 @@
         <v>9.25</v>
       </c>
       <c r="BX44" t="n">
-        <v>2.521670910160942</v>
+        <v>2.521670926637602</v>
       </c>
       <c r="BY44" t="n">
-        <v>4.677699538348548</v>
+        <v>4.677699568912752</v>
       </c>
       <c r="BZ44" t="n">
         <v>13.66360089186176</v>
@@ -24132,19 +24116,19 @@
         <v>15.44242552617786</v>
       </c>
       <c r="CB44" t="n">
-        <v>10.73109422139046</v>
+        <v>10.73109422399308</v>
       </c>
       <c r="CC44" t="n">
-        <v>7.312738778525191</v>
+        <v>7.31273877698746</v>
       </c>
       <c r="CD44" t="n">
-        <v>7.026196825353156</v>
+        <v>7.026196810824699</v>
       </c>
       <c r="CE44" t="n">
         <v>10.33342380121613</v>
       </c>
       <c r="CF44" t="n">
-        <v>9.883882797553301</v>
+        <v>9.883882799996249</v>
       </c>
       <c r="CG44" t="n">
         <v>10.33342380121613</v>
@@ -24165,7 +24149,7 @@
         <v>0.5414207685893846</v>
       </c>
       <c r="CM44" t="n">
-        <v>6.852787000576233</v>
+        <v>6.852787026986462</v>
       </c>
       <c r="CN44" t="inlineStr">
         <is>
@@ -24446,10 +24430,10 @@
         <v>6.400000095367432</v>
       </c>
       <c r="BX45" t="n">
-        <v>7.59659094360428</v>
+        <v>7.596590879773317</v>
       </c>
       <c r="BY45" t="n">
-        <v>11.06063641388783</v>
+        <v>11.06063632094995</v>
       </c>
       <c r="BZ45" t="n">
         <v>8.29925199399268</v>
@@ -24468,7 +24452,7 @@
         <v>5.369614780864673</v>
       </c>
       <c r="CF45" t="n">
-        <v>8.37170326954211</v>
+        <v>8.371703243413968</v>
       </c>
       <c r="CG45" t="n">
         <v>8.587865965618855</v>
@@ -24489,7 +24473,7 @@
         <v>20.76686334194866</v>
       </c>
       <c r="CM45" t="n">
-        <v>30.80786163740643</v>
+        <v>30.80786122915422</v>
       </c>
       <c r="CN45" t="inlineStr">
         <is>
@@ -24772,37 +24756,37 @@
         <v>38.86000061035156</v>
       </c>
       <c r="BX46" t="n">
-        <v>30.97422553314541</v>
+        <v>30.97422549754169</v>
       </c>
       <c r="BY46" t="n">
-        <v>37.33904013124479</v>
+        <v>37.3390401610258</v>
       </c>
       <c r="BZ46" t="n">
-        <v>41.77389246890377</v>
+        <v>41.77389255023949</v>
       </c>
       <c r="CA46" t="n">
         <v>51.32924379406393</v>
       </c>
       <c r="CB46" t="n">
-        <v>64.51021348156419</v>
+        <v>64.51021351972372</v>
       </c>
       <c r="CC46" t="n">
-        <v>16.34210046821733</v>
+        <v>16.34210047152813</v>
       </c>
       <c r="CD46" t="n">
-        <v>19.48042950804467</v>
+        <v>19.48042957114587</v>
       </c>
       <c r="CE46" t="n">
         <v>27.99121924833823</v>
       </c>
       <c r="CF46" t="n">
-        <v>36.21754557919029</v>
+        <v>36.21754560170086</v>
       </c>
       <c r="CG46" t="n">
-        <v>34.1566328321951</v>
+        <v>34.15663282928374</v>
       </c>
       <c r="CH46" t="n">
-        <v>30.74096954897559</v>
+        <v>30.74096954635537</v>
       </c>
       <c r="CI46" t="n">
         <v>8</v>
@@ -24814,10 +24798,10 @@
         <v>3.9</v>
       </c>
       <c r="CL46" t="n">
-        <v>-20.89302865119672</v>
+        <v>-20.89302865793944</v>
       </c>
       <c r="CM46" t="n">
-        <v>-6.799935639881016</v>
+        <v>-6.799935581953642</v>
       </c>
       <c r="CN46" t="inlineStr">
         <is>
@@ -25078,35 +25062,35 @@
         <v>16.78000068664551</v>
       </c>
       <c r="BX47" t="n">
-        <v>9.985664037482243</v>
+        <v>9.985664095091371</v>
       </c>
       <c r="BY47" t="n">
-        <v>18.36675921097795</v>
+        <v>18.36675920107432</v>
       </c>
       <c r="BZ47" t="n">
-        <v>31.67453741556876</v>
+        <v>31.67453721575315</v>
       </c>
       <c r="CA47" t="n">
         <v>30.47653407949944</v>
       </c>
       <c r="CB47" t="n">
-        <v>34.39875972103142</v>
+        <v>34.39875972294948</v>
       </c>
       <c r="CC47" t="n">
-        <v>27.99338998062349</v>
+        <v>27.99338996813274</v>
       </c>
       <c r="CD47" t="n">
-        <v>15.43712491437256</v>
+        <v>15.43712484273907</v>
       </c>
       <c r="CE47" t="inlineStr"/>
       <c r="CF47" t="n">
-        <v>22.00508766116311</v>
+        <v>22.0050876200129</v>
       </c>
       <c r="CG47" t="n">
-        <v>23.18007459580072</v>
+        <v>23.18007458460353</v>
       </c>
       <c r="CH47" t="n">
-        <v>20.86206713622065</v>
+        <v>20.86206712614318</v>
       </c>
       <c r="CI47" t="n">
         <v>4</v>
@@ -25118,10 +25102,10 @@
         <v>3.2</v>
       </c>
       <c r="CL47" t="n">
-        <v>24.32697427017321</v>
+        <v>24.32697421011678</v>
       </c>
       <c r="CM47" t="n">
-        <v>31.13877688143378</v>
+        <v>31.13877663620011</v>
       </c>
       <c r="CN47" t="inlineStr">
         <is>
@@ -25400,10 +25384,10 @@
         <v>34.09000015258789</v>
       </c>
       <c r="BX48" t="n">
-        <v>14.76402953259265</v>
+        <v>14.76402957937178</v>
       </c>
       <c r="BY48" t="n">
-        <v>27.38727478295937</v>
+        <v>27.38727486973465</v>
       </c>
       <c r="BZ48" t="n">
         <v>56.25062291678574</v>
@@ -25412,25 +25396,25 @@
         <v>43.51071962247149</v>
       </c>
       <c r="CB48" t="n">
-        <v>72.55360783857934</v>
+        <v>72.5536077793973</v>
       </c>
       <c r="CC48" t="n">
-        <v>38.45081142924435</v>
+        <v>38.45081141776329</v>
       </c>
       <c r="CD48" t="n">
-        <v>40.76646247639871</v>
+        <v>40.76646238793377</v>
       </c>
       <c r="CE48" t="n">
         <v>21.06667845031192</v>
       </c>
       <c r="CF48" t="n">
-        <v>42.85516821667871</v>
+        <v>42.85516820634259</v>
       </c>
       <c r="CG48" t="n">
-        <v>40.76646247639871</v>
+        <v>40.76646238793377</v>
       </c>
       <c r="CH48" t="n">
-        <v>36.68981622875884</v>
+        <v>36.6898161491404</v>
       </c>
       <c r="CI48" t="n">
         <v>7</v>
@@ -25442,10 +25426,10 @@
         <v>4.9</v>
       </c>
       <c r="CL48" t="n">
-        <v>7.626330491446454</v>
+        <v>7.626330257892788</v>
       </c>
       <c r="CM48" t="n">
-        <v>25.71184518878749</v>
+        <v>25.7118451584674</v>
       </c>
       <c r="CN48" t="inlineStr">
         <is>
@@ -25724,37 +25708,37 @@
         <v>44.2400016784668</v>
       </c>
       <c r="BX49" t="n">
-        <v>32.08407771579532</v>
+        <v>32.08407778047199</v>
       </c>
       <c r="BY49" t="n">
-        <v>48.69139697039319</v>
+        <v>48.6913968229324</v>
       </c>
       <c r="BZ49" t="n">
-        <v>58.3415491316569</v>
+        <v>58.34154883736311</v>
       </c>
       <c r="CA49" t="n">
         <v>49.68675315451532</v>
       </c>
       <c r="CB49" t="n">
-        <v>78.17304702080875</v>
+        <v>78.17304689164709</v>
       </c>
       <c r="CC49" t="n">
-        <v>60.40706011937741</v>
+        <v>60.40706009364182</v>
       </c>
       <c r="CD49" t="n">
-        <v>29.16704220964456</v>
+        <v>29.16704205921701</v>
       </c>
       <c r="CE49" t="n">
         <v>77.58261943552711</v>
       </c>
       <c r="CF49" t="n">
-        <v>54.26669321971482</v>
+        <v>54.26669313441448</v>
       </c>
       <c r="CG49" t="n">
-        <v>54.01415114308611</v>
+        <v>54.01415099593922</v>
       </c>
       <c r="CH49" t="n">
-        <v>48.6127360287775</v>
+        <v>48.6127358963453</v>
       </c>
       <c r="CI49" t="n">
         <v>8</v>
@@ -25766,10 +25750,10 @@
         <v>2.7</v>
       </c>
       <c r="CL49" t="n">
-        <v>9.884118861684099</v>
+        <v>9.884118562334665</v>
       </c>
       <c r="CM49" t="n">
-        <v>22.66431094221315</v>
+        <v>22.66431074940043</v>
       </c>
       <c r="CN49" t="inlineStr">
         <is>
@@ -26048,10 +26032,10 @@
         <v>32.65999984741211</v>
       </c>
       <c r="BX50" t="n">
-        <v>11.0979993579001</v>
+        <v>11.0979994234726</v>
       </c>
       <c r="BY50" t="n">
-        <v>20.58678880890468</v>
+        <v>20.58678893054168</v>
       </c>
       <c r="BZ50" t="n">
         <v>56.94013131292242</v>
@@ -26060,19 +26044,19 @@
         <v>53.82541566292831</v>
       </c>
       <c r="CB50" t="n">
-        <v>59.89734832641072</v>
+        <v>59.89734831519161</v>
       </c>
       <c r="CC50" t="n">
-        <v>28.27275368887696</v>
+        <v>28.27275384797169</v>
       </c>
       <c r="CD50" t="n">
-        <v>36.27955948750253</v>
+        <v>36.27955940452447</v>
       </c>
       <c r="CE50" t="n">
         <v>53.57698797570033</v>
       </c>
       <c r="CF50" t="n">
-        <v>44.19699789474942</v>
+        <v>44.19699792139721</v>
       </c>
       <c r="CG50" t="n">
         <v>53.57698797570033</v>
@@ -26093,7 +26077,7 @@
         <v>47.64020025539306</v>
       </c>
       <c r="CM50" t="n">
-        <v>35.32455021812093</v>
+        <v>35.32455029971246</v>
       </c>
       <c r="CN50" t="inlineStr">
         <is>
@@ -26372,10 +26356,10 @@
         <v>12.96000003814697</v>
       </c>
       <c r="BX51" t="n">
-        <v>1.595679011519226</v>
+        <v>1.595679009295536</v>
       </c>
       <c r="BY51" t="n">
-        <v>2.959984566368163</v>
+        <v>2.959984562243219</v>
       </c>
       <c r="BZ51" t="n">
         <v>13.02883160132378</v>
@@ -26384,7 +26368,7 @@
         <v>9.525658668173282</v>
       </c>
       <c r="CB51" t="n">
-        <v>16.44457562469452</v>
+        <v>16.44457562233248</v>
       </c>
       <c r="CC51" t="n">
         <v>6.104046666666666</v>
@@ -26442,7 +26426,7 @@
         <v>-13.54235999978114</v>
       </c>
       <c r="CZ51" t="n">
-        <v>-28.70447669205222</v>
+        <v>-28.7044691786816</v>
       </c>
       <c r="DA51" t="b">
         <v>0</v>
@@ -26686,37 +26670,37 @@
         <v>10.59000015258789</v>
       </c>
       <c r="BX52" t="n">
-        <v>8.101227378904682</v>
+        <v>8.101227399746547</v>
       </c>
       <c r="BY52" t="n">
-        <v>11.55102779006567</v>
+        <v>11.55102779592079</v>
       </c>
       <c r="BZ52" t="n">
-        <v>17.45216307864644</v>
+        <v>17.45216304259397</v>
       </c>
       <c r="CA52" t="n">
         <v>24.15149214812595</v>
       </c>
       <c r="CB52" t="n">
-        <v>24.87656901471751</v>
+        <v>24.87656902907697</v>
       </c>
       <c r="CC52" t="n">
-        <v>21.04926982505205</v>
+        <v>21.04926982116424</v>
       </c>
       <c r="CD52" t="n">
-        <v>8.678711534005169</v>
+        <v>8.678711513353385</v>
       </c>
       <c r="CE52" t="n">
         <v>10.2336008131</v>
       </c>
       <c r="CF52" t="n">
-        <v>15.76175769782718</v>
+        <v>15.76175769538523</v>
       </c>
       <c r="CG52" t="n">
-        <v>14.50159543435606</v>
+        <v>14.50159541925738</v>
       </c>
       <c r="CH52" t="n">
-        <v>13.05143589092045</v>
+        <v>13.05143587733164</v>
       </c>
       <c r="CI52" t="n">
         <v>8</v>
@@ -26728,10 +26712,10 @@
         <v>3.1</v>
       </c>
       <c r="CL52" t="n">
-        <v>23.24301891280951</v>
+        <v>23.24301878449218</v>
       </c>
       <c r="CM52" t="n">
-        <v>48.83623673957609</v>
+        <v>48.83623671651706</v>
       </c>
       <c r="CN52" t="inlineStr">
         <is>
@@ -26996,10 +26980,10 @@
         <v>54.20000076293945</v>
       </c>
       <c r="BX53" t="n">
-        <v>10.59687587099957</v>
+        <v>10.59687587170016</v>
       </c>
       <c r="BY53" t="n">
-        <v>19.65720474070419</v>
+        <v>19.6572047420038</v>
       </c>
       <c r="BZ53" t="n">
         <v>63.89234965382096</v>
@@ -27008,7 +26992,7 @@
         <v>47.83445546432147</v>
       </c>
       <c r="CB53" t="n">
-        <v>85.52991758345958</v>
+        <v>85.52991758433221</v>
       </c>
       <c r="CC53" t="n">
         <v>11.76833333333333</v>
@@ -27018,7 +27002,7 @@
       </c>
       <c r="CE53" t="inlineStr"/>
       <c r="CF53" t="n">
-        <v>14.00747131501237</v>
+        <v>14.0074713156791</v>
       </c>
       <c r="CG53" t="n">
         <v>11.76833333333333</v>
@@ -27039,7 +27023,7 @@
         <v>-80.45848735994448</v>
       </c>
       <c r="CM53" t="n">
-        <v>-74.15595734716243</v>
+        <v>-74.15595734593229</v>
       </c>
       <c r="CN53" t="inlineStr">
         <is>
@@ -27147,7 +27131,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -27316,10 +27300,10 @@
         <v>4.639999866485596</v>
       </c>
       <c r="BX54" t="n">
-        <v>1.073494102797005</v>
+        <v>1.073494106500404</v>
       </c>
       <c r="BY54" t="n">
-        <v>1.991331560688444</v>
+        <v>1.991331567558249</v>
       </c>
       <c r="BZ54" t="n">
         <v>10.07868823457937</v>
@@ -27328,13 +27312,13 @@
         <v>9.446029690082037</v>
       </c>
       <c r="CB54" t="n">
-        <v>11.32627913874063</v>
+        <v>11.32627913971196</v>
       </c>
       <c r="CC54" t="n">
-        <v>4.230026072135482</v>
+        <v>4.230026071760521</v>
       </c>
       <c r="CD54" t="n">
-        <v>7.602765640627252</v>
+        <v>7.602765635895197</v>
       </c>
       <c r="CE54" t="n">
         <v>7.2410239750103</v>
@@ -27365,11 +27349,7 @@
       </c>
       <c r="CP54" t="inlineStr"/>
       <c r="CQ54" t="inlineStr"/>
-      <c r="CR54" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
+      <c r="CR54" t="inlineStr"/>
       <c r="CS54" t="b">
         <v>0</v>
       </c>
@@ -27390,20 +27370,20 @@
         <v>7.906968852776419</v>
       </c>
       <c r="CZ54" t="n">
-        <v>-35.92780109506861</v>
+        <v>-35.92779681249883</v>
       </c>
       <c r="DA54" t="b">
         <v>0</v>
       </c>
       <c r="DB54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC54" t="b">
         <v>0</v>
       </c>
       <c r="DD54" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$4.03 (candidato)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -27632,10 +27612,10 @@
         <v>10.51000022888184</v>
       </c>
       <c r="BX55" t="n">
-        <v>13.086966536379</v>
+        <v>13.08696658629271</v>
       </c>
       <c r="BY55" t="n">
-        <v>19.05462327696782</v>
+        <v>19.05462334964219</v>
       </c>
       <c r="BZ55" t="n">
         <v>17.18616389628476</v>
@@ -27654,7 +27634,7 @@
         <v>14.72238167572673</v>
       </c>
       <c r="CF55" t="n">
-        <v>16.32432246669353</v>
+        <v>16.32432248712488</v>
       </c>
       <c r="CG55" t="n">
         <v>15.95427278600574</v>
@@ -27675,7 +27655,7 @@
         <v>36.62079157664122</v>
       </c>
       <c r="CM55" t="n">
-        <v>55.32180886003925</v>
+        <v>55.32180905443833</v>
       </c>
       <c r="CN55" t="inlineStr">
         <is>
@@ -27936,10 +27916,10 @@
         <v>29.69000053405762</v>
       </c>
       <c r="BX56" t="n">
-        <v>15.52022464562511</v>
+        <v>15.52022456197782</v>
       </c>
       <c r="BY56" t="n">
-        <v>28.79001671763458</v>
+        <v>28.79001656246886</v>
       </c>
       <c r="BZ56" t="n">
         <v>54.8664584485723</v>
@@ -27948,23 +27928,23 @@
         <v>49.47692096413685</v>
       </c>
       <c r="CB56" t="n">
-        <v>61.18292634510964</v>
+        <v>61.18292636552124</v>
       </c>
       <c r="CC56" t="n">
-        <v>36.64283818153474</v>
+        <v>36.64283819666568</v>
       </c>
       <c r="CD56" t="n">
-        <v>30.47133158302231</v>
+        <v>30.47133169851579</v>
       </c>
       <c r="CE56" t="inlineStr"/>
       <c r="CF56" t="n">
-        <v>33.95488449834168</v>
+        <v>33.95488444242116</v>
       </c>
       <c r="CG56" t="n">
-        <v>32.71642744958466</v>
+        <v>32.71642737956727</v>
       </c>
       <c r="CH56" t="n">
-        <v>29.44478470462619</v>
+        <v>29.44478464161055</v>
       </c>
       <c r="CI56" t="n">
         <v>4</v>
@@ -27976,10 +27956,10 @@
         <v>3.5</v>
       </c>
       <c r="CL56" t="n">
-        <v>-0.8259205962294902</v>
+        <v>-0.8259208084748337</v>
       </c>
       <c r="CM56" t="n">
-        <v>14.36471501370227</v>
+        <v>14.36471482535429</v>
       </c>
       <c r="CN56" t="inlineStr">
         <is>
@@ -28262,37 +28242,37 @@
         <v>23.78000068664551</v>
       </c>
       <c r="BX57" t="n">
-        <v>10.50498165492592</v>
+        <v>10.50498167323484</v>
       </c>
       <c r="BY57" t="n">
-        <v>15.22159729527519</v>
+        <v>15.22159728410938</v>
       </c>
       <c r="BZ57" t="n">
-        <v>19.8484716652772</v>
+        <v>19.84847161612383</v>
       </c>
       <c r="CA57" t="n">
         <v>22.05215577512442</v>
       </c>
       <c r="CB57" t="n">
-        <v>19.44680932788322</v>
+        <v>19.44680930505625</v>
       </c>
       <c r="CC57" t="n">
-        <v>23.36371005195449</v>
+        <v>23.36371004685678</v>
       </c>
       <c r="CD57" t="n">
-        <v>9.891671196153721</v>
+        <v>9.891671168811909</v>
       </c>
       <c r="CE57" t="n">
         <v>19.45038570269356</v>
       </c>
       <c r="CF57" t="n">
-        <v>17.47247283366097</v>
+        <v>17.47247282150137</v>
       </c>
       <c r="CG57" t="n">
-        <v>19.44859751528839</v>
+        <v>19.4485975038749</v>
       </c>
       <c r="CH57" t="n">
-        <v>17.50373776375955</v>
+        <v>17.50373775348741</v>
       </c>
       <c r="CI57" t="n">
         <v>8</v>
@@ -28304,10 +28284,10 @@
         <v>2.4</v>
       </c>
       <c r="CL57" t="n">
-        <v>-26.3930308732523</v>
+        <v>-26.39303091644884</v>
       </c>
       <c r="CM57" t="n">
-        <v>-26.52450660578305</v>
+        <v>-26.52450665691676</v>
       </c>
       <c r="CN57" t="inlineStr">
         <is>
@@ -28586,10 +28566,10 @@
         <v>24.32999992370605</v>
       </c>
       <c r="BX58" t="n">
-        <v>4.265826982686783</v>
+        <v>4.265826978363862</v>
       </c>
       <c r="BY58" t="n">
-        <v>7.913109052883983</v>
+        <v>7.913109044864963</v>
       </c>
       <c r="BZ58" t="n">
         <v>29.33325741484123</v>
@@ -28598,13 +28578,13 @@
         <v>29.21395447941907</v>
       </c>
       <c r="CB58" t="n">
-        <v>26.33700607156679</v>
+        <v>26.33700607388524</v>
       </c>
       <c r="CC58" t="n">
-        <v>2.973172390117484</v>
+        <v>2.973172390213512</v>
       </c>
       <c r="CD58" t="n">
-        <v>19.05301341526689</v>
+        <v>19.05301342018568</v>
       </c>
       <c r="CE58" t="n">
         <v>18.00727121747286</v>
@@ -28900,10 +28880,10 @@
         <v>49.58000183105469</v>
       </c>
       <c r="BX59" t="n">
-        <v>8.25200272869739</v>
+        <v>8.252002627485941</v>
       </c>
       <c r="BY59" t="n">
-        <v>15.30746506173366</v>
+        <v>15.30746487398642</v>
       </c>
       <c r="BZ59" t="n">
         <v>19.94943893900621</v>
@@ -28912,25 +28892,25 @@
         <v>12.40196818721602</v>
       </c>
       <c r="CB59" t="n">
-        <v>15.12548798384509</v>
+        <v>15.12548841067966</v>
       </c>
       <c r="CC59" t="n">
-        <v>20.74522886900135</v>
+        <v>20.74522892910431</v>
       </c>
       <c r="CD59" t="n">
-        <v>11.32438883826405</v>
+        <v>11.32438913360716</v>
       </c>
       <c r="CE59" t="n">
         <v>12.98629942513824</v>
       </c>
       <c r="CF59" t="n">
-        <v>14.51153500411275</v>
+        <v>14.51153506577799</v>
       </c>
       <c r="CG59" t="n">
-        <v>14.05589370449167</v>
+        <v>14.05589391790895</v>
       </c>
       <c r="CH59" t="n">
-        <v>12.6503043340425</v>
+        <v>12.65030452611806</v>
       </c>
       <c r="CI59" t="n">
         <v>8</v>
@@ -28942,10 +28922,10 @@
         <v>2.5</v>
       </c>
       <c r="CL59" t="n">
-        <v>-74.48506682765203</v>
+        <v>-74.48506644024673</v>
       </c>
       <c r="CM59" t="n">
-        <v>-70.73107206901437</v>
+        <v>-70.73107194463914</v>
       </c>
       <c r="CN59" t="inlineStr">
         <is>
@@ -29240,10 +29220,10 @@
         <v>33.61999893188477</v>
       </c>
       <c r="BX60" t="n">
-        <v>11.88440173407689</v>
+        <v>11.88440178507505</v>
       </c>
       <c r="BY60" t="n">
-        <v>22.04556521671263</v>
+        <v>22.04556531131421</v>
       </c>
       <c r="BZ60" t="n">
         <v>39.73817893376209</v>
@@ -29252,25 +29232,25 @@
         <v>32.40852551699374</v>
       </c>
       <c r="CB60" t="n">
-        <v>40.54661348329596</v>
+        <v>40.54661340954677</v>
       </c>
       <c r="CC60" t="n">
-        <v>23.78010070769682</v>
+        <v>23.7801006976594</v>
       </c>
       <c r="CD60" t="n">
-        <v>24.16893075898049</v>
+        <v>24.16893067258962</v>
       </c>
       <c r="CE60" t="n">
         <v>25.56648631344748</v>
       </c>
       <c r="CF60" t="n">
-        <v>27.51735033312076</v>
+        <v>27.51735033004854</v>
       </c>
       <c r="CG60" t="n">
-        <v>24.86770853621398</v>
+        <v>24.86770849301855</v>
       </c>
       <c r="CH60" t="n">
-        <v>22.38093768259258</v>
+        <v>22.38093764371669</v>
       </c>
       <c r="CI60" t="n">
         <v>8</v>
@@ -29282,10 +29262,10 @@
         <v>3.4</v>
       </c>
       <c r="CL60" t="n">
-        <v>-33.42968948946992</v>
+        <v>-33.42968960510315</v>
       </c>
       <c r="CM60" t="n">
-        <v>-18.15184054921647</v>
+        <v>-18.15184055835454</v>
       </c>
       <c r="CN60" t="inlineStr">
         <is>
@@ -29564,10 +29544,10 @@
         <v>4.519999980926514</v>
       </c>
       <c r="BX61" t="n">
-        <v>2.935043319749744</v>
+        <v>2.935043324165362</v>
       </c>
       <c r="BY61" t="n">
-        <v>5.444505358135775</v>
+        <v>5.444505366326747</v>
       </c>
       <c r="BZ61" t="n">
         <v>13.76781603385662</v>
@@ -29576,13 +29556,13 @@
         <v>15.32423511716514</v>
       </c>
       <c r="CB61" t="n">
-        <v>15.90374916695663</v>
+        <v>15.90374917481285</v>
       </c>
       <c r="CC61" t="n">
-        <v>9.471435211363815</v>
+        <v>9.471435210818441</v>
       </c>
       <c r="CD61" t="n">
-        <v>6.834912650321556</v>
+        <v>6.834912646327012</v>
       </c>
       <c r="CE61" t="n">
         <v>1.44645468896914</v>
@@ -29878,37 +29858,37 @@
         <v>30</v>
       </c>
       <c r="BX62" t="n">
-        <v>13.81421961956552</v>
+        <v>13.81421964189702</v>
       </c>
       <c r="BY62" t="n">
-        <v>14.67667818667521</v>
+        <v>14.67667819153985</v>
       </c>
       <c r="BZ62" t="n">
-        <v>15.82099672212732</v>
+        <v>15.82099670179566</v>
       </c>
       <c r="CA62" t="n">
         <v>31.15287379381833</v>
       </c>
       <c r="CB62" t="n">
-        <v>14.95526753828155</v>
+        <v>14.95526752858739</v>
       </c>
       <c r="CC62" t="n">
-        <v>30.52562436162667</v>
+        <v>30.52562435705925</v>
       </c>
       <c r="CD62" t="n">
-        <v>6.521907980627405</v>
+        <v>6.521907960877421</v>
       </c>
       <c r="CE62" t="n">
         <v>38.80831925964276</v>
       </c>
       <c r="CF62" t="n">
-        <v>18.20965260038886</v>
+        <v>18.2096525965107</v>
       </c>
       <c r="CG62" t="n">
-        <v>14.95526753828155</v>
+        <v>14.95526752858739</v>
       </c>
       <c r="CH62" t="n">
-        <v>13.45974078445339</v>
+        <v>13.45974077572865</v>
       </c>
       <c r="CI62" t="n">
         <v>7</v>
@@ -29920,10 +29900,10 @@
         <v>6</v>
       </c>
       <c r="CL62" t="n">
-        <v>-55.13419738515536</v>
+        <v>-55.13419741423782</v>
       </c>
       <c r="CM62" t="n">
-        <v>-39.30115799870381</v>
+        <v>-39.30115801163099</v>
       </c>
       <c r="CN62" t="inlineStr">
         <is>
@@ -29958,7 +29938,7 @@
         <v>-5.213268999738752</v>
       </c>
       <c r="CZ62" t="n">
-        <v>-27.23199551707314</v>
+        <v>-27.23200229546583</v>
       </c>
       <c r="DA62" t="b">
         <v>0</v>
@@ -30202,35 +30182,35 @@
         <v>3.509999990463257</v>
       </c>
       <c r="BX63" t="n">
-        <v>2.694277181360765</v>
+        <v>2.694277163452418</v>
       </c>
       <c r="BY63" t="n">
-        <v>3.221309606253355</v>
+        <v>3.221309599973381</v>
       </c>
       <c r="BZ63" t="n">
-        <v>4.095040424583558</v>
+        <v>4.095040443819191</v>
       </c>
       <c r="CA63" t="n">
         <v>7.355188608855169</v>
       </c>
       <c r="CB63" t="n">
-        <v>6.136182382847855</v>
+        <v>6.136182372690808</v>
       </c>
       <c r="CC63" t="n">
-        <v>8.504201674334045</v>
+        <v>8.504201678521301</v>
       </c>
       <c r="CD63" t="n">
-        <v>1.898979071752606</v>
+        <v>1.898979086897337</v>
       </c>
       <c r="CE63" t="inlineStr"/>
       <c r="CF63" t="n">
-        <v>4.843596992855336</v>
+        <v>4.843596993458514</v>
       </c>
       <c r="CG63" t="n">
-        <v>4.095040424583558</v>
+        <v>4.095040443819191</v>
       </c>
       <c r="CH63" t="n">
-        <v>3.685536382125202</v>
+        <v>3.685536399437272</v>
       </c>
       <c r="CI63" t="n">
         <v>7</v>
@@ -30242,10 +30222,10 @@
         <v>4.5</v>
       </c>
       <c r="CL63" t="n">
-        <v>5.001036813073534</v>
+        <v>5.001037306294909</v>
       </c>
       <c r="CM63" t="n">
-        <v>37.99421669559801</v>
+        <v>37.99421671278258</v>
       </c>
       <c r="CN63" t="inlineStr">
         <is>
@@ -30524,37 +30504,37 @@
         <v>18.63999938964844</v>
       </c>
       <c r="BX64" t="n">
-        <v>8.74514038693229</v>
+        <v>8.745140371059565</v>
       </c>
       <c r="BY64" t="n">
-        <v>9.253022841577703</v>
+        <v>9.253022842372346</v>
       </c>
       <c r="BZ64" t="n">
-        <v>9.762664743788223</v>
+        <v>9.762664762346203</v>
       </c>
       <c r="CA64" t="n">
         <v>16.97559723955254</v>
       </c>
       <c r="CB64" t="n">
-        <v>9.361180426655146</v>
+        <v>9.361180440143773</v>
       </c>
       <c r="CC64" t="n">
-        <v>17.55266733759782</v>
+        <v>17.55266734149678</v>
       </c>
       <c r="CD64" t="n">
-        <v>4.001855345021139</v>
+        <v>4.001855363179535</v>
       </c>
       <c r="CE64" t="n">
         <v>16.08382941914014</v>
       </c>
       <c r="CF64" t="n">
-        <v>11.46699471753313</v>
+        <v>11.46699472241136</v>
       </c>
       <c r="CG64" t="n">
-        <v>9.561922585221684</v>
+        <v>9.561922601244987</v>
       </c>
       <c r="CH64" t="n">
-        <v>8.605730326699515</v>
+        <v>8.60573034112049</v>
       </c>
       <c r="CI64" t="n">
         <v>8</v>
@@ -30566,10 +30546,10 @@
         <v>4.4</v>
       </c>
       <c r="CL64" t="n">
-        <v>-53.83191733644244</v>
+        <v>-53.8319172590767</v>
       </c>
       <c r="CM64" t="n">
-        <v>-38.48178598170329</v>
+        <v>-38.4817859555325</v>
       </c>
       <c r="CN64" t="inlineStr">
         <is>
@@ -30850,25 +30830,25 @@
         <v>2.170000076293945</v>
       </c>
       <c r="BX65" t="n">
-        <v>0.6228125152856525</v>
+        <v>0.622812515465324</v>
       </c>
       <c r="BY65" t="n">
-        <v>0.8890945896734218</v>
+        <v>0.8890945898941852</v>
       </c>
       <c r="BZ65" t="n">
-        <v>3.517804534945287</v>
+        <v>3.517804534803933</v>
       </c>
       <c r="CA65" t="n">
         <v>7.255221841107573</v>
       </c>
       <c r="CB65" t="n">
-        <v>2.703577542440828</v>
+        <v>2.703577542712195</v>
       </c>
       <c r="CC65" t="n">
-        <v>2.232512847970693</v>
+        <v>2.232512847962681</v>
       </c>
       <c r="CD65" t="n">
-        <v>1.749669828519031</v>
+        <v>1.749669828438236</v>
       </c>
       <c r="CE65" t="n">
         <v>4.906142470300746</v>
@@ -31164,10 +31144,10 @@
         <v>36.06999969482422</v>
       </c>
       <c r="BX66" t="n">
-        <v>10.32734671252357</v>
+        <v>10.32734665671983</v>
       </c>
       <c r="BY66" t="n">
-        <v>19.15722815173122</v>
+        <v>19.15722804821528</v>
       </c>
       <c r="BZ66" t="n">
         <v>29.79597855089906</v>
@@ -31176,25 +31156,25 @@
         <v>22.11977982655244</v>
       </c>
       <c r="CB66" t="n">
-        <v>27.68991886838946</v>
+        <v>27.68991900140225</v>
       </c>
       <c r="CC66" t="n">
-        <v>22.9549793382587</v>
+        <v>22.95497935538594</v>
       </c>
       <c r="CD66" t="n">
-        <v>17.74659913481667</v>
+        <v>17.74659924904023</v>
       </c>
       <c r="CE66" t="n">
         <v>27.14442054393252</v>
       </c>
       <c r="CF66" t="n">
-        <v>22.11703139088795</v>
+        <v>22.11703140401844</v>
       </c>
       <c r="CG66" t="n">
-        <v>22.53737958240557</v>
+        <v>22.53737959096919</v>
       </c>
       <c r="CH66" t="n">
-        <v>20.28364162416501</v>
+        <v>20.28364163187227</v>
       </c>
       <c r="CI66" t="n">
         <v>8</v>
@@ -31206,10 +31186,10 @@
         <v>2.9</v>
       </c>
       <c r="CL66" t="n">
-        <v>-43.76589466099838</v>
+        <v>-43.76589463963087</v>
       </c>
       <c r="CM66" t="n">
-        <v>-38.68302861654422</v>
+        <v>-38.68302858014143</v>
       </c>
       <c r="CN66" t="inlineStr">
         <is>
@@ -31248,7 +31228,7 @@
         <v>4.42964313474894</v>
       </c>
       <c r="CZ66" t="n">
-        <v>-19.75884710571682</v>
+        <v>-19.75885395890232</v>
       </c>
       <c r="DA66" t="b">
         <v>0</v>
@@ -31492,10 +31472,10 @@
         <v>8.960000038146973</v>
       </c>
       <c r="BX67" t="n">
-        <v>0.5329077806602136</v>
+        <v>0.5329077803032847</v>
       </c>
       <c r="BY67" t="n">
-        <v>0.9885439331246964</v>
+        <v>0.988543932462593</v>
       </c>
       <c r="BZ67" t="n">
         <v>10.18181822516701</v>
@@ -31504,13 +31484,13 @@
         <v>9.355421567964147</v>
       </c>
       <c r="CB67" t="n">
-        <v>11.1930400234452</v>
+        <v>11.19304002377668</v>
       </c>
       <c r="CC67" t="n">
-        <v>0.7359287832324234</v>
+        <v>0.7359287832388234</v>
       </c>
       <c r="CD67" t="n">
-        <v>8.686260803571571</v>
+        <v>8.686260804049313</v>
       </c>
       <c r="CE67" t="inlineStr"/>
       <c r="CF67" t="inlineStr"/>
@@ -31808,10 +31788,10 @@
         <v>8.510000228881836</v>
       </c>
       <c r="BX68" t="n">
-        <v>1.637947944173167</v>
+        <v>1.637947944873653</v>
       </c>
       <c r="BY68" t="n">
-        <v>3.038393436441224</v>
+        <v>3.038393437740626</v>
       </c>
       <c r="BZ68" t="n">
         <v>25.00166364361071</v>
@@ -31820,13 +31800,13 @@
         <v>24.7460880607331</v>
       </c>
       <c r="CB68" t="n">
-        <v>26.74944032623308</v>
+        <v>26.74944032712579</v>
       </c>
       <c r="CC68" t="n">
-        <v>6.710964368476396</v>
+        <v>6.710964368435504</v>
       </c>
       <c r="CD68" t="n">
-        <v>18.65870461681319</v>
+        <v>18.65870461600752</v>
       </c>
       <c r="CE68" t="n">
         <v>14.23395771137433</v>
@@ -32122,10 +32102,10 @@
         <v>21.79999923706055</v>
       </c>
       <c r="BX69" t="n">
-        <v>6.028554346258669</v>
+        <v>6.02855436224046</v>
       </c>
       <c r="BY69" t="n">
-        <v>11.18296831230983</v>
+        <v>11.18296834195605</v>
       </c>
       <c r="BZ69" t="n">
         <v>33.43171179294585</v>
@@ -32134,25 +32114,25 @@
         <v>34.49643348400799</v>
       </c>
       <c r="CB69" t="n">
-        <v>30.08621130040702</v>
+        <v>30.08621129923029</v>
       </c>
       <c r="CC69" t="n">
-        <v>25.30591858354294</v>
+        <v>25.30591858102999</v>
       </c>
       <c r="CD69" t="n">
-        <v>19.51154839285337</v>
+        <v>19.51154837583596</v>
       </c>
       <c r="CE69" t="n">
         <v>13.40148489337126</v>
       </c>
       <c r="CF69" t="n">
-        <v>23.91661096563404</v>
+        <v>23.91661096691105</v>
       </c>
       <c r="CG69" t="n">
-        <v>25.30591858354294</v>
+        <v>25.30591858102999</v>
       </c>
       <c r="CH69" t="n">
-        <v>22.77532672518865</v>
+        <v>22.77532672292699</v>
       </c>
       <c r="CI69" t="n">
         <v>7</v>
@@ -32164,10 +32144,10 @@
         <v>5.7</v>
       </c>
       <c r="CL69" t="n">
-        <v>4.473979459916766</v>
+        <v>4.47397944954222</v>
       </c>
       <c r="CM69" t="n">
-        <v>9.70922845251847</v>
+        <v>9.709228458376341</v>
       </c>
       <c r="CN69" t="inlineStr">
         <is>
@@ -32206,7 +32186,7 @@
         <v>-0.1831543738455732</v>
       </c>
       <c r="CZ69" t="n">
-        <v>-18.67055636992362</v>
+        <v>-18.67055002568029</v>
       </c>
       <c r="DA69" t="b">
         <v>0</v>
@@ -32450,10 +32430,10 @@
         <v>24.69000053405762</v>
       </c>
       <c r="BX70" t="n">
-        <v>4.528795221897692</v>
+        <v>4.528795225015497</v>
       </c>
       <c r="BY70" t="n">
-        <v>8.400915136620219</v>
+        <v>8.400915142403747</v>
       </c>
       <c r="BZ70" t="n">
         <v>31.27557429027375</v>
@@ -32462,13 +32442,13 @@
         <v>26.55156008995373</v>
       </c>
       <c r="CB70" t="n">
-        <v>36.79121578817753</v>
+        <v>36.79121578458093</v>
       </c>
       <c r="CC70" t="n">
-        <v>11.80687700223436</v>
+        <v>11.80687700189049</v>
       </c>
       <c r="CD70" t="n">
-        <v>25.62152608239638</v>
+        <v>25.62152607751264</v>
       </c>
       <c r="CE70" t="n">
         <v>25.17925941757476</v>
@@ -32764,25 +32744,25 @@
         <v>17.30999946594238</v>
       </c>
       <c r="BX71" t="n">
-        <v>4.028449978070674</v>
+        <v>4.028449979766058</v>
       </c>
       <c r="BY71" t="n">
-        <v>6.922307411470418</v>
+        <v>6.922307413562582</v>
       </c>
       <c r="BZ71" t="n">
-        <v>23.65950143490909</v>
+        <v>23.65950143210265</v>
       </c>
       <c r="CA71" t="n">
         <v>32.98569202610356</v>
       </c>
       <c r="CB71" t="n">
-        <v>16.71223337052959</v>
+        <v>16.71223337135697</v>
       </c>
       <c r="CC71" t="n">
-        <v>20.30046208507653</v>
+        <v>20.30046208489512</v>
       </c>
       <c r="CD71" t="n">
-        <v>11.70662164015804</v>
+        <v>11.7066216390167</v>
       </c>
       <c r="CE71" t="n">
         <v>21.93193610654263</v>
@@ -33078,35 +33058,35 @@
         <v>23.89999961853027</v>
       </c>
       <c r="BX72" t="n">
-        <v>22.96133611046082</v>
+        <v>22.9613361388748</v>
       </c>
       <c r="BY72" t="n">
-        <v>29.32452638621756</v>
+        <v>29.32452639428848</v>
       </c>
       <c r="BZ72" t="n">
-        <v>39.49704741927707</v>
+        <v>39.49704738127131</v>
       </c>
       <c r="CA72" t="n">
         <v>62.81937459029582</v>
       </c>
       <c r="CB72" t="n">
-        <v>70.08903045030866</v>
+        <v>70.0890304800874</v>
       </c>
       <c r="CC72" t="n">
-        <v>41.76900675550808</v>
+        <v>41.76900675153746</v>
       </c>
       <c r="CD72" t="n">
-        <v>19.01744461799239</v>
+        <v>19.01744459141282</v>
       </c>
       <c r="CE72" t="inlineStr"/>
       <c r="CF72" t="n">
-        <v>40.78253804715148</v>
+        <v>40.78253804682401</v>
       </c>
       <c r="CG72" t="n">
-        <v>39.49704741927707</v>
+        <v>39.49704738127131</v>
       </c>
       <c r="CH72" t="n">
-        <v>35.54734267734936</v>
+        <v>35.54734264314418</v>
       </c>
       <c r="CI72" t="n">
         <v>7</v>
@@ -33118,10 +33098,10 @@
         <v>3.7</v>
       </c>
       <c r="CL72" t="n">
-        <v>48.73365374361182</v>
+        <v>48.73365360049389</v>
       </c>
       <c r="CM72" t="n">
-        <v>70.63823723047993</v>
+        <v>70.63823722910973</v>
       </c>
       <c r="CN72" t="inlineStr">
         <is>
@@ -33400,10 +33380,10 @@
         <v>4.050000190734863</v>
       </c>
       <c r="BX73" t="n">
-        <v>0.9834174955160336</v>
+        <v>0.9834174937255474</v>
       </c>
       <c r="BY73" t="n">
-        <v>1.824239454182242</v>
+        <v>1.82423945086089</v>
       </c>
       <c r="BZ73" t="n">
         <v>6.261668906328697</v>
@@ -33412,7 +33392,7 @@
         <v>4.158686841231277</v>
       </c>
       <c r="CB73" t="n">
-        <v>8.695198109480446</v>
+        <v>8.695198106555496</v>
       </c>
       <c r="CC73" t="n">
         <v>3.760485277130923</v>
@@ -33470,7 +33450,7 @@
         <v>1.50376393620828</v>
       </c>
       <c r="CZ73" t="n">
-        <v>-44.6329217901767</v>
+        <v>-44.63291810308804</v>
       </c>
       <c r="DA73" t="b">
         <v>0</v>
@@ -33714,10 +33694,10 @@
         <v>12.53999996185303</v>
       </c>
       <c r="BX74" t="n">
-        <v>2.073799234551615</v>
+        <v>2.073799235128572</v>
       </c>
       <c r="BY74" t="n">
-        <v>3.846897580093246</v>
+        <v>3.846897581163501</v>
       </c>
       <c r="BZ74" t="n">
         <v>16.58233527889746</v>
@@ -33726,7 +33706,7 @@
         <v>13.15648423765553</v>
       </c>
       <c r="CB74" t="n">
-        <v>21.66997891332515</v>
+        <v>21.66997891413128</v>
       </c>
       <c r="CC74" t="n">
         <v>9.294207014285712</v>
@@ -34030,10 +34010,10 @@
         <v>55.5</v>
       </c>
       <c r="BX75" t="n">
-        <v>40.36268322185821</v>
+        <v>40.36268300414741</v>
       </c>
       <c r="BY75" t="n">
-        <v>58.76806677102556</v>
+        <v>58.76806645403865</v>
       </c>
       <c r="BZ75" t="n">
         <v>35.98503740648379</v>
@@ -34052,13 +34032,13 @@
         <v>47.31284142717968</v>
       </c>
       <c r="CF75" t="n">
-        <v>43.20016089001607</v>
+        <v>43.20016080089979</v>
       </c>
       <c r="CG75" t="n">
-        <v>41.66677586297625</v>
+        <v>41.66677575412086</v>
       </c>
       <c r="CH75" t="n">
-        <v>37.50009827667863</v>
+        <v>37.50009817870877</v>
       </c>
       <c r="CI75" t="n">
         <v>6</v>
@@ -34070,10 +34050,10 @@
         <v>6.4</v>
       </c>
       <c r="CL75" t="n">
-        <v>-32.43225535733581</v>
+        <v>-32.43225553385808</v>
       </c>
       <c r="CM75" t="n">
-        <v>-22.16187227024131</v>
+        <v>-22.16187243081119</v>
       </c>
       <c r="CN75" t="inlineStr">
         <is>
@@ -34332,35 +34312,35 @@
         <v>12.85999965667725</v>
       </c>
       <c r="BX76" t="n">
-        <v>10.87454816796245</v>
+        <v>10.8745481329745</v>
       </c>
       <c r="BY76" t="n">
-        <v>11.49697209321865</v>
+        <v>11.49697211602799</v>
       </c>
       <c r="BZ76" t="n">
-        <v>11.90131687345846</v>
+        <v>11.90131693536148</v>
       </c>
       <c r="CA76" t="n">
         <v>16.82961568340781</v>
       </c>
       <c r="CB76" t="n">
-        <v>19.71212208266349</v>
+        <v>19.71212211913191</v>
       </c>
       <c r="CC76" t="n">
-        <v>7.382415584655944</v>
+        <v>7.382415589146119</v>
       </c>
       <c r="CD76" t="n">
-        <v>4.873141766269742</v>
+        <v>4.873141826924843</v>
       </c>
       <c r="CE76" t="inlineStr"/>
       <c r="CF76" t="n">
-        <v>10.41381317982388</v>
+        <v>10.41381319337752</v>
       </c>
       <c r="CG76" t="n">
-        <v>11.18576013059055</v>
+        <v>11.18576012450125</v>
       </c>
       <c r="CH76" t="n">
-        <v>10.06718411753149</v>
+        <v>10.06718411205112</v>
       </c>
       <c r="CI76" t="n">
         <v>4</v>
@@ -34372,10 +34352,10 @@
         <v>1.6</v>
       </c>
       <c r="CL76" t="n">
-        <v>-21.71707320144173</v>
+        <v>-21.71707324405737</v>
       </c>
       <c r="CM76" t="n">
-        <v>-19.02166829050611</v>
+        <v>-19.02166818511227</v>
       </c>
       <c r="CN76" t="inlineStr">
         <is>
@@ -34654,10 +34634,10 @@
         <v>28.85000038146973</v>
       </c>
       <c r="BX77" t="n">
-        <v>13.47679399227867</v>
+        <v>13.47679394165723</v>
       </c>
       <c r="BY77" t="n">
-        <v>24.99945285567694</v>
+        <v>24.99945276177415</v>
       </c>
       <c r="BZ77" t="n">
         <v>38.1119147611639</v>
@@ -34666,25 +34646,25 @@
         <v>26.54383559620355</v>
       </c>
       <c r="CB77" t="n">
-        <v>44.90735159546294</v>
+        <v>44.90735171168915</v>
       </c>
       <c r="CC77" t="n">
-        <v>42.35229042710036</v>
+        <v>42.35229045232871</v>
       </c>
       <c r="CD77" t="n">
-        <v>24.08739122375856</v>
+        <v>24.08739134122866</v>
       </c>
       <c r="CE77" t="n">
         <v>24.8974245271389</v>
       </c>
       <c r="CF77" t="n">
-        <v>29.92205687234797</v>
+        <v>29.92205688664803</v>
       </c>
       <c r="CG77" t="n">
-        <v>25.77164422594024</v>
+        <v>25.77164417898885</v>
       </c>
       <c r="CH77" t="n">
-        <v>23.19447980334622</v>
+        <v>23.19447976108997</v>
       </c>
       <c r="CI77" t="n">
         <v>8</v>
@@ -34696,10 +34676,10 @@
         <v>3.3</v>
       </c>
       <c r="CL77" t="n">
-        <v>-19.60319065283629</v>
+        <v>-19.6031907993051</v>
       </c>
       <c r="CM77" t="n">
-        <v>3.715966990304875</v>
+        <v>3.715967039871804</v>
       </c>
       <c r="CN77" t="inlineStr">
         <is>
@@ -34742,7 +34722,7 @@
         <v>-2.337816543811788</v>
       </c>
       <c r="CZ77" t="n">
-        <v>-24.19493061245316</v>
+        <v>-24.19493858539801</v>
       </c>
       <c r="DA77" t="b">
         <v>0</v>
@@ -34986,10 +34966,10 @@
         <v>15.11999988555908</v>
       </c>
       <c r="BX78" t="n">
-        <v>2.439882943900921</v>
+        <v>2.439882940938409</v>
       </c>
       <c r="BY78" t="n">
-        <v>4.525982860936208</v>
+        <v>4.525982855440749</v>
       </c>
       <c r="BZ78" t="n">
         <v>26.57029157608194</v>
@@ -34998,7 +34978,7 @@
         <v>20.33365271794082</v>
       </c>
       <c r="CB78" t="n">
-        <v>34.60986200238716</v>
+        <v>34.60986199688647</v>
       </c>
       <c r="CC78" t="n">
         <v>10.38593205872702</v>
@@ -35304,10 +35284,10 @@
         <v>14.64999961853027</v>
       </c>
       <c r="BX79" t="n">
-        <v>9.578902405897873</v>
+        <v>9.57890238984289</v>
       </c>
       <c r="BY79" t="n">
-        <v>17.76886396294055</v>
+        <v>17.76886393315856</v>
       </c>
       <c r="BZ79" t="n">
         <v>14.2102851351044</v>
@@ -35328,7 +35308,7 @@
         <v>12.06136669897467</v>
       </c>
       <c r="CF79" t="n">
-        <v>15.18293137088104</v>
+        <v>15.18293136515142</v>
       </c>
       <c r="CG79" t="n">
         <v>13.55468557413323</v>
@@ -35349,7 +35329,7 @@
         <v>-16.72889191553597</v>
       </c>
       <c r="CM79" t="n">
-        <v>3.637759496434967</v>
+        <v>3.637759457324918</v>
       </c>
       <c r="CN79" t="inlineStr">
         <is>
@@ -35628,25 +35608,25 @@
         <v>26.55999946594238</v>
       </c>
       <c r="BX80" t="n">
-        <v>12.09583914676028</v>
+        <v>12.095839200167</v>
       </c>
       <c r="BY80" t="n">
-        <v>12.89484429399581</v>
+        <v>12.89484431927655</v>
       </c>
       <c r="BZ80" t="n">
-        <v>14.41525916557178</v>
+        <v>14.41525913018569</v>
       </c>
       <c r="CA80" t="n">
         <v>33.30354002524292</v>
       </c>
       <c r="CB80" t="n">
-        <v>13.52156654665155</v>
+        <v>13.52156654558672</v>
       </c>
       <c r="CC80" t="n">
-        <v>24.69737288395405</v>
+        <v>24.6973728769165</v>
       </c>
       <c r="CD80" t="n">
-        <v>5.969673603814106</v>
+        <v>5.969673569646622</v>
       </c>
       <c r="CE80" t="n">
         <v>64.9533816160684</v>
@@ -35698,7 +35678,7 @@
         <v>-2.572884986294177</v>
       </c>
       <c r="CZ80" t="n">
-        <v>-18.09285086071385</v>
+        <v>-18.09284111970466</v>
       </c>
       <c r="DA80" t="b">
         <v>0</v>
@@ -35942,35 +35922,35 @@
         <v>2.740000009536743</v>
       </c>
       <c r="BX81" t="n">
-        <v>1.259649643459965</v>
+        <v>1.259649642526742</v>
       </c>
       <c r="BY81" t="n">
-        <v>1.7684043440741</v>
+        <v>1.768404343139931</v>
       </c>
       <c r="BZ81" t="n">
-        <v>4.169355425550364</v>
+        <v>4.169355426436785</v>
       </c>
       <c r="CA81" t="n">
         <v>7.812220106719857</v>
       </c>
       <c r="CB81" t="n">
-        <v>4.198816920906828</v>
+        <v>4.198816919755203</v>
       </c>
       <c r="CC81" t="n">
-        <v>1.343758969986019</v>
+        <v>1.343758970011925</v>
       </c>
       <c r="CD81" t="n">
-        <v>2.067905432035935</v>
+        <v>2.06790543255824</v>
       </c>
       <c r="CE81" t="inlineStr"/>
       <c r="CF81" t="n">
-        <v>2.467981789335535</v>
+        <v>2.467981789071471</v>
       </c>
       <c r="CG81" t="n">
-        <v>1.918154888055017</v>
+        <v>1.918154887849086</v>
       </c>
       <c r="CH81" t="n">
-        <v>1.726339399249516</v>
+        <v>1.726339399064177</v>
       </c>
       <c r="CI81" t="n">
         <v>6</v>
@@ -35982,10 +35962,10 @@
         <v>6.2</v>
       </c>
       <c r="CL81" t="n">
-        <v>-36.99491265544225</v>
+        <v>-36.99491266220644</v>
       </c>
       <c r="CM81" t="n">
-        <v>-9.92767223556319</v>
+        <v>-9.927672245200569</v>
       </c>
       <c r="CN81" t="inlineStr">
         <is>
@@ -36264,10 +36244,10 @@
         <v>6.949999809265137</v>
       </c>
       <c r="BX82" t="n">
-        <v>1.251744408289311</v>
+        <v>1.251744407614615</v>
       </c>
       <c r="BY82" t="n">
-        <v>2.321985877376673</v>
+        <v>2.32198587612511</v>
       </c>
       <c r="BZ82" t="n">
         <v>10.83382323208977</v>
@@ -36276,13 +36256,13 @@
         <v>10.63720103437324</v>
       </c>
       <c r="CB82" t="n">
-        <v>10.59280611176632</v>
+        <v>10.59280611190945</v>
       </c>
       <c r="CC82" t="n">
-        <v>1.875514633786436</v>
+        <v>1.875514633812491</v>
       </c>
       <c r="CD82" t="n">
-        <v>7.546697301894066</v>
+        <v>7.546697302682543</v>
       </c>
       <c r="CE82" t="n">
         <v>10.17050614593439</v>
@@ -36578,10 +36558,10 @@
         <v>9.840000152587891</v>
       </c>
       <c r="BX83" t="n">
-        <v>6.03175285881263</v>
+        <v>6.031752871925047</v>
       </c>
       <c r="BY83" t="n">
-        <v>11.18890155309743</v>
+        <v>11.18890157742096</v>
       </c>
       <c r="BZ83" t="n">
         <v>8.033271843609951</v>
@@ -36602,7 +36582,7 @@
         <v>40.23059672158782</v>
       </c>
       <c r="CF83" t="n">
-        <v>10.14916136498508</v>
+        <v>10.14916137033308</v>
       </c>
       <c r="CG83" t="n">
         <v>8.033271843609951</v>
@@ -36623,7 +36603,7 @@
         <v>-26.52495378927914</v>
       </c>
       <c r="CM83" t="n">
-        <v>3.141882191087997</v>
+        <v>3.141882245437522</v>
       </c>
       <c r="CN83" t="inlineStr">
         <is>
@@ -36900,10 +36880,10 @@
         <v>5.159999847412109</v>
       </c>
       <c r="BX84" t="n">
-        <v>3.051395882818362</v>
+        <v>3.051395867510251</v>
       </c>
       <c r="BY84" t="n">
-        <v>4.442832405383536</v>
+        <v>4.442832383094926</v>
       </c>
       <c r="BZ84" t="n">
         <v>4.377161371377319</v>
@@ -37188,10 +37168,10 @@
         <v>52.93999862670898</v>
       </c>
       <c r="BX85" t="n">
-        <v>11.11616392129055</v>
+        <v>11.11616388231794</v>
       </c>
       <c r="BY85" t="n">
-        <v>16.18513466939904</v>
+        <v>16.18513461265492</v>
       </c>
       <c r="BZ85" t="inlineStr"/>
       <c r="CA85" t="inlineStr"/>
@@ -37202,13 +37182,13 @@
       <c r="CD85" t="inlineStr"/>
       <c r="CE85" t="inlineStr"/>
       <c r="CF85" t="n">
-        <v>17.8763328635632</v>
+        <v>17.87633283165762</v>
       </c>
       <c r="CG85" t="n">
-        <v>16.18513466939904</v>
+        <v>16.18513461265492</v>
       </c>
       <c r="CH85" t="n">
-        <v>14.56662120245913</v>
+        <v>14.56662115138943</v>
       </c>
       <c r="CI85" t="n">
         <v>3</v>
@@ -37220,10 +37200,10 @@
         <v>2.4</v>
       </c>
       <c r="CL85" t="n">
-        <v>-72.48465889625078</v>
+        <v>-72.48465899271793</v>
       </c>
       <c r="CM85" t="n">
-        <v>-66.23284222273415</v>
+        <v>-66.23284228300159</v>
       </c>
       <c r="CN85" t="inlineStr">
         <is>
@@ -37514,10 +37494,10 @@
         <v>22.45000076293945</v>
       </c>
       <c r="BX86" t="n">
-        <v>11.31405128315595</v>
+        <v>11.31405125808305</v>
       </c>
       <c r="BY86" t="n">
-        <v>20.98756513025429</v>
+        <v>20.98756508374407</v>
       </c>
       <c r="BZ86" t="n">
         <v>15.19216088401163</v>
@@ -37538,13 +37518,13 @@
         <v>23.03202693646428</v>
       </c>
       <c r="CF86" t="n">
-        <v>19.65754610517116</v>
+        <v>19.65754609622327</v>
       </c>
       <c r="CG86" t="n">
-        <v>18.08986300713296</v>
+        <v>18.08986298387785</v>
       </c>
       <c r="CH86" t="n">
-        <v>16.28087670641966</v>
+        <v>16.28087668549006</v>
       </c>
       <c r="CI86" t="n">
         <v>8</v>
@@ -37556,10 +37536,10 @@
         <v>3</v>
       </c>
       <c r="CL86" t="n">
-        <v>-27.47939352725459</v>
+        <v>-27.4793936204822</v>
       </c>
       <c r="CM86" t="n">
-        <v>-12.43855039140169</v>
+        <v>-12.43855043125867</v>
       </c>
       <c r="CN86" t="inlineStr">
         <is>
@@ -37979,7 +37959,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S88" t="n">
@@ -38150,10 +38130,10 @@
         <v>18.45999908447266</v>
       </c>
       <c r="BX88" t="n">
-        <v>4.484582523342956</v>
+        <v>4.48458252957108</v>
       </c>
       <c r="BY88" t="n">
-        <v>8.318900580801182</v>
+        <v>8.318900592354353</v>
       </c>
       <c r="BZ88" t="n">
         <v>31.00063217607892</v>
@@ -38162,13 +38142,13 @@
         <v>33.42141293239761</v>
       </c>
       <c r="CB88" t="n">
-        <v>26.78755093128893</v>
+        <v>26.78755093274879</v>
       </c>
       <c r="CC88" t="n">
-        <v>11.12047331874309</v>
+        <v>11.12047331832117</v>
       </c>
       <c r="CD88" t="n">
-        <v>18.08633564317109</v>
+        <v>18.08633563714226</v>
       </c>
       <c r="CE88" t="n">
         <v>39.71865914645217</v>
@@ -38199,11 +38179,7 @@
       </c>
       <c r="CP88" t="inlineStr"/>
       <c r="CQ88" t="inlineStr"/>
-      <c r="CR88" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
+      <c r="CR88" t="inlineStr"/>
       <c r="CS88" t="b">
         <v>0</v>
       </c>
@@ -38230,14 +38206,14 @@
         <v>0</v>
       </c>
       <c r="DB88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC88" t="b">
         <v>0</v>
       </c>
       <c r="DD88" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$16.37 (candidato)</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -38468,25 +38444,25 @@
         <v>1.690000057220459</v>
       </c>
       <c r="BX89" t="n">
-        <v>0.1506862966979866</v>
+        <v>0.1506862965373912</v>
       </c>
       <c r="BY89" t="n">
-        <v>0.1716968778821741</v>
+        <v>0.1716968777063397</v>
       </c>
       <c r="BZ89" t="n">
-        <v>0.7749058947919139</v>
+        <v>0.7749058948241984</v>
       </c>
       <c r="CA89" t="n">
         <v>3.21621281095181</v>
       </c>
       <c r="CB89" t="n">
-        <v>0.2641169346043211</v>
+        <v>0.2641169345217216</v>
       </c>
       <c r="CC89" t="n">
-        <v>0.5414796436194493</v>
+        <v>0.5414796436219179</v>
       </c>
       <c r="CD89" t="n">
-        <v>0.3456600224227291</v>
+        <v>0.3456600224504286</v>
       </c>
       <c r="CE89" t="inlineStr"/>
       <c r="CF89" t="inlineStr"/>
@@ -38782,10 +38758,10 @@
         <v>13.89999961853027</v>
       </c>
       <c r="BX90" t="n">
-        <v>6.000512473969495</v>
+        <v>6.000512433763483</v>
       </c>
       <c r="BY90" t="n">
-        <v>8.736746162099585</v>
+        <v>8.73674610355963</v>
       </c>
       <c r="BZ90" t="n">
         <v>3.740232756344498</v>
@@ -39094,10 +39070,10 @@
         <v>7.420000076293945</v>
       </c>
       <c r="BX91" t="n">
-        <v>3.087450359731478</v>
+        <v>3.087450360197063</v>
       </c>
       <c r="BY91" t="n">
-        <v>5.727220417301892</v>
+        <v>5.727220418165552</v>
       </c>
       <c r="BZ91" t="n">
         <v>15.03287477230807</v>
@@ -39106,23 +39082,23 @@
         <v>16.21959651842132</v>
       </c>
       <c r="CB91" t="n">
-        <v>14.39085493494747</v>
+        <v>14.39085493522192</v>
       </c>
       <c r="CC91" t="n">
-        <v>14.99868039746931</v>
+        <v>14.99868039737996</v>
       </c>
       <c r="CD91" t="n">
-        <v>7.922199669621802</v>
+        <v>7.922199669167838</v>
       </c>
       <c r="CE91" t="inlineStr"/>
       <c r="CF91" t="n">
-        <v>13.71284125855359</v>
+        <v>13.71284125849982</v>
       </c>
       <c r="CG91" t="n">
-        <v>14.99868039746931</v>
+        <v>14.99868039737996</v>
       </c>
       <c r="CH91" t="n">
-        <v>13.49881235772238</v>
+        <v>13.49881235764196</v>
       </c>
       <c r="CI91" t="n">
         <v>5</v>
@@ -39134,10 +39110,10 @@
         <v>5.3</v>
       </c>
       <c r="CL91" t="n">
-        <v>81.92469297742389</v>
+        <v>81.92469297634015</v>
       </c>
       <c r="CM91" t="n">
-        <v>84.8091794818784</v>
+        <v>84.80917948115373</v>
       </c>
       <c r="CN91" t="inlineStr">
         <is>
@@ -39418,10 +39394,10 @@
         <v>3.690000057220459</v>
       </c>
       <c r="BX92" t="n">
-        <v>33.80143550034843</v>
+        <v>33.80143532585153</v>
       </c>
       <c r="BY92" t="n">
-        <v>62.70166285314632</v>
+        <v>62.70166252945458</v>
       </c>
       <c r="BZ92" t="n">
         <v>4.860089538585594</v>
@@ -39714,35 +39690,35 @@
         <v>19.56999969482422</v>
       </c>
       <c r="BX93" t="n">
-        <v>11.66679780424779</v>
+        <v>11.66679781967728</v>
       </c>
       <c r="BY93" t="n">
-        <v>15.42108797443522</v>
+        <v>15.42108798469061</v>
       </c>
       <c r="BZ93" t="n">
-        <v>25.10431134270869</v>
+        <v>25.10431132620287</v>
       </c>
       <c r="CA93" t="n">
         <v>44.54686696093374</v>
       </c>
       <c r="CB93" t="n">
-        <v>30.38694753338507</v>
+        <v>30.38694754547522</v>
       </c>
       <c r="CC93" t="n">
-        <v>15.82484537433523</v>
+        <v>15.82484537333875</v>
       </c>
       <c r="CD93" t="n">
-        <v>12.25417621259106</v>
+        <v>12.25417620174227</v>
       </c>
       <c r="CE93" t="inlineStr"/>
       <c r="CF93" t="n">
-        <v>17.00426062393174</v>
+        <v>17.00426062597738</v>
       </c>
       <c r="CG93" t="n">
-        <v>15.62296667438523</v>
+        <v>15.62296667901468</v>
       </c>
       <c r="CH93" t="n">
-        <v>14.06067000694671</v>
+        <v>14.06067001111321</v>
       </c>
       <c r="CI93" t="n">
         <v>4</v>
@@ -39754,10 +39730,10 @@
         <v>2.2</v>
       </c>
       <c r="CL93" t="n">
-        <v>-28.15191504236249</v>
+        <v>-28.15191502107222</v>
       </c>
       <c r="CM93" t="n">
-        <v>-13.11057287124566</v>
+        <v>-13.11057286079271</v>
       </c>
       <c r="CN93" t="inlineStr">
         <is>
@@ -40046,10 +40022,10 @@
         <v>78.69999694824219</v>
       </c>
       <c r="BX94" t="n">
-        <v>58.83949676437168</v>
+        <v>58.83949702635157</v>
       </c>
       <c r="BY94" t="n">
-        <v>85.67030728892516</v>
+        <v>85.67030767036788</v>
       </c>
       <c r="BZ94" t="n">
         <v>24.78740061361959</v>
@@ -40362,10 +40338,10 @@
         <v>35.65000152587891</v>
       </c>
       <c r="BX95" t="n">
-        <v>8.823433620759227</v>
+        <v>8.823433607042103</v>
       </c>
       <c r="BY95" t="n">
-        <v>16.36746936650837</v>
+        <v>16.3674693410631</v>
       </c>
       <c r="BZ95" t="n">
         <v>42.70908862729615</v>
@@ -40374,19 +40350,19 @@
         <v>42.97434148367212</v>
       </c>
       <c r="CB95" t="n">
-        <v>36.27793360147332</v>
+        <v>36.2779336083645</v>
       </c>
       <c r="CC95" t="n">
-        <v>50.14199040421468</v>
+        <v>50.14199040771505</v>
       </c>
       <c r="CD95" t="n">
-        <v>24.39370806351415</v>
+        <v>24.39370807875991</v>
       </c>
       <c r="CE95" t="n">
         <v>54.38971422125846</v>
       </c>
       <c r="CF95" t="n">
-        <v>38.17917796684818</v>
+        <v>38.17917796687561</v>
       </c>
       <c r="CG95" t="n">
         <v>42.70908862729615</v>
@@ -40407,7 +40383,7 @@
         <v>7.820976491862575</v>
       </c>
       <c r="CM95" t="n">
-        <v>7.094463766385273</v>
+        <v>7.094463766462211</v>
       </c>
       <c r="CN95" t="inlineStr">
         <is>
@@ -40694,10 +40670,10 @@
         <v>19.59000015258789</v>
       </c>
       <c r="BX96" t="n">
-        <v>2.021554705666515</v>
+        <v>2.021554706097281</v>
       </c>
       <c r="BY96" t="n">
-        <v>3.749983979011385</v>
+        <v>3.749983979810457</v>
       </c>
       <c r="BZ96" t="n">
         <v>10.85148419823535</v>
@@ -40706,19 +40682,19 @@
         <v>9.057717523549277</v>
       </c>
       <c r="CB96" t="n">
-        <v>11.05024977989582</v>
+        <v>11.05024977903769</v>
       </c>
       <c r="CC96" t="n">
-        <v>7.567164103013291</v>
+        <v>7.567164102921736</v>
       </c>
       <c r="CD96" t="n">
-        <v>8.390001921994815</v>
+        <v>8.390001921296937</v>
       </c>
       <c r="CE96" t="n">
         <v>14.26878965170031</v>
       </c>
       <c r="CF96" t="n">
-        <v>9.276484451057177</v>
+        <v>9.276484450935964</v>
       </c>
       <c r="CG96" t="n">
         <v>9.057717523549277</v>
@@ -40739,7 +40715,7 @@
         <v>-58.38720925115738</v>
       </c>
       <c r="CM96" t="n">
-        <v>-52.64683829095463</v>
+        <v>-52.6468382915734</v>
       </c>
       <c r="CN96" t="inlineStr">
         <is>
@@ -41020,10 +40996,10 @@
         <v>7.78000020980835</v>
       </c>
       <c r="BX97" t="n">
-        <v>5.007638608110152</v>
+        <v>5.007638627088665</v>
       </c>
       <c r="BY97" t="n">
-        <v>7.291121813408381</v>
+        <v>7.291121841041097</v>
       </c>
       <c r="BZ97" t="n">
         <v>5.804304317217133</v>
@@ -41042,13 +41018,13 @@
         <v>7.482269761699905</v>
       </c>
       <c r="CF97" t="n">
-        <v>6.550785511618052</v>
+        <v>6.55078551938659</v>
       </c>
       <c r="CG97" t="n">
-        <v>6.547713065312757</v>
+        <v>6.547713079129115</v>
       </c>
       <c r="CH97" t="n">
-        <v>5.892941758781482</v>
+        <v>5.892941771216203</v>
       </c>
       <c r="CI97" t="n">
         <v>6</v>
@@ -41060,10 +41036,10 @@
         <v>5.9</v>
       </c>
       <c r="CL97" t="n">
-        <v>-24.25524935909164</v>
+        <v>-24.25524919926232</v>
       </c>
       <c r="CM97" t="n">
-        <v>-15.79967435785683</v>
+        <v>-15.79967425800416</v>
       </c>
       <c r="CN97" t="inlineStr">
         <is>
@@ -41342,10 +41318,10 @@
         <v>15.90999984741211</v>
       </c>
       <c r="BX98" t="n">
-        <v>8.011259054289059</v>
+        <v>8.011259040111675</v>
       </c>
       <c r="BY98" t="n">
-        <v>14.8608855457062</v>
+        <v>14.86088551940716</v>
       </c>
       <c r="BZ98" t="n">
         <v>10.43085096379072</v>
@@ -41366,7 +41342,7 @@
         <v>8.936869495263364</v>
       </c>
       <c r="CF98" t="n">
-        <v>12.31270293390986</v>
+        <v>12.31270292885031</v>
       </c>
       <c r="CG98" t="n">
         <v>9.978191393663952</v>
@@ -41387,7 +41363,7 @@
         <v>-43.55517070757051</v>
       </c>
       <c r="CM98" t="n">
-        <v>-22.61028879951482</v>
+        <v>-22.61028883131592</v>
       </c>
       <c r="CN98" t="inlineStr">
         <is>
@@ -41666,10 +41642,10 @@
         <v>6.96999979019165</v>
       </c>
       <c r="BX99" t="n">
-        <v>3.118821969423426</v>
+        <v>3.11882195960837</v>
       </c>
       <c r="BY99" t="n">
-        <v>5.785414753280454</v>
+        <v>5.785414735073527</v>
       </c>
       <c r="BZ99" t="inlineStr"/>
       <c r="CA99" t="inlineStr"/>
@@ -41680,13 +41656,13 @@
         <v>9.526511531301223</v>
       </c>
       <c r="CF99" t="n">
-        <v>6.143582751335035</v>
+        <v>6.143582741994373</v>
       </c>
       <c r="CG99" t="n">
-        <v>5.785414753280454</v>
+        <v>5.785414735073527</v>
       </c>
       <c r="CH99" t="n">
-        <v>5.206873277952409</v>
+        <v>5.206873261566174</v>
       </c>
       <c r="CI99" t="n">
         <v>3</v>
@@ -41698,10 +41674,10 @@
         <v>3.1</v>
       </c>
       <c r="CL99" t="n">
-        <v>-25.29593350519687</v>
+        <v>-25.29593374029351</v>
       </c>
       <c r="CM99" t="n">
-        <v>-11.85677279387539</v>
+        <v>-11.85677292788776</v>
       </c>
       <c r="CN99" t="inlineStr">
         <is>
@@ -41980,25 +41956,25 @@
         <v>47.2400016784668</v>
       </c>
       <c r="BX100" t="n">
-        <v>18.15640576604682</v>
+        <v>18.15640571213811</v>
       </c>
       <c r="BY100" t="n">
-        <v>20.57934589188578</v>
+        <v>20.57934586536246</v>
       </c>
       <c r="BZ100" t="n">
-        <v>25.36192500085788</v>
+        <v>25.36192504347344</v>
       </c>
       <c r="CA100" t="n">
         <v>53.3467002990466</v>
       </c>
       <c r="CB100" t="n">
-        <v>21.45195356794589</v>
+        <v>21.45195357661538</v>
       </c>
       <c r="CC100" t="n">
-        <v>23.33743286668126</v>
+        <v>23.33743287099234</v>
       </c>
       <c r="CD100" t="n">
-        <v>11.2574219338688</v>
+        <v>11.25742197077686</v>
       </c>
       <c r="CE100" t="n">
         <v>121.096867054075</v>
@@ -42294,37 +42270,37 @@
         <v>23.35000038146973</v>
       </c>
       <c r="BX101" t="n">
-        <v>5.114427492218534</v>
+        <v>5.114427508279144</v>
       </c>
       <c r="BY101" t="n">
-        <v>7.202559910278175</v>
+        <v>7.20255991377094</v>
       </c>
       <c r="BZ101" t="n">
-        <v>10.55646943140762</v>
+        <v>10.55646940337679</v>
       </c>
       <c r="CA101" t="n">
         <v>14.59026773421743</v>
       </c>
       <c r="CB101" t="n">
-        <v>7.092388201669571</v>
+        <v>7.092388185647724</v>
       </c>
       <c r="CC101" t="n">
-        <v>8.429566137245022</v>
+        <v>8.429566135221071</v>
       </c>
       <c r="CD101" t="n">
-        <v>5.238787021228078</v>
+        <v>5.238787004805141</v>
       </c>
       <c r="CE101" t="n">
         <v>10.33412711493239</v>
       </c>
       <c r="CF101" t="n">
-        <v>8.569824130399603</v>
+        <v>8.569824125031328</v>
       </c>
       <c r="CG101" t="n">
-        <v>7.816063023761599</v>
+        <v>7.816063024496005</v>
       </c>
       <c r="CH101" t="n">
-        <v>7.034456721385439</v>
+        <v>7.034456722046404</v>
       </c>
       <c r="CI101" t="n">
         <v>8</v>
@@ -42336,10 +42312,10 @@
         <v>2.9</v>
       </c>
       <c r="CL101" t="n">
-        <v>-69.87384750979319</v>
+        <v>-69.87384750696252</v>
       </c>
       <c r="CM101" t="n">
-        <v>-63.29839832807664</v>
+        <v>-63.29839835106712</v>
       </c>
       <c r="CN101" t="inlineStr">
         <is>
@@ -42622,10 +42598,10 @@
         <v>12.18000030517578</v>
       </c>
       <c r="BX102" t="n">
-        <v>2.166666232411048</v>
+        <v>2.166666232431601</v>
       </c>
       <c r="BY102" t="n">
-        <v>4.019165861122495</v>
+        <v>4.019165861160619</v>
       </c>
       <c r="BZ102" t="n">
         <v>12.84912452576267</v>
@@ -42634,25 +42610,25 @@
         <v>14.24321699181254</v>
       </c>
       <c r="CB102" t="n">
-        <v>9.379078961444545</v>
+        <v>9.379078961437388</v>
       </c>
       <c r="CC102" t="n">
-        <v>5.744344356697985</v>
+        <v>5.744344356696323</v>
       </c>
       <c r="CD102" t="n">
-        <v>6.967979817055708</v>
+        <v>6.967979817036809</v>
       </c>
       <c r="CE102" t="n">
         <v>12.18000030517578</v>
       </c>
       <c r="CF102" t="n">
-        <v>9.34041583129596</v>
+        <v>9.340415831297447</v>
       </c>
       <c r="CG102" t="n">
-        <v>9.379078961444545</v>
+        <v>9.379078961437388</v>
       </c>
       <c r="CH102" t="n">
-        <v>8.441171065300091</v>
+        <v>8.44117106529365</v>
       </c>
       <c r="CI102" t="n">
         <v>7</v>
@@ -42664,10 +42640,10 @@
         <v>6.6</v>
       </c>
       <c r="CL102" t="n">
-        <v>-30.69646261245912</v>
+        <v>-30.696462612512</v>
       </c>
       <c r="CM102" t="n">
-        <v>-23.31350084345372</v>
+        <v>-23.31350084344151</v>
       </c>
       <c r="CN102" t="inlineStr">
         <is>
@@ -42706,7 +42682,7 @@
         <v>-2.090026398533917</v>
       </c>
       <c r="CZ102" t="n">
-        <v>-25.25442765560502</v>
+        <v>-25.25441878355007</v>
       </c>
       <c r="DA102" t="b">
         <v>0</v>
@@ -42950,10 +42926,10 @@
         <v>46.34000015258789</v>
       </c>
       <c r="BX103" t="n">
-        <v>10.13865028202517</v>
+        <v>10.13865032889544</v>
       </c>
       <c r="BY103" t="n">
-        <v>18.8071962731567</v>
+        <v>18.80719636010103</v>
       </c>
       <c r="BZ103" t="n">
         <v>85.63528619550759</v>
@@ -42962,13 +42938,13 @@
         <v>75.5695277891077</v>
       </c>
       <c r="CB103" t="n">
-        <v>102.7137955453257</v>
+        <v>102.713795528967</v>
       </c>
       <c r="CC103" t="n">
-        <v>15.99814152321454</v>
+        <v>15.99814152084787</v>
       </c>
       <c r="CD103" t="n">
-        <v>69.38497643643309</v>
+        <v>69.38497636862495</v>
       </c>
       <c r="CE103" t="n">
         <v>21.49551710110895</v>
@@ -43268,37 +43244,37 @@
         <v>53.65000152587891</v>
       </c>
       <c r="BX104" t="n">
-        <v>16.38838750787029</v>
+        <v>16.38838750919277</v>
       </c>
       <c r="BY104" t="n">
-        <v>25.10603633543943</v>
+        <v>25.10603633621325</v>
       </c>
       <c r="BZ104" t="n">
-        <v>45.79263204683181</v>
+        <v>45.79263204454791</v>
       </c>
       <c r="CA104" t="n">
         <v>63.31865958566679</v>
       </c>
       <c r="CB104" t="n">
-        <v>36.53709860140184</v>
+        <v>36.5370986010205</v>
       </c>
       <c r="CC104" t="n">
-        <v>26.7781074603687</v>
+        <v>26.77810746025687</v>
       </c>
       <c r="CD104" t="n">
-        <v>22.89631174456208</v>
+        <v>22.89631174341459</v>
       </c>
       <c r="CE104" t="n">
         <v>21.28296611184845</v>
       </c>
       <c r="CF104" t="n">
-        <v>32.26252492424867</v>
+        <v>32.26252492402014</v>
       </c>
       <c r="CG104" t="n">
-        <v>25.94207189790406</v>
+        <v>25.94207189823506</v>
       </c>
       <c r="CH104" t="n">
-        <v>23.34786470811366</v>
+        <v>23.34786470841155</v>
       </c>
       <c r="CI104" t="n">
         <v>8</v>
@@ -43310,10 +43286,10 @@
         <v>3.9</v>
       </c>
       <c r="CL104" t="n">
-        <v>-56.48114810052437</v>
+        <v>-56.48114809996911</v>
       </c>
       <c r="CM104" t="n">
-        <v>-39.86482011806402</v>
+        <v>-39.86482011848999</v>
       </c>
       <c r="CN104" t="inlineStr">
         <is>
@@ -43608,10 +43584,10 @@
         <v>3.009999990463257</v>
       </c>
       <c r="BX105" t="n">
-        <v>0.6298002122623935</v>
+        <v>0.6298002101155826</v>
       </c>
       <c r="BY105" t="n">
-        <v>1.16827939374674</v>
+        <v>1.168279389764406</v>
       </c>
       <c r="BZ105" t="n">
         <v>3.655591189151068</v>
@@ -43620,13 +43596,13 @@
         <v>4.238661238286214</v>
       </c>
       <c r="CB105" t="n">
-        <v>2.604672399754464</v>
+        <v>2.604672399875917</v>
       </c>
       <c r="CC105" t="n">
-        <v>2.640588270386397</v>
+        <v>2.640588270644858</v>
       </c>
       <c r="CD105" t="n">
-        <v>1.866256391568846</v>
+        <v>1.866256393376804</v>
       </c>
       <c r="CE105" t="n">
         <v>9.198296956105558</v>
@@ -43922,25 +43898,25 @@
         <v>14.64000034332275</v>
       </c>
       <c r="BX106" t="n">
-        <v>3.695138816303984</v>
+        <v>3.69513882885689</v>
       </c>
       <c r="BY106" t="n">
-        <v>4.706896824861083</v>
+        <v>4.706896838777946</v>
       </c>
       <c r="BZ106" t="n">
-        <v>14.38487144154272</v>
+        <v>14.38487143520698</v>
       </c>
       <c r="CA106" t="n">
         <v>37.51681749325965</v>
       </c>
       <c r="CB106" t="n">
-        <v>9.873209678960782</v>
+        <v>9.87320969085691</v>
       </c>
       <c r="CC106" t="n">
-        <v>48.41659564510339</v>
+        <v>48.41659564299174</v>
       </c>
       <c r="CD106" t="n">
-        <v>6.917949868796486</v>
+        <v>6.917949864344725</v>
       </c>
       <c r="CE106" t="n">
         <v>21.52179483859446</v>
@@ -44536,10 +44512,10 @@
         <v>58.11999893188477</v>
       </c>
       <c r="BX108" t="n">
-        <v>65.75643233938598</v>
+        <v>65.75643254497751</v>
       </c>
       <c r="BY108" t="n">
-        <v>95.74136548614599</v>
+        <v>95.74136578548726</v>
       </c>
       <c r="BZ108" t="n">
         <v>24.17791955566406</v>
@@ -45454,10 +45430,10 @@
         <v>96.33999633789062</v>
       </c>
       <c r="BX111" t="n">
-        <v>4.919793614619158</v>
+        <v>4.919793617114246</v>
       </c>
       <c r="BY111" t="n">
-        <v>9.126217155118537</v>
+        <v>9.126217159746927</v>
       </c>
       <c r="BZ111" t="n">
         <v>40.88741036121239</v>
@@ -45466,13 +45442,13 @@
         <v>40.58994084391919</v>
       </c>
       <c r="CB111" t="n">
-        <v>33.39208159901381</v>
+        <v>33.39208159558813</v>
       </c>
       <c r="CC111" t="n">
-        <v>17.63215568158022</v>
+        <v>17.63215568134438</v>
       </c>
       <c r="CD111" t="n">
-        <v>27.84617054063945</v>
+        <v>27.84617053778286</v>
       </c>
       <c r="CE111" t="n">
         <v>40.97990082873793</v>
@@ -45768,10 +45744,10 @@
         <v>17.45000076293945</v>
       </c>
       <c r="BX112" t="n">
-        <v>3.276083604449043</v>
+        <v>3.276083610302049</v>
       </c>
       <c r="BY112" t="n">
-        <v>6.077135086252974</v>
+        <v>6.077135097110301</v>
       </c>
       <c r="BZ112" t="n">
         <v>14.63370317145239</v>
@@ -45780,23 +45756,23 @@
         <v>15.60803264394471</v>
       </c>
       <c r="CB112" t="n">
-        <v>10.20015846456556</v>
+        <v>10.20015846049232</v>
       </c>
       <c r="CC112" t="n">
-        <v>13.0059406848976</v>
+        <v>13.00594068387477</v>
       </c>
       <c r="CD112" t="n">
-        <v>7.537281018892449</v>
+        <v>7.537281013072218</v>
       </c>
       <c r="CE112" t="inlineStr"/>
       <c r="CF112" t="n">
-        <v>11.17704184500095</v>
+        <v>11.17704184499112</v>
       </c>
       <c r="CG112" t="n">
-        <v>11.60304957473158</v>
+        <v>11.60304957218355</v>
       </c>
       <c r="CH112" t="n">
-        <v>10.44274461725842</v>
+        <v>10.44274461496519</v>
       </c>
       <c r="CI112" t="n">
         <v>6</v>
@@ -45808,10 +45784,10 @@
         <v>4.8</v>
       </c>
       <c r="CL112" t="n">
-        <v>-40.15619392156782</v>
+        <v>-40.15619393470955</v>
       </c>
       <c r="CM112" t="n">
-        <v>-35.94818706977423</v>
+        <v>-35.94818706983056</v>
       </c>
       <c r="CN112" t="inlineStr">
         <is>
@@ -46090,10 +46066,10 @@
         <v>14.52999973297119</v>
       </c>
       <c r="BX113" t="n">
-        <v>1.359804413051002</v>
+        <v>1.359804409499072</v>
       </c>
       <c r="BY113" t="n">
-        <v>2.522437186209608</v>
+        <v>2.522437179620779</v>
       </c>
       <c r="BZ113" t="n">
         <v>8.9254750330027</v>
@@ -46102,13 +46078,13 @@
         <v>10.96999041107547</v>
       </c>
       <c r="CB113" t="n">
-        <v>4.980524740385874</v>
+        <v>4.980524742297348</v>
       </c>
       <c r="CC113" t="n">
-        <v>7.696681031615996</v>
+        <v>7.696681032070176</v>
       </c>
       <c r="CD113" t="n">
-        <v>4.375380390907757</v>
+        <v>4.375380393558349</v>
       </c>
       <c r="CE113" t="n">
         <v>11.24969464648006</v>
@@ -46408,10 +46384,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX114" t="n">
-        <v>11.98290318703899</v>
+        <v>11.9829032728864</v>
       </c>
       <c r="BY114" t="n">
-        <v>14.9525791942617</v>
+        <v>14.95257930138434</v>
       </c>
       <c r="BZ114" t="inlineStr"/>
       <c r="CA114" t="inlineStr"/>
@@ -46714,10 +46690,10 @@
         <v>11.18000030517578</v>
       </c>
       <c r="BX115" t="n">
-        <v>2.429612152241572</v>
+        <v>2.429612155142877</v>
       </c>
       <c r="BY115" t="n">
-        <v>4.506930542408115</v>
+        <v>4.506930547790037</v>
       </c>
       <c r="BZ115" t="n">
         <v>12.21228392774766</v>
@@ -46726,13 +46702,13 @@
         <v>12.73311481937156</v>
       </c>
       <c r="CB115" t="n">
-        <v>9.672110408086258</v>
+        <v>9.672110406637819</v>
       </c>
       <c r="CC115" t="n">
-        <v>0.7924908650735042</v>
+        <v>0.7924908650351182</v>
       </c>
       <c r="CD115" t="n">
-        <v>6.779198843823884</v>
+        <v>6.779198840808614</v>
       </c>
       <c r="CE115" t="n">
         <v>7.307661395663775</v>
@@ -47028,10 +47004,10 @@
         <v>3.430000066757202</v>
       </c>
       <c r="BX116" t="n">
-        <v>1.689358881558354</v>
+        <v>1.689358879924533</v>
       </c>
       <c r="BY116" t="n">
-        <v>3.133760725290748</v>
+        <v>3.133760722260009</v>
       </c>
       <c r="BZ116" t="n">
         <v>1.168015956939936</v>
@@ -47040,7 +47016,7 @@
         <v>4.684615221800192</v>
       </c>
       <c r="CB116" t="n">
-        <v>1.621588925970825</v>
+        <v>1.621588925382969</v>
       </c>
       <c r="CC116" t="n">
         <v>0.7445919647652398</v>
@@ -47342,10 +47318,10 @@
         <v>4.809999942779541</v>
       </c>
       <c r="BX117" t="n">
-        <v>1.479418497515615</v>
+        <v>1.479418504494636</v>
       </c>
       <c r="BY117" t="n">
-        <v>1.541882834077386</v>
+        <v>1.541882841351076</v>
       </c>
       <c r="BZ117" t="inlineStr"/>
       <c r="CA117" t="inlineStr"/>
@@ -47646,25 +47622,25 @@
         <v>8.739999771118164</v>
       </c>
       <c r="BX118" t="n">
-        <v>2.247634684342729</v>
+        <v>2.247634679547916</v>
       </c>
       <c r="BY118" t="n">
-        <v>2.421011758180439</v>
+        <v>2.421011754352162</v>
       </c>
       <c r="BZ118" t="n">
-        <v>3.136387959709285</v>
+        <v>3.136387961440567</v>
       </c>
       <c r="CA118" t="n">
         <v>9.827685355919407</v>
       </c>
       <c r="CB118" t="n">
-        <v>1.829365608483809</v>
+        <v>1.829365607964123</v>
       </c>
       <c r="CC118" t="n">
-        <v>5.905845202067193</v>
+        <v>5.905845202442174</v>
       </c>
       <c r="CD118" t="n">
-        <v>1.316356164754305</v>
+        <v>1.316356166395666</v>
       </c>
       <c r="CE118" t="n">
         <v>12.81521599596358</v>
@@ -47960,10 +47936,10 @@
         <v>6.559999942779541</v>
       </c>
       <c r="BX119" t="n">
-        <v>1.053466679878761</v>
+        <v>1.053466678466391</v>
       </c>
       <c r="BY119" t="n">
-        <v>1.954180691175101</v>
+        <v>1.954180688555155</v>
       </c>
       <c r="BZ119" t="inlineStr"/>
       <c r="CA119" t="inlineStr"/>
@@ -48264,25 +48240,25 @@
         <v>3.700000047683716</v>
       </c>
       <c r="BX120" t="n">
-        <v>1.267030928589983</v>
+        <v>1.267030927375455</v>
       </c>
       <c r="BY120" t="n">
-        <v>1.30289296055145</v>
+        <v>1.302892959735767</v>
       </c>
       <c r="BZ120" t="n">
-        <v>1.408844262616528</v>
+        <v>1.408844263084978</v>
       </c>
       <c r="CA120" t="n">
         <v>4.28417545380731</v>
       </c>
       <c r="CB120" t="n">
-        <v>0.9846225511757564</v>
+        <v>0.9846225510611476</v>
       </c>
       <c r="CC120" t="n">
-        <v>2.173299920822292</v>
+        <v>2.173299920908887</v>
       </c>
       <c r="CD120" t="n">
-        <v>0.5532971883591499</v>
+        <v>0.5532971888411715</v>
       </c>
       <c r="CE120" t="n">
         <v>5.184427633155422</v>
@@ -48582,10 +48558,10 @@
         <v>5.510000228881836</v>
       </c>
       <c r="BX121" t="n">
-        <v>5.460017772915138</v>
+        <v>5.460017774836723</v>
       </c>
       <c r="BY121" t="n">
-        <v>7.949785877364442</v>
+        <v>7.94978588016227</v>
       </c>
       <c r="BZ121" t="inlineStr"/>
       <c r="CA121" t="inlineStr"/>
@@ -48594,13 +48570,13 @@
       <c r="CD121" t="inlineStr"/>
       <c r="CE121" t="inlineStr"/>
       <c r="CF121" t="n">
-        <v>6.70490182513979</v>
+        <v>6.704901827499496</v>
       </c>
       <c r="CG121" t="n">
-        <v>6.70490182513979</v>
+        <v>6.704901827499496</v>
       </c>
       <c r="CH121" t="n">
-        <v>6.034411642625811</v>
+        <v>6.034411644749547</v>
       </c>
       <c r="CI121" t="n">
         <v>2</v>
@@ -48612,10 +48588,10 @@
         <v>1.5</v>
       </c>
       <c r="CL121" t="n">
-        <v>9.517448129950367</v>
+        <v>9.517448168493647</v>
       </c>
       <c r="CM121" t="n">
-        <v>21.68605347772263</v>
+        <v>21.68605352054851</v>
       </c>
       <c r="CN121" t="inlineStr">
         <is>
@@ -48894,10 +48870,10 @@
         <v>5.079999923706055</v>
       </c>
       <c r="BX122" t="n">
-        <v>5.591984110918216</v>
+        <v>5.591984107803732</v>
       </c>
       <c r="BY122" t="n">
-        <v>9.969901310044307</v>
+        <v>9.96990130449152</v>
       </c>
       <c r="BZ122" t="inlineStr"/>
       <c r="CA122" t="inlineStr"/>
@@ -48906,13 +48882,13 @@
       <c r="CD122" t="inlineStr"/>
       <c r="CE122" t="inlineStr"/>
       <c r="CF122" t="n">
-        <v>7.780942710481261</v>
+        <v>7.780942706147626</v>
       </c>
       <c r="CG122" t="n">
-        <v>7.780942710481261</v>
+        <v>7.780942706147626</v>
       </c>
       <c r="CH122" t="n">
-        <v>7.002848439433135</v>
+        <v>7.002848435532863</v>
       </c>
       <c r="CI122" t="n">
         <v>2</v>
@@ -48924,10 +48900,10 @@
         <v>1.8</v>
       </c>
       <c r="CL122" t="n">
-        <v>37.85134930325529</v>
+        <v>37.85134922647828</v>
       </c>
       <c r="CM122" t="n">
-        <v>53.16816589250586</v>
+        <v>53.1681658071981</v>
       </c>
       <c r="CN122" t="inlineStr">
         <is>
@@ -49192,10 +49168,10 @@
         <v>21.88999938964844</v>
       </c>
       <c r="BX123" t="n">
-        <v>37.94222254853295</v>
+        <v>37.94222268302835</v>
       </c>
       <c r="BY123" t="n">
-        <v>70.38282282752863</v>
+        <v>70.38282307701759</v>
       </c>
       <c r="BZ123" t="n">
         <v>20.07214476905479</v>
@@ -49214,7 +49190,7 @@
       </c>
       <c r="CE123" t="inlineStr"/>
       <c r="CF123" t="n">
-        <v>26.06992673983088</v>
+        <v>26.06992676224678</v>
       </c>
       <c r="CG123" t="n">
         <v>23.36448533113464</v>
@@ -49235,7 +49211,7 @@
         <v>-3.937700391325161</v>
       </c>
       <c r="CM123" t="n">
-        <v>19.09514603348546</v>
+        <v>19.09514613588792</v>
       </c>
       <c r="CN123" t="inlineStr">
         <is>
@@ -49514,25 +49490,25 @@
         <v>9.210000038146973</v>
       </c>
       <c r="BX124" t="n">
-        <v>3.562432704321006</v>
+        <v>3.562432711923043</v>
       </c>
       <c r="BY124" t="n">
-        <v>3.670924901888007</v>
+        <v>3.670924908504101</v>
       </c>
       <c r="BZ124" t="n">
-        <v>4.387649662036944</v>
+        <v>4.387649660581783</v>
       </c>
       <c r="CA124" t="n">
         <v>19.06106624245507</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.445242680944758</v>
+        <v>3.44524268545998</v>
       </c>
       <c r="CC124" t="n">
-        <v>7.613744425479803</v>
+        <v>7.613744425177771</v>
       </c>
       <c r="CD124" t="n">
-        <v>1.728975899933417</v>
+        <v>1.728975898441593</v>
       </c>
       <c r="CE124" t="n">
         <v>20.19385877757074</v>
@@ -49828,10 +49804,10 @@
         <v>11.46000003814697</v>
       </c>
       <c r="BX125" t="n">
-        <v>0.7792719061356694</v>
+        <v>0.7792719063752643</v>
       </c>
       <c r="BY125" t="n">
-        <v>1.445549385881667</v>
+        <v>1.445549386326115</v>
       </c>
       <c r="BZ125" t="n">
         <v>16.15372345802631</v>
@@ -49840,13 +49816,13 @@
         <v>16.82869587224833</v>
       </c>
       <c r="CB125" t="n">
-        <v>14.21481600336672</v>
+        <v>14.21481600332909</v>
       </c>
       <c r="CC125" t="n">
-        <v>1.741983299190928</v>
+        <v>1.741983299185836</v>
       </c>
       <c r="CD125" t="n">
-        <v>11.46236536769968</v>
+        <v>11.46236536745172</v>
       </c>
       <c r="CE125" t="inlineStr"/>
       <c r="CF125" t="inlineStr"/>
@@ -50434,25 +50410,25 @@
         <v>19</v>
       </c>
       <c r="BX127" t="n">
-        <v>0.5916775938526385</v>
+        <v>0.5916775922706038</v>
       </c>
       <c r="BY127" t="n">
-        <v>0.7950536082428489</v>
+        <v>0.7950536062625092</v>
       </c>
       <c r="BZ127" t="n">
-        <v>4.662824168693428</v>
+        <v>4.662824169546663</v>
       </c>
       <c r="CA127" t="n">
         <v>11.65078630453671</v>
       </c>
       <c r="CB127" t="n">
-        <v>1.787429577069247</v>
+        <v>1.787429577368941</v>
       </c>
       <c r="CC127" t="n">
-        <v>0.6882468011063573</v>
+        <v>0.6882468011182408</v>
       </c>
       <c r="CD127" t="n">
-        <v>2.288200648570193</v>
+        <v>2.28820064911454</v>
       </c>
       <c r="CE127" t="n">
         <v>19</v>
@@ -50752,10 +50728,10 @@
         <v>5.150000095367432</v>
       </c>
       <c r="BX128" t="n">
-        <v>1.268396230781867</v>
+        <v>1.268396220627904</v>
       </c>
       <c r="BY128" t="n">
-        <v>2.122834055335833</v>
+        <v>2.122834038341793</v>
       </c>
       <c r="BZ128" t="inlineStr"/>
       <c r="CA128" t="inlineStr"/>
@@ -50766,13 +50742,13 @@
         <v>5.988941589713868</v>
       </c>
       <c r="CF128" t="n">
-        <v>1.69561514305885</v>
+        <v>1.695615129484849</v>
       </c>
       <c r="CG128" t="n">
-        <v>1.69561514305885</v>
+        <v>1.695615129484849</v>
       </c>
       <c r="CH128" t="n">
-        <v>1.526053628752965</v>
+        <v>1.526053616536364</v>
       </c>
       <c r="CI128" t="n">
         <v>2</v>
@@ -50784,10 +50760,10 @@
         <v>4.7</v>
       </c>
       <c r="CL128" t="n">
-        <v>-70.36789125255176</v>
+        <v>-70.36789148976732</v>
       </c>
       <c r="CM128" t="n">
-        <v>-67.07543472505752</v>
+        <v>-67.07543498863035</v>
       </c>
       <c r="CN128" t="inlineStr">
         <is>
@@ -51070,37 +51046,37 @@
         <v>17.20999908447266</v>
       </c>
       <c r="BX129" t="n">
-        <v>2.072597801662844</v>
+        <v>2.072597801449315</v>
       </c>
       <c r="BY129" t="n">
-        <v>3.775021108484919</v>
+        <v>3.775021108266213</v>
       </c>
       <c r="BZ129" t="n">
-        <v>10.46758215585021</v>
+        <v>10.46758215632219</v>
       </c>
       <c r="CA129" t="n">
         <v>12.60778163571021</v>
       </c>
       <c r="CB129" t="n">
-        <v>6.07375064058401</v>
+        <v>6.07375064071838</v>
       </c>
       <c r="CC129" t="n">
-        <v>5.548158129579353</v>
+        <v>5.548158129597208</v>
       </c>
       <c r="CD129" t="n">
-        <v>5.114486566395594</v>
+        <v>5.114486566567903</v>
       </c>
       <c r="CE129" t="n">
         <v>15.99015396619785</v>
       </c>
       <c r="CF129" t="n">
-        <v>7.264463372767382</v>
+        <v>7.264463372863683</v>
       </c>
       <c r="CG129" t="n">
-        <v>5.810954385081681</v>
+        <v>5.810954385157794</v>
       </c>
       <c r="CH129" t="n">
-        <v>5.229858946573513</v>
+        <v>5.229858946642015</v>
       </c>
       <c r="CI129" t="n">
         <v>6</v>
@@ -51112,10 +51088,10 @@
         <v>7.7</v>
       </c>
       <c r="CL129" t="n">
-        <v>-69.61150944341399</v>
+        <v>-69.61150944301595</v>
       </c>
       <c r="CM129" t="n">
-        <v>-57.78928669832653</v>
+        <v>-57.78928669776696</v>
       </c>
       <c r="CN129" t="inlineStr">
         <is>
@@ -51992,10 +51968,10 @@
         <v>4.21999979019165</v>
       </c>
       <c r="BX132" t="n">
-        <v>0.8881979179583234</v>
+        <v>0.8881979188081729</v>
       </c>
       <c r="BY132" t="n">
-        <v>0.9831240704401192</v>
+        <v>0.9831240713807964</v>
       </c>
       <c r="BZ132" t="inlineStr"/>
       <c r="CA132" t="inlineStr"/>
@@ -52004,13 +51980,13 @@
       <c r="CD132" t="inlineStr"/>
       <c r="CE132" t="inlineStr"/>
       <c r="CF132" t="n">
-        <v>0.9356609941992213</v>
+        <v>0.9356609950944846</v>
       </c>
       <c r="CG132" t="n">
-        <v>0.9356609941992213</v>
+        <v>0.9356609950944846</v>
       </c>
       <c r="CH132" t="n">
-        <v>0.8420948947792992</v>
+        <v>0.8420948955850361</v>
       </c>
       <c r="CI132" t="n">
         <v>2</v>
@@ -52022,10 +51998,10 @@
         <v>1.1</v>
       </c>
       <c r="CL132" t="n">
-        <v>-80.04514368136839</v>
+        <v>-80.04514366227509</v>
       </c>
       <c r="CM132" t="n">
-        <v>-77.82793742374265</v>
+        <v>-77.82793740252789</v>
       </c>
       <c r="CN132" t="inlineStr">
         <is>
@@ -52306,10 +52282,10 @@
         <v>1.220000028610229</v>
       </c>
       <c r="BX133" t="n">
-        <v>0.3579768036191621</v>
+        <v>0.3579768030146158</v>
       </c>
       <c r="BY133" t="n">
-        <v>0.6640469707135457</v>
+        <v>0.6640469695921123</v>
       </c>
       <c r="BZ133" t="inlineStr"/>
       <c r="CA133" t="inlineStr"/>
@@ -52318,13 +52294,13 @@
       <c r="CD133" t="inlineStr"/>
       <c r="CE133" t="inlineStr"/>
       <c r="CF133" t="n">
-        <v>0.5110118871663539</v>
+        <v>0.511011886303364</v>
       </c>
       <c r="CG133" t="n">
-        <v>0.5110118871663539</v>
+        <v>0.511011886303364</v>
       </c>
       <c r="CH133" t="n">
-        <v>0.4599106984497185</v>
+        <v>0.4599106976730276</v>
       </c>
       <c r="CI133" t="n">
         <v>2</v>
@@ -52336,10 +52312,10 @@
         <v>1.9</v>
       </c>
       <c r="CL133" t="n">
-        <v>-62.30240265046316</v>
+        <v>-62.30240271412634</v>
       </c>
       <c r="CM133" t="n">
-        <v>-58.11378072273685</v>
+        <v>-58.11378079347372</v>
       </c>
       <c r="CN133" t="inlineStr">
         <is>
@@ -52926,10 +52902,10 @@
         <v>5.460000038146973</v>
       </c>
       <c r="BX135" t="n">
-        <v>1.04055658505233</v>
+        <v>1.040556584531107</v>
       </c>
       <c r="BY135" t="n">
-        <v>1.930232465272072</v>
+        <v>1.930232464305204</v>
       </c>
       <c r="BZ135" t="inlineStr"/>
       <c r="CA135" t="inlineStr"/>
@@ -52940,13 +52916,13 @@
         <v>2.857508361672422</v>
       </c>
       <c r="CF135" t="n">
-        <v>1.942765803998941</v>
+        <v>1.942765803502911</v>
       </c>
       <c r="CG135" t="n">
-        <v>1.930232465272072</v>
+        <v>1.930232464305204</v>
       </c>
       <c r="CH135" t="n">
-        <v>1.737209218744865</v>
+        <v>1.737209217874684</v>
       </c>
       <c r="CI135" t="n">
         <v>3</v>
@@ -52958,10 +52934,10 @@
         <v>2.7</v>
       </c>
       <c r="CL135" t="n">
-        <v>-68.18298156396271</v>
+        <v>-68.1829815799001</v>
       </c>
       <c r="CM135" t="n">
-        <v>-64.41820896656473</v>
+        <v>-64.41820897564953</v>
       </c>
       <c r="CN135" t="inlineStr">
         <is>
@@ -53238,10 +53214,10 @@
         <v>37.15000152587891</v>
       </c>
       <c r="BX136" t="n">
-        <v>8.367448543929402</v>
+        <v>8.367448523268322</v>
       </c>
       <c r="BY136" t="n">
-        <v>12.18300507996121</v>
+        <v>12.18300504987868</v>
       </c>
       <c r="BZ136" t="n">
         <v>8.093004102830763</v>
@@ -53550,25 +53526,25 @@
         <v>4.840000152587891</v>
       </c>
       <c r="BX137" t="n">
-        <v>1.502502730193916</v>
+        <v>1.502502729733199</v>
       </c>
       <c r="BY137" t="n">
-        <v>1.672911392047966</v>
+        <v>1.672911391644893</v>
       </c>
       <c r="BZ137" t="n">
-        <v>2.547478598018235</v>
+        <v>2.547478598185582</v>
       </c>
       <c r="CA137" t="n">
         <v>7.892423639597566</v>
       </c>
       <c r="CB137" t="n">
-        <v>1.797906281227365</v>
+        <v>1.7979062810385</v>
       </c>
       <c r="CC137" t="n">
-        <v>1.843026215586434</v>
+        <v>1.843026215599957</v>
       </c>
       <c r="CD137" t="n">
-        <v>1.110767097235213</v>
+        <v>1.110767097384817</v>
       </c>
       <c r="CE137" t="n">
         <v>0.03519118999648198</v>
@@ -53862,10 +53838,10 @@
         <v>1.990000009536743</v>
       </c>
       <c r="BX138" t="n">
-        <v>0.5586583815869235</v>
+        <v>0.5586583797686923</v>
       </c>
       <c r="BY138" t="n">
-        <v>0.8134066035905607</v>
+        <v>0.8134066009432162</v>
       </c>
       <c r="BZ138" t="n">
         <v>0.3613128508935427</v>
@@ -53928,7 +53904,7 @@
         <v>-0.9950239314132636</v>
       </c>
       <c r="CZ138" t="n">
-        <v>-53.22526227613638</v>
+        <v>-53.22525700906506</v>
       </c>
       <c r="DA138" t="b">
         <v>0</v>
@@ -54170,10 +54146,10 @@
         <v>6.889999866485596</v>
       </c>
       <c r="BX139" t="n">
-        <v>1.890787837944808</v>
+        <v>1.890787840472596</v>
       </c>
       <c r="BY139" t="n">
-        <v>2.75298709204764</v>
+        <v>2.7529870957281</v>
       </c>
       <c r="BZ139" t="n">
         <v>1.758861036118071</v>
@@ -55656,10 +55632,10 @@
         <v>18.30999946594238</v>
       </c>
       <c r="BX144" t="n">
-        <v>27.8510749884693</v>
+        <v>27.85107500824987</v>
       </c>
       <c r="BY144" t="n">
-        <v>37.25854920679671</v>
+        <v>37.25854923325872</v>
       </c>
       <c r="BZ144" t="n">
         <v>2.504827732555547</v>
@@ -55668,7 +55644,7 @@
         <v>6.943403056792157</v>
       </c>
       <c r="CB144" t="n">
-        <v>6.421002836500871</v>
+        <v>6.421002840465481</v>
       </c>
       <c r="CC144" t="n">
         <v>3.046690502845772</v>
@@ -55970,10 +55946,10 @@
         <v>3.75</v>
       </c>
       <c r="BX145" t="n">
-        <v>0.6782855629857154</v>
+        <v>0.6782855620059272</v>
       </c>
       <c r="BY145" t="n">
-        <v>1.258219719338502</v>
+        <v>1.258219717520995</v>
       </c>
       <c r="BZ145" t="inlineStr"/>
       <c r="CA145" t="inlineStr"/>
@@ -55984,13 +55960,13 @@
         <v>3.40392002364466</v>
       </c>
       <c r="CF145" t="n">
-        <v>0.9682526411621087</v>
+        <v>0.968252639763461</v>
       </c>
       <c r="CG145" t="n">
-        <v>0.9682526411621087</v>
+        <v>0.968252639763461</v>
       </c>
       <c r="CH145" t="n">
-        <v>0.8714273770458979</v>
+        <v>0.8714273757871149</v>
       </c>
       <c r="CI145" t="n">
         <v>2</v>
@@ -56002,10 +55978,10 @@
         <v>5</v>
       </c>
       <c r="CL145" t="n">
-        <v>-76.76193661210939</v>
+        <v>-76.76193664567693</v>
       </c>
       <c r="CM145" t="n">
-        <v>-74.17992956901043</v>
+        <v>-74.17992960630771</v>
       </c>
       <c r="CN145" t="inlineStr">
         <is>
@@ -56282,10 +56258,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX146" t="n">
-        <v>9.498030414271254</v>
+        <v>9.498030423145073</v>
       </c>
       <c r="BY146" t="n">
-        <v>13.82913228317895</v>
+        <v>13.82913229609923</v>
       </c>
       <c r="BZ146" t="n">
         <v>4.692896643862964</v>
@@ -56431,7 +56407,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Bandeira de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S147" t="n">
@@ -56641,11 +56617,7 @@
       </c>
       <c r="CP147" t="inlineStr"/>
       <c r="CQ147" t="inlineStr"/>
-      <c r="CR147" t="inlineStr">
-        <is>
-          <t>Bandeira de alta</t>
-        </is>
-      </c>
+      <c r="CR147" t="inlineStr"/>
       <c r="CS147" t="b">
         <v>0</v>
       </c>
@@ -56672,14 +56644,14 @@
         <v>0</v>
       </c>
       <c r="DB147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC147" t="b">
         <v>0</v>
       </c>
       <c r="DD147" t="inlineStr">
         <is>
-          <t>Bandeira de alta — mastro +33%, recuo 44% (candidato)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -57218,10 +57190,10 @@
         <v>10.71000003814697</v>
       </c>
       <c r="BX149" t="n">
-        <v>5.722370889056207</v>
+        <v>5.722370878007752</v>
       </c>
       <c r="BY149" t="n">
-        <v>10.47405812359843</v>
+        <v>10.47405810337567</v>
       </c>
       <c r="BZ149" t="inlineStr"/>
       <c r="CA149" t="inlineStr"/>
@@ -57232,13 +57204,13 @@
         <v>2.986819537882496</v>
       </c>
       <c r="CF149" t="n">
-        <v>6.394416183512379</v>
+        <v>6.39441617308864</v>
       </c>
       <c r="CG149" t="n">
-        <v>5.722370889056207</v>
+        <v>5.722370878007752</v>
       </c>
       <c r="CH149" t="n">
-        <v>5.150133800150586</v>
+        <v>5.150133790206977</v>
       </c>
       <c r="CI149" t="n">
         <v>3</v>
@@ -57250,10 +57222,10 @@
         <v>3.5</v>
       </c>
       <c r="CL149" t="n">
-        <v>-51.91284984307381</v>
+        <v>-51.91284993591797</v>
       </c>
       <c r="CM149" t="n">
-        <v>-40.29490045997487</v>
+        <v>-40.29490055730204</v>
       </c>
       <c r="CN149" t="inlineStr">
         <is>
@@ -57850,10 +57822,10 @@
         <v>15.35000038146973</v>
       </c>
       <c r="BX151" t="n">
-        <v>3.926670156039753</v>
+        <v>3.926670159407258</v>
       </c>
       <c r="BY151" t="n">
-        <v>5.717231747193881</v>
+        <v>5.717231752096968</v>
       </c>
       <c r="BZ151" t="inlineStr"/>
       <c r="CA151" t="inlineStr"/>
@@ -57864,7 +57836,7 @@
         <v>5.079183152512682</v>
       </c>
       <c r="CF151" t="n">
-        <v>4.907695018582105</v>
+        <v>4.907695021338969</v>
       </c>
       <c r="CG151" t="n">
         <v>5.079183152512682</v>
@@ -57885,7 +57857,7 @@
         <v>-70.21977378723865</v>
       </c>
       <c r="CM151" t="n">
-        <v>-68.02804627609915</v>
+        <v>-68.02804625813911</v>
       </c>
       <c r="CN151" t="inlineStr">
         <is>

--- a/reports/screener_2026-08-25.xlsx
+++ b/reports/screener_2026-08-25.xlsx
@@ -1186,10 +1186,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.868715973941502</v>
+        <v>5.868716083158859</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.88646813166149</v>
+        <v>10.88646833425968</v>
       </c>
       <c r="BZ2" t="n">
         <v>42.10015429633837</v>
@@ -1198,7 +1198,7 @@
         <v>28.26125673506212</v>
       </c>
       <c r="CB2" t="n">
-        <v>72.78655314526678</v>
+        <v>72.78655361286401</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -1268,7 +1268,7 @@
         <v>-4.94053016263244</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-26.59162359529691</v>
+        <v>-26.59161854099229</v>
       </c>
       <c r="DA2" t="b">
         <v>1</v>
@@ -1512,10 +1512,10 @@
         <v>13.60999965667725</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.01575560910662</v>
+        <v>15.01575552163967</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.85422665489277</v>
+        <v>27.85422649264158</v>
       </c>
       <c r="BZ3" t="n">
         <v>38.94870312116058</v>
@@ -1524,13 +1524,13 @@
         <v>23.57226802449605</v>
       </c>
       <c r="CB3" t="n">
-        <v>74.76041603016105</v>
+        <v>74.76041619500492</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.40383466993469</v>
+        <v>48.40383473421028</v>
       </c>
       <c r="CD3" t="n">
-        <v>26.30532685669047</v>
+        <v>26.30532712655051</v>
       </c>
       <c r="CE3" t="n">
         <v>8.655042371031668</v>
@@ -1830,10 +1830,10 @@
         <v>24.54000091552734</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.25388476298676</v>
+        <v>16.25388477199722</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.15095623534045</v>
+        <v>30.15095625205485</v>
       </c>
       <c r="BZ4" t="n">
         <v>74.06720094094243</v>
@@ -1842,13 +1842,13 @@
         <v>53.70833445174577</v>
       </c>
       <c r="CB4" t="n">
-        <v>132.6406024865115</v>
+        <v>132.640602484492</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.79451766935813</v>
+        <v>25.79451766811822</v>
       </c>
       <c r="CD4" t="n">
-        <v>65.72549929547127</v>
+        <v>65.72549927613987</v>
       </c>
       <c r="CE4" t="n">
         <v>43.53105147803891</v>
@@ -2146,10 +2146,10 @@
         <v>4.190000057220459</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.548072984339422</v>
+        <v>3.548072967645033</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.581675385949628</v>
+        <v>6.581675354981536</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.82159370858454</v>
@@ -2158,25 +2158,25 @@
         <v>8.61209444827186</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.80877191788858</v>
+        <v>24.80877193010127</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.29418311857289</v>
+        <v>11.2941831253625</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.96827541452747</v>
+        <v>10.96827545613256</v>
       </c>
       <c r="CE5" t="n">
         <v>5.153758142621466</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.238596703087977</v>
+        <v>9.238596705992412</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.790184931399665</v>
+        <v>9.790184952202209</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.811166438259699</v>
+        <v>8.811166456981988</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -2188,10 +2188,10 @@
         <v>7</v>
       </c>
       <c r="CL5" t="n">
-        <v>110.2903655830689</v>
+        <v>110.2903660299016</v>
       </c>
       <c r="CM5" t="n">
-        <v>120.4915650816633</v>
+        <v>120.4915651509816</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -2456,10 +2456,10 @@
         <v>48.2400016784668</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.38294919612916</v>
+        <v>18.38294911262449</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.10037075881959</v>
+        <v>34.10037060391842</v>
       </c>
       <c r="BZ6" t="n">
         <v>76.54850565744731</v>
@@ -2468,23 +2468,23 @@
         <v>57.29789298233228</v>
       </c>
       <c r="CB6" t="n">
-        <v>103.9926848938095</v>
+        <v>103.9926850208162</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.49285961704108</v>
+        <v>48.49285963693413</v>
       </c>
       <c r="CD6" t="n">
-        <v>61.42668270152836</v>
+        <v>61.42668286936607</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>44.38117130735928</v>
+        <v>44.38117125273109</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.29661518793034</v>
+        <v>41.29661512042627</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.1669536691373</v>
+        <v>37.16695360838365</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -2496,10 +2496,10 @@
         <v>4.2</v>
       </c>
       <c r="CL6" t="n">
-        <v>-22.95407882266357</v>
+        <v>-22.95407894860396</v>
       </c>
       <c r="CM6" t="n">
-        <v>-7.999233492626534</v>
+        <v>-7.999233605869049</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -2782,10 +2782,10 @@
         <v>4.510000228881836</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.052774371111656</v>
+        <v>3.052774367495619</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.662896458412121</v>
+        <v>5.662896451704373</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.93452446594899</v>
@@ -2794,7 +2794,7 @@
         <v>8.695832933160331</v>
       </c>
       <c r="CB7" t="n">
-        <v>23.89368931359106</v>
+        <v>23.89368930263338</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -2806,7 +2806,7 @@
         <v>5.186344183602181</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.39433292546434</v>
+        <v>11.39433292294071</v>
       </c>
       <c r="CG7" t="n">
         <v>11.57513776217851</v>
@@ -2827,7 +2827,7 @@
         <v>130.9894336423016</v>
       </c>
       <c r="CM7" t="n">
-        <v>152.6459500488615</v>
+        <v>152.6459499929051</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -3110,10 +3110,10 @@
         <v>32.58000183105469</v>
       </c>
       <c r="BX8" t="n">
-        <v>24.20136270938934</v>
+        <v>24.20136284443951</v>
       </c>
       <c r="BY8" t="n">
-        <v>44.89352782591723</v>
+        <v>44.89352807643529</v>
       </c>
       <c r="BZ8" t="n">
         <v>50.78647344252641</v>
@@ -3122,25 +3122,25 @@
         <v>22.31995674309305</v>
       </c>
       <c r="CB8" t="n">
-        <v>69.38361365461598</v>
+        <v>69.38361262200334</v>
       </c>
       <c r="CC8" t="n">
-        <v>53.12760909190684</v>
+        <v>53.12760893038791</v>
       </c>
       <c r="CD8" t="n">
-        <v>28.79645784915928</v>
+        <v>28.79645706027183</v>
       </c>
       <c r="CE8" t="n">
         <v>25.44421854454374</v>
       </c>
       <c r="CF8" t="n">
-        <v>39.86915248264399</v>
+        <v>39.86915228296264</v>
       </c>
       <c r="CG8" t="n">
-        <v>36.84499283753826</v>
+        <v>36.84499256835356</v>
       </c>
       <c r="CH8" t="n">
-        <v>33.16049355378443</v>
+        <v>33.16049331151821</v>
       </c>
       <c r="CI8" t="n">
         <v>8</v>
@@ -3152,10 +3152,10 @@
         <v>3.1</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.781742449677925</v>
+        <v>1.781741706073836</v>
       </c>
       <c r="CM8" t="n">
-        <v>22.37308238774072</v>
+        <v>22.37308177484527</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>41.34999847412109</v>
       </c>
       <c r="BX9" t="n">
-        <v>121.1494715592892</v>
+        <v>121.1494721090868</v>
       </c>
       <c r="BY9" t="n">
-        <v>224.7322697424814</v>
+        <v>224.7322707623559</v>
       </c>
       <c r="BZ9" t="n">
         <v>134.6160883985514</v>
@@ -3472,13 +3472,13 @@
         <v>57.31088302327341</v>
       </c>
       <c r="CF9" t="n">
-        <v>139.1218202109569</v>
+        <v>139.1218204071659</v>
       </c>
       <c r="CG9" t="n">
-        <v>122.0409497276624</v>
+        <v>122.0409500025612</v>
       </c>
       <c r="CH9" t="n">
-        <v>109.8368547548962</v>
+        <v>109.8368550023051</v>
       </c>
       <c r="CI9" t="n">
         <v>8</v>
@@ -3490,10 +3490,10 @@
         <v>5.4</v>
       </c>
       <c r="CL9" t="n">
-        <v>165.6272280726627</v>
+        <v>165.6272286709915</v>
       </c>
       <c r="CM9" t="n">
-        <v>236.4493962388568</v>
+        <v>236.4493967133646</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -3776,10 +3776,10 @@
         <v>15.75</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.426879073367735</v>
+        <v>6.426879084015115</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.92186068109715</v>
+        <v>11.92186070084804</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.38777372262773</v>
@@ -3788,19 +3788,19 @@
         <v>18.61263551273508</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.14401441449393</v>
+        <v>35.14401439713617</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.29380745183323</v>
+        <v>12.29380744981134</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.32877932610295</v>
+        <v>20.32877930379371</v>
       </c>
       <c r="CE10" t="n">
         <v>17.80443971854372</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.21333011820483</v>
+        <v>20.21333011507083</v>
       </c>
       <c r="CG10" t="n">
         <v>18.61263551273508</v>
@@ -3821,7 +3821,7 @@
         <v>6.357917215629039</v>
       </c>
       <c r="CM10" t="n">
-        <v>28.33860392511003</v>
+        <v>28.33860390521161</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -4104,10 +4104,10 @@
         <v>32.97999954223633</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.05539017224547</v>
+        <v>46.05539022505743</v>
       </c>
       <c r="BY11" t="n">
-        <v>85.43274876951534</v>
+        <v>85.43274886748152</v>
       </c>
       <c r="BZ11" t="n">
         <v>69.25277241436312</v>
@@ -4128,7 +4128,7 @@
         <v>25.25865933859778</v>
       </c>
       <c r="CF11" t="n">
-        <v>78.35175841802865</v>
+        <v>78.35175843956839</v>
       </c>
       <c r="CG11" t="n">
         <v>69.25277241436312</v>
@@ -4149,7 +4149,7 @@
         <v>88.98573692551504</v>
       </c>
       <c r="CM11" t="n">
-        <v>137.5735582339421</v>
+        <v>137.5735582992536</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -4434,10 +4434,10 @@
         <v>45.97999954223633</v>
       </c>
       <c r="BX12" t="n">
-        <v>127.6301656054059</v>
+        <v>127.6301653037027</v>
       </c>
       <c r="BY12" t="n">
-        <v>236.7539571980278</v>
+        <v>236.7539566383685</v>
       </c>
       <c r="BZ12" t="n">
         <v>134.1927299415487</v>
@@ -4458,13 +4458,13 @@
         <v>55.9815638034286</v>
       </c>
       <c r="CF12" t="n">
-        <v>141.013655733659</v>
+        <v>141.0136556259887</v>
       </c>
       <c r="CG12" t="n">
-        <v>125.0879896816743</v>
+        <v>125.0879895308227</v>
       </c>
       <c r="CH12" t="n">
-        <v>112.5791907135068</v>
+        <v>112.5791905777404</v>
       </c>
       <c r="CI12" t="n">
         <v>8</v>
@@ -4476,10 +4476,10 @@
         <v>5.4</v>
       </c>
       <c r="CL12" t="n">
-        <v>144.8438273908502</v>
+        <v>144.8438270955775</v>
       </c>
       <c r="CM12" t="n">
-        <v>206.6847697641376</v>
+        <v>206.6847695299699</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>-4.327813207567233</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-13.44221145597109</v>
+        <v>-13.4422178413344</v>
       </c>
       <c r="DA12" t="b">
         <v>1</v>
@@ -4762,10 +4762,10 @@
         <v>7.449999809265137</v>
       </c>
       <c r="BX13" t="n">
-        <v>3.363729737629919</v>
+        <v>3.363729731999764</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.239718663303499</v>
+        <v>6.239718652859561</v>
       </c>
       <c r="BZ13" t="n">
         <v>21.74284085303151</v>
@@ -4774,7 +4774,7 @@
         <v>14.8939109083963</v>
       </c>
       <c r="CB13" t="n">
-        <v>34.9872716885013</v>
+        <v>34.9872716711396</v>
       </c>
       <c r="CC13" t="n">
         <v>10.95072400487419</v>
@@ -5070,10 +5070,10 @@
         <v>19.13999938964844</v>
       </c>
       <c r="BX14" t="n">
-        <v>13.15731125484445</v>
+        <v>13.15731125139662</v>
       </c>
       <c r="BY14" t="n">
-        <v>24.40681237773645</v>
+        <v>24.40681237134073</v>
       </c>
       <c r="BZ14" t="n">
         <v>20.45201547684208</v>
@@ -5082,7 +5082,7 @@
         <v>12.7798316087502</v>
       </c>
       <c r="CB14" t="n">
-        <v>34.61244756091308</v>
+        <v>34.61244755702038</v>
       </c>
       <c r="CC14" t="n">
         <v>22.8984489302328</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="CE14" t="inlineStr"/>
       <c r="CF14" t="n">
-        <v>20.22864700991394</v>
+        <v>20.22864700745306</v>
       </c>
       <c r="CG14" t="n">
         <v>21.67523220353744</v>
@@ -5113,7 +5113,7 @@
         <v>1.9211578122313</v>
       </c>
       <c r="CM14" t="n">
-        <v>5.687814289347792</v>
+        <v>5.687814276490499</v>
       </c>
       <c r="CN14" t="inlineStr">
         <is>
@@ -5396,10 +5396,10 @@
         <v>17.53000068664551</v>
       </c>
       <c r="BX15" t="n">
-        <v>10.74426549734245</v>
+        <v>10.74426543933461</v>
       </c>
       <c r="BY15" t="n">
-        <v>19.93061249757024</v>
+        <v>19.93061238996571</v>
       </c>
       <c r="BZ15" t="n">
         <v>37.89111078271664</v>
@@ -5408,25 +5408,25 @@
         <v>37.31646064248518</v>
       </c>
       <c r="CB15" t="n">
-        <v>42.4039025135667</v>
+        <v>42.40390248812157</v>
       </c>
       <c r="CC15" t="n">
-        <v>34.52246247160851</v>
+        <v>34.52246248377015</v>
       </c>
       <c r="CD15" t="n">
-        <v>18.8693152365392</v>
+        <v>18.86931530381901</v>
       </c>
       <c r="CE15" t="n">
         <v>31.49264348607277</v>
       </c>
       <c r="CF15" t="n">
-        <v>31.77521537579418</v>
+        <v>31.77521536813586</v>
       </c>
       <c r="CG15" t="n">
-        <v>34.52246247160851</v>
+        <v>34.52246248377015</v>
       </c>
       <c r="CH15" t="n">
-        <v>31.07021622444766</v>
+        <v>31.07021623539313</v>
       </c>
       <c r="CI15" t="n">
         <v>7</v>
@@ -5438,10 +5438,10 @@
         <v>3.9</v>
       </c>
       <c r="CL15" t="n">
-        <v>77.24024533619782</v>
+        <v>77.24024539863635</v>
       </c>
       <c r="CM15" t="n">
-        <v>81.2619174624493</v>
+        <v>81.26191741876237</v>
       </c>
       <c r="CN15" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="BX16" t="n">
-        <v>10.37863324143814</v>
+        <v>10.37863324080722</v>
       </c>
       <c r="BY16" t="n">
-        <v>19.25236466286776</v>
+        <v>19.25236466169739</v>
       </c>
       <c r="BZ16" t="n">
         <v>25.85122324877091</v>
@@ -5736,25 +5736,25 @@
         <v>18.56165831752405</v>
       </c>
       <c r="CB16" t="n">
-        <v>39.76450200271903</v>
+        <v>39.76450200325498</v>
       </c>
       <c r="CC16" t="n">
-        <v>24.31404884323738</v>
+        <v>24.31404884349509</v>
       </c>
       <c r="CD16" t="n">
-        <v>13.00688756251821</v>
+        <v>13.0068875639007</v>
       </c>
       <c r="CE16" t="n">
         <v>10.35999965667725</v>
       </c>
       <c r="CF16" t="n">
-        <v>20.18616469196909</v>
+        <v>20.18616469201595</v>
       </c>
       <c r="CG16" t="n">
-        <v>18.9070114901959</v>
+        <v>18.90701148961072</v>
       </c>
       <c r="CH16" t="n">
-        <v>17.01631034117631</v>
+        <v>17.01631034064965</v>
       </c>
       <c r="CI16" t="n">
         <v>8</v>
@@ -5766,10 +5766,10 @@
         <v>3.8</v>
       </c>
       <c r="CL16" t="n">
-        <v>64.25010526143143</v>
+        <v>64.25010525634778</v>
       </c>
       <c r="CM16" t="n">
-        <v>94.84715599347211</v>
+        <v>94.84715599392443</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -5956,13 +5956,13 @@
         <v>1</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.5</v>
+        <v>0.31</v>
       </c>
       <c r="AS17" t="b">
         <v>1</v>
       </c>
       <c r="AT17" t="n">
-        <v>3694495232</v>
+        <v>5870842368</v>
       </c>
       <c r="AU17" t="n">
         <v>6.47</v>
@@ -6052,10 +6052,10 @@
         <v>11.28999996185303</v>
       </c>
       <c r="BX17" t="n">
-        <v>9.774107164473406</v>
+        <v>9.774107132824012</v>
       </c>
       <c r="BY17" t="n">
-        <v>18.13096879009817</v>
+        <v>18.13096873138854</v>
       </c>
       <c r="BZ17" t="n">
         <v>23.1209427348613</v>
@@ -6064,25 +6064,25 @@
         <v>13.6472321924953</v>
       </c>
       <c r="CB17" t="n">
-        <v>35.00095083530591</v>
+        <v>35.00095092979096</v>
       </c>
       <c r="CC17" t="n">
-        <v>25.51476116243877</v>
+        <v>25.51476118451542</v>
       </c>
       <c r="CD17" t="n">
-        <v>13.36818428647778</v>
+        <v>13.36818438891547</v>
       </c>
       <c r="CE17" t="n">
         <v>9.880299501333878</v>
       </c>
       <c r="CF17" t="n">
-        <v>18.55468083343556</v>
+        <v>18.55468084951561</v>
       </c>
       <c r="CG17" t="n">
-        <v>15.88910049129673</v>
+        <v>15.88910046194192</v>
       </c>
       <c r="CH17" t="n">
-        <v>14.30019044216706</v>
+        <v>14.30019041574773</v>
       </c>
       <c r="CI17" t="n">
         <v>8</v>
@@ -6094,10 +6094,10 @@
         <v>3.6</v>
       </c>
       <c r="CL17" t="n">
-        <v>26.66244898569488</v>
+        <v>26.66244875168839</v>
       </c>
       <c r="CM17" t="n">
-        <v>64.34615497013858</v>
+        <v>64.34615511256592</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="BX18" t="n">
-        <v>5.044350349791416</v>
+        <v>5.044350317845809</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.357269898863075</v>
+        <v>9.357269839603974</v>
       </c>
       <c r="BZ18" t="n">
         <v>8.453839145587175</v>
@@ -6700,10 +6700,10 @@
         <v>11.07999992370605</v>
       </c>
       <c r="BX19" t="n">
-        <v>3.454302374336679</v>
+        <v>3.454302373763291</v>
       </c>
       <c r="BY19" t="n">
-        <v>6.407730904394539</v>
+        <v>6.407730903330905</v>
       </c>
       <c r="BZ19" t="n">
         <v>20.4470750681205</v>
@@ -6712,13 +6712,13 @@
         <v>19.3263652032129</v>
       </c>
       <c r="CB19" t="n">
-        <v>22.00385754061454</v>
+        <v>22.00385754065327</v>
       </c>
       <c r="CC19" t="n">
-        <v>16.46863777362829</v>
+        <v>16.46863777374062</v>
       </c>
       <c r="CD19" t="n">
-        <v>13.71979386663865</v>
+        <v>13.71979386736575</v>
       </c>
       <c r="CE19" t="n">
         <v>30.3956356510297</v>
@@ -6774,7 +6774,7 @@
         <v>-18.94659940111765</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-32.89648837260555</v>
+        <v>-32.89649636084019</v>
       </c>
       <c r="DA19" t="b">
         <v>1</v>
@@ -7018,10 +7018,10 @@
         <v>27.52000045776367</v>
       </c>
       <c r="BX20" t="n">
-        <v>7.290978513671294</v>
+        <v>7.290978493666847</v>
       </c>
       <c r="BY20" t="n">
-        <v>13.52476514286025</v>
+        <v>13.524765105752</v>
       </c>
       <c r="BZ20" t="n">
         <v>36.57372177185242</v>
@@ -7030,19 +7030,19 @@
         <v>28.87454744278962</v>
       </c>
       <c r="CB20" t="n">
-        <v>45.93352492840341</v>
+        <v>45.93352495778168</v>
       </c>
       <c r="CC20" t="n">
-        <v>26.49482249861916</v>
+        <v>26.49482250350369</v>
       </c>
       <c r="CD20" t="n">
-        <v>29.81102742050766</v>
+        <v>29.81102745663089</v>
       </c>
       <c r="CE20" t="n">
         <v>24.2620728130642</v>
       </c>
       <c r="CF20" t="n">
-        <v>29.35349743115668</v>
+        <v>29.35349743591064</v>
       </c>
       <c r="CG20" t="n">
         <v>28.87454744278962</v>
@@ -7063,7 +7063,7 @@
         <v>-5.570158916260349</v>
       </c>
       <c r="CM20" t="n">
-        <v>6.662416216914546</v>
+        <v>6.662416234189128</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>-5.331954775825187</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-21.99140136548733</v>
+        <v>-21.99140983840919</v>
       </c>
       <c r="DA20" t="b">
         <v>1</v>
@@ -7346,10 +7346,10 @@
         <v>22.06999969482422</v>
       </c>
       <c r="BX21" t="n">
-        <v>3.108072446053702</v>
+        <v>3.108072449167506</v>
       </c>
       <c r="BY21" t="n">
-        <v>5.765474387429617</v>
+        <v>5.765474393205723</v>
       </c>
       <c r="BZ21" t="n">
         <v>33.57376532220675</v>
@@ -7358,7 +7358,7 @@
         <v>28.04300293143303</v>
       </c>
       <c r="CB21" t="n">
-        <v>43.00378985845179</v>
+        <v>43.00378986345676</v>
       </c>
       <c r="CC21" t="n">
         <v>10.85340539909456</v>
@@ -7644,10 +7644,10 @@
         <v>38.90000152587891</v>
       </c>
       <c r="BX22" t="n">
-        <v>35.62892559158855</v>
+        <v>35.62892563789725</v>
       </c>
       <c r="BY22" t="n">
-        <v>51.87571566135294</v>
+        <v>51.8757157287784</v>
       </c>
       <c r="BZ22" t="n">
         <v>50.25590259243982</v>
@@ -7664,13 +7664,13 @@
       </c>
       <c r="CE22" t="inlineStr"/>
       <c r="CF22" t="n">
-        <v>49.31617720729976</v>
+        <v>49.31617723573329</v>
       </c>
       <c r="CG22" t="n">
-        <v>51.06580912689638</v>
+        <v>51.06580916060911</v>
       </c>
       <c r="CH22" t="n">
-        <v>45.95922821420675</v>
+        <v>45.9592282445482</v>
       </c>
       <c r="CI22" t="n">
         <v>4</v>
@@ -7682,10 +7682,10 @@
         <v>1.7</v>
       </c>
       <c r="CL22" t="n">
-        <v>18.14711159749329</v>
+        <v>18.14711167549188</v>
       </c>
       <c r="CM22" t="n">
-        <v>26.77680018724757</v>
+        <v>26.77680026034148</v>
       </c>
       <c r="CN22" t="inlineStr">
         <is>
@@ -7950,35 +7950,35 @@
         <v>23.04999923706055</v>
       </c>
       <c r="BX23" t="n">
-        <v>16.54376617069508</v>
+        <v>16.54376614373064</v>
       </c>
       <c r="BY23" t="n">
-        <v>30.07147189256665</v>
+        <v>30.07147189666543</v>
       </c>
       <c r="BZ23" t="n">
-        <v>51.50946628219135</v>
+        <v>51.50946637316667</v>
       </c>
       <c r="CA23" t="n">
         <v>50.09186275696137</v>
       </c>
       <c r="CB23" t="n">
-        <v>63.06344045694706</v>
+        <v>63.06344044501155</v>
       </c>
       <c r="CC23" t="n">
-        <v>45.81097523878608</v>
+        <v>45.81097524457223</v>
       </c>
       <c r="CD23" t="n">
-        <v>25.18054540102311</v>
+        <v>25.18054543436194</v>
       </c>
       <c r="CE23" t="inlineStr"/>
       <c r="CF23" t="n">
-        <v>35.98391989605979</v>
+        <v>35.98391991453374</v>
       </c>
       <c r="CG23" t="n">
-        <v>37.94122356567637</v>
+        <v>37.94122357061883</v>
       </c>
       <c r="CH23" t="n">
-        <v>34.14710120910873</v>
+        <v>34.14710121355695</v>
       </c>
       <c r="CI23" t="n">
         <v>4</v>
@@ -7990,10 +7990,10 @@
         <v>3.1</v>
       </c>
       <c r="CL23" t="n">
-        <v>48.1436110167236</v>
+        <v>48.14361103602172</v>
       </c>
       <c r="CM23" t="n">
-        <v>56.11245590934188</v>
+        <v>56.1124559894892</v>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
@@ -8276,10 +8276,10 @@
         <v>32.75</v>
       </c>
       <c r="BX24" t="n">
-        <v>3.249356703185835</v>
+        <v>3.249356695245596</v>
       </c>
       <c r="BY24" t="n">
-        <v>6.027556684409724</v>
+        <v>6.02755666968058</v>
       </c>
       <c r="BZ24" t="n">
         <v>33.45701619121048</v>
@@ -8288,7 +8288,7 @@
         <v>23.42786572511178</v>
       </c>
       <c r="CB24" t="n">
-        <v>41.38326860791069</v>
+        <v>41.38326859933989</v>
       </c>
       <c r="CC24" t="n">
         <v>10.59424454785779</v>
@@ -8358,7 +8358,7 @@
         <v>0.738239590458023</v>
       </c>
       <c r="CZ24" t="n">
-        <v>-31.31834368818209</v>
+        <v>-31.318349352401</v>
       </c>
       <c r="DA24" t="b">
         <v>1</v>
@@ -8582,10 +8582,10 @@
         <v>14.77999973297119</v>
       </c>
       <c r="BX25" t="n">
-        <v>9.186484942523455</v>
+        <v>9.186484864776657</v>
       </c>
       <c r="BY25" t="n">
-        <v>17.04092956838101</v>
+        <v>17.0409294241607</v>
       </c>
       <c r="BZ25" t="n">
         <v>31.89495056382219</v>
@@ -8594,23 +8594,23 @@
         <v>30.33345456974609</v>
       </c>
       <c r="CB25" t="n">
-        <v>36.78693480627849</v>
+        <v>36.78693478280437</v>
       </c>
       <c r="CC25" t="n">
-        <v>25.58128744681195</v>
+        <v>25.5812874621472</v>
       </c>
       <c r="CD25" t="n">
-        <v>16.38749076950991</v>
+        <v>16.38749086618339</v>
       </c>
       <c r="CE25" t="inlineStr"/>
       <c r="CF25" t="n">
-        <v>20.92591313038465</v>
+        <v>20.92591307872669</v>
       </c>
       <c r="CG25" t="n">
-        <v>21.31110850759648</v>
+        <v>21.31110844315395</v>
       </c>
       <c r="CH25" t="n">
-        <v>19.17999765683683</v>
+        <v>19.17999759883855</v>
       </c>
       <c r="CI25" t="n">
         <v>4</v>
@@ -8622,10 +8622,10 @@
         <v>3.5</v>
       </c>
       <c r="CL25" t="n">
-        <v>29.76994589553432</v>
+        <v>29.76994550312377</v>
       </c>
       <c r="CM25" t="n">
-        <v>41.58263537517642</v>
+        <v>41.58263502566379</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>-7.171627471148123</v>
       </c>
       <c r="CZ25" t="n">
-        <v>-18.74746959920818</v>
+        <v>-18.74747840191868</v>
       </c>
       <c r="DA25" t="b">
         <v>1</v>
@@ -8888,35 +8888,35 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BX26" t="n">
-        <v>8.627042101504598</v>
+        <v>8.627042116836234</v>
       </c>
       <c r="BY26" t="n">
-        <v>14.3473089881045</v>
+        <v>14.3473089692186</v>
       </c>
       <c r="BZ26" t="n">
-        <v>19.54486185013556</v>
+        <v>19.54486178967358</v>
       </c>
       <c r="CA26" t="n">
         <v>17.74926644976348</v>
       </c>
       <c r="CB26" t="n">
-        <v>23.9353952809524</v>
+        <v>23.93539526688062</v>
       </c>
       <c r="CC26" t="n">
-        <v>17.38495028879861</v>
+        <v>17.3849502846228</v>
       </c>
       <c r="CD26" t="n">
-        <v>9.719867150456352</v>
+        <v>9.719867124336151</v>
       </c>
       <c r="CE26" t="inlineStr"/>
       <c r="CF26" t="n">
-        <v>14.97604080713582</v>
+        <v>14.9760407900878</v>
       </c>
       <c r="CG26" t="n">
-        <v>15.86612963845156</v>
+        <v>15.8661296269207</v>
       </c>
       <c r="CH26" t="n">
-        <v>14.2795166746064</v>
+        <v>14.27951666422863</v>
       </c>
       <c r="CI26" t="n">
         <v>4</v>
@@ -8928,10 +8928,10 @@
         <v>2.3</v>
       </c>
       <c r="CL26" t="n">
-        <v>11.1246400832649</v>
+        <v>11.12464000250404</v>
       </c>
       <c r="CM26" t="n">
-        <v>16.54506118717272</v>
+        <v>16.54506105450333</v>
       </c>
       <c r="CN26" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         <v>5.880000114440918</v>
       </c>
       <c r="BX27" t="n">
-        <v>6.97575081720508</v>
+        <v>6.975750804712934</v>
       </c>
       <c r="BY27" t="n">
-        <v>12.94001776591542</v>
+        <v>12.94001774274249</v>
       </c>
       <c r="BZ27" t="n">
         <v>5.605036080312384</v>
@@ -9246,7 +9246,7 @@
         <v>5.348622529323849</v>
       </c>
       <c r="CF27" t="n">
-        <v>7.296291367611541</v>
+        <v>7.296291363153406</v>
       </c>
       <c r="CG27" t="n">
         <v>5.869184706822859</v>
@@ -9267,7 +9267,7 @@
         <v>-10.16554195011574</v>
       </c>
       <c r="CM27" t="n">
-        <v>24.08658546948492</v>
+        <v>24.0865853936663</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -9532,10 +9532,10 @@
         <v>39.43999862670898</v>
       </c>
       <c r="BX28" t="n">
-        <v>20.16127590415178</v>
+        <v>20.16127576378087</v>
       </c>
       <c r="BY28" t="n">
-        <v>37.39916680220153</v>
+        <v>37.39916654181352</v>
       </c>
       <c r="BZ28" t="n">
         <v>57.05021635413689</v>
@@ -9544,23 +9544,23 @@
         <v>43.06721646336476</v>
       </c>
       <c r="CB28" t="n">
-        <v>64.10972902841927</v>
+        <v>64.10972925506432</v>
       </c>
       <c r="CC28" t="n">
-        <v>45.28400684795875</v>
+        <v>45.28400689102889</v>
       </c>
       <c r="CD28" t="n">
-        <v>32.43094038342355</v>
+        <v>32.4309406607403</v>
       </c>
       <c r="CE28" t="inlineStr"/>
       <c r="CF28" t="n">
-        <v>39.97366647711224</v>
+        <v>39.97366638769005</v>
       </c>
       <c r="CG28" t="n">
-        <v>41.34158682508014</v>
+        <v>41.3415867164212</v>
       </c>
       <c r="CH28" t="n">
-        <v>37.20742814257213</v>
+        <v>37.20742804477909</v>
       </c>
       <c r="CI28" t="n">
         <v>4</v>
@@ -9572,10 +9572,10 @@
         <v>2.8</v>
       </c>
       <c r="CL28" t="n">
-        <v>-5.66067586682153</v>
+        <v>-5.660676114775498</v>
       </c>
       <c r="CM28" t="n">
-        <v>1.353113258076677</v>
+        <v>1.353113031346953</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -9858,37 +9858,37 @@
         <v>26.45999908447266</v>
       </c>
       <c r="BX29" t="n">
-        <v>16.91893496395116</v>
+        <v>16.91893506893802</v>
       </c>
       <c r="BY29" t="n">
-        <v>28.67982834511886</v>
+        <v>28.67982835899834</v>
       </c>
       <c r="BZ29" t="n">
-        <v>49.21350845818002</v>
+        <v>49.21350817661271</v>
       </c>
       <c r="CA29" t="n">
         <v>53.99475108321082</v>
       </c>
       <c r="CB29" t="n">
-        <v>57.93925171177568</v>
+        <v>57.93925175074026</v>
       </c>
       <c r="CC29" t="n">
-        <v>43.01388445567864</v>
+        <v>43.0138844369042</v>
       </c>
       <c r="CD29" t="n">
-        <v>24.40657263841013</v>
+        <v>24.40657252098443</v>
       </c>
       <c r="CE29" t="n">
         <v>30.06721996094383</v>
       </c>
       <c r="CF29" t="n">
-        <v>38.02924395215864</v>
+        <v>38.02924391966657</v>
       </c>
       <c r="CG29" t="n">
-        <v>36.54055220831123</v>
+        <v>36.54055219892401</v>
       </c>
       <c r="CH29" t="n">
-        <v>32.88649698748011</v>
+        <v>32.88649697903161</v>
       </c>
       <c r="CI29" t="n">
         <v>8</v>
@@ -9900,10 +9900,10 @@
         <v>3.4</v>
       </c>
       <c r="CL29" t="n">
-        <v>24.28759684568043</v>
+        <v>24.28759681375112</v>
       </c>
       <c r="CM29" t="n">
-        <v>43.72352708989731</v>
+        <v>43.72352696710038</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -10186,37 +10186,37 @@
         <v>15.3100004196167</v>
       </c>
       <c r="BX30" t="n">
-        <v>5.939526976484671</v>
+        <v>5.939526966495125</v>
       </c>
       <c r="BY30" t="n">
-        <v>8.534880597786364</v>
+        <v>8.534880606033607</v>
       </c>
       <c r="BZ30" t="n">
-        <v>10.81501542525123</v>
+        <v>10.81501545389127</v>
       </c>
       <c r="CA30" t="n">
         <v>11.65944891202323</v>
       </c>
       <c r="CB30" t="n">
-        <v>9.81040379362247</v>
+        <v>9.810403809730376</v>
       </c>
       <c r="CC30" t="n">
-        <v>14.90925677649959</v>
+        <v>14.90925678000476</v>
       </c>
       <c r="CD30" t="n">
-        <v>5.384140019951317</v>
+        <v>5.384140036126389</v>
       </c>
       <c r="CE30" t="n">
         <v>10.69689722735973</v>
       </c>
       <c r="CF30" t="n">
-        <v>9.718696216122325</v>
+        <v>9.718696223958061</v>
       </c>
       <c r="CG30" t="n">
-        <v>10.2536505104911</v>
+        <v>10.25365051854505</v>
       </c>
       <c r="CH30" t="n">
-        <v>9.22828545944199</v>
+        <v>9.228285466690549</v>
       </c>
       <c r="CI30" t="n">
         <v>8</v>
@@ -10228,10 +10228,10 @@
         <v>2.8</v>
       </c>
       <c r="CL30" t="n">
-        <v>-39.72380661977128</v>
+        <v>-39.72380657242602</v>
       </c>
       <c r="CM30" t="n">
-        <v>-36.52060124263771</v>
+        <v>-36.5206011914572</v>
       </c>
       <c r="CN30" t="inlineStr">
         <is>
@@ -10514,10 +10514,10 @@
         <v>9.25</v>
       </c>
       <c r="BX31" t="n">
-        <v>2.521670927333336</v>
+        <v>2.521670923786019</v>
       </c>
       <c r="BY31" t="n">
-        <v>4.677699570203337</v>
+        <v>4.677699563623064</v>
       </c>
       <c r="BZ31" t="n">
         <v>13.66360089186176</v>
@@ -10526,19 +10526,19 @@
         <v>15.44242552617786</v>
       </c>
       <c r="CB31" t="n">
-        <v>10.73109422410298</v>
+        <v>10.73109422354266</v>
       </c>
       <c r="CC31" t="n">
-        <v>7.312738776922527</v>
+        <v>7.312738777253591</v>
       </c>
       <c r="CD31" t="n">
-        <v>7.026196810211229</v>
+        <v>7.026196813339111</v>
       </c>
       <c r="CE31" t="n">
         <v>10.33342380121613</v>
       </c>
       <c r="CF31" t="n">
-        <v>9.883882800099403</v>
+        <v>9.883882799573454</v>
       </c>
       <c r="CG31" t="n">
         <v>10.33342380121613</v>
@@ -10559,7 +10559,7 @@
         <v>0.5414207685893846</v>
       </c>
       <c r="CM31" t="n">
-        <v>6.852787028101659</v>
+        <v>6.852787022415718</v>
       </c>
       <c r="CN31" t="inlineStr">
         <is>
@@ -10842,37 +10842,37 @@
         <v>38.86000061035156</v>
       </c>
       <c r="BX32" t="n">
-        <v>30.97422543793434</v>
+        <v>30.97422548036206</v>
       </c>
       <c r="BY32" t="n">
-        <v>37.33904021088482</v>
+        <v>37.33904017539584</v>
       </c>
       <c r="BZ32" t="n">
-        <v>41.77389268641083</v>
+        <v>41.77389258948588</v>
       </c>
       <c r="CA32" t="n">
         <v>51.32924379406393</v>
       </c>
       <c r="CB32" t="n">
-        <v>64.51021358360998</v>
+        <v>64.5102135381366</v>
       </c>
       <c r="CC32" t="n">
-        <v>16.34210047707102</v>
+        <v>16.34210047312566</v>
       </c>
       <c r="CD32" t="n">
-        <v>19.48042967678916</v>
+        <v>19.48042960159367</v>
       </c>
       <c r="CE32" t="n">
         <v>27.99121924833823</v>
       </c>
       <c r="CF32" t="n">
-        <v>36.21754563938779</v>
+        <v>36.21754561256273</v>
       </c>
       <c r="CG32" t="n">
-        <v>34.15663282440958</v>
+        <v>34.15663282787895</v>
       </c>
       <c r="CH32" t="n">
-        <v>30.74096954196863</v>
+        <v>30.74096954509106</v>
       </c>
       <c r="CI32" t="n">
         <v>8</v>
@@ -10884,10 +10884,10 @@
         <v>3.9</v>
       </c>
       <c r="CL32" t="n">
-        <v>-20.89302866922802</v>
+        <v>-20.89302866119295</v>
       </c>
       <c r="CM32" t="n">
-        <v>-6.799935484972353</v>
+        <v>-6.799935554002367</v>
       </c>
       <c r="CN32" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>1</v>
       </c>
       <c r="AT33" t="n">
-        <v>182762307584</v>
+        <v>182443720704</v>
       </c>
       <c r="AU33" t="n">
         <v>6.96</v>
@@ -11152,35 +11152,35 @@
         <v>16.78000068664551</v>
       </c>
       <c r="BX33" t="n">
-        <v>9.985664050312705</v>
+        <v>9.985664018193983</v>
       </c>
       <c r="BY33" t="n">
-        <v>18.36675920877225</v>
+        <v>18.36675921429381</v>
       </c>
       <c r="BZ33" t="n">
-        <v>31.67453737106667</v>
+        <v>31.67453748246954</v>
       </c>
       <c r="CA33" t="n">
         <v>30.47653407949944</v>
       </c>
       <c r="CB33" t="n">
-        <v>34.39875972145861</v>
+        <v>34.39875972038924</v>
       </c>
       <c r="CC33" t="n">
-        <v>27.99338997784159</v>
+        <v>27.99338998480554</v>
       </c>
       <c r="CD33" t="n">
-        <v>15.43712489841865</v>
+        <v>15.43712493835636</v>
       </c>
       <c r="CE33" t="inlineStr"/>
       <c r="CF33" t="n">
-        <v>22.0050876519983</v>
+        <v>22.00508767494072</v>
       </c>
       <c r="CG33" t="n">
-        <v>23.18007459330693</v>
+        <v>23.18007459954968</v>
       </c>
       <c r="CH33" t="n">
-        <v>20.86206713397624</v>
+        <v>20.86206713959471</v>
       </c>
       <c r="CI33" t="n">
         <v>4</v>
@@ -11192,10 +11192,10 @@
         <v>3.2</v>
       </c>
       <c r="CL33" t="n">
-        <v>24.32697425679768</v>
+        <v>24.32697429028086</v>
       </c>
       <c r="CM33" t="n">
-        <v>31.13877682681634</v>
+        <v>31.1387769635411</v>
       </c>
       <c r="CN33" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>-7.744448996751174</v>
       </c>
       <c r="CZ33" t="n">
-        <v>-20.99429475986069</v>
+        <v>-20.99430199889827</v>
       </c>
       <c r="DA33" t="b">
         <v>1</v>
@@ -11478,37 +11478,37 @@
         <v>44.2400016784668</v>
       </c>
       <c r="BX34" t="n">
-        <v>32.08407761727376</v>
+        <v>32.08407766834327</v>
       </c>
       <c r="BY34" t="n">
-        <v>48.69139719501933</v>
+        <v>48.69139707858242</v>
       </c>
       <c r="BZ34" t="n">
-        <v>58.34154957995293</v>
+        <v>58.34154934757478</v>
       </c>
       <c r="CA34" t="n">
         <v>49.68675315451532</v>
       </c>
       <c r="CB34" t="n">
-        <v>78.17304721755997</v>
+        <v>78.17304711557226</v>
       </c>
       <c r="CC34" t="n">
-        <v>60.4070601585803</v>
+        <v>60.40706013825914</v>
       </c>
       <c r="CD34" t="n">
-        <v>29.16704243878997</v>
+        <v>29.16704232001045</v>
       </c>
       <c r="CE34" t="n">
         <v>77.58261943552711</v>
       </c>
       <c r="CF34" t="n">
-        <v>54.26669334965234</v>
+        <v>54.26669328229809</v>
       </c>
       <c r="CG34" t="n">
-        <v>54.01415136723412</v>
+        <v>54.01415125104505</v>
       </c>
       <c r="CH34" t="n">
-        <v>48.61273623051071</v>
+        <v>48.61273612594054</v>
       </c>
       <c r="CI34" t="n">
         <v>8</v>
@@ -11520,10 +11520,10 @@
         <v>2.7</v>
       </c>
       <c r="CL34" t="n">
-        <v>9.884119317681407</v>
+        <v>9.884119081311237</v>
       </c>
       <c r="CM34" t="n">
-        <v>22.66431123592361</v>
+        <v>22.66431108367621</v>
       </c>
       <c r="CN34" t="inlineStr">
         <is>
@@ -11806,10 +11806,10 @@
         <v>32.65999984741211</v>
       </c>
       <c r="BX35" t="n">
-        <v>11.09799946397964</v>
+        <v>11.09799935577486</v>
       </c>
       <c r="BY35" t="n">
-        <v>20.58678900568224</v>
+        <v>20.58678880496236</v>
       </c>
       <c r="BZ35" t="n">
         <v>56.94013131292242</v>
@@ -11818,19 +11818,19 @@
         <v>53.82541566292831</v>
       </c>
       <c r="CB35" t="n">
-        <v>59.89734830826107</v>
+        <v>59.89734832677433</v>
       </c>
       <c r="CC35" t="n">
-        <v>28.27275394625155</v>
+        <v>28.27275368372061</v>
       </c>
       <c r="CD35" t="n">
-        <v>36.27955935326523</v>
+        <v>36.27955949019191</v>
       </c>
       <c r="CE35" t="n">
         <v>53.57698797570033</v>
       </c>
       <c r="CF35" t="n">
-        <v>44.19699793785873</v>
+        <v>44.19699789388574</v>
       </c>
       <c r="CG35" t="n">
         <v>53.57698797570033</v>
@@ -11851,7 +11851,7 @@
         <v>47.64020025539306</v>
       </c>
       <c r="CM35" t="n">
-        <v>35.32455035011515</v>
+        <v>35.32455021547649</v>
       </c>
       <c r="CN35" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>-0.2500150878204321</v>
       </c>
       <c r="CZ35" t="n">
-        <v>-10.82895234146481</v>
+        <v>-10.82896174015665</v>
       </c>
       <c r="DA35" t="b">
         <v>1</v>
@@ -12116,10 +12116,10 @@
         <v>54.20000076293945</v>
       </c>
       <c r="BX36" t="n">
-        <v>10.59687587206031</v>
+        <v>10.59687590922912</v>
       </c>
       <c r="BY36" t="n">
-        <v>19.65720474267188</v>
+        <v>19.65720481162001</v>
       </c>
       <c r="BZ36" t="n">
         <v>63.89234965382096</v>
@@ -12128,7 +12128,7 @@
         <v>47.83445546432147</v>
       </c>
       <c r="CB36" t="n">
-        <v>85.5299175847808</v>
+        <v>85.52991763107646</v>
       </c>
       <c r="CC36" t="n">
         <v>11.76833333333333</v>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="CE36" t="inlineStr"/>
       <c r="CF36" t="n">
-        <v>14.00747131602184</v>
+        <v>14.00747135139415</v>
       </c>
       <c r="CG36" t="n">
         <v>11.76833333333333</v>
@@ -12159,7 +12159,7 @@
         <v>-80.45848735994448</v>
       </c>
       <c r="CM36" t="n">
-        <v>-74.15595734529991</v>
+        <v>-74.15595728003734</v>
       </c>
       <c r="CN36" t="inlineStr">
         <is>
@@ -12440,10 +12440,10 @@
         <v>10.51000022888184</v>
       </c>
       <c r="BX37" t="n">
-        <v>13.08696664000438</v>
+        <v>13.08696646779218</v>
       </c>
       <c r="BY37" t="n">
-        <v>19.05462342784638</v>
+        <v>19.05462317710542</v>
       </c>
       <c r="BZ37" t="n">
         <v>17.18616389628476</v>
@@ -12462,7 +12462,7 @@
         <v>14.72238167572673</v>
       </c>
       <c r="CF37" t="n">
-        <v>16.32432250911085</v>
+        <v>16.32432243861866</v>
       </c>
       <c r="CG37" t="n">
         <v>15.95427278600574</v>
@@ -12483,7 +12483,7 @@
         <v>36.62079157664122</v>
       </c>
       <c r="CM37" t="n">
-        <v>55.32180926362935</v>
+        <v>55.32180859291393</v>
       </c>
       <c r="CN37" t="inlineStr">
         <is>
@@ -12748,10 +12748,10 @@
         <v>29.69000053405762</v>
       </c>
       <c r="BX38" t="n">
-        <v>15.52022459055369</v>
+        <v>15.52022457565406</v>
       </c>
       <c r="BY38" t="n">
-        <v>28.79001661547709</v>
+        <v>28.79001658783828</v>
       </c>
       <c r="BZ38" t="n">
         <v>54.8664584485723</v>
@@ -12760,23 +12760,23 @@
         <v>49.47692096413685</v>
       </c>
       <c r="CB38" t="n">
-        <v>61.18292635854815</v>
+        <v>61.18292636218396</v>
       </c>
       <c r="CC38" t="n">
-        <v>36.6428381914966</v>
+        <v>36.64283819419179</v>
       </c>
       <c r="CD38" t="n">
-        <v>30.47133165906052</v>
+        <v>30.47133167963273</v>
       </c>
       <c r="CE38" t="inlineStr"/>
       <c r="CF38" t="n">
-        <v>33.95488446152492</v>
+        <v>33.95488445156411</v>
       </c>
       <c r="CG38" t="n">
-        <v>32.71642740348685</v>
+        <v>32.71642739101503</v>
       </c>
       <c r="CH38" t="n">
-        <v>29.44478466313816</v>
+        <v>29.44478465191353</v>
       </c>
       <c r="CI38" t="n">
         <v>4</v>
@@ -12788,10 +12788,10 @@
         <v>3.5</v>
       </c>
       <c r="CL38" t="n">
-        <v>-0.8259207359668674</v>
+        <v>-0.8259207737729701</v>
       </c>
       <c r="CM38" t="n">
-        <v>14.36471488969837</v>
+        <v>14.36471485614899</v>
       </c>
       <c r="CN38" t="inlineStr">
         <is>
@@ -13082,37 +13082,37 @@
         <v>23.78000068664551</v>
       </c>
       <c r="BX39" t="n">
-        <v>10.50498166912102</v>
+        <v>10.50498159885169</v>
       </c>
       <c r="BY39" t="n">
-        <v>15.22159728661822</v>
+        <v>15.22159732947241</v>
       </c>
       <c r="BZ39" t="n">
-        <v>19.84847162716806</v>
+        <v>19.84847181581782</v>
       </c>
       <c r="CA39" t="n">
         <v>22.05215577512442</v>
       </c>
       <c r="CB39" t="n">
-        <v>19.44680931018522</v>
+        <v>19.44680939779476</v>
       </c>
       <c r="CC39" t="n">
-        <v>23.36371004800218</v>
+        <v>23.36371006756711</v>
       </c>
       <c r="CD39" t="n">
-        <v>9.891671174955322</v>
+        <v>9.891671279892723</v>
       </c>
       <c r="CE39" t="n">
         <v>19.45038570269356</v>
       </c>
       <c r="CF39" t="n">
-        <v>17.4724728242335</v>
+        <v>17.47247287090181</v>
       </c>
       <c r="CG39" t="n">
-        <v>19.44859750643939</v>
+        <v>19.44859755024416</v>
       </c>
       <c r="CH39" t="n">
-        <v>17.50373775579545</v>
+        <v>17.50373779521974</v>
       </c>
       <c r="CI39" t="n">
         <v>8</v>
@@ -13124,10 +13124,10 @@
         <v>2.4</v>
       </c>
       <c r="CL39" t="n">
-        <v>-26.39303090674304</v>
+        <v>-26.39303074095545</v>
       </c>
       <c r="CM39" t="n">
-        <v>-26.52450664542757</v>
+        <v>-26.52450644917731</v>
       </c>
       <c r="CN39" t="inlineStr">
         <is>
@@ -13418,37 +13418,37 @@
         <v>18.63999938964844</v>
       </c>
       <c r="BX40" t="n">
-        <v>8.745140387725304</v>
+        <v>8.745140400157554</v>
       </c>
       <c r="BY40" t="n">
-        <v>9.253022841538003</v>
+        <v>9.2530228409156</v>
       </c>
       <c r="BZ40" t="n">
-        <v>9.762664742861054</v>
+        <v>9.762664728325589</v>
       </c>
       <c r="CA40" t="n">
         <v>16.97559723955254</v>
       </c>
       <c r="CB40" t="n">
-        <v>9.361180425981244</v>
+        <v>9.36118041541633</v>
       </c>
       <c r="CC40" t="n">
-        <v>17.55266733740303</v>
+        <v>17.55266733434918</v>
       </c>
       <c r="CD40" t="n">
-        <v>4.00185534411393</v>
+        <v>4.001855329891438</v>
       </c>
       <c r="CE40" t="n">
         <v>16.08382941914014</v>
       </c>
       <c r="CF40" t="n">
-        <v>11.46699471728941</v>
+        <v>11.46699471346854</v>
       </c>
       <c r="CG40" t="n">
-        <v>9.561922584421149</v>
+        <v>9.561922571870959</v>
       </c>
       <c r="CH40" t="n">
-        <v>8.605730325979033</v>
+        <v>8.605730314683862</v>
       </c>
       <c r="CI40" t="n">
         <v>8</v>
@@ -13460,10 +13460,10 @@
         <v>4.4</v>
       </c>
       <c r="CL40" t="n">
-        <v>-53.83191734030768</v>
+        <v>-53.8319174009041</v>
       </c>
       <c r="CM40" t="n">
-        <v>-38.48178598301079</v>
+        <v>-38.48178600350899</v>
       </c>
       <c r="CN40" t="inlineStr">
         <is>
@@ -14310,10 +14310,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.868715973941502</v>
+        <v>5.868716083158859</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.88646813166149</v>
+        <v>10.88646833425968</v>
       </c>
       <c r="BZ2" t="n">
         <v>42.10015429633837</v>
@@ -14322,7 +14322,7 @@
         <v>28.26125673506212</v>
       </c>
       <c r="CB2" t="n">
-        <v>72.78655314526678</v>
+        <v>72.78655361286401</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -14392,7 +14392,7 @@
         <v>-4.94053016263244</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-26.59162359529691</v>
+        <v>-26.59161854099229</v>
       </c>
       <c r="DA2" t="b">
         <v>1</v>
@@ -14636,10 +14636,10 @@
         <v>13.60999965667725</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.01575560910662</v>
+        <v>15.01575552163967</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.85422665489277</v>
+        <v>27.85422649264158</v>
       </c>
       <c r="BZ3" t="n">
         <v>38.94870312116058</v>
@@ -14648,13 +14648,13 @@
         <v>23.57226802449605</v>
       </c>
       <c r="CB3" t="n">
-        <v>74.76041603016105</v>
+        <v>74.76041619500492</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.40383466993469</v>
+        <v>48.40383473421028</v>
       </c>
       <c r="CD3" t="n">
-        <v>26.30532685669047</v>
+        <v>26.30532712655051</v>
       </c>
       <c r="CE3" t="n">
         <v>8.655042371031668</v>
@@ -14954,10 +14954,10 @@
         <v>24.54000091552734</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.25388476298676</v>
+        <v>16.25388477199722</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.15095623534045</v>
+        <v>30.15095625205485</v>
       </c>
       <c r="BZ4" t="n">
         <v>74.06720094094243</v>
@@ -14966,13 +14966,13 @@
         <v>53.70833445174577</v>
       </c>
       <c r="CB4" t="n">
-        <v>132.6406024865115</v>
+        <v>132.640602484492</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.79451766935813</v>
+        <v>25.79451766811822</v>
       </c>
       <c r="CD4" t="n">
-        <v>65.72549929547127</v>
+        <v>65.72549927613987</v>
       </c>
       <c r="CE4" t="n">
         <v>43.53105147803891</v>
@@ -15270,10 +15270,10 @@
         <v>4.190000057220459</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.548072984339422</v>
+        <v>3.548072967645033</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.581675385949628</v>
+        <v>6.581675354981536</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.82159370858454</v>
@@ -15282,25 +15282,25 @@
         <v>8.61209444827186</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.80877191788858</v>
+        <v>24.80877193010127</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.29418311857289</v>
+        <v>11.2941831253625</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.96827541452747</v>
+        <v>10.96827545613256</v>
       </c>
       <c r="CE5" t="n">
         <v>5.153758142621466</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.238596703087977</v>
+        <v>9.238596705992412</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.790184931399665</v>
+        <v>9.790184952202209</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.811166438259699</v>
+        <v>8.811166456981988</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -15312,10 +15312,10 @@
         <v>7</v>
       </c>
       <c r="CL5" t="n">
-        <v>110.2903655830689</v>
+        <v>110.2903660299016</v>
       </c>
       <c r="CM5" t="n">
-        <v>120.4915650816633</v>
+        <v>120.4915651509816</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -15580,10 +15580,10 @@
         <v>48.2400016784668</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.38294919612916</v>
+        <v>18.38294911262449</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.10037075881959</v>
+        <v>34.10037060391842</v>
       </c>
       <c r="BZ6" t="n">
         <v>76.54850565744731</v>
@@ -15592,23 +15592,23 @@
         <v>57.29789298233228</v>
       </c>
       <c r="CB6" t="n">
-        <v>103.9926848938095</v>
+        <v>103.9926850208162</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.49285961704108</v>
+        <v>48.49285963693413</v>
       </c>
       <c r="CD6" t="n">
-        <v>61.42668270152836</v>
+        <v>61.42668286936607</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>44.38117130735928</v>
+        <v>44.38117125273109</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.29661518793034</v>
+        <v>41.29661512042627</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.1669536691373</v>
+        <v>37.16695360838365</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -15620,10 +15620,10 @@
         <v>4.2</v>
       </c>
       <c r="CL6" t="n">
-        <v>-22.95407882266357</v>
+        <v>-22.95407894860396</v>
       </c>
       <c r="CM6" t="n">
-        <v>-7.999233492626534</v>
+        <v>-7.999233605869049</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -15906,10 +15906,10 @@
         <v>4.510000228881836</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.052774371111656</v>
+        <v>3.052774367495619</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.662896458412121</v>
+        <v>5.662896451704373</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.93452446594899</v>
@@ -15918,7 +15918,7 @@
         <v>8.695832933160331</v>
       </c>
       <c r="CB7" t="n">
-        <v>23.89368931359106</v>
+        <v>23.89368930263338</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -15930,7 +15930,7 @@
         <v>5.186344183602181</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.39433292546434</v>
+        <v>11.39433292294071</v>
       </c>
       <c r="CG7" t="n">
         <v>11.57513776217851</v>
@@ -15951,7 +15951,7 @@
         <v>130.9894336423016</v>
       </c>
       <c r="CM7" t="n">
-        <v>152.6459500488615</v>
+        <v>152.6459499929051</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -16234,10 +16234,10 @@
         <v>32.58000183105469</v>
       </c>
       <c r="BX8" t="n">
-        <v>24.20136270938934</v>
+        <v>24.20136284443951</v>
       </c>
       <c r="BY8" t="n">
-        <v>44.89352782591723</v>
+        <v>44.89352807643529</v>
       </c>
       <c r="BZ8" t="n">
         <v>50.78647344252641</v>
@@ -16246,25 +16246,25 @@
         <v>22.31995674309305</v>
       </c>
       <c r="CB8" t="n">
-        <v>69.38361365461598</v>
+        <v>69.38361262200334</v>
       </c>
       <c r="CC8" t="n">
-        <v>53.12760909190684</v>
+        <v>53.12760893038791</v>
       </c>
       <c r="CD8" t="n">
-        <v>28.79645784915928</v>
+        <v>28.79645706027183</v>
       </c>
       <c r="CE8" t="n">
         <v>25.44421854454374</v>
       </c>
       <c r="CF8" t="n">
-        <v>39.86915248264399</v>
+        <v>39.86915228296264</v>
       </c>
       <c r="CG8" t="n">
-        <v>36.84499283753826</v>
+        <v>36.84499256835356</v>
       </c>
       <c r="CH8" t="n">
-        <v>33.16049355378443</v>
+        <v>33.16049331151821</v>
       </c>
       <c r="CI8" t="n">
         <v>8</v>
@@ -16276,10 +16276,10 @@
         <v>3.1</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.781742449677925</v>
+        <v>1.781741706073836</v>
       </c>
       <c r="CM8" t="n">
-        <v>22.37308238774072</v>
+        <v>22.37308177484527</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -16572,10 +16572,10 @@
         <v>41.34999847412109</v>
       </c>
       <c r="BX9" t="n">
-        <v>121.1494715592892</v>
+        <v>121.1494721090868</v>
       </c>
       <c r="BY9" t="n">
-        <v>224.7322697424814</v>
+        <v>224.7322707623559</v>
       </c>
       <c r="BZ9" t="n">
         <v>134.6160883985514</v>
@@ -16596,13 +16596,13 @@
         <v>57.31088302327341</v>
       </c>
       <c r="CF9" t="n">
-        <v>139.1218202109569</v>
+        <v>139.1218204071659</v>
       </c>
       <c r="CG9" t="n">
-        <v>122.0409497276624</v>
+        <v>122.0409500025612</v>
       </c>
       <c r="CH9" t="n">
-        <v>109.8368547548962</v>
+        <v>109.8368550023051</v>
       </c>
       <c r="CI9" t="n">
         <v>8</v>
@@ -16614,10 +16614,10 @@
         <v>5.4</v>
       </c>
       <c r="CL9" t="n">
-        <v>165.6272280726627</v>
+        <v>165.6272286709915</v>
       </c>
       <c r="CM9" t="n">
-        <v>236.4493962388568</v>
+        <v>236.4493967133646</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -16900,10 +16900,10 @@
         <v>15.75</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.426879073367735</v>
+        <v>6.426879084015115</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.92186068109715</v>
+        <v>11.92186070084804</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.38777372262773</v>
@@ -16912,19 +16912,19 @@
         <v>18.61263551273508</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.14401441449393</v>
+        <v>35.14401439713617</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.29380745183323</v>
+        <v>12.29380744981134</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.32877932610295</v>
+        <v>20.32877930379371</v>
       </c>
       <c r="CE10" t="n">
         <v>17.80443971854372</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.21333011820483</v>
+        <v>20.21333011507083</v>
       </c>
       <c r="CG10" t="n">
         <v>18.61263551273508</v>
@@ -16945,7 +16945,7 @@
         <v>6.357917215629039</v>
       </c>
       <c r="CM10" t="n">
-        <v>28.33860392511003</v>
+        <v>28.33860390521161</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -17228,10 +17228,10 @@
         <v>32.97999954223633</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.05539017224547</v>
+        <v>46.05539022505743</v>
       </c>
       <c r="BY11" t="n">
-        <v>85.43274876951534</v>
+        <v>85.43274886748152</v>
       </c>
       <c r="BZ11" t="n">
         <v>69.25277241436312</v>
@@ -17252,7 +17252,7 @@
         <v>25.25865933859778</v>
       </c>
       <c r="CF11" t="n">
-        <v>78.35175841802865</v>
+        <v>78.35175843956839</v>
       </c>
       <c r="CG11" t="n">
         <v>69.25277241436312</v>
@@ -17273,7 +17273,7 @@
         <v>88.98573692551504</v>
       </c>
       <c r="CM11" t="n">
-        <v>137.5735582339421</v>
+        <v>137.5735582992536</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -17556,10 +17556,10 @@
         <v>7.050000190734863</v>
       </c>
       <c r="BX12" t="n">
-        <v>6.617251162640617</v>
+        <v>6.617251151832512</v>
       </c>
       <c r="BY12" t="n">
-        <v>12.27500090669835</v>
+        <v>12.27500088664931</v>
       </c>
       <c r="BZ12" t="n">
         <v>41.70201005680219</v>
@@ -17568,7 +17568,7 @@
         <v>28.15049940691006</v>
       </c>
       <c r="CB12" t="n">
-        <v>88.56764247231767</v>
+        <v>88.56764240476701</v>
       </c>
       <c r="CC12" t="n">
         <v>51.88018214566937</v>
@@ -18082,10 +18082,10 @@
         <v>45.97999954223633</v>
       </c>
       <c r="BX14" t="n">
-        <v>127.6301656054059</v>
+        <v>127.6301653037027</v>
       </c>
       <c r="BY14" t="n">
-        <v>236.7539571980278</v>
+        <v>236.7539566383685</v>
       </c>
       <c r="BZ14" t="n">
         <v>134.1927299415487</v>
@@ -18106,13 +18106,13 @@
         <v>55.9815638034286</v>
       </c>
       <c r="CF14" t="n">
-        <v>141.013655733659</v>
+        <v>141.0136556259887</v>
       </c>
       <c r="CG14" t="n">
-        <v>125.0879896816743</v>
+        <v>125.0879895308227</v>
       </c>
       <c r="CH14" t="n">
-        <v>112.5791907135068</v>
+        <v>112.5791905777404</v>
       </c>
       <c r="CI14" t="n">
         <v>8</v>
@@ -18124,10 +18124,10 @@
         <v>5.4</v>
       </c>
       <c r="CL14" t="n">
-        <v>144.8438273908502</v>
+        <v>144.8438270955775</v>
       </c>
       <c r="CM14" t="n">
-        <v>206.6847697641376</v>
+        <v>206.6847695299699</v>
       </c>
       <c r="CN14" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>-4.327813207567233</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-13.44221145597109</v>
+        <v>-13.4422178413344</v>
       </c>
       <c r="DA14" t="b">
         <v>1</v>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="CB15" t="inlineStr"/>
       <c r="CC15" t="n">
-        <v>0.4165</v>
+        <v>0.4136666666666666</v>
       </c>
       <c r="CD15" t="n">
         <v>20.0647511097215</v>
@@ -18706,10 +18706,10 @@
         <v>14</v>
       </c>
       <c r="BX16" t="n">
-        <v>10.1625514321637</v>
+        <v>10.16255145479927</v>
       </c>
       <c r="BY16" t="n">
-        <v>18.85153290666366</v>
+        <v>18.85153294865264</v>
       </c>
       <c r="BZ16" t="n">
         <v>51.38504155124654</v>
@@ -18718,23 +18718,23 @@
         <v>50.44813029652846</v>
       </c>
       <c r="CB16" t="n">
-        <v>71.9696190366476</v>
+        <v>71.9696190824103</v>
       </c>
       <c r="CC16" t="n">
-        <v>33.97319735450779</v>
+        <v>33.97319735111179</v>
       </c>
       <c r="CD16" t="n">
-        <v>30.82517849453211</v>
+        <v>30.82517846811912</v>
       </c>
       <c r="CE16" t="inlineStr"/>
       <c r="CF16" t="n">
-        <v>34.73659060413933</v>
+        <v>34.73659061700366</v>
       </c>
       <c r="CG16" t="n">
-        <v>33.97319735450779</v>
+        <v>33.97319735111179</v>
       </c>
       <c r="CH16" t="n">
-        <v>30.57587761905701</v>
+        <v>30.57587761600061</v>
       </c>
       <c r="CI16" t="n">
         <v>3</v>
@@ -18746,10 +18746,10 @@
         <v>5.1</v>
       </c>
       <c r="CL16" t="n">
-        <v>118.3991258504072</v>
+        <v>118.3991258285757</v>
       </c>
       <c r="CM16" t="n">
-        <v>148.1185043152809</v>
+        <v>148.118504407169</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -19028,10 +19028,10 @@
         <v>7.449999809265137</v>
       </c>
       <c r="BX17" t="n">
-        <v>3.363729737629919</v>
+        <v>3.363729731999764</v>
       </c>
       <c r="BY17" t="n">
-        <v>6.239718663303499</v>
+        <v>6.239718652859561</v>
       </c>
       <c r="BZ17" t="n">
         <v>21.74284085303151</v>
@@ -19040,7 +19040,7 @@
         <v>14.8939109083963</v>
       </c>
       <c r="CB17" t="n">
-        <v>34.9872716885013</v>
+        <v>34.9872716711396</v>
       </c>
       <c r="CC17" t="n">
         <v>10.95072400487419</v>
@@ -19336,10 +19336,10 @@
         <v>19.13999938964844</v>
       </c>
       <c r="BX18" t="n">
-        <v>13.15731125484445</v>
+        <v>13.15731125139662</v>
       </c>
       <c r="BY18" t="n">
-        <v>24.40681237773645</v>
+        <v>24.40681237134073</v>
       </c>
       <c r="BZ18" t="n">
         <v>20.45201547684208</v>
@@ -19348,7 +19348,7 @@
         <v>12.7798316087502</v>
       </c>
       <c r="CB18" t="n">
-        <v>34.61244756091308</v>
+        <v>34.61244755702038</v>
       </c>
       <c r="CC18" t="n">
         <v>22.8984489302328</v>
@@ -19358,7 +19358,7 @@
       </c>
       <c r="CE18" t="inlineStr"/>
       <c r="CF18" t="n">
-        <v>20.22864700991394</v>
+        <v>20.22864700745306</v>
       </c>
       <c r="CG18" t="n">
         <v>21.67523220353744</v>
@@ -19379,7 +19379,7 @@
         <v>1.9211578122313</v>
       </c>
       <c r="CM18" t="n">
-        <v>5.687814289347792</v>
+        <v>5.687814276490499</v>
       </c>
       <c r="CN18" t="inlineStr">
         <is>
@@ -19662,10 +19662,10 @@
         <v>17.53000068664551</v>
       </c>
       <c r="BX19" t="n">
-        <v>10.74426549734245</v>
+        <v>10.74426543933461</v>
       </c>
       <c r="BY19" t="n">
-        <v>19.93061249757024</v>
+        <v>19.93061238996571</v>
       </c>
       <c r="BZ19" t="n">
         <v>37.89111078271664</v>
@@ -19674,25 +19674,25 @@
         <v>37.31646064248518</v>
       </c>
       <c r="CB19" t="n">
-        <v>42.4039025135667</v>
+        <v>42.40390248812157</v>
       </c>
       <c r="CC19" t="n">
-        <v>34.52246247160851</v>
+        <v>34.52246248377015</v>
       </c>
       <c r="CD19" t="n">
-        <v>18.8693152365392</v>
+        <v>18.86931530381901</v>
       </c>
       <c r="CE19" t="n">
         <v>31.49264348607277</v>
       </c>
       <c r="CF19" t="n">
-        <v>31.77521537579418</v>
+        <v>31.77521536813586</v>
       </c>
       <c r="CG19" t="n">
-        <v>34.52246247160851</v>
+        <v>34.52246248377015</v>
       </c>
       <c r="CH19" t="n">
-        <v>31.07021622444766</v>
+        <v>31.07021623539313</v>
       </c>
       <c r="CI19" t="n">
         <v>7</v>
@@ -19704,10 +19704,10 @@
         <v>3.9</v>
       </c>
       <c r="CL19" t="n">
-        <v>77.24024533619782</v>
+        <v>77.24024539863635</v>
       </c>
       <c r="CM19" t="n">
-        <v>81.2619174624493</v>
+        <v>81.26191741876237</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -19990,10 +19990,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="BX20" t="n">
-        <v>10.37863324143814</v>
+        <v>10.37863324080722</v>
       </c>
       <c r="BY20" t="n">
-        <v>19.25236466286776</v>
+        <v>19.25236466169739</v>
       </c>
       <c r="BZ20" t="n">
         <v>25.85122324877091</v>
@@ -20002,25 +20002,25 @@
         <v>18.56165831752405</v>
       </c>
       <c r="CB20" t="n">
-        <v>39.76450200271903</v>
+        <v>39.76450200325498</v>
       </c>
       <c r="CC20" t="n">
-        <v>24.31404884323738</v>
+        <v>24.31404884349509</v>
       </c>
       <c r="CD20" t="n">
-        <v>13.00688756251821</v>
+        <v>13.0068875639007</v>
       </c>
       <c r="CE20" t="n">
         <v>10.35999965667725</v>
       </c>
       <c r="CF20" t="n">
-        <v>20.18616469196909</v>
+        <v>20.18616469201595</v>
       </c>
       <c r="CG20" t="n">
-        <v>18.9070114901959</v>
+        <v>18.90701148961072</v>
       </c>
       <c r="CH20" t="n">
-        <v>17.01631034117631</v>
+        <v>17.01631034064965</v>
       </c>
       <c r="CI20" t="n">
         <v>8</v>
@@ -20032,10 +20032,10 @@
         <v>3.8</v>
       </c>
       <c r="CL20" t="n">
-        <v>64.25010526143143</v>
+        <v>64.25010525634778</v>
       </c>
       <c r="CM20" t="n">
-        <v>94.84715599347211</v>
+        <v>94.84715599392443</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -20222,13 +20222,13 @@
         <v>1</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.5</v>
+        <v>0.31</v>
       </c>
       <c r="AS21" t="b">
         <v>1</v>
       </c>
       <c r="AT21" t="n">
-        <v>3694495232</v>
+        <v>5870842368</v>
       </c>
       <c r="AU21" t="n">
         <v>6.47</v>
@@ -20318,10 +20318,10 @@
         <v>11.28999996185303</v>
       </c>
       <c r="BX21" t="n">
-        <v>9.774107164473406</v>
+        <v>9.774107132824012</v>
       </c>
       <c r="BY21" t="n">
-        <v>18.13096879009817</v>
+        <v>18.13096873138854</v>
       </c>
       <c r="BZ21" t="n">
         <v>23.1209427348613</v>
@@ -20330,25 +20330,25 @@
         <v>13.6472321924953</v>
       </c>
       <c r="CB21" t="n">
-        <v>35.00095083530591</v>
+        <v>35.00095092979096</v>
       </c>
       <c r="CC21" t="n">
-        <v>25.51476116243877</v>
+        <v>25.51476118451542</v>
       </c>
       <c r="CD21" t="n">
-        <v>13.36818428647778</v>
+        <v>13.36818438891547</v>
       </c>
       <c r="CE21" t="n">
         <v>9.880299501333878</v>
       </c>
       <c r="CF21" t="n">
-        <v>18.55468083343556</v>
+        <v>18.55468084951561</v>
       </c>
       <c r="CG21" t="n">
-        <v>15.88910049129673</v>
+        <v>15.88910046194192</v>
       </c>
       <c r="CH21" t="n">
-        <v>14.30019044216706</v>
+        <v>14.30019041574773</v>
       </c>
       <c r="CI21" t="n">
         <v>8</v>
@@ -20360,10 +20360,10 @@
         <v>3.6</v>
       </c>
       <c r="CL21" t="n">
-        <v>26.66244898569488</v>
+        <v>26.66244875168839</v>
       </c>
       <c r="CM21" t="n">
-        <v>64.34615497013858</v>
+        <v>64.34615511256592</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -20648,10 +20648,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="BX22" t="n">
-        <v>5.044350349791416</v>
+        <v>5.044350317845809</v>
       </c>
       <c r="BY22" t="n">
-        <v>9.357269898863075</v>
+        <v>9.357269839603974</v>
       </c>
       <c r="BZ22" t="n">
         <v>8.453839145587175</v>
@@ -20966,37 +20966,37 @@
         <v>35.20000076293945</v>
       </c>
       <c r="BX23" t="n">
-        <v>25.31139907087614</v>
+        <v>25.31139910355626</v>
       </c>
       <c r="BY23" t="n">
-        <v>31.13019018140537</v>
+        <v>31.13019013244854</v>
       </c>
       <c r="BZ23" t="n">
-        <v>34.28259770388132</v>
+        <v>34.28259760570383</v>
       </c>
       <c r="CA23" t="n">
         <v>36.6578293511453</v>
       </c>
       <c r="CB23" t="n">
-        <v>48.45443001187616</v>
+        <v>48.45442994570239</v>
       </c>
       <c r="CC23" t="n">
-        <v>48.46302885692295</v>
+        <v>48.46302884273917</v>
       </c>
       <c r="CD23" t="n">
-        <v>16.18810975312541</v>
+        <v>16.18810967964742</v>
       </c>
       <c r="CE23" t="n">
         <v>30.16806884283779</v>
       </c>
       <c r="CF23" t="n">
-        <v>33.8319567215088</v>
+        <v>33.83195668797259</v>
       </c>
       <c r="CG23" t="n">
-        <v>32.70639394264334</v>
+        <v>32.70639386907618</v>
       </c>
       <c r="CH23" t="n">
-        <v>29.43575454837901</v>
+        <v>29.43575448216856</v>
       </c>
       <c r="CI23" t="n">
         <v>8</v>
@@ -21008,10 +21008,10 @@
         <v>3</v>
       </c>
       <c r="CL23" t="n">
-        <v>-16.37569911824935</v>
+        <v>-16.37569930634722</v>
       </c>
       <c r="CM23" t="n">
-        <v>-3.886488669826971</v>
+        <v>-3.886488765100315</v>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
@@ -21294,10 +21294,10 @@
         <v>11.07999992370605</v>
       </c>
       <c r="BX24" t="n">
-        <v>3.454302374336679</v>
+        <v>3.454302373763291</v>
       </c>
       <c r="BY24" t="n">
-        <v>6.407730904394539</v>
+        <v>6.407730903330905</v>
       </c>
       <c r="BZ24" t="n">
         <v>20.4470750681205</v>
@@ -21306,13 +21306,13 @@
         <v>19.3263652032129</v>
       </c>
       <c r="CB24" t="n">
-        <v>22.00385754061454</v>
+        <v>22.00385754065327</v>
       </c>
       <c r="CC24" t="n">
-        <v>16.46863777362829</v>
+        <v>16.46863777374062</v>
       </c>
       <c r="CD24" t="n">
-        <v>13.71979386663865</v>
+        <v>13.71979386736575</v>
       </c>
       <c r="CE24" t="n">
         <v>30.3956356510297</v>
@@ -21368,7 +21368,7 @@
         <v>-18.94659940111765</v>
       </c>
       <c r="CZ24" t="n">
-        <v>-32.89648837260555</v>
+        <v>-32.89649636084019</v>
       </c>
       <c r="DA24" t="b">
         <v>1</v>
@@ -21612,10 +21612,10 @@
         <v>14.13000011444092</v>
       </c>
       <c r="BX25" t="n">
-        <v>4.339755641457224</v>
+        <v>4.339755634461686</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.050246714903151</v>
+        <v>8.050246701926426</v>
       </c>
       <c r="BZ25" t="n">
         <v>24.63453967320291</v>
@@ -21624,25 +21624,25 @@
         <v>20.77142752850562</v>
       </c>
       <c r="CB25" t="n">
-        <v>30.61150736881369</v>
+        <v>30.61150737362448</v>
       </c>
       <c r="CC25" t="n">
-        <v>16.75489077685345</v>
+        <v>16.75489077827534</v>
       </c>
       <c r="CD25" t="n">
-        <v>19.18328686164304</v>
+        <v>19.18328687276707</v>
       </c>
       <c r="CE25" t="n">
         <v>14.37360703573516</v>
       </c>
       <c r="CF25" t="n">
-        <v>19.197072279951</v>
+        <v>19.19707228057672</v>
       </c>
       <c r="CG25" t="n">
-        <v>19.18328686164304</v>
+        <v>19.18328687276707</v>
       </c>
       <c r="CH25" t="n">
-        <v>17.26495817547874</v>
+        <v>17.26495818549037</v>
       </c>
       <c r="CI25" t="n">
         <v>7</v>
@@ -21654,10 +21654,10 @@
         <v>7.1</v>
       </c>
       <c r="CL25" t="n">
-        <v>22.1865395304129</v>
+        <v>22.1865396012666</v>
       </c>
       <c r="CM25" t="n">
-        <v>35.86038304650485</v>
+        <v>35.86038305093309</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -22250,10 +22250,10 @@
         <v>13.23999977111816</v>
       </c>
       <c r="BX27" t="n">
-        <v>8.302142152401363</v>
+        <v>8.302142137638233</v>
       </c>
       <c r="BY27" t="n">
-        <v>15.40047369270453</v>
+        <v>15.40047366531892</v>
       </c>
       <c r="BZ27" t="n">
         <v>14.18189142823894</v>
@@ -22274,7 +22274,7 @@
         <v>6.364116594565261</v>
       </c>
       <c r="CF27" t="n">
-        <v>11.29369907898543</v>
+        <v>11.29369907296419</v>
       </c>
       <c r="CG27" t="n">
         <v>11.52626939957729</v>
@@ -22295,7 +22295,7 @@
         <v>-21.64922478134251</v>
       </c>
       <c r="CM27" t="n">
-        <v>-14.70015653911421</v>
+        <v>-14.70015658459189</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -22578,10 +22578,10 @@
         <v>27.52000045776367</v>
       </c>
       <c r="BX28" t="n">
-        <v>7.290978513671294</v>
+        <v>7.290978493666847</v>
       </c>
       <c r="BY28" t="n">
-        <v>13.52476514286025</v>
+        <v>13.524765105752</v>
       </c>
       <c r="BZ28" t="n">
         <v>36.57372177185242</v>
@@ -22590,19 +22590,19 @@
         <v>28.87454744278962</v>
       </c>
       <c r="CB28" t="n">
-        <v>45.93352492840341</v>
+        <v>45.93352495778168</v>
       </c>
       <c r="CC28" t="n">
-        <v>26.49482249861916</v>
+        <v>26.49482250350369</v>
       </c>
       <c r="CD28" t="n">
-        <v>29.81102742050766</v>
+        <v>29.81102745663089</v>
       </c>
       <c r="CE28" t="n">
         <v>24.2620728130642</v>
       </c>
       <c r="CF28" t="n">
-        <v>29.35349743115668</v>
+        <v>29.35349743591064</v>
       </c>
       <c r="CG28" t="n">
         <v>28.87454744278962</v>
@@ -22623,7 +22623,7 @@
         <v>-5.570158916260349</v>
       </c>
       <c r="CM28" t="n">
-        <v>6.662416216914546</v>
+        <v>6.662416234189128</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>-5.331954775825187</v>
       </c>
       <c r="CZ28" t="n">
-        <v>-21.99140136548733</v>
+        <v>-21.99140983840919</v>
       </c>
       <c r="DA28" t="b">
         <v>1</v>
@@ -22906,10 +22906,10 @@
         <v>22.06999969482422</v>
       </c>
       <c r="BX29" t="n">
-        <v>3.108072446053702</v>
+        <v>3.108072449167506</v>
       </c>
       <c r="BY29" t="n">
-        <v>5.765474387429617</v>
+        <v>5.765474393205723</v>
       </c>
       <c r="BZ29" t="n">
         <v>33.57376532220675</v>
@@ -22918,7 +22918,7 @@
         <v>28.04300293143303</v>
       </c>
       <c r="CB29" t="n">
-        <v>43.00378985845179</v>
+        <v>43.00378986345676</v>
       </c>
       <c r="CC29" t="n">
         <v>10.85340539909456</v>
@@ -23204,10 +23204,10 @@
         <v>38.90000152587891</v>
       </c>
       <c r="BX30" t="n">
-        <v>35.62892559158855</v>
+        <v>35.62892563789725</v>
       </c>
       <c r="BY30" t="n">
-        <v>51.87571566135294</v>
+        <v>51.8757157287784</v>
       </c>
       <c r="BZ30" t="n">
         <v>50.25590259243982</v>
@@ -23224,13 +23224,13 @@
       </c>
       <c r="CE30" t="inlineStr"/>
       <c r="CF30" t="n">
-        <v>49.31617720729976</v>
+        <v>49.31617723573329</v>
       </c>
       <c r="CG30" t="n">
-        <v>51.06580912689638</v>
+        <v>51.06580916060911</v>
       </c>
       <c r="CH30" t="n">
-        <v>45.95922821420675</v>
+        <v>45.9592282445482</v>
       </c>
       <c r="CI30" t="n">
         <v>4</v>
@@ -23242,10 +23242,10 @@
         <v>1.7</v>
       </c>
       <c r="CL30" t="n">
-        <v>18.14711159749329</v>
+        <v>18.14711167549188</v>
       </c>
       <c r="CM30" t="n">
-        <v>26.77680018724757</v>
+        <v>26.77680026034148</v>
       </c>
       <c r="CN30" t="inlineStr">
         <is>
@@ -23528,10 +23528,10 @@
         <v>24.72999954223633</v>
       </c>
       <c r="BX31" t="n">
-        <v>12.83053370570825</v>
+        <v>12.83053368943437</v>
       </c>
       <c r="BY31" t="n">
-        <v>23.8006400240888</v>
+        <v>23.80063999390076</v>
       </c>
       <c r="BZ31" t="n">
         <v>61.59257404786302</v>
@@ -23540,13 +23540,13 @@
         <v>51.63850781741169</v>
       </c>
       <c r="CB31" t="n">
-        <v>85.84612580035729</v>
+        <v>85.84612579913383</v>
       </c>
       <c r="CC31" t="n">
-        <v>33.66425527009655</v>
+        <v>33.66425527280584</v>
       </c>
       <c r="CD31" t="n">
-        <v>45.15510816065936</v>
+        <v>45.15510818680953</v>
       </c>
       <c r="CE31" t="n">
         <v>5.142038558436727</v>
@@ -23842,10 +23842,10 @@
         <v>12.02999973297119</v>
       </c>
       <c r="BX32" t="n">
-        <v>2.080017508669553</v>
+        <v>2.080017511162542</v>
       </c>
       <c r="BY32" t="n">
-        <v>3.858432478582021</v>
+        <v>3.858432483206515</v>
       </c>
       <c r="BZ32" t="n">
         <v>28.61714478669089</v>
@@ -23854,7 +23854,7 @@
         <v>24.30030260991828</v>
       </c>
       <c r="CB32" t="n">
-        <v>37.6248188718028</v>
+        <v>37.62481887806884</v>
       </c>
       <c r="CC32" t="n">
         <v>9.158754146</v>
@@ -24156,10 +24156,10 @@
         <v>33.43000030517578</v>
       </c>
       <c r="BX33" t="n">
-        <v>7.930922164176469</v>
+        <v>7.930922153366162</v>
       </c>
       <c r="BY33" t="n">
-        <v>14.71186061454735</v>
+        <v>14.71186059449423</v>
       </c>
       <c r="BZ33" t="n">
         <v>67.41971142215816</v>
@@ -24168,7 +24168,7 @@
         <v>39.36375120302754</v>
       </c>
       <c r="CB33" t="n">
-        <v>93.22418795678955</v>
+        <v>93.22418793375388</v>
       </c>
       <c r="CC33" t="n">
         <v>22.51480113099953</v>
@@ -24452,35 +24452,35 @@
         <v>23.04999923706055</v>
       </c>
       <c r="BX34" t="n">
-        <v>16.54376617069508</v>
+        <v>16.54376614373064</v>
       </c>
       <c r="BY34" t="n">
-        <v>30.07147189256665</v>
+        <v>30.07147189666543</v>
       </c>
       <c r="BZ34" t="n">
-        <v>51.50946628219135</v>
+        <v>51.50946637316667</v>
       </c>
       <c r="CA34" t="n">
         <v>50.09186275696137</v>
       </c>
       <c r="CB34" t="n">
-        <v>63.06344045694706</v>
+        <v>63.06344044501155</v>
       </c>
       <c r="CC34" t="n">
-        <v>45.81097523878608</v>
+        <v>45.81097524457223</v>
       </c>
       <c r="CD34" t="n">
-        <v>25.18054540102311</v>
+        <v>25.18054543436194</v>
       </c>
       <c r="CE34" t="inlineStr"/>
       <c r="CF34" t="n">
-        <v>35.98391989605979</v>
+        <v>35.98391991453374</v>
       </c>
       <c r="CG34" t="n">
-        <v>37.94122356567637</v>
+        <v>37.94122357061883</v>
       </c>
       <c r="CH34" t="n">
-        <v>34.14710120910873</v>
+        <v>34.14710121355695</v>
       </c>
       <c r="CI34" t="n">
         <v>4</v>
@@ -24492,10 +24492,10 @@
         <v>3.1</v>
       </c>
       <c r="CL34" t="n">
-        <v>48.1436110167236</v>
+        <v>48.14361103602172</v>
       </c>
       <c r="CM34" t="n">
-        <v>56.11245590934188</v>
+        <v>56.1124559894892</v>
       </c>
       <c r="CN34" t="inlineStr">
         <is>
@@ -24778,10 +24778,10 @@
         <v>32.75</v>
       </c>
       <c r="BX35" t="n">
-        <v>3.249356703185835</v>
+        <v>3.249356695245596</v>
       </c>
       <c r="BY35" t="n">
-        <v>6.027556684409724</v>
+        <v>6.02755666968058</v>
       </c>
       <c r="BZ35" t="n">
         <v>33.45701619121048</v>
@@ -24790,7 +24790,7 @@
         <v>23.42786572511178</v>
       </c>
       <c r="CB35" t="n">
-        <v>41.38326860791069</v>
+        <v>41.38326859933989</v>
       </c>
       <c r="CC35" t="n">
         <v>10.59424454785779</v>
@@ -24860,7 +24860,7 @@
         <v>0.738239590458023</v>
       </c>
       <c r="CZ35" t="n">
-        <v>-31.31834368818209</v>
+        <v>-31.318349352401</v>
       </c>
       <c r="DA35" t="b">
         <v>1</v>
@@ -25104,10 +25104,10 @@
         <v>33.65000152587891</v>
       </c>
       <c r="BX36" t="n">
-        <v>15.24688682451942</v>
+        <v>15.2468868394871</v>
       </c>
       <c r="BY36" t="n">
-        <v>28.28297505948352</v>
+        <v>28.28297508724857</v>
       </c>
       <c r="BZ36" t="n">
         <v>20.22969692458691</v>
@@ -25116,7 +25116,7 @@
         <v>37.31912959637818</v>
       </c>
       <c r="CB36" t="n">
-        <v>27.24280549414153</v>
+        <v>27.24280550364913</v>
       </c>
       <c r="CC36" t="n">
         <v>15.03391666666667</v>
@@ -25128,7 +25128,7 @@
         <v>77.67169119949854</v>
       </c>
       <c r="CF36" t="n">
-        <v>22.63863277142798</v>
+        <v>22.63863277889089</v>
       </c>
       <c r="CG36" t="n">
         <v>20.22969692458691</v>
@@ -25149,7 +25149,7 @@
         <v>-45.89382940108894</v>
       </c>
       <c r="CM36" t="n">
-        <v>-32.72323404200297</v>
+        <v>-32.72323401982494</v>
       </c>
       <c r="CN36" t="inlineStr">
         <is>
@@ -25408,10 +25408,10 @@
         <v>14.77999973297119</v>
       </c>
       <c r="BX37" t="n">
-        <v>9.186484942523455</v>
+        <v>9.186484864776657</v>
       </c>
       <c r="BY37" t="n">
-        <v>17.04092956838101</v>
+        <v>17.0409294241607</v>
       </c>
       <c r="BZ37" t="n">
         <v>31.89495056382219</v>
@@ -25420,23 +25420,23 @@
         <v>30.33345456974609</v>
       </c>
       <c r="CB37" t="n">
-        <v>36.78693480627849</v>
+        <v>36.78693478280437</v>
       </c>
       <c r="CC37" t="n">
-        <v>25.58128744681195</v>
+        <v>25.5812874621472</v>
       </c>
       <c r="CD37" t="n">
-        <v>16.38749076950991</v>
+        <v>16.38749086618339</v>
       </c>
       <c r="CE37" t="inlineStr"/>
       <c r="CF37" t="n">
-        <v>20.92591313038465</v>
+        <v>20.92591307872669</v>
       </c>
       <c r="CG37" t="n">
-        <v>21.31110850759648</v>
+        <v>21.31110844315395</v>
       </c>
       <c r="CH37" t="n">
-        <v>19.17999765683683</v>
+        <v>19.17999759883855</v>
       </c>
       <c r="CI37" t="n">
         <v>4</v>
@@ -25448,10 +25448,10 @@
         <v>3.5</v>
       </c>
       <c r="CL37" t="n">
-        <v>29.76994589553432</v>
+        <v>29.76994550312377</v>
       </c>
       <c r="CM37" t="n">
-        <v>41.58263537517642</v>
+        <v>41.58263502566379</v>
       </c>
       <c r="CN37" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>-7.171627471148123</v>
       </c>
       <c r="CZ37" t="n">
-        <v>-18.74746959920818</v>
+        <v>-18.74747840191868</v>
       </c>
       <c r="DA37" t="b">
         <v>1</v>
@@ -25714,35 +25714,35 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BX38" t="n">
-        <v>8.627042101504598</v>
+        <v>8.627042116836234</v>
       </c>
       <c r="BY38" t="n">
-        <v>14.3473089881045</v>
+        <v>14.3473089692186</v>
       </c>
       <c r="BZ38" t="n">
-        <v>19.54486185013556</v>
+        <v>19.54486178967358</v>
       </c>
       <c r="CA38" t="n">
         <v>17.74926644976348</v>
       </c>
       <c r="CB38" t="n">
-        <v>23.9353952809524</v>
+        <v>23.93539526688062</v>
       </c>
       <c r="CC38" t="n">
-        <v>17.38495028879861</v>
+        <v>17.3849502846228</v>
       </c>
       <c r="CD38" t="n">
-        <v>9.719867150456352</v>
+        <v>9.719867124336151</v>
       </c>
       <c r="CE38" t="inlineStr"/>
       <c r="CF38" t="n">
-        <v>14.97604080713582</v>
+        <v>14.9760407900878</v>
       </c>
       <c r="CG38" t="n">
-        <v>15.86612963845156</v>
+        <v>15.8661296269207</v>
       </c>
       <c r="CH38" t="n">
-        <v>14.2795166746064</v>
+        <v>14.27951666422863</v>
       </c>
       <c r="CI38" t="n">
         <v>4</v>
@@ -25754,10 +25754,10 @@
         <v>2.3</v>
       </c>
       <c r="CL38" t="n">
-        <v>11.1246400832649</v>
+        <v>11.12464000250404</v>
       </c>
       <c r="CM38" t="n">
-        <v>16.54506118717272</v>
+        <v>16.54506105450333</v>
       </c>
       <c r="CN38" t="inlineStr">
         <is>
@@ -26048,10 +26048,10 @@
         <v>5.880000114440918</v>
       </c>
       <c r="BX39" t="n">
-        <v>6.97575081720508</v>
+        <v>6.975750804712934</v>
       </c>
       <c r="BY39" t="n">
-        <v>12.94001776591542</v>
+        <v>12.94001774274249</v>
       </c>
       <c r="BZ39" t="n">
         <v>5.605036080312384</v>
@@ -26072,7 +26072,7 @@
         <v>5.348622529323849</v>
       </c>
       <c r="CF39" t="n">
-        <v>7.296291367611541</v>
+        <v>7.296291363153406</v>
       </c>
       <c r="CG39" t="n">
         <v>5.869184706822859</v>
@@ -26093,7 +26093,7 @@
         <v>-10.16554195011574</v>
       </c>
       <c r="CM39" t="n">
-        <v>24.08658546948492</v>
+        <v>24.0865853936663</v>
       </c>
       <c r="CN39" t="inlineStr">
         <is>
@@ -26358,10 +26358,10 @@
         <v>39.43999862670898</v>
       </c>
       <c r="BX40" t="n">
-        <v>20.16127590415178</v>
+        <v>20.16127576378087</v>
       </c>
       <c r="BY40" t="n">
-        <v>37.39916680220153</v>
+        <v>37.39916654181352</v>
       </c>
       <c r="BZ40" t="n">
         <v>57.05021635413689</v>
@@ -26370,23 +26370,23 @@
         <v>43.06721646336476</v>
       </c>
       <c r="CB40" t="n">
-        <v>64.10972902841927</v>
+        <v>64.10972925506432</v>
       </c>
       <c r="CC40" t="n">
-        <v>45.28400684795875</v>
+        <v>45.28400689102889</v>
       </c>
       <c r="CD40" t="n">
-        <v>32.43094038342355</v>
+        <v>32.4309406607403</v>
       </c>
       <c r="CE40" t="inlineStr"/>
       <c r="CF40" t="n">
-        <v>39.97366647711224</v>
+        <v>39.97366638769005</v>
       </c>
       <c r="CG40" t="n">
-        <v>41.34158682508014</v>
+        <v>41.3415867164212</v>
       </c>
       <c r="CH40" t="n">
-        <v>37.20742814257213</v>
+        <v>37.20742804477909</v>
       </c>
       <c r="CI40" t="n">
         <v>4</v>
@@ -26398,10 +26398,10 @@
         <v>2.8</v>
       </c>
       <c r="CL40" t="n">
-        <v>-5.66067586682153</v>
+        <v>-5.660676114775498</v>
       </c>
       <c r="CM40" t="n">
-        <v>1.353113258076677</v>
+        <v>1.353113031346953</v>
       </c>
       <c r="CN40" t="inlineStr">
         <is>
@@ -26684,37 +26684,37 @@
         <v>26.45999908447266</v>
       </c>
       <c r="BX41" t="n">
-        <v>16.91893496395116</v>
+        <v>16.91893506893802</v>
       </c>
       <c r="BY41" t="n">
-        <v>28.67982834511886</v>
+        <v>28.67982835899834</v>
       </c>
       <c r="BZ41" t="n">
-        <v>49.21350845818002</v>
+        <v>49.21350817661271</v>
       </c>
       <c r="CA41" t="n">
         <v>53.99475108321082</v>
       </c>
       <c r="CB41" t="n">
-        <v>57.93925171177568</v>
+        <v>57.93925175074026</v>
       </c>
       <c r="CC41" t="n">
-        <v>43.01388445567864</v>
+        <v>43.0138844369042</v>
       </c>
       <c r="CD41" t="n">
-        <v>24.40657263841013</v>
+        <v>24.40657252098443</v>
       </c>
       <c r="CE41" t="n">
         <v>30.06721996094383</v>
       </c>
       <c r="CF41" t="n">
-        <v>38.02924395215864</v>
+        <v>38.02924391966657</v>
       </c>
       <c r="CG41" t="n">
-        <v>36.54055220831123</v>
+        <v>36.54055219892401</v>
       </c>
       <c r="CH41" t="n">
-        <v>32.88649698748011</v>
+        <v>32.88649697903161</v>
       </c>
       <c r="CI41" t="n">
         <v>8</v>
@@ -26726,10 +26726,10 @@
         <v>3.4</v>
       </c>
       <c r="CL41" t="n">
-        <v>24.28759684568043</v>
+        <v>24.28759681375112</v>
       </c>
       <c r="CM41" t="n">
-        <v>43.72352708989731</v>
+        <v>43.72352696710038</v>
       </c>
       <c r="CN41" t="inlineStr">
         <is>
@@ -27012,10 +27012,10 @@
         <v>11.76000022888184</v>
       </c>
       <c r="BX42" t="n">
-        <v>4.779815376590163</v>
+        <v>4.779815371273065</v>
       </c>
       <c r="BY42" t="n">
-        <v>8.866557523574752</v>
+        <v>8.866557513711536</v>
       </c>
       <c r="BZ42" t="n">
         <v>27.09913096220597</v>
@@ -27024,25 +27024,25 @@
         <v>30.54574135914352</v>
       </c>
       <c r="CB42" t="n">
-        <v>25.60465062732849</v>
+        <v>25.60465062193811</v>
       </c>
       <c r="CC42" t="n">
-        <v>14.19260756894574</v>
+        <v>14.19260756943654</v>
       </c>
       <c r="CD42" t="n">
-        <v>14.24280839636142</v>
+        <v>14.24280840111065</v>
       </c>
       <c r="CE42" t="n">
         <v>5.07221344413531</v>
       </c>
       <c r="CF42" t="n">
-        <v>20.09191607292665</v>
+        <v>20.09191607125772</v>
       </c>
       <c r="CG42" t="n">
-        <v>19.92372951184496</v>
+        <v>19.92372951152438</v>
       </c>
       <c r="CH42" t="n">
-        <v>17.93135656066046</v>
+        <v>17.93135656037195</v>
       </c>
       <c r="CI42" t="n">
         <v>6</v>
@@ -27054,10 +27054,10 @@
         <v>6.4</v>
       </c>
       <c r="CL42" t="n">
-        <v>52.47751880669318</v>
+        <v>52.47751880423981</v>
       </c>
       <c r="CM42" t="n">
-        <v>70.84962314526268</v>
+        <v>70.84962313107113</v>
       </c>
       <c r="CN42" t="inlineStr">
         <is>
@@ -27340,37 +27340,37 @@
         <v>15.3100004196167</v>
       </c>
       <c r="BX43" t="n">
-        <v>5.939526976484671</v>
+        <v>5.939526966495125</v>
       </c>
       <c r="BY43" t="n">
-        <v>8.534880597786364</v>
+        <v>8.534880606033607</v>
       </c>
       <c r="BZ43" t="n">
-        <v>10.81501542525123</v>
+        <v>10.81501545389127</v>
       </c>
       <c r="CA43" t="n">
         <v>11.65944891202323</v>
       </c>
       <c r="CB43" t="n">
-        <v>9.81040379362247</v>
+        <v>9.810403809730376</v>
       </c>
       <c r="CC43" t="n">
-        <v>14.90925677649959</v>
+        <v>14.90925678000476</v>
       </c>
       <c r="CD43" t="n">
-        <v>5.384140019951317</v>
+        <v>5.384140036126389</v>
       </c>
       <c r="CE43" t="n">
         <v>10.69689722735973</v>
       </c>
       <c r="CF43" t="n">
-        <v>9.718696216122325</v>
+        <v>9.718696223958061</v>
       </c>
       <c r="CG43" t="n">
-        <v>10.2536505104911</v>
+        <v>10.25365051854505</v>
       </c>
       <c r="CH43" t="n">
-        <v>9.22828545944199</v>
+        <v>9.228285466690549</v>
       </c>
       <c r="CI43" t="n">
         <v>8</v>
@@ -27382,10 +27382,10 @@
         <v>2.8</v>
       </c>
       <c r="CL43" t="n">
-        <v>-39.72380661977128</v>
+        <v>-39.72380657242602</v>
       </c>
       <c r="CM43" t="n">
-        <v>-36.52060124263771</v>
+        <v>-36.5206011914572</v>
       </c>
       <c r="CN43" t="inlineStr">
         <is>
@@ -27668,10 +27668,10 @@
         <v>9.25</v>
       </c>
       <c r="BX44" t="n">
-        <v>2.521670927333336</v>
+        <v>2.521670923786019</v>
       </c>
       <c r="BY44" t="n">
-        <v>4.677699570203337</v>
+        <v>4.677699563623064</v>
       </c>
       <c r="BZ44" t="n">
         <v>13.66360089186176</v>
@@ -27680,19 +27680,19 @@
         <v>15.44242552617786</v>
       </c>
       <c r="CB44" t="n">
-        <v>10.73109422410298</v>
+        <v>10.73109422354266</v>
       </c>
       <c r="CC44" t="n">
-        <v>7.312738776922527</v>
+        <v>7.312738777253591</v>
       </c>
       <c r="CD44" t="n">
-        <v>7.026196810211229</v>
+        <v>7.026196813339111</v>
       </c>
       <c r="CE44" t="n">
         <v>10.33342380121613</v>
       </c>
       <c r="CF44" t="n">
-        <v>9.883882800099403</v>
+        <v>9.883882799573454</v>
       </c>
       <c r="CG44" t="n">
         <v>10.33342380121613</v>
@@ -27713,7 +27713,7 @@
         <v>0.5414207685893846</v>
       </c>
       <c r="CM44" t="n">
-        <v>6.852787028101659</v>
+        <v>6.852787022415718</v>
       </c>
       <c r="CN44" t="inlineStr">
         <is>
@@ -27994,10 +27994,10 @@
         <v>6.400000095367432</v>
       </c>
       <c r="BX45" t="n">
-        <v>7.596590947920403</v>
+        <v>7.596590894294517</v>
       </c>
       <c r="BY45" t="n">
-        <v>11.06063642017211</v>
+        <v>11.06063634209282</v>
       </c>
       <c r="BZ45" t="n">
         <v>8.29925199399268</v>
@@ -28016,7 +28016,7 @@
         <v>5.369614780864673</v>
       </c>
       <c r="CF45" t="n">
-        <v>8.371703271308844</v>
+        <v>8.37170324935798</v>
       </c>
       <c r="CG45" t="n">
         <v>8.587865965618855</v>
@@ -28037,7 +28037,7 @@
         <v>20.76686334194866</v>
       </c>
       <c r="CM45" t="n">
-        <v>30.80786166501166</v>
+        <v>30.8078613220294</v>
       </c>
       <c r="CN45" t="inlineStr">
         <is>
@@ -28320,37 +28320,37 @@
         <v>38.86000061035156</v>
       </c>
       <c r="BX46" t="n">
-        <v>30.97422543793434</v>
+        <v>30.97422548036206</v>
       </c>
       <c r="BY46" t="n">
-        <v>37.33904021088482</v>
+        <v>37.33904017539584</v>
       </c>
       <c r="BZ46" t="n">
-        <v>41.77389268641083</v>
+        <v>41.77389258948588</v>
       </c>
       <c r="CA46" t="n">
         <v>51.32924379406393</v>
       </c>
       <c r="CB46" t="n">
-        <v>64.51021358360998</v>
+        <v>64.5102135381366</v>
       </c>
       <c r="CC46" t="n">
-        <v>16.34210047707102</v>
+        <v>16.34210047312566</v>
       </c>
       <c r="CD46" t="n">
-        <v>19.48042967678916</v>
+        <v>19.48042960159367</v>
       </c>
       <c r="CE46" t="n">
         <v>27.99121924833823</v>
       </c>
       <c r="CF46" t="n">
-        <v>36.21754563938779</v>
+        <v>36.21754561256273</v>
       </c>
       <c r="CG46" t="n">
-        <v>34.15663282440958</v>
+        <v>34.15663282787895</v>
       </c>
       <c r="CH46" t="n">
-        <v>30.74096954196863</v>
+        <v>30.74096954509106</v>
       </c>
       <c r="CI46" t="n">
         <v>8</v>
@@ -28362,10 +28362,10 @@
         <v>3.9</v>
       </c>
       <c r="CL46" t="n">
-        <v>-20.89302866922802</v>
+        <v>-20.89302866119295</v>
       </c>
       <c r="CM46" t="n">
-        <v>-6.799935484972353</v>
+        <v>-6.799935554002367</v>
       </c>
       <c r="CN46" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>1</v>
       </c>
       <c r="AT47" t="n">
-        <v>182762307584</v>
+        <v>182443720704</v>
       </c>
       <c r="AU47" t="n">
         <v>6.96</v>
@@ -28630,35 +28630,35 @@
         <v>16.78000068664551</v>
       </c>
       <c r="BX47" t="n">
-        <v>9.985664050312705</v>
+        <v>9.985664018193983</v>
       </c>
       <c r="BY47" t="n">
-        <v>18.36675920877225</v>
+        <v>18.36675921429381</v>
       </c>
       <c r="BZ47" t="n">
-        <v>31.67453737106667</v>
+        <v>31.67453748246954</v>
       </c>
       <c r="CA47" t="n">
         <v>30.47653407949944</v>
       </c>
       <c r="CB47" t="n">
-        <v>34.39875972145861</v>
+        <v>34.39875972038924</v>
       </c>
       <c r="CC47" t="n">
-        <v>27.99338997784159</v>
+        <v>27.99338998480554</v>
       </c>
       <c r="CD47" t="n">
-        <v>15.43712489841865</v>
+        <v>15.43712493835636</v>
       </c>
       <c r="CE47" t="inlineStr"/>
       <c r="CF47" t="n">
-        <v>22.0050876519983</v>
+        <v>22.00508767494072</v>
       </c>
       <c r="CG47" t="n">
-        <v>23.18007459330693</v>
+        <v>23.18007459954968</v>
       </c>
       <c r="CH47" t="n">
-        <v>20.86206713397624</v>
+        <v>20.86206713959471</v>
       </c>
       <c r="CI47" t="n">
         <v>4</v>
@@ -28670,10 +28670,10 @@
         <v>3.2</v>
       </c>
       <c r="CL47" t="n">
-        <v>24.32697425679768</v>
+        <v>24.32697429028086</v>
       </c>
       <c r="CM47" t="n">
-        <v>31.13877682681634</v>
+        <v>31.1387769635411</v>
       </c>
       <c r="CN47" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>-7.744448996751174</v>
       </c>
       <c r="CZ47" t="n">
-        <v>-20.99429475986069</v>
+        <v>-20.99430199889827</v>
       </c>
       <c r="DA47" t="b">
         <v>1</v>
@@ -28956,10 +28956,10 @@
         <v>34.09000015258789</v>
       </c>
       <c r="BX48" t="n">
-        <v>14.76402959172009</v>
+        <v>14.76402957143722</v>
       </c>
       <c r="BY48" t="n">
-        <v>27.38727489264076</v>
+        <v>27.38727485501604</v>
       </c>
       <c r="BZ48" t="n">
         <v>56.25062291678574</v>
@@ -28968,25 +28968,25 @@
         <v>43.51071962247149</v>
       </c>
       <c r="CB48" t="n">
-        <v>72.55360776377499</v>
+        <v>72.5536077894356</v>
       </c>
       <c r="CC48" t="n">
-        <v>38.45081141473263</v>
+        <v>38.45081141971068</v>
       </c>
       <c r="CD48" t="n">
-        <v>40.76646236458164</v>
+        <v>40.76646240293898</v>
       </c>
       <c r="CE48" t="n">
         <v>21.06667845031192</v>
       </c>
       <c r="CF48" t="n">
-        <v>42.85516820361418</v>
+        <v>42.85516820809578</v>
       </c>
       <c r="CG48" t="n">
-        <v>40.76646236458164</v>
+        <v>40.76646240293898</v>
       </c>
       <c r="CH48" t="n">
-        <v>36.68981612812348</v>
+        <v>36.68981616264508</v>
       </c>
       <c r="CI48" t="n">
         <v>7</v>
@@ -28998,10 +28998,10 @@
         <v>4.9</v>
       </c>
       <c r="CL48" t="n">
-        <v>7.626330196241526</v>
+        <v>7.626330297507566</v>
       </c>
       <c r="CM48" t="n">
-        <v>25.71184515046385</v>
+        <v>25.71184516361025</v>
       </c>
       <c r="CN48" t="inlineStr">
         <is>
@@ -29280,37 +29280,37 @@
         <v>44.2400016784668</v>
       </c>
       <c r="BX49" t="n">
-        <v>32.08407761727376</v>
+        <v>32.08407766834327</v>
       </c>
       <c r="BY49" t="n">
-        <v>48.69139719501933</v>
+        <v>48.69139707858242</v>
       </c>
       <c r="BZ49" t="n">
-        <v>58.34154957995293</v>
+        <v>58.34154934757478</v>
       </c>
       <c r="CA49" t="n">
         <v>49.68675315451532</v>
       </c>
       <c r="CB49" t="n">
-        <v>78.17304721755997</v>
+        <v>78.17304711557226</v>
       </c>
       <c r="CC49" t="n">
-        <v>60.4070601585803</v>
+        <v>60.40706013825914</v>
       </c>
       <c r="CD49" t="n">
-        <v>29.16704243878997</v>
+        <v>29.16704232001045</v>
       </c>
       <c r="CE49" t="n">
         <v>77.58261943552711</v>
       </c>
       <c r="CF49" t="n">
-        <v>54.26669334965234</v>
+        <v>54.26669328229809</v>
       </c>
       <c r="CG49" t="n">
-        <v>54.01415136723412</v>
+        <v>54.01415125104505</v>
       </c>
       <c r="CH49" t="n">
-        <v>48.61273623051071</v>
+        <v>48.61273612594054</v>
       </c>
       <c r="CI49" t="n">
         <v>8</v>
@@ -29322,10 +29322,10 @@
         <v>2.7</v>
       </c>
       <c r="CL49" t="n">
-        <v>9.884119317681407</v>
+        <v>9.884119081311237</v>
       </c>
       <c r="CM49" t="n">
-        <v>22.66431123592361</v>
+        <v>22.66431108367621</v>
       </c>
       <c r="CN49" t="inlineStr">
         <is>
@@ -29608,10 +29608,10 @@
         <v>32.65999984741211</v>
       </c>
       <c r="BX50" t="n">
-        <v>11.09799946397964</v>
+        <v>11.09799935577486</v>
       </c>
       <c r="BY50" t="n">
-        <v>20.58678900568224</v>
+        <v>20.58678880496236</v>
       </c>
       <c r="BZ50" t="n">
         <v>56.94013131292242</v>
@@ -29620,19 +29620,19 @@
         <v>53.82541566292831</v>
       </c>
       <c r="CB50" t="n">
-        <v>59.89734830826107</v>
+        <v>59.89734832677433</v>
       </c>
       <c r="CC50" t="n">
-        <v>28.27275394625155</v>
+        <v>28.27275368372061</v>
       </c>
       <c r="CD50" t="n">
-        <v>36.27955935326523</v>
+        <v>36.27955949019191</v>
       </c>
       <c r="CE50" t="n">
         <v>53.57698797570033</v>
       </c>
       <c r="CF50" t="n">
-        <v>44.19699793785873</v>
+        <v>44.19699789388574</v>
       </c>
       <c r="CG50" t="n">
         <v>53.57698797570033</v>
@@ -29653,7 +29653,7 @@
         <v>47.64020025539306</v>
       </c>
       <c r="CM50" t="n">
-        <v>35.32455035011515</v>
+        <v>35.32455021547649</v>
       </c>
       <c r="CN50" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>-0.2500150878204321</v>
       </c>
       <c r="CZ50" t="n">
-        <v>-10.82895234146481</v>
+        <v>-10.82896174015665</v>
       </c>
       <c r="DA50" t="b">
         <v>1</v>
@@ -29936,10 +29936,10 @@
         <v>12.96000003814697</v>
       </c>
       <c r="BX51" t="n">
-        <v>1.595679010322607</v>
+        <v>1.595679009169382</v>
       </c>
       <c r="BY51" t="n">
-        <v>2.959984564148437</v>
+        <v>2.959984562009204</v>
       </c>
       <c r="BZ51" t="n">
         <v>13.02883160132378</v>
@@ -29948,7 +29948,7 @@
         <v>9.525658668173282</v>
       </c>
       <c r="CB51" t="n">
-        <v>16.44457562342345</v>
+        <v>16.44457562219848</v>
       </c>
       <c r="CC51" t="n">
         <v>6.104046666666666</v>
@@ -30160,7 +30160,7 @@
         <v>1</v>
       </c>
       <c r="AT52" t="n">
-        <v>3107975680</v>
+        <v>3102966016</v>
       </c>
       <c r="AU52" t="n">
         <v>6.18</v>
@@ -30250,37 +30250,37 @@
         <v>10.59000015258789</v>
       </c>
       <c r="BX52" t="n">
-        <v>8.10122735683394</v>
+        <v>8.101227363412146</v>
       </c>
       <c r="BY52" t="n">
-        <v>11.55102778386532</v>
+        <v>11.55102778571334</v>
       </c>
       <c r="BZ52" t="n">
-        <v>17.45216311682464</v>
+        <v>17.45216310544559</v>
       </c>
       <c r="CA52" t="n">
         <v>24.15149214812595</v>
       </c>
       <c r="CB52" t="n">
-        <v>24.87656899951138</v>
+        <v>24.87656900404358</v>
       </c>
       <c r="CC52" t="n">
-        <v>21.04926982916909</v>
+        <v>21.049269827942</v>
       </c>
       <c r="CD52" t="n">
-        <v>8.678711555874626</v>
+        <v>8.678711549356413</v>
       </c>
       <c r="CE52" t="n">
         <v>10.2336008131</v>
       </c>
       <c r="CF52" t="n">
-        <v>15.76175770041312</v>
+        <v>15.76175769964238</v>
       </c>
       <c r="CG52" t="n">
-        <v>14.50159545034498</v>
+        <v>14.50159544557946</v>
       </c>
       <c r="CH52" t="n">
-        <v>13.05143590531048</v>
+        <v>13.05143590102152</v>
       </c>
       <c r="CI52" t="n">
         <v>8</v>
@@ -30292,10 +30292,10 @@
         <v>3.1</v>
       </c>
       <c r="CL52" t="n">
-        <v>23.24301904869273</v>
+        <v>23.24301900819259</v>
       </c>
       <c r="CM52" t="n">
-        <v>48.83623676399473</v>
+        <v>48.83623675671673</v>
       </c>
       <c r="CN52" t="inlineStr">
         <is>
@@ -30560,10 +30560,10 @@
         <v>54.20000076293945</v>
       </c>
       <c r="BX53" t="n">
-        <v>10.59687587206031</v>
+        <v>10.59687590922912</v>
       </c>
       <c r="BY53" t="n">
-        <v>19.65720474267188</v>
+        <v>19.65720481162001</v>
       </c>
       <c r="BZ53" t="n">
         <v>63.89234965382096</v>
@@ -30572,7 +30572,7 @@
         <v>47.83445546432147</v>
       </c>
       <c r="CB53" t="n">
-        <v>85.5299175847808</v>
+        <v>85.52991763107646</v>
       </c>
       <c r="CC53" t="n">
         <v>11.76833333333333</v>
@@ -30582,7 +30582,7 @@
       </c>
       <c r="CE53" t="inlineStr"/>
       <c r="CF53" t="n">
-        <v>14.00747131602184</v>
+        <v>14.00747135139415</v>
       </c>
       <c r="CG53" t="n">
         <v>11.76833333333333</v>
@@ -30603,7 +30603,7 @@
         <v>-80.45848735994448</v>
       </c>
       <c r="CM53" t="n">
-        <v>-74.15595734529991</v>
+        <v>-74.15595728003734</v>
       </c>
       <c r="CN53" t="inlineStr">
         <is>
@@ -30884,10 +30884,10 @@
         <v>4.639999866485596</v>
       </c>
       <c r="BX54" t="n">
-        <v>1.073494105683135</v>
+        <v>1.073494104123279</v>
       </c>
       <c r="BY54" t="n">
-        <v>1.991331566042215</v>
+        <v>1.991331563148683</v>
       </c>
       <c r="BZ54" t="n">
         <v>10.07868823457937</v>
@@ -30896,13 +30896,13 @@
         <v>9.446029690082037</v>
       </c>
       <c r="CB54" t="n">
-        <v>11.32627913949761</v>
+        <v>11.32627913908849</v>
       </c>
       <c r="CC54" t="n">
-        <v>4.230026071843267</v>
+        <v>4.230026072001199</v>
       </c>
       <c r="CD54" t="n">
-        <v>7.602765636939471</v>
+        <v>7.602765638932593</v>
       </c>
       <c r="CE54" t="n">
         <v>7.2410239750103</v>
@@ -30954,7 +30954,7 @@
         <v>7.906968852776419</v>
       </c>
       <c r="CZ54" t="n">
-        <v>-35.92779681249883</v>
+        <v>-35.92780109506861</v>
       </c>
       <c r="DA54" t="b">
         <v>0</v>
@@ -31196,10 +31196,10 @@
         <v>10.51000022888184</v>
       </c>
       <c r="BX55" t="n">
-        <v>13.08696664000438</v>
+        <v>13.08696646779218</v>
       </c>
       <c r="BY55" t="n">
-        <v>19.05462342784638</v>
+        <v>19.05462317710542</v>
       </c>
       <c r="BZ55" t="n">
         <v>17.18616389628476</v>
@@ -31218,7 +31218,7 @@
         <v>14.72238167572673</v>
       </c>
       <c r="CF55" t="n">
-        <v>16.32432250911085</v>
+        <v>16.32432243861866</v>
       </c>
       <c r="CG55" t="n">
         <v>15.95427278600574</v>
@@ -31239,7 +31239,7 @@
         <v>36.62079157664122</v>
       </c>
       <c r="CM55" t="n">
-        <v>55.32180926362935</v>
+        <v>55.32180859291393</v>
       </c>
       <c r="CN55" t="inlineStr">
         <is>
@@ -31504,10 +31504,10 @@
         <v>29.69000053405762</v>
       </c>
       <c r="BX56" t="n">
-        <v>15.52022459055369</v>
+        <v>15.52022457565406</v>
       </c>
       <c r="BY56" t="n">
-        <v>28.79001661547709</v>
+        <v>28.79001658783828</v>
       </c>
       <c r="BZ56" t="n">
         <v>54.8664584485723</v>
@@ -31516,23 +31516,23 @@
         <v>49.47692096413685</v>
       </c>
       <c r="CB56" t="n">
-        <v>61.18292635854815</v>
+        <v>61.18292636218396</v>
       </c>
       <c r="CC56" t="n">
-        <v>36.6428381914966</v>
+        <v>36.64283819419179</v>
       </c>
       <c r="CD56" t="n">
-        <v>30.47133165906052</v>
+        <v>30.47133167963273</v>
       </c>
       <c r="CE56" t="inlineStr"/>
       <c r="CF56" t="n">
-        <v>33.95488446152492</v>
+        <v>33.95488445156411</v>
       </c>
       <c r="CG56" t="n">
-        <v>32.71642740348685</v>
+        <v>32.71642739101503</v>
       </c>
       <c r="CH56" t="n">
-        <v>29.44478466313816</v>
+        <v>29.44478465191353</v>
       </c>
       <c r="CI56" t="n">
         <v>4</v>
@@ -31544,10 +31544,10 @@
         <v>3.5</v>
       </c>
       <c r="CL56" t="n">
-        <v>-0.8259207359668674</v>
+        <v>-0.8259207737729701</v>
       </c>
       <c r="CM56" t="n">
-        <v>14.36471488969837</v>
+        <v>14.36471485614899</v>
       </c>
       <c r="CN56" t="inlineStr">
         <is>
@@ -31838,37 +31838,37 @@
         <v>23.78000068664551</v>
       </c>
       <c r="BX57" t="n">
-        <v>10.50498166912102</v>
+        <v>10.50498159885169</v>
       </c>
       <c r="BY57" t="n">
-        <v>15.22159728661822</v>
+        <v>15.22159732947241</v>
       </c>
       <c r="BZ57" t="n">
-        <v>19.84847162716806</v>
+        <v>19.84847181581782</v>
       </c>
       <c r="CA57" t="n">
         <v>22.05215577512442</v>
       </c>
       <c r="CB57" t="n">
-        <v>19.44680931018522</v>
+        <v>19.44680939779476</v>
       </c>
       <c r="CC57" t="n">
-        <v>23.36371004800218</v>
+        <v>23.36371006756711</v>
       </c>
       <c r="CD57" t="n">
-        <v>9.891671174955322</v>
+        <v>9.891671279892723</v>
       </c>
       <c r="CE57" t="n">
         <v>19.45038570269356</v>
       </c>
       <c r="CF57" t="n">
-        <v>17.4724728242335</v>
+        <v>17.47247287090181</v>
       </c>
       <c r="CG57" t="n">
-        <v>19.44859750643939</v>
+        <v>19.44859755024416</v>
       </c>
       <c r="CH57" t="n">
-        <v>17.50373775579545</v>
+        <v>17.50373779521974</v>
       </c>
       <c r="CI57" t="n">
         <v>8</v>
@@ -31880,10 +31880,10 @@
         <v>2.4</v>
       </c>
       <c r="CL57" t="n">
-        <v>-26.39303090674304</v>
+        <v>-26.39303074095545</v>
       </c>
       <c r="CM57" t="n">
-        <v>-26.52450664542757</v>
+        <v>-26.52450644917731</v>
       </c>
       <c r="CN57" t="inlineStr">
         <is>
@@ -32170,10 +32170,10 @@
         <v>24.32999992370605</v>
       </c>
       <c r="BX58" t="n">
-        <v>4.265826965173018</v>
+        <v>4.26582696589546</v>
       </c>
       <c r="BY58" t="n">
-        <v>7.913109020395948</v>
+        <v>7.913109021736078</v>
       </c>
       <c r="BZ58" t="n">
         <v>29.33325741484123</v>
@@ -32182,13 +32182,13 @@
         <v>29.21395447941907</v>
       </c>
       <c r="CB58" t="n">
-        <v>26.33700608095968</v>
+        <v>26.33700608057222</v>
       </c>
       <c r="CC58" t="n">
-        <v>2.973172390506528</v>
+        <v>2.97317239049048</v>
       </c>
       <c r="CD58" t="n">
-        <v>19.05301343519475</v>
+        <v>19.05301343437272</v>
       </c>
       <c r="CE58" t="n">
         <v>18.00727121747286</v>
@@ -32388,7 +32388,7 @@
         <v>1</v>
       </c>
       <c r="AR59" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="AS59" t="b">
         <v>1</v>
@@ -32484,10 +32484,10 @@
         <v>49.58000183105469</v>
       </c>
       <c r="BX59" t="n">
-        <v>8.252002669311878</v>
+        <v>8.252002693460369</v>
       </c>
       <c r="BY59" t="n">
-        <v>15.30746495157353</v>
+        <v>15.30746499636898</v>
       </c>
       <c r="BZ59" t="n">
         <v>19.94943893900621</v>
@@ -32496,25 +32496,25 @@
         <v>12.40196818721602</v>
       </c>
       <c r="CB59" t="n">
-        <v>15.12548823428899</v>
+        <v>15.12548813244862</v>
       </c>
       <c r="CC59" t="n">
-        <v>20.74522890426658</v>
+        <v>20.74522888992635</v>
       </c>
       <c r="CD59" t="n">
-        <v>11.32438901155573</v>
+        <v>11.3243889410885</v>
       </c>
       <c r="CE59" t="n">
         <v>12.98629942513824</v>
       </c>
       <c r="CF59" t="n">
-        <v>14.51153504029465</v>
+        <v>14.51153502558166</v>
       </c>
       <c r="CG59" t="n">
-        <v>14.05589382971361</v>
+        <v>14.05589377879343</v>
       </c>
       <c r="CH59" t="n">
-        <v>12.65030444674225</v>
+        <v>12.65030440091409</v>
       </c>
       <c r="CI59" t="n">
         <v>8</v>
@@ -32526,10 +32526,10 @@
         <v>2.5</v>
       </c>
       <c r="CL59" t="n">
-        <v>-74.48506660034315</v>
+        <v>-74.4850666927759</v>
       </c>
       <c r="CM59" t="n">
-        <v>-70.73107199603758</v>
+        <v>-70.73107202571282</v>
       </c>
       <c r="CN59" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>0.6291888987432825</v>
       </c>
       <c r="CZ59" t="n">
-        <v>-8.667873268803072</v>
+        <v>-8.667879823856294</v>
       </c>
       <c r="DA59" t="b">
         <v>0</v>
@@ -32734,7 +32734,7 @@
         <v>1</v>
       </c>
       <c r="AT60" t="n">
-        <v>35826143232</v>
+        <v>35772293120</v>
       </c>
       <c r="AU60" t="n">
         <v>11.21</v>
@@ -32824,10 +32824,10 @@
         <v>33.61999893188477</v>
       </c>
       <c r="BX60" t="n">
-        <v>11.88440177175877</v>
+        <v>11.88440177792765</v>
       </c>
       <c r="BY60" t="n">
-        <v>22.04556528661253</v>
+        <v>22.04556529805579</v>
       </c>
       <c r="BZ60" t="n">
         <v>39.73817893376209</v>
@@ -32836,25 +32836,25 @@
         <v>32.40852551699374</v>
       </c>
       <c r="CB60" t="n">
-        <v>40.54661342880363</v>
+        <v>40.54661341988273</v>
       </c>
       <c r="CC60" t="n">
-        <v>23.7801007002803</v>
+        <v>23.78010069906615</v>
       </c>
       <c r="CD60" t="n">
-        <v>24.16893069514738</v>
+        <v>24.16893068469731</v>
       </c>
       <c r="CE60" t="n">
         <v>25.56648631344748</v>
       </c>
       <c r="CF60" t="n">
-        <v>27.51735033085074</v>
+        <v>27.51735033047912</v>
       </c>
       <c r="CG60" t="n">
-        <v>24.86770850429743</v>
+        <v>24.86770849907239</v>
       </c>
       <c r="CH60" t="n">
-        <v>22.38093765386768</v>
+        <v>22.38093764916515</v>
       </c>
       <c r="CI60" t="n">
         <v>8</v>
@@ -32866,10 +32866,10 @@
         <v>3.4</v>
       </c>
       <c r="CL60" t="n">
-        <v>-33.42968957490985</v>
+        <v>-33.42968958889714</v>
       </c>
       <c r="CM60" t="n">
-        <v>-18.15184055596847</v>
+        <v>-18.15184055707383</v>
       </c>
       <c r="CN60" t="inlineStr">
         <is>
@@ -33148,10 +33148,10 @@
         <v>4.519999980926514</v>
       </c>
       <c r="BX61" t="n">
-        <v>2.935043323348943</v>
+        <v>2.935043315088623</v>
       </c>
       <c r="BY61" t="n">
-        <v>5.444505364812288</v>
+        <v>5.444505349489396</v>
       </c>
       <c r="BZ61" t="n">
         <v>13.76781603385662</v>
@@ -33160,13 +33160,13 @@
         <v>15.32423511716514</v>
       </c>
       <c r="CB61" t="n">
-        <v>15.90374917336029</v>
+        <v>15.9037491586636</v>
       </c>
       <c r="CC61" t="n">
-        <v>9.471435210919275</v>
+        <v>9.471435211939511</v>
       </c>
       <c r="CD61" t="n">
-        <v>6.834912647065576</v>
+        <v>6.834912654538192</v>
       </c>
       <c r="CE61" t="n">
         <v>1.44645468896914</v>
@@ -33462,37 +33462,37 @@
         <v>30</v>
       </c>
       <c r="BX62" t="n">
-        <v>13.81421958653848</v>
+        <v>13.81421959349261</v>
       </c>
       <c r="BY62" t="n">
-        <v>14.67667817948069</v>
+        <v>14.67667818099556</v>
       </c>
       <c r="BZ62" t="n">
-        <v>15.82099675219668</v>
+        <v>15.82099674586532</v>
       </c>
       <c r="CA62" t="n">
         <v>31.15287379381833</v>
       </c>
       <c r="CB62" t="n">
-        <v>14.95526755261865</v>
+        <v>14.95526754959985</v>
       </c>
       <c r="CC62" t="n">
-        <v>30.52562436838162</v>
+        <v>30.52562436695931</v>
       </c>
       <c r="CD62" t="n">
-        <v>6.521908009836516</v>
+        <v>6.52190800368628</v>
       </c>
       <c r="CE62" t="n">
         <v>38.80831925964276</v>
       </c>
       <c r="CF62" t="n">
-        <v>18.20965260612443</v>
+        <v>18.20965260491675</v>
       </c>
       <c r="CG62" t="n">
-        <v>14.95526755261865</v>
+        <v>14.95526754959985</v>
       </c>
       <c r="CH62" t="n">
-        <v>13.45974079735679</v>
+        <v>13.45974079463987</v>
       </c>
       <c r="CI62" t="n">
         <v>7</v>
@@ -33504,10 +33504,10 @@
         <v>6</v>
       </c>
       <c r="CL62" t="n">
-        <v>-55.13419734214404</v>
+        <v>-55.13419735120044</v>
       </c>
       <c r="CM62" t="n">
-        <v>-39.30115797958524</v>
+        <v>-39.30115798361084</v>
       </c>
       <c r="CN62" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>-5.213268999738752</v>
       </c>
       <c r="CZ62" t="n">
-        <v>-27.23200907385727</v>
+        <v>-27.23200229546583</v>
       </c>
       <c r="DA62" t="b">
         <v>0</v>
@@ -33786,35 +33786,35 @@
         <v>3.509999990463257</v>
       </c>
       <c r="BX63" t="n">
-        <v>2.694277163240034</v>
+        <v>2.6942771766252</v>
       </c>
       <c r="BY63" t="n">
-        <v>3.221309599898904</v>
+        <v>3.22130960459272</v>
       </c>
       <c r="BZ63" t="n">
-        <v>4.095040444047315</v>
+        <v>4.095040429670101</v>
       </c>
       <c r="CA63" t="n">
         <v>7.355188608855169</v>
       </c>
       <c r="CB63" t="n">
-        <v>6.136182372570351</v>
+        <v>6.136182380161993</v>
       </c>
       <c r="CC63" t="n">
-        <v>8.50420167857096</v>
+        <v>8.504201675441294</v>
       </c>
       <c r="CD63" t="n">
-        <v>1.898979087076945</v>
+        <v>1.898979075757378</v>
       </c>
       <c r="CE63" t="inlineStr"/>
       <c r="CF63" t="n">
-        <v>4.843596993465668</v>
+        <v>4.843596993014837</v>
       </c>
       <c r="CG63" t="n">
-        <v>4.095040444047315</v>
+        <v>4.095040429670101</v>
       </c>
       <c r="CH63" t="n">
-        <v>3.685536399642584</v>
+        <v>3.685536386703091</v>
       </c>
       <c r="CI63" t="n">
         <v>7</v>
@@ -33826,10 +33826,10 @@
         <v>4.5</v>
       </c>
       <c r="CL63" t="n">
-        <v>5.001037312144252</v>
+        <v>5.001036943497739</v>
       </c>
       <c r="CM63" t="n">
-        <v>37.99421671298637</v>
+        <v>37.9942167001422</v>
       </c>
       <c r="CN63" t="inlineStr">
         <is>
@@ -34108,37 +34108,37 @@
         <v>18.63999938964844</v>
       </c>
       <c r="BX64" t="n">
-        <v>8.745140387725304</v>
+        <v>8.745140400157554</v>
       </c>
       <c r="BY64" t="n">
-        <v>9.253022841538003</v>
+        <v>9.2530228409156</v>
       </c>
       <c r="BZ64" t="n">
-        <v>9.762664742861054</v>
+        <v>9.762664728325589</v>
       </c>
       <c r="CA64" t="n">
         <v>16.97559723955254</v>
       </c>
       <c r="CB64" t="n">
-        <v>9.361180425981244</v>
+        <v>9.36118041541633</v>
       </c>
       <c r="CC64" t="n">
-        <v>17.55266733740303</v>
+        <v>17.55266733434918</v>
       </c>
       <c r="CD64" t="n">
-        <v>4.00185534411393</v>
+        <v>4.001855329891438</v>
       </c>
       <c r="CE64" t="n">
         <v>16.08382941914014</v>
       </c>
       <c r="CF64" t="n">
-        <v>11.46699471728941</v>
+        <v>11.46699471346854</v>
       </c>
       <c r="CG64" t="n">
-        <v>9.561922584421149</v>
+        <v>9.561922571870959</v>
       </c>
       <c r="CH64" t="n">
-        <v>8.605730325979033</v>
+        <v>8.605730314683862</v>
       </c>
       <c r="CI64" t="n">
         <v>8</v>
@@ -34150,10 +34150,10 @@
         <v>4.4</v>
       </c>
       <c r="CL64" t="n">
-        <v>-53.83191734030768</v>
+        <v>-53.8319174009041</v>
       </c>
       <c r="CM64" t="n">
-        <v>-38.48178598301079</v>
+        <v>-38.48178600350899</v>
       </c>
       <c r="CN64" t="inlineStr">
         <is>
@@ -34442,25 +34442,25 @@
         <v>2.170000076293945</v>
       </c>
       <c r="BX65" t="n">
-        <v>0.622812515465324</v>
+        <v>0.6228125131894856</v>
       </c>
       <c r="BY65" t="n">
-        <v>0.8890945898941852</v>
+        <v>0.8890945870978471</v>
       </c>
       <c r="BZ65" t="n">
-        <v>3.517804534803933</v>
+        <v>3.517804536594418</v>
       </c>
       <c r="CA65" t="n">
         <v>7.255221841107573</v>
       </c>
       <c r="CB65" t="n">
-        <v>2.703577542712195</v>
+        <v>2.703577539274871</v>
       </c>
       <c r="CC65" t="n">
-        <v>2.232512847962681</v>
+        <v>2.232512848064165</v>
       </c>
       <c r="CD65" t="n">
-        <v>1.749669828438236</v>
+        <v>1.749669829461635</v>
       </c>
       <c r="CE65" t="n">
         <v>4.906142470300746</v>
@@ -34756,10 +34756,10 @@
         <v>36.06999969482422</v>
       </c>
       <c r="BX66" t="n">
-        <v>10.32734671003141</v>
+        <v>10.32734669462519</v>
       </c>
       <c r="BY66" t="n">
-        <v>19.15722814710826</v>
+        <v>19.15722811852973</v>
       </c>
       <c r="BZ66" t="n">
         <v>29.79597855089906</v>
@@ -34768,25 +34768,25 @@
         <v>22.11977982655244</v>
       </c>
       <c r="CB66" t="n">
-        <v>27.68991887432972</v>
+        <v>27.6899189110517</v>
       </c>
       <c r="CC66" t="n">
-        <v>22.95497933902359</v>
+        <v>22.95497934375206</v>
       </c>
       <c r="CD66" t="n">
-        <v>17.74659913991782</v>
+        <v>17.74659917145249</v>
       </c>
       <c r="CE66" t="n">
         <v>27.14442054393252</v>
       </c>
       <c r="CF66" t="n">
-        <v>22.11703139147435</v>
+        <v>22.1170313950994</v>
       </c>
       <c r="CG66" t="n">
-        <v>22.53737958278801</v>
+        <v>22.53737958515225</v>
       </c>
       <c r="CH66" t="n">
-        <v>20.28364162450921</v>
+        <v>20.28364162663702</v>
       </c>
       <c r="CI66" t="n">
         <v>8</v>
@@ -34798,10 +34798,10 @@
         <v>2.9</v>
       </c>
       <c r="CL66" t="n">
-        <v>-43.76589466004413</v>
+        <v>-43.76589465414501</v>
       </c>
       <c r="CM66" t="n">
-        <v>-38.68302861491849</v>
+        <v>-38.68302860486845</v>
       </c>
       <c r="CN66" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>4.42964313474894</v>
       </c>
       <c r="CZ66" t="n">
-        <v>-19.75885395890232</v>
+        <v>-19.75884710571682</v>
       </c>
       <c r="DA66" t="b">
         <v>0</v>
@@ -35084,10 +35084,10 @@
         <v>8.960000038146973</v>
       </c>
       <c r="BX67" t="n">
-        <v>0.5329077798067285</v>
+        <v>0.5329077770726239</v>
       </c>
       <c r="BY67" t="n">
-        <v>0.9885439315414815</v>
+        <v>0.9885439264697174</v>
       </c>
       <c r="BZ67" t="n">
         <v>10.18181822516701</v>
@@ -35096,13 +35096,13 @@
         <v>9.355421567964147</v>
       </c>
       <c r="CB67" t="n">
-        <v>11.19304002423784</v>
+        <v>11.19304002677704</v>
       </c>
       <c r="CC67" t="n">
-        <v>0.735928783247727</v>
+        <v>0.7359287832967513</v>
       </c>
       <c r="CD67" t="n">
-        <v>8.686260804713942</v>
+        <v>8.686260808373488</v>
       </c>
       <c r="CE67" t="inlineStr"/>
       <c r="CF67" t="inlineStr"/>
@@ -35400,10 +35400,10 @@
         <v>8.510000228881836</v>
       </c>
       <c r="BX68" t="n">
-        <v>1.637947945064283</v>
+        <v>1.637947946062169</v>
       </c>
       <c r="BY68" t="n">
-        <v>3.038393438094245</v>
+        <v>3.038393439945323</v>
       </c>
       <c r="BZ68" t="n">
         <v>25.00166364361071</v>
@@ -35412,13 +35412,13 @@
         <v>24.7460880607331</v>
       </c>
       <c r="CB68" t="n">
-        <v>26.74944032736873</v>
+        <v>26.74944032864045</v>
       </c>
       <c r="CC68" t="n">
-        <v>6.710964368424377</v>
+        <v>6.710964368366126</v>
       </c>
       <c r="CD68" t="n">
-        <v>18.65870461578827</v>
+        <v>18.65870461464053</v>
       </c>
       <c r="CE68" t="n">
         <v>14.23395771137433</v>
@@ -35714,10 +35714,10 @@
         <v>21.79999923706055</v>
       </c>
       <c r="BX69" t="n">
-        <v>6.02855433274051</v>
+        <v>6.028554364643994</v>
       </c>
       <c r="BY69" t="n">
-        <v>11.18296828723365</v>
+        <v>11.18296834641461</v>
       </c>
       <c r="BZ69" t="n">
         <v>33.43171179294585</v>
@@ -35726,25 +35726,25 @@
         <v>34.49643348400799</v>
       </c>
       <c r="CB69" t="n">
-        <v>30.08621130140236</v>
+        <v>30.08621129905332</v>
       </c>
       <c r="CC69" t="n">
-        <v>25.30591858566851</v>
+        <v>25.30591858065207</v>
       </c>
       <c r="CD69" t="n">
-        <v>19.51154840724751</v>
+        <v>19.51154837327667</v>
       </c>
       <c r="CE69" t="n">
         <v>13.40148489337126</v>
       </c>
       <c r="CF69" t="n">
-        <v>23.91661096455388</v>
+        <v>23.91661096710311</v>
       </c>
       <c r="CG69" t="n">
-        <v>25.30591858566851</v>
+        <v>25.30591858065207</v>
       </c>
       <c r="CH69" t="n">
-        <v>22.77532672710166</v>
+        <v>22.77532672258686</v>
       </c>
       <c r="CI69" t="n">
         <v>7</v>
@@ -35756,10 +35756,10 @@
         <v>5.7</v>
       </c>
       <c r="CL69" t="n">
-        <v>4.473979468692035</v>
+        <v>4.473979447981957</v>
       </c>
       <c r="CM69" t="n">
-        <v>9.709228447563589</v>
+        <v>9.709228459257325</v>
       </c>
       <c r="CN69" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>1</v>
       </c>
       <c r="AR70" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AS70" t="b">
         <v>1</v>
@@ -36038,10 +36038,10 @@
         <v>24.69000053405762</v>
       </c>
       <c r="BX70" t="n">
-        <v>4.528795228837069</v>
+        <v>4.528795225188754</v>
       </c>
       <c r="BY70" t="n">
-        <v>8.400915149492763</v>
+        <v>8.40091514272514</v>
       </c>
       <c r="BZ70" t="n">
         <v>31.27557429027375</v>
@@ -36050,13 +36050,13 @@
         <v>26.55156008995373</v>
       </c>
       <c r="CB70" t="n">
-        <v>36.7912157801725</v>
+        <v>36.79121578438107</v>
       </c>
       <c r="CC70" t="n">
-        <v>11.806877001469</v>
+        <v>11.80687700187138</v>
       </c>
       <c r="CD70" t="n">
-        <v>25.62152607152654</v>
+        <v>25.62152607724126</v>
       </c>
       <c r="CE70" t="n">
         <v>25.17925941757476</v>
@@ -36352,25 +36352,25 @@
         <v>17.30999946594238</v>
       </c>
       <c r="BX71" t="n">
-        <v>4.028450005233362</v>
+        <v>4.028449951312262</v>
       </c>
       <c r="BY71" t="n">
-        <v>6.922307444990164</v>
+        <v>6.922307378449564</v>
       </c>
       <c r="BZ71" t="n">
-        <v>23.65950138994574</v>
+        <v>23.65950147920323</v>
       </c>
       <c r="CA71" t="n">
         <v>32.98569202610356</v>
       </c>
       <c r="CB71" t="n">
-        <v>16.71223338378553</v>
+        <v>16.71223335747095</v>
       </c>
       <c r="CC71" t="n">
-        <v>20.30046208217011</v>
+        <v>20.30046208793969</v>
       </c>
       <c r="CD71" t="n">
-        <v>11.70662162187211</v>
+        <v>11.7066216581718</v>
       </c>
       <c r="CE71" t="n">
         <v>21.93193610654263</v>
@@ -36422,7 +36422,7 @@
         <v>-1.364797304640797</v>
       </c>
       <c r="CZ71" t="n">
-        <v>-40.04429185860444</v>
+        <v>-40.04428381701424</v>
       </c>
       <c r="DA71" t="b">
         <v>0</v>
@@ -36666,35 +36666,35 @@
         <v>23.89999961853027</v>
       </c>
       <c r="BX72" t="n">
-        <v>22.96133597378055</v>
+        <v>22.96133604319394</v>
       </c>
       <c r="BY72" t="n">
-        <v>29.32452634739392</v>
+        <v>29.3245263671106</v>
       </c>
       <c r="BZ72" t="n">
-        <v>39.49704760209692</v>
+        <v>39.49704750925143</v>
       </c>
       <c r="CA72" t="n">
         <v>62.81937459029582</v>
       </c>
       <c r="CB72" t="n">
-        <v>70.08903030706335</v>
+        <v>70.08903037981081</v>
       </c>
       <c r="CC72" t="n">
-        <v>41.76900677460803</v>
+        <v>41.76900676490808</v>
       </c>
       <c r="CD72" t="n">
-        <v>19.01744474584859</v>
+        <v>19.01744468091652</v>
       </c>
       <c r="CE72" t="inlineStr"/>
       <c r="CF72" t="n">
-        <v>40.78253804872674</v>
+        <v>40.78253804792674</v>
       </c>
       <c r="CG72" t="n">
-        <v>39.49704760209692</v>
+        <v>39.49704750925143</v>
       </c>
       <c r="CH72" t="n">
-        <v>35.54734284188723</v>
+        <v>35.54734275832629</v>
       </c>
       <c r="CI72" t="n">
         <v>7</v>
@@ -36706,10 +36706,10 @@
         <v>3.7</v>
       </c>
       <c r="CL72" t="n">
-        <v>48.7336544320548</v>
+        <v>48.7336540824274</v>
       </c>
       <c r="CM72" t="n">
-        <v>70.63823723707097</v>
+        <v>70.63823723372364</v>
       </c>
       <c r="CN72" t="inlineStr">
         <is>
@@ -36992,10 +36992,10 @@
         <v>4.050000190734863</v>
       </c>
       <c r="BX73" t="n">
-        <v>0.9834174977154738</v>
+        <v>0.9834174963118183</v>
       </c>
       <c r="BY73" t="n">
-        <v>1.824239458262204</v>
+        <v>1.824239455658423</v>
       </c>
       <c r="BZ73" t="n">
         <v>6.261668906328697</v>
@@ -37004,7 +37004,7 @@
         <v>4.158686841231277</v>
       </c>
       <c r="CB73" t="n">
-        <v>8.695198113073463</v>
+        <v>8.695198110780444</v>
       </c>
       <c r="CC73" t="n">
         <v>3.760485277130923</v>
@@ -37062,7 +37062,7 @@
         <v>1.50376393620828</v>
       </c>
       <c r="CZ73" t="n">
-        <v>-44.63291810308804</v>
+        <v>-44.6329217901767</v>
       </c>
       <c r="DA73" t="b">
         <v>0</v>
@@ -37306,10 +37306,10 @@
         <v>12.53999996185303</v>
       </c>
       <c r="BX74" t="n">
-        <v>2.073799232553127</v>
+        <v>2.073799234861448</v>
       </c>
       <c r="BY74" t="n">
-        <v>3.846897576386051</v>
+        <v>3.846897580667985</v>
       </c>
       <c r="BZ74" t="n">
         <v>16.58233527889746</v>
@@ -37318,7 +37318,7 @@
         <v>13.15648423765553</v>
       </c>
       <c r="CB74" t="n">
-        <v>21.66997891053285</v>
+        <v>21.66997891375805</v>
       </c>
       <c r="CC74" t="n">
         <v>9.294207014285712</v>
@@ -37622,10 +37622,10 @@
         <v>55.5</v>
       </c>
       <c r="BX75" t="n">
-        <v>40.36268297638262</v>
+        <v>40.36268323818693</v>
       </c>
       <c r="BY75" t="n">
-        <v>58.76806641361311</v>
+        <v>58.76806679480018</v>
       </c>
       <c r="BZ75" t="n">
         <v>35.98503740648379</v>
@@ -37644,13 +37644,13 @@
         <v>47.31284142717968</v>
       </c>
       <c r="CF75" t="n">
-        <v>43.20016078953474</v>
+        <v>43.20016089669997</v>
       </c>
       <c r="CG75" t="n">
-        <v>41.66677574023846</v>
+        <v>41.66677587114062</v>
       </c>
       <c r="CH75" t="n">
-        <v>37.50009816621462</v>
+        <v>37.50009828402656</v>
       </c>
       <c r="CI75" t="n">
         <v>6</v>
@@ -37662,10 +37662,10 @@
         <v>6.4</v>
       </c>
       <c r="CL75" t="n">
-        <v>-32.43225555637005</v>
+        <v>-32.4322553440963</v>
       </c>
       <c r="CM75" t="n">
-        <v>-22.16187245128875</v>
+        <v>-22.16187225819826</v>
       </c>
       <c r="CN75" t="inlineStr">
         <is>
@@ -37928,35 +37928,35 @@
         <v>12.85999965667725</v>
       </c>
       <c r="BX76" t="n">
-        <v>10.87454811780624</v>
+        <v>10.87454815877388</v>
       </c>
       <c r="BY76" t="n">
-        <v>11.49697212591648</v>
+        <v>11.49697209920886</v>
       </c>
       <c r="BZ76" t="n">
-        <v>11.9013169621982</v>
+        <v>11.9013168897155</v>
       </c>
       <c r="CA76" t="n">
         <v>16.82961568340781</v>
       </c>
       <c r="CB76" t="n">
-        <v>19.712122134942</v>
+        <v>19.71212209224086</v>
       </c>
       <c r="CC76" t="n">
-        <v>7.382415591092738</v>
+        <v>7.382415585835159</v>
       </c>
       <c r="CD76" t="n">
-        <v>4.87314185322055</v>
+        <v>4.873141782199048</v>
       </c>
       <c r="CE76" t="inlineStr"/>
       <c r="CF76" t="n">
-        <v>10.41381319925341</v>
+        <v>10.41381318338335</v>
       </c>
       <c r="CG76" t="n">
-        <v>11.18576012186136</v>
+        <v>11.18576012899137</v>
       </c>
       <c r="CH76" t="n">
-        <v>10.06718410967522</v>
+        <v>10.06718411609223</v>
       </c>
       <c r="CI76" t="n">
         <v>4</v>
@@ -37968,10 +37968,10 @@
         <v>1.6</v>
       </c>
       <c r="CL76" t="n">
-        <v>-21.71707326253247</v>
+        <v>-21.7170732126335</v>
       </c>
       <c r="CM76" t="n">
-        <v>-19.02166813942105</v>
+        <v>-19.02166826282748</v>
       </c>
       <c r="CN76" t="inlineStr">
         <is>
@@ -38250,10 +38250,10 @@
         <v>28.85000038146973</v>
       </c>
       <c r="BX77" t="n">
-        <v>13.47679402060411</v>
+        <v>13.47679398972994</v>
       </c>
       <c r="BY77" t="n">
-        <v>24.99945290822062</v>
+        <v>24.99945285094905</v>
       </c>
       <c r="BZ77" t="n">
         <v>38.1119147611639</v>
@@ -38262,25 +38262,25 @@
         <v>26.54383559620355</v>
       </c>
       <c r="CB77" t="n">
-        <v>44.90735153042809</v>
+        <v>44.90735160131479</v>
       </c>
       <c r="CC77" t="n">
-        <v>42.35229041298373</v>
+        <v>42.35229042837058</v>
       </c>
       <c r="CD77" t="n">
-        <v>24.08739115802768</v>
+        <v>24.08739122967303</v>
       </c>
       <c r="CE77" t="n">
         <v>24.8974245271389</v>
       </c>
       <c r="CF77" t="n">
-        <v>29.92205686434632</v>
+        <v>29.92205687306797</v>
       </c>
       <c r="CG77" t="n">
-        <v>25.77164425221208</v>
+        <v>25.7716442235763</v>
       </c>
       <c r="CH77" t="n">
-        <v>23.19447982699088</v>
+        <v>23.19447980121867</v>
       </c>
       <c r="CI77" t="n">
         <v>8</v>
@@ -38292,10 +38292,10 @@
         <v>3.3</v>
       </c>
       <c r="CL77" t="n">
-        <v>-19.60319057087908</v>
+        <v>-19.6031906602108</v>
       </c>
       <c r="CM77" t="n">
-        <v>3.715966962569528</v>
+        <v>3.715966992800523</v>
       </c>
       <c r="CN77" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>-2.337816543811788</v>
       </c>
       <c r="CZ77" t="n">
-        <v>-24.19493061245316</v>
+        <v>-24.19493858539801</v>
       </c>
       <c r="DA77" t="b">
         <v>0</v>
@@ -38582,10 +38582,10 @@
         <v>15.11999988555908</v>
       </c>
       <c r="BX78" t="n">
-        <v>2.439882942534382</v>
+        <v>2.439882946599169</v>
       </c>
       <c r="BY78" t="n">
-        <v>4.525982858401279</v>
+        <v>4.525982865941458</v>
       </c>
       <c r="BZ78" t="n">
         <v>26.57029157608194</v>
@@ -38594,7 +38594,7 @@
         <v>20.33365271794082</v>
       </c>
       <c r="CB78" t="n">
-        <v>34.60986199984981</v>
+        <v>34.60986200739716</v>
       </c>
       <c r="CC78" t="n">
         <v>10.38593205872702</v>
@@ -38900,10 +38900,10 @@
         <v>14.64999961853027</v>
       </c>
       <c r="BX79" t="n">
-        <v>9.578902435186352</v>
+        <v>9.578902401522585</v>
       </c>
       <c r="BY79" t="n">
-        <v>17.76886401727068</v>
+        <v>17.76886395482439</v>
       </c>
       <c r="BZ79" t="n">
         <v>14.2102851351044</v>
@@ -38924,7 +38924,7 @@
         <v>12.06136669897467</v>
       </c>
       <c r="CF79" t="n">
-        <v>15.18293138133337</v>
+        <v>15.18293136931961</v>
       </c>
       <c r="CG79" t="n">
         <v>13.55468557413323</v>
@@ -38945,7 +38945,7 @@
         <v>-16.72889191553597</v>
       </c>
       <c r="CM79" t="n">
-        <v>3.637759567781917</v>
+        <v>3.637759485776737</v>
       </c>
       <c r="CN79" t="inlineStr">
         <is>
@@ -39224,25 +39224,25 @@
         <v>26.55999946594238</v>
       </c>
       <c r="BX80" t="n">
-        <v>12.09583914872502</v>
+        <v>12.0958391973713</v>
       </c>
       <c r="BY80" t="n">
-        <v>12.89484429492584</v>
+        <v>12.89484431795317</v>
       </c>
       <c r="BZ80" t="n">
-        <v>14.41525916426998</v>
+        <v>14.41525913203805</v>
       </c>
       <c r="CA80" t="n">
         <v>33.30354002524292</v>
       </c>
       <c r="CB80" t="n">
-        <v>13.52156654661238</v>
+        <v>13.52156654564246</v>
       </c>
       <c r="CC80" t="n">
-        <v>24.69737288369514</v>
+        <v>24.69737287728489</v>
       </c>
       <c r="CD80" t="n">
-        <v>5.969673602557141</v>
+        <v>5.969673571435193</v>
       </c>
       <c r="CE80" t="n">
         <v>64.9533816160684</v>
@@ -39538,35 +39538,35 @@
         <v>2.740000009536743</v>
       </c>
       <c r="BX81" t="n">
-        <v>1.259649645948559</v>
+        <v>1.25964964149074</v>
       </c>
       <c r="BY81" t="n">
-        <v>1.768404346565216</v>
+        <v>1.768404342102879</v>
       </c>
       <c r="BZ81" t="n">
-        <v>4.169355423186575</v>
+        <v>4.169355427420831</v>
       </c>
       <c r="CA81" t="n">
         <v>7.812220106719857</v>
       </c>
       <c r="CB81" t="n">
-        <v>4.19881692397783</v>
+        <v>4.198816918476743</v>
       </c>
       <c r="CC81" t="n">
-        <v>1.343758969916935</v>
+        <v>1.343758970040684</v>
       </c>
       <c r="CD81" t="n">
-        <v>2.067905430643118</v>
+        <v>2.06790543313807</v>
       </c>
       <c r="CE81" t="inlineStr"/>
       <c r="CF81" t="n">
-        <v>2.467981790039705</v>
+        <v>2.467981788778324</v>
       </c>
       <c r="CG81" t="n">
-        <v>1.918154888604167</v>
+        <v>1.918154887620474</v>
       </c>
       <c r="CH81" t="n">
-        <v>1.72633939974375</v>
+        <v>1.726339398858427</v>
       </c>
       <c r="CI81" t="n">
         <v>6</v>
@@ -39578,10 +39578,10 @@
         <v>6.2</v>
       </c>
       <c r="CL81" t="n">
-        <v>-36.99491263740449</v>
+        <v>-36.99491266971556</v>
       </c>
       <c r="CM81" t="n">
-        <v>-9.927672209863559</v>
+        <v>-9.927672255899346</v>
       </c>
       <c r="CN81" t="inlineStr">
         <is>
@@ -39860,10 +39860,10 @@
         <v>6.949999809265137</v>
       </c>
       <c r="BX82" t="n">
-        <v>1.25174440850934</v>
+        <v>1.251744408426012</v>
       </c>
       <c r="BY82" t="n">
-        <v>2.321985877784825</v>
+        <v>2.321985877630251</v>
       </c>
       <c r="BZ82" t="n">
         <v>10.83382323208977</v>
@@ -39872,13 +39872,13 @@
         <v>10.63720103437324</v>
       </c>
       <c r="CB82" t="n">
-        <v>10.59280611171964</v>
+        <v>10.59280611173732</v>
       </c>
       <c r="CC82" t="n">
-        <v>1.875514633777939</v>
+        <v>1.875514633781157</v>
       </c>
       <c r="CD82" t="n">
-        <v>7.546697301636931</v>
+        <v>7.546697301734312</v>
       </c>
       <c r="CE82" t="n">
         <v>10.17050614593439</v>
@@ -40174,10 +40174,10 @@
         <v>9.840000152587891</v>
       </c>
       <c r="BX83" t="n">
-        <v>6.031752912341034</v>
+        <v>6.031752830819144</v>
       </c>
       <c r="BY83" t="n">
-        <v>11.18890165239262</v>
+        <v>11.18890150116951</v>
       </c>
       <c r="BZ83" t="n">
         <v>8.033271843609951</v>
@@ -40198,7 +40198,7 @@
         <v>40.23059672158782</v>
       </c>
       <c r="CF83" t="n">
-        <v>10.14916138681703</v>
+        <v>10.14916135356774</v>
       </c>
       <c r="CG83" t="n">
         <v>8.033271843609951</v>
@@ -40219,7 +40219,7 @@
         <v>-26.52495378927914</v>
       </c>
       <c r="CM83" t="n">
-        <v>3.141882412957342</v>
+        <v>3.1418820750581</v>
       </c>
       <c r="CN83" t="inlineStr">
         <is>
@@ -40500,10 +40500,10 @@
         <v>5.159999847412109</v>
       </c>
       <c r="BX84" t="n">
-        <v>3.05139588659716</v>
+        <v>3.051395880817301</v>
       </c>
       <c r="BY84" t="n">
-        <v>4.442832410885465</v>
+        <v>4.442832402469991</v>
       </c>
       <c r="BZ84" t="n">
         <v>4.377161371377319</v>
@@ -40788,10 +40788,10 @@
         <v>52.93999862670898</v>
       </c>
       <c r="BX85" t="n">
-        <v>11.11616390667582</v>
+        <v>11.11616389693267</v>
       </c>
       <c r="BY85" t="n">
-        <v>16.18513464811999</v>
+        <v>16.18513463393396</v>
       </c>
       <c r="BZ85" t="inlineStr"/>
       <c r="CA85" t="inlineStr"/>
@@ -40802,13 +40802,13 @@
       <c r="CD85" t="inlineStr"/>
       <c r="CE85" t="inlineStr"/>
       <c r="CF85" t="n">
-        <v>17.8763328515986</v>
+        <v>17.87633284362221</v>
       </c>
       <c r="CG85" t="n">
-        <v>16.18513464811999</v>
+        <v>16.18513463393396</v>
       </c>
       <c r="CH85" t="n">
-        <v>14.566621183308</v>
+        <v>14.56662117054057</v>
       </c>
       <c r="CI85" t="n">
         <v>3</v>
@@ -40820,10 +40820,10 @@
         <v>2.4</v>
       </c>
       <c r="CL85" t="n">
-        <v>-72.48465893242594</v>
+        <v>-72.48465895654275</v>
       </c>
       <c r="CM85" t="n">
-        <v>-66.23284224533444</v>
+        <v>-66.2328422604013</v>
       </c>
       <c r="CN85" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>-2.665932669996351</v>
       </c>
       <c r="CZ85" t="n">
-        <v>-18.20648739516069</v>
+        <v>-18.20649245743299</v>
       </c>
       <c r="DA85" t="b">
         <v>0</v>
@@ -41114,10 +41114,10 @@
         <v>22.45000076293945</v>
       </c>
       <c r="BX86" t="n">
-        <v>11.3140513013114</v>
+        <v>11.31405125502387</v>
       </c>
       <c r="BY86" t="n">
-        <v>20.98756516393264</v>
+        <v>20.98756507806927</v>
       </c>
       <c r="BZ86" t="n">
         <v>15.19216088401163</v>
@@ -41138,13 +41138,13 @@
         <v>23.03202693646428</v>
       </c>
       <c r="CF86" t="n">
-        <v>19.65754611165039</v>
+        <v>19.65754609513153</v>
       </c>
       <c r="CG86" t="n">
-        <v>18.08986302397214</v>
+        <v>18.08986298104045</v>
       </c>
       <c r="CH86" t="n">
-        <v>16.28087672157492</v>
+        <v>16.28087668293641</v>
       </c>
       <c r="CI86" t="n">
         <v>8</v>
@@ -41156,10 +41156,10 @@
         <v>3</v>
       </c>
       <c r="CL86" t="n">
-        <v>-27.47939345974786</v>
+        <v>-27.47939363185708</v>
       </c>
       <c r="CM86" t="n">
-        <v>-12.438550362541</v>
+        <v>-12.43855043612168</v>
       </c>
       <c r="CN86" t="inlineStr">
         <is>
@@ -41754,10 +41754,10 @@
         <v>18.45999908447266</v>
       </c>
       <c r="BX88" t="n">
-        <v>4.484582530846104</v>
+        <v>4.48458253558868</v>
       </c>
       <c r="BY88" t="n">
-        <v>8.318900594719523</v>
+        <v>8.318900603516999</v>
       </c>
       <c r="BZ88" t="n">
         <v>31.00063217607892</v>
@@ -41766,13 +41766,13 @@
         <v>33.42141293239761</v>
       </c>
       <c r="CB88" t="n">
-        <v>26.78755093304765</v>
+        <v>26.78755093415931</v>
       </c>
       <c r="CC88" t="n">
-        <v>11.12047331823479</v>
+        <v>11.12047331791351</v>
       </c>
       <c r="CD88" t="n">
-        <v>18.08633563590804</v>
+        <v>18.08633563131723</v>
       </c>
       <c r="CE88" t="n">
         <v>39.71865914645217</v>
@@ -42068,25 +42068,25 @@
         <v>1.690000057220459</v>
       </c>
       <c r="BX89" t="n">
-        <v>0.1506862967698173</v>
+        <v>0.1506862965852784</v>
       </c>
       <c r="BY89" t="n">
-        <v>0.1716968779608208</v>
+        <v>0.1716968777587709</v>
       </c>
       <c r="BZ89" t="n">
-        <v>0.774905894777474</v>
+        <v>0.7749058948145716</v>
       </c>
       <c r="CA89" t="n">
         <v>3.21621281095181</v>
       </c>
       <c r="CB89" t="n">
-        <v>0.2641169346412659</v>
+        <v>0.2641169345463516</v>
       </c>
       <c r="CC89" t="n">
-        <v>0.5414796436183452</v>
+        <v>0.5414796436211818</v>
       </c>
       <c r="CD89" t="n">
-        <v>0.3456600224103397</v>
+        <v>0.345660022442169</v>
       </c>
       <c r="CE89" t="inlineStr"/>
       <c r="CF89" t="inlineStr"/>
@@ -42382,10 +42382,10 @@
         <v>13.89999961853027</v>
       </c>
       <c r="BX90" t="n">
-        <v>6.000512486920178</v>
+        <v>6.000512444818219</v>
       </c>
       <c r="BY90" t="n">
-        <v>8.73674618095578</v>
+        <v>8.736746119655328</v>
       </c>
       <c r="BZ90" t="n">
         <v>3.740232756344498</v>
@@ -42598,13 +42598,13 @@
         <v>0</v>
       </c>
       <c r="AR91" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="AS91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="n">
-        <v>2998888960</v>
+        <v>2975689216</v>
       </c>
       <c r="AU91" t="n">
         <v>6.54</v>
@@ -42694,10 +42694,10 @@
         <v>7.420000076293945</v>
       </c>
       <c r="BX91" t="n">
-        <v>3.087450366224078</v>
+        <v>3.087450369808338</v>
       </c>
       <c r="BY91" t="n">
-        <v>5.727220429345665</v>
+        <v>5.727220435994467</v>
       </c>
       <c r="BZ91" t="n">
         <v>15.03287477230807</v>
@@ -42706,23 +42706,23 @@
         <v>16.21959651842132</v>
       </c>
       <c r="CB91" t="n">
-        <v>14.39085493877468</v>
+        <v>14.3908549408875</v>
       </c>
       <c r="CC91" t="n">
-        <v>14.99868039622335</v>
+        <v>14.99868039553552</v>
       </c>
       <c r="CD91" t="n">
-        <v>7.922199663291257</v>
+        <v>7.92219965979646</v>
       </c>
       <c r="CE91" t="inlineStr"/>
       <c r="CF91" t="n">
-        <v>13.71284125780373</v>
+        <v>13.71284125738977</v>
       </c>
       <c r="CG91" t="n">
-        <v>14.99868039622335</v>
+        <v>14.99868039553552</v>
       </c>
       <c r="CH91" t="n">
-        <v>13.49881235660101</v>
+        <v>13.49881235598197</v>
       </c>
       <c r="CI91" t="n">
         <v>5</v>
@@ -42734,10 +42734,10 @@
         <v>5.3</v>
       </c>
       <c r="CL91" t="n">
-        <v>81.92469296231116</v>
+        <v>81.9246929539682</v>
       </c>
       <c r="CM91" t="n">
-        <v>84.80917947177251</v>
+        <v>84.80917946619351</v>
       </c>
       <c r="CN91" t="inlineStr">
         <is>
@@ -43018,10 +43018,10 @@
         <v>3.690000057220459</v>
       </c>
       <c r="BX92" t="n">
-        <v>33.80143544520377</v>
+        <v>33.80143535665922</v>
       </c>
       <c r="BY92" t="n">
-        <v>62.70166275085298</v>
+        <v>62.70166258660284</v>
       </c>
       <c r="BZ92" t="n">
         <v>4.860089538585594</v>
@@ -43314,35 +43314,35 @@
         <v>19.56999969482422</v>
       </c>
       <c r="BX93" t="n">
-        <v>11.66679776259345</v>
+        <v>11.66679785846165</v>
       </c>
       <c r="BY93" t="n">
-        <v>15.42108794674919</v>
+        <v>15.42108801046908</v>
       </c>
       <c r="BZ93" t="n">
-        <v>25.10431138726875</v>
+        <v>25.10431128471299</v>
       </c>
       <c r="CA93" t="n">
         <v>44.54686696093374</v>
       </c>
       <c r="CB93" t="n">
-        <v>30.38694750074582</v>
+        <v>30.38694757586564</v>
       </c>
       <c r="CC93" t="n">
-        <v>15.8248453770254</v>
+        <v>15.82484537083394</v>
       </c>
       <c r="CD93" t="n">
-        <v>12.25417624187906</v>
+        <v>12.25417617447221</v>
       </c>
       <c r="CE93" t="inlineStr"/>
       <c r="CF93" t="n">
-        <v>17.0042606184092</v>
+        <v>17.00426063111941</v>
       </c>
       <c r="CG93" t="n">
-        <v>15.6229666618873</v>
+        <v>15.62296669065151</v>
       </c>
       <c r="CH93" t="n">
-        <v>14.06066999569857</v>
+        <v>14.06067002158636</v>
       </c>
       <c r="CI93" t="n">
         <v>4</v>
@@ -43354,10 +43354,10 @@
         <v>2.2</v>
       </c>
       <c r="CL93" t="n">
-        <v>-28.15191509983892</v>
+        <v>-28.15191496755588</v>
       </c>
       <c r="CM93" t="n">
-        <v>-13.11057289946507</v>
+        <v>-13.11057283451761</v>
       </c>
       <c r="CN93" t="inlineStr">
         <is>
@@ -43646,10 +43646,10 @@
         <v>78.69999694824219</v>
       </c>
       <c r="BX94" t="n">
-        <v>58.83949706320842</v>
+        <v>58.83949674989157</v>
       </c>
       <c r="BY94" t="n">
-        <v>85.67030772403146</v>
+        <v>85.67030726784213</v>
       </c>
       <c r="BZ94" t="n">
         <v>24.78740061361959</v>
@@ -43962,10 +43962,10 @@
         <v>35.65000152587891</v>
       </c>
       <c r="BX95" t="n">
-        <v>8.823433615553208</v>
+        <v>8.823433576615182</v>
       </c>
       <c r="BY95" t="n">
-        <v>16.3674693568512</v>
+        <v>16.36746928462116</v>
       </c>
       <c r="BZ95" t="n">
         <v>42.70908862729615</v>
@@ -43974,19 +43974,19 @@
         <v>42.97434148367212</v>
       </c>
       <c r="CB95" t="n">
-        <v>36.27793360408871</v>
+        <v>36.27793362365029</v>
       </c>
       <c r="CC95" t="n">
-        <v>50.14199040554316</v>
+        <v>50.14199041547946</v>
       </c>
       <c r="CD95" t="n">
-        <v>24.39370806930032</v>
+        <v>24.3937081125776</v>
       </c>
       <c r="CE95" t="n">
         <v>54.38971422125846</v>
       </c>
       <c r="CF95" t="n">
-        <v>38.1791779668586</v>
+        <v>38.17917796693647</v>
       </c>
       <c r="CG95" t="n">
         <v>42.70908862729615</v>
@@ -44007,7 +44007,7 @@
         <v>7.820976491862575</v>
       </c>
       <c r="CM95" t="n">
-        <v>7.094463766414494</v>
+        <v>7.094463766632919</v>
       </c>
       <c r="CN95" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>1</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AS96" t="b">
         <v>1</v>
@@ -44294,10 +44294,10 @@
         <v>19.59000015258789</v>
       </c>
       <c r="BX96" t="n">
-        <v>2.02155471245337</v>
+        <v>2.021554713123317</v>
       </c>
       <c r="BY96" t="n">
-        <v>3.749983991601002</v>
+        <v>3.749983992843753</v>
       </c>
       <c r="BZ96" t="n">
         <v>10.85148419823535</v>
@@ -44306,19 +44306,19 @@
         <v>9.057717523549277</v>
       </c>
       <c r="CB96" t="n">
-        <v>11.05024976637562</v>
+        <v>11.05024976504101</v>
       </c>
       <c r="CC96" t="n">
-        <v>7.567164101570822</v>
+        <v>7.567164101428432</v>
       </c>
       <c r="CD96" t="n">
-        <v>8.390001910999565</v>
+        <v>8.390001909914199</v>
       </c>
       <c r="CE96" t="n">
         <v>14.26878965170031</v>
       </c>
       <c r="CF96" t="n">
-        <v>9.27648444914742</v>
+        <v>9.276484448958902</v>
       </c>
       <c r="CG96" t="n">
         <v>9.057717523549277</v>
@@ -44339,7 +44339,7 @@
         <v>-58.38720925115738</v>
       </c>
       <c r="CM96" t="n">
-        <v>-52.64683830070327</v>
+        <v>-52.64683830166559</v>
       </c>
       <c r="CN96" t="inlineStr">
         <is>
@@ -44616,10 +44616,10 @@
         <v>7.78000020980835</v>
       </c>
       <c r="BX97" t="n">
-        <v>5.007638596634138</v>
+        <v>5.007638613855274</v>
       </c>
       <c r="BY97" t="n">
-        <v>7.291121796699305</v>
+        <v>7.291121821773279</v>
       </c>
       <c r="BZ97" t="n">
         <v>5.804304317217133</v>
@@ -44638,13 +44638,13 @@
         <v>7.482269761699905</v>
       </c>
       <c r="CF97" t="n">
-        <v>6.550785506920537</v>
+        <v>6.550785513969722</v>
       </c>
       <c r="CG97" t="n">
-        <v>6.547713056958219</v>
+        <v>6.547713069495206</v>
       </c>
       <c r="CH97" t="n">
-        <v>5.892941751262398</v>
+        <v>5.892941762545686</v>
       </c>
       <c r="CI97" t="n">
         <v>6</v>
@@ -44656,10 +44656,10 @@
         <v>5.9</v>
       </c>
       <c r="CL97" t="n">
-        <v>-24.25524945573796</v>
+        <v>-24.25524931070856</v>
       </c>
       <c r="CM97" t="n">
-        <v>-15.7996744182362</v>
+        <v>-15.79967432762971</v>
       </c>
       <c r="CN97" t="inlineStr">
         <is>
@@ -44938,10 +44938,10 @@
         <v>15.90999984741211</v>
       </c>
       <c r="BX98" t="n">
-        <v>8.011259046187043</v>
+        <v>8.011259054584569</v>
       </c>
       <c r="BY98" t="n">
-        <v>14.86088553067697</v>
+        <v>14.86088554625437</v>
       </c>
       <c r="BZ98" t="n">
         <v>10.43085096379072</v>
@@ -44962,7 +44962,7 @@
         <v>8.936869495263364</v>
       </c>
       <c r="CF98" t="n">
-        <v>12.29449222800119</v>
+        <v>12.29449223099806</v>
       </c>
       <c r="CG98" t="n">
         <v>9.978191393663952</v>
@@ -44983,7 +44983,7 @@
         <v>-43.55517070757051</v>
       </c>
       <c r="CM98" t="n">
-        <v>-22.72474955428116</v>
+        <v>-22.7247495354448</v>
       </c>
       <c r="CN98" t="inlineStr">
         <is>
@@ -45262,10 +45262,10 @@
         <v>6.96999979019165</v>
       </c>
       <c r="BX99" t="n">
-        <v>3.11882195960837</v>
+        <v>3.11882197498492</v>
       </c>
       <c r="BY99" t="n">
-        <v>5.785414735073527</v>
+        <v>5.785414763597026</v>
       </c>
       <c r="BZ99" t="inlineStr"/>
       <c r="CA99" t="inlineStr"/>
@@ -45276,13 +45276,13 @@
         <v>9.526511531301223</v>
       </c>
       <c r="CF99" t="n">
-        <v>6.143582741994373</v>
+        <v>6.143582756627723</v>
       </c>
       <c r="CG99" t="n">
-        <v>5.785414735073527</v>
+        <v>5.785414763597026</v>
       </c>
       <c r="CH99" t="n">
-        <v>5.206873261566174</v>
+        <v>5.206873287237324</v>
       </c>
       <c r="CI99" t="n">
         <v>3</v>
@@ -45294,10 +45294,10 @@
         <v>3.1</v>
       </c>
       <c r="CL99" t="n">
-        <v>-25.29593374029351</v>
+        <v>-25.29593337198433</v>
       </c>
       <c r="CM99" t="n">
-        <v>-11.85677292788776</v>
+        <v>-11.85677271794013</v>
       </c>
       <c r="CN99" t="inlineStr">
         <is>
@@ -45576,25 +45576,25 @@
         <v>47.2400016784668</v>
       </c>
       <c r="BX100" t="n">
-        <v>18.15640575952109</v>
+        <v>18.15640573644396</v>
       </c>
       <c r="BY100" t="n">
-        <v>20.57934588867509</v>
+        <v>20.57934587732104</v>
       </c>
       <c r="BZ100" t="n">
-        <v>25.36192500601656</v>
+        <v>25.36192502425934</v>
       </c>
       <c r="CA100" t="n">
         <v>53.3467002990466</v>
       </c>
       <c r="CB100" t="n">
-        <v>21.45195356899534</v>
+        <v>21.45195357270656</v>
       </c>
       <c r="CC100" t="n">
-        <v>23.33743286720312</v>
+        <v>23.3374328690486</v>
       </c>
       <c r="CD100" t="n">
-        <v>11.25742193833658</v>
+        <v>11.2574219541361</v>
       </c>
       <c r="CE100" t="n">
         <v>121.096867054075</v>
@@ -45890,37 +45890,37 @@
         <v>23.35000038146973</v>
       </c>
       <c r="BX101" t="n">
-        <v>5.11442745226174</v>
+        <v>5.114427464309239</v>
       </c>
       <c r="BY101" t="n">
-        <v>7.202559901588604</v>
+        <v>7.202559904208624</v>
       </c>
       <c r="BZ101" t="n">
-        <v>10.5564695011448</v>
+        <v>10.55646948011812</v>
       </c>
       <c r="CA101" t="n">
         <v>14.59026773421743</v>
       </c>
       <c r="CB101" t="n">
-        <v>7.092388241529929</v>
+        <v>7.092388229511508</v>
       </c>
       <c r="CC101" t="n">
-        <v>8.429566142280361</v>
+        <v>8.429566140762141</v>
       </c>
       <c r="CD101" t="n">
-        <v>5.238787062086296</v>
+        <v>5.238787049767007</v>
       </c>
       <c r="CE101" t="n">
         <v>10.33412711493239</v>
       </c>
       <c r="CF101" t="n">
-        <v>8.569824143755195</v>
+        <v>8.569824139728308</v>
       </c>
       <c r="CG101" t="n">
-        <v>7.816063021934482</v>
+        <v>7.816063022485382</v>
       </c>
       <c r="CH101" t="n">
-        <v>7.034456719741034</v>
+        <v>7.034456720236844</v>
       </c>
       <c r="CI101" t="n">
         <v>8</v>
@@ -45932,10 +45932,10 @@
         <v>2.9</v>
       </c>
       <c r="CL101" t="n">
-        <v>-69.87384751683562</v>
+        <v>-69.87384751471224</v>
       </c>
       <c r="CM101" t="n">
-        <v>-63.29839827087924</v>
+        <v>-63.29839828812502</v>
       </c>
       <c r="CN101" t="inlineStr">
         <is>
@@ -46218,10 +46218,10 @@
         <v>12.18000030517578</v>
       </c>
       <c r="BX102" t="n">
-        <v>2.166666229178234</v>
+        <v>2.166666230980119</v>
       </c>
       <c r="BY102" t="n">
-        <v>4.019165855125624</v>
+        <v>4.019165858468121</v>
       </c>
       <c r="BZ102" t="n">
         <v>12.84912452576267</v>
@@ -46230,25 +46230,25 @@
         <v>14.24321699181254</v>
       </c>
       <c r="CB102" t="n">
-        <v>9.379078962570699</v>
+        <v>9.379078961943009</v>
       </c>
       <c r="CC102" t="n">
-        <v>5.744344356959375</v>
+        <v>5.744344356813682</v>
       </c>
       <c r="CD102" t="n">
-        <v>6.967979820028605</v>
+        <v>6.967979818371591</v>
       </c>
       <c r="CE102" t="n">
         <v>12.18000030517578</v>
       </c>
       <c r="CF102" t="n">
-        <v>9.340415831062185</v>
+        <v>9.340415831192484</v>
       </c>
       <c r="CG102" t="n">
-        <v>9.379078962570699</v>
+        <v>9.379078961943009</v>
       </c>
       <c r="CH102" t="n">
-        <v>8.441171066313629</v>
+        <v>8.441171065748708</v>
       </c>
       <c r="CI102" t="n">
         <v>7</v>
@@ -46260,10 +46260,10 @@
         <v>6.6</v>
       </c>
       <c r="CL102" t="n">
-        <v>-30.69646260413779</v>
+        <v>-30.69646260877589</v>
       </c>
       <c r="CM102" t="n">
-        <v>-23.31350084537306</v>
+        <v>-23.31350084430328</v>
       </c>
       <c r="CN102" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>-2.090026398533917</v>
       </c>
       <c r="CZ102" t="n">
-        <v>-25.25441878355007</v>
+        <v>-25.25442765560502</v>
       </c>
       <c r="DA102" t="b">
         <v>0</v>
@@ -46542,10 +46542,10 @@
         <v>46.34000015258789</v>
       </c>
       <c r="BX103" t="n">
-        <v>10.13865031749336</v>
+        <v>10.1386503368159</v>
       </c>
       <c r="BY103" t="n">
-        <v>18.80719633895018</v>
+        <v>18.8071963747935</v>
       </c>
       <c r="BZ103" t="n">
         <v>85.63528619550759</v>
@@ -46554,13 +46554,13 @@
         <v>75.5695277891077</v>
       </c>
       <c r="CB103" t="n">
-        <v>102.7137955329465</v>
+        <v>102.7137955262026</v>
       </c>
       <c r="CC103" t="n">
-        <v>15.99814152142361</v>
+        <v>15.99814152044793</v>
       </c>
       <c r="CD103" t="n">
-        <v>69.38497638512055</v>
+        <v>69.38497635716627</v>
       </c>
       <c r="CE103" t="n">
         <v>21.49551710110895</v>
@@ -46860,37 +46860,37 @@
         <v>53.65000152587891</v>
       </c>
       <c r="BX104" t="n">
-        <v>16.38838751321266</v>
+        <v>16.38838750334706</v>
       </c>
       <c r="BY104" t="n">
-        <v>25.10603633856535</v>
+        <v>25.1060363327928</v>
       </c>
       <c r="BZ104" t="n">
-        <v>45.79263203760566</v>
+        <v>45.79263205464331</v>
       </c>
       <c r="CA104" t="n">
         <v>63.31865958566679</v>
       </c>
       <c r="CB104" t="n">
-        <v>36.53709859986134</v>
+        <v>36.53709860270615</v>
       </c>
       <c r="CC104" t="n">
-        <v>26.77810745991694</v>
+        <v>26.77810746075119</v>
       </c>
       <c r="CD104" t="n">
-        <v>22.89631173992661</v>
+        <v>22.8963117484868</v>
       </c>
       <c r="CE104" t="n">
         <v>21.28296611184845</v>
       </c>
       <c r="CF104" t="n">
-        <v>32.26252492332547</v>
+        <v>32.26252492503032</v>
       </c>
       <c r="CG104" t="n">
-        <v>25.94207189924114</v>
+        <v>25.942071896772</v>
       </c>
       <c r="CH104" t="n">
-        <v>23.34786470931703</v>
+        <v>23.3478647070948</v>
       </c>
       <c r="CI104" t="n">
         <v>8</v>
@@ -46902,10 +46902,10 @@
         <v>3.9</v>
       </c>
       <c r="CL104" t="n">
-        <v>-56.48114809828137</v>
+        <v>-56.48114810242345</v>
       </c>
       <c r="CM104" t="n">
-        <v>-39.86482011978482</v>
+        <v>-39.86482011660709</v>
       </c>
       <c r="CN104" t="inlineStr">
         <is>
@@ -47196,10 +47196,10 @@
         <v>3.009999990463257</v>
       </c>
       <c r="BX105" t="n">
-        <v>0.6298002091145828</v>
+        <v>0.6298002102054431</v>
       </c>
       <c r="BY105" t="n">
-        <v>1.168279387907551</v>
+        <v>1.168279389931097</v>
       </c>
       <c r="BZ105" t="n">
         <v>3.655591189151068</v>
@@ -47208,13 +47208,13 @@
         <v>4.238661238286214</v>
       </c>
       <c r="CB105" t="n">
-        <v>2.604672399932547</v>
+        <v>2.604672399870833</v>
       </c>
       <c r="CC105" t="n">
-        <v>2.640588270765372</v>
+        <v>2.640588270634039</v>
       </c>
       <c r="CD105" t="n">
-        <v>1.866256394219806</v>
+        <v>1.866256393301127</v>
       </c>
       <c r="CE105" t="n">
         <v>9.198296956105558</v>
@@ -47510,25 +47510,25 @@
         <v>14.64000034332275</v>
       </c>
       <c r="BX106" t="n">
-        <v>3.695138832292627</v>
+        <v>3.695138832396376</v>
       </c>
       <c r="BY106" t="n">
-        <v>4.706896842586999</v>
+        <v>4.706896842702021</v>
       </c>
       <c r="BZ106" t="n">
-        <v>14.38487143347289</v>
+        <v>14.38487143342053</v>
       </c>
       <c r="CA106" t="n">
         <v>37.51681749325965</v>
       </c>
       <c r="CB106" t="n">
-        <v>9.873209694112886</v>
+        <v>9.873209694211205</v>
       </c>
       <c r="CC106" t="n">
-        <v>48.41659564241377</v>
+        <v>48.41659564239632</v>
       </c>
       <c r="CD106" t="n">
-        <v>6.917949863126274</v>
+        <v>6.917949863089481</v>
       </c>
       <c r="CE106" t="n">
         <v>21.52179483859446</v>
@@ -48120,10 +48120,10 @@
         <v>58.11999893188477</v>
       </c>
       <c r="BX108" t="n">
-        <v>65.75643235269054</v>
+        <v>65.75643217720778</v>
       </c>
       <c r="BY108" t="n">
-        <v>95.74136550551742</v>
+        <v>95.74136525001454</v>
       </c>
       <c r="BZ108" t="n">
         <v>24.17791955566406</v>
@@ -48430,10 +48430,10 @@
         <v>6.420000076293945</v>
       </c>
       <c r="BX109" t="n">
-        <v>0.0613760399881119</v>
+        <v>0.06137604026835535</v>
       </c>
       <c r="BY109" t="n">
-        <v>0.1138525541779476</v>
+        <v>0.1138525546977992</v>
       </c>
       <c r="BZ109" t="inlineStr"/>
       <c r="CA109" t="inlineStr"/>
@@ -49038,10 +49038,10 @@
         <v>96.33999633789062</v>
       </c>
       <c r="BX111" t="n">
-        <v>4.919793613174007</v>
+        <v>4.91979362341863</v>
       </c>
       <c r="BY111" t="n">
-        <v>9.126217152437784</v>
+        <v>9.126217171441558</v>
       </c>
       <c r="BZ111" t="n">
         <v>40.88741036121239</v>
@@ -49050,13 +49050,13 @@
         <v>40.58994084391919</v>
       </c>
       <c r="CB111" t="n">
-        <v>33.39208160099796</v>
+        <v>33.39208158693241</v>
       </c>
       <c r="CC111" t="n">
-        <v>17.63215568171682</v>
+        <v>17.63215568074849</v>
       </c>
       <c r="CD111" t="n">
-        <v>27.84617054229397</v>
+        <v>27.8461705305651</v>
       </c>
       <c r="CE111" t="n">
         <v>40.97990082873793</v>
@@ -49352,10 +49352,10 @@
         <v>17.45000076293945</v>
       </c>
       <c r="BX112" t="n">
-        <v>3.27608360707357</v>
+        <v>3.276083585906649</v>
       </c>
       <c r="BY112" t="n">
-        <v>6.077135091121471</v>
+        <v>6.077135051856834</v>
       </c>
       <c r="BZ112" t="n">
         <v>14.63370317145239</v>
@@ -49364,23 +49364,23 @@
         <v>15.60803264394471</v>
       </c>
       <c r="CB112" t="n">
-        <v>10.20015846273909</v>
+        <v>10.20015847746966</v>
       </c>
       <c r="CC112" t="n">
-        <v>13.00594068443896</v>
+        <v>13.00594068813793</v>
       </c>
       <c r="CD112" t="n">
-        <v>7.537281016282621</v>
+        <v>7.537281037331006</v>
       </c>
       <c r="CE112" t="inlineStr"/>
       <c r="CF112" t="n">
-        <v>11.17704184499654</v>
+        <v>11.17704184503209</v>
       </c>
       <c r="CG112" t="n">
-        <v>11.60304957358903</v>
+        <v>11.60304958280379</v>
       </c>
       <c r="CH112" t="n">
-        <v>10.44274461623012</v>
+        <v>10.44274462452342</v>
       </c>
       <c r="CI112" t="n">
         <v>6</v>
@@ -49392,10 +49392,10 @@
         <v>4.8</v>
       </c>
       <c r="CL112" t="n">
-        <v>-40.15619392746065</v>
+        <v>-40.15619387993462</v>
       </c>
       <c r="CM112" t="n">
-        <v>-35.94818706979947</v>
+        <v>-35.94818706959578</v>
       </c>
       <c r="CN112" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>0</v>
       </c>
       <c r="AT113" t="n">
-        <v>26965680128</v>
+        <v>26963605504</v>
       </c>
       <c r="AU113" t="n">
         <v>21.57</v>
@@ -49674,10 +49674,10 @@
         <v>14.52999973297119</v>
       </c>
       <c r="BX113" t="n">
-        <v>1.359804413897712</v>
+        <v>1.359804413056631</v>
       </c>
       <c r="BY113" t="n">
-        <v>2.522437187780256</v>
+        <v>2.52243718622005</v>
       </c>
       <c r="BZ113" t="n">
         <v>8.9254750330027</v>
@@ -49686,13 +49686,13 @@
         <v>10.96999041107547</v>
       </c>
       <c r="CB113" t="n">
-        <v>4.980524739930217</v>
+        <v>4.980524740382846</v>
       </c>
       <c r="CC113" t="n">
-        <v>7.696681031507728</v>
+        <v>7.696681031615275</v>
       </c>
       <c r="CD113" t="n">
-        <v>4.375380390275907</v>
+        <v>4.375380390903556</v>
       </c>
       <c r="CE113" t="n">
         <v>11.24969464648006</v>
@@ -49992,10 +49992,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX114" t="n">
-        <v>11.98290326030796</v>
+        <v>11.98290321959356</v>
       </c>
       <c r="BY114" t="n">
-        <v>14.95257928568863</v>
+        <v>14.95257923488414</v>
       </c>
       <c r="BZ114" t="inlineStr"/>
       <c r="CA114" t="inlineStr"/>
@@ -50298,10 +50298,10 @@
         <v>11.18000030517578</v>
       </c>
       <c r="BX115" t="n">
-        <v>2.429612154081693</v>
+        <v>2.429612155142877</v>
       </c>
       <c r="BY115" t="n">
-        <v>4.50693054582154</v>
+        <v>4.506930547790037</v>
       </c>
       <c r="BZ115" t="n">
         <v>12.21228392774766</v>
@@ -50310,13 +50310,13 @@
         <v>12.73311481937156</v>
       </c>
       <c r="CB115" t="n">
-        <v>9.672110407167599</v>
+        <v>9.672110406637819</v>
       </c>
       <c r="CC115" t="n">
-        <v>0.7924908650491582</v>
+        <v>0.7924908650351182</v>
       </c>
       <c r="CD115" t="n">
-        <v>6.779198841911483</v>
+        <v>6.779198840808614</v>
       </c>
       <c r="CE115" t="n">
         <v>7.307661395663775</v>
@@ -50612,10 +50612,10 @@
         <v>3.430000066757202</v>
       </c>
       <c r="BX116" t="n">
-        <v>1.68935888072427</v>
+        <v>1.689358876800245</v>
       </c>
       <c r="BY116" t="n">
-        <v>3.133760723743521</v>
+        <v>3.133760716464454</v>
       </c>
       <c r="BZ116" t="n">
         <v>1.168015956939936</v>
@@ -50624,7 +50624,7 @@
         <v>4.684615221800192</v>
       </c>
       <c r="CB116" t="n">
-        <v>1.621588925670717</v>
+        <v>1.621588924258835</v>
       </c>
       <c r="CC116" t="n">
         <v>0.7445919647652398</v>
@@ -50926,10 +50926,10 @@
         <v>4.809999942779541</v>
       </c>
       <c r="BX117" t="n">
-        <v>1.479418500841632</v>
+        <v>1.479418508084515</v>
       </c>
       <c r="BY117" t="n">
-        <v>1.541882837543834</v>
+        <v>1.541882845092528</v>
       </c>
       <c r="BZ117" t="inlineStr"/>
       <c r="CA117" t="inlineStr"/>
@@ -51230,25 +51230,25 @@
         <v>8.739999771118164</v>
       </c>
       <c r="BX118" t="n">
-        <v>2.247634683530642</v>
+        <v>2.247634687271938</v>
       </c>
       <c r="BY118" t="n">
-        <v>2.421011757532052</v>
+        <v>2.421011760519181</v>
       </c>
       <c r="BZ118" t="n">
-        <v>3.136387960002509</v>
+        <v>3.136387958651625</v>
       </c>
       <c r="CA118" t="n">
         <v>9.827685355919407</v>
       </c>
       <c r="CB118" t="n">
-        <v>1.829365608395791</v>
+        <v>1.829365608801292</v>
       </c>
       <c r="CC118" t="n">
-        <v>5.905845202130703</v>
+        <v>5.905845201838114</v>
       </c>
       <c r="CD118" t="n">
-        <v>1.316356165032299</v>
+        <v>1.316356163751579</v>
       </c>
       <c r="CE118" t="n">
         <v>12.81521599596358</v>
@@ -51544,10 +51544,10 @@
         <v>6.559999942779541</v>
       </c>
       <c r="BX119" t="n">
-        <v>1.053466676892449</v>
+        <v>1.053466686002944</v>
       </c>
       <c r="BY119" t="n">
-        <v>1.954180685635493</v>
+        <v>1.954180702535462</v>
       </c>
       <c r="BZ119" t="inlineStr"/>
       <c r="CA119" t="inlineStr"/>
@@ -51848,25 +51848,25 @@
         <v>3.700000047683716</v>
       </c>
       <c r="BX120" t="n">
-        <v>1.267030931060026</v>
+        <v>1.267030929244537</v>
       </c>
       <c r="BY120" t="n">
-        <v>1.302892962210345</v>
+        <v>1.302892960991052</v>
       </c>
       <c r="BZ120" t="n">
-        <v>1.40884426166382</v>
+        <v>1.408844262364063</v>
       </c>
       <c r="CA120" t="n">
         <v>4.28417545380731</v>
       </c>
       <c r="CB120" t="n">
-        <v>0.9846225514088409</v>
+        <v>0.9846225512375228</v>
       </c>
       <c r="CC120" t="n">
-        <v>2.173299920646181</v>
+        <v>2.173299920775623</v>
       </c>
       <c r="CD120" t="n">
-        <v>0.5532971873788393</v>
+        <v>0.5532971880993706</v>
       </c>
       <c r="CE120" t="n">
         <v>5.184427633155422</v>
@@ -52166,10 +52166,10 @@
         <v>5.510000228881836</v>
       </c>
       <c r="BX121" t="n">
-        <v>5.460017763917192</v>
+        <v>5.460017769389337</v>
       </c>
       <c r="BY121" t="n">
-        <v>7.949785864263432</v>
+        <v>7.949785872230875</v>
       </c>
       <c r="BZ121" t="inlineStr"/>
       <c r="CA121" t="inlineStr"/>
@@ -52178,13 +52178,13 @@
       <c r="CD121" t="inlineStr"/>
       <c r="CE121" t="inlineStr"/>
       <c r="CF121" t="n">
-        <v>6.704901814090312</v>
+        <v>6.704901820810106</v>
       </c>
       <c r="CG121" t="n">
-        <v>6.704901814090312</v>
+        <v>6.704901820810106</v>
       </c>
       <c r="CH121" t="n">
-        <v>6.034411632681281</v>
+        <v>6.034411638729095</v>
       </c>
       <c r="CI121" t="n">
         <v>2</v>
@@ -52196,10 +52196,10 @@
         <v>1.5</v>
       </c>
       <c r="CL121" t="n">
-        <v>9.517447949468893</v>
+        <v>9.517448059229562</v>
       </c>
       <c r="CM121" t="n">
-        <v>21.68605327718765</v>
+        <v>21.68605339914396</v>
       </c>
       <c r="CN121" t="inlineStr">
         <is>
@@ -52478,10 +52478,10 @@
         <v>5.079999923706055</v>
       </c>
       <c r="BX122" t="n">
-        <v>5.591984094258464</v>
+        <v>5.591984111780663</v>
       </c>
       <c r="BY122" t="n">
-        <v>9.969901280341777</v>
+        <v>9.969901311581957</v>
       </c>
       <c r="BZ122" t="inlineStr"/>
       <c r="CA122" t="inlineStr"/>
@@ -52490,13 +52490,13 @@
       <c r="CD122" t="inlineStr"/>
       <c r="CE122" t="inlineStr"/>
       <c r="CF122" t="n">
-        <v>7.78094268730012</v>
+        <v>7.78094271168131</v>
       </c>
       <c r="CG122" t="n">
-        <v>7.78094268730012</v>
+        <v>7.78094271168131</v>
       </c>
       <c r="CH122" t="n">
-        <v>7.002848418570109</v>
+        <v>7.002848440513179</v>
       </c>
       <c r="CI122" t="n">
         <v>2</v>
@@ -52508,10 +52508,10 @@
         <v>1.8</v>
       </c>
       <c r="CL122" t="n">
-        <v>37.85134889256578</v>
+        <v>37.85134932451599</v>
       </c>
       <c r="CM122" t="n">
-        <v>53.16816543618419</v>
+        <v>53.16816591612887</v>
       </c>
       <c r="CN122" t="inlineStr">
         <is>
@@ -52776,10 +52776,10 @@
         <v>21.88999938964844</v>
       </c>
       <c r="BX123" t="n">
-        <v>37.94222250406597</v>
+        <v>37.94222215713103</v>
       </c>
       <c r="BY123" t="n">
-        <v>70.38282274504238</v>
+        <v>70.38282210147807</v>
       </c>
       <c r="BZ123" t="n">
         <v>20.07214476905479</v>
@@ -52798,7 +52798,7 @@
       </c>
       <c r="CE123" t="inlineStr"/>
       <c r="CF123" t="n">
-        <v>26.06992673241972</v>
+        <v>26.06992667459723</v>
       </c>
       <c r="CG123" t="n">
         <v>23.36448533113464</v>
@@ -52819,7 +52819,7 @@
         <v>-3.937700391325161</v>
       </c>
       <c r="CM123" t="n">
-        <v>19.09514599962907</v>
+        <v>19.09514573547881</v>
       </c>
       <c r="CN123" t="inlineStr">
         <is>
@@ -53098,25 +53098,25 @@
         <v>9.210000038146973</v>
       </c>
       <c r="BX124" t="n">
-        <v>3.562432716307367</v>
+        <v>3.562432717972003</v>
       </c>
       <c r="BY124" t="n">
-        <v>3.670924912319801</v>
+        <v>3.670924913768543</v>
       </c>
       <c r="BZ124" t="n">
-        <v>4.387649659742548</v>
+        <v>4.387649659423908</v>
       </c>
       <c r="CA124" t="n">
         <v>19.06106624245507</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.445242688064043</v>
+        <v>3.445242689052752</v>
       </c>
       <c r="CC124" t="n">
-        <v>7.740640165420308</v>
+        <v>7.740640165353069</v>
       </c>
       <c r="CD124" t="n">
-        <v>1.728975897581214</v>
+        <v>1.728975897254545</v>
       </c>
       <c r="CE124" t="n">
         <v>20.19385877757074</v>
@@ -53412,10 +53412,10 @@
         <v>11.46000003814697</v>
       </c>
       <c r="BX125" t="n">
-        <v>0.7792719060731134</v>
+        <v>0.7792719071193254</v>
       </c>
       <c r="BY125" t="n">
-        <v>1.445549385765625</v>
+        <v>1.445549387706349</v>
       </c>
       <c r="BZ125" t="n">
         <v>16.15372345802631</v>
@@ -53424,13 +53424,13 @@
         <v>16.82869587224833</v>
       </c>
       <c r="CB125" t="n">
-        <v>14.21481600337654</v>
+        <v>14.21481600321225</v>
       </c>
       <c r="CC125" t="n">
-        <v>1.741983299192257</v>
+        <v>1.741983299170025</v>
       </c>
       <c r="CD125" t="n">
-        <v>11.46236536776441</v>
+        <v>11.46236536668171</v>
       </c>
       <c r="CE125" t="inlineStr"/>
       <c r="CF125" t="inlineStr"/>
@@ -54018,25 +54018,25 @@
         <v>19</v>
       </c>
       <c r="BX127" t="n">
-        <v>0.5916775935083307</v>
+        <v>0.5916775935514221</v>
       </c>
       <c r="BY127" t="n">
-        <v>0.7950536078118555</v>
+        <v>0.795053607865796</v>
       </c>
       <c r="BZ127" t="n">
-        <v>4.662824168879123</v>
+        <v>4.662824168855883</v>
       </c>
       <c r="CA127" t="n">
         <v>11.65078630453671</v>
       </c>
       <c r="CB127" t="n">
-        <v>1.787429577134471</v>
+        <v>1.787429577126308</v>
       </c>
       <c r="CC127" t="n">
-        <v>0.6882468011089437</v>
+        <v>0.68824680110862</v>
       </c>
       <c r="CD127" t="n">
-        <v>2.288200648688663</v>
+        <v>2.288200648673836</v>
       </c>
       <c r="CE127" t="n">
         <v>19</v>
@@ -54336,10 +54336,10 @@
         <v>5.150000095367432</v>
       </c>
       <c r="BX128" t="n">
-        <v>1.268396228570193</v>
+        <v>1.268396229458081</v>
       </c>
       <c r="BY128" t="n">
-        <v>2.122834051634295</v>
+        <v>2.122834053120297</v>
       </c>
       <c r="BZ128" t="inlineStr"/>
       <c r="CA128" t="inlineStr"/>
@@ -54350,13 +54350,13 @@
         <v>5.988941589713868</v>
       </c>
       <c r="CF128" t="n">
-        <v>1.695615140102244</v>
+        <v>1.695615141289189</v>
       </c>
       <c r="CG128" t="n">
-        <v>1.695615140102244</v>
+        <v>1.695615141289189</v>
       </c>
       <c r="CH128" t="n">
-        <v>1.526053626092019</v>
+        <v>1.52605362716027</v>
       </c>
       <c r="CI128" t="n">
         <v>2</v>
@@ -54368,10 +54368,10 @@
         <v>4.7</v>
       </c>
       <c r="CL128" t="n">
-        <v>-70.36789130422061</v>
+        <v>-70.36789128347789</v>
       </c>
       <c r="CM128" t="n">
-        <v>-67.07543478246734</v>
+        <v>-67.07543475941988</v>
       </c>
       <c r="CN128" t="inlineStr">
         <is>
@@ -54650,37 +54650,37 @@
         <v>17.20999908447266</v>
       </c>
       <c r="BX129" t="n">
-        <v>2.072597801188352</v>
+        <v>2.072597794680712</v>
       </c>
       <c r="BY129" t="n">
-        <v>3.775021107998922</v>
+        <v>3.775021101333499</v>
       </c>
       <c r="BZ129" t="n">
-        <v>10.46758215689902</v>
+        <v>10.46758217128338</v>
       </c>
       <c r="CA129" t="n">
         <v>12.60778163571021</v>
       </c>
       <c r="CB129" t="n">
-        <v>6.073750640882602</v>
+        <v>6.073750644977784</v>
       </c>
       <c r="CC129" t="n">
-        <v>5.548158129619031</v>
+        <v>5.548158130163228</v>
       </c>
       <c r="CD129" t="n">
-        <v>5.114486566778489</v>
+        <v>5.114486572029895</v>
       </c>
       <c r="CE129" t="n">
         <v>15.99015396619785</v>
       </c>
       <c r="CF129" t="n">
-        <v>7.264463372981378</v>
+        <v>7.264463375916332</v>
       </c>
       <c r="CG129" t="n">
-        <v>5.810954385250817</v>
+        <v>5.810954387570506</v>
       </c>
       <c r="CH129" t="n">
-        <v>5.229858946725735</v>
+        <v>5.229858948813455</v>
       </c>
       <c r="CI129" t="n">
         <v>6</v>
@@ -54692,10 +54692,10 @@
         <v>7.7</v>
       </c>
       <c r="CL129" t="n">
-        <v>-69.61150944252948</v>
+        <v>-69.61150943039863</v>
       </c>
       <c r="CM129" t="n">
-        <v>-57.78928669708309</v>
+        <v>-57.78928668002932</v>
       </c>
       <c r="CN129" t="inlineStr">
         <is>
@@ -54970,10 +54970,10 @@
         <v>18.20000076293945</v>
       </c>
       <c r="BX130" t="n">
-        <v>1.401802102910439</v>
+        <v>1.401802103201183</v>
       </c>
       <c r="BY130" t="n">
-        <v>2.041023861837599</v>
+        <v>2.041023862260923</v>
       </c>
       <c r="BZ130" t="inlineStr"/>
       <c r="CA130" t="inlineStr"/>
@@ -55572,10 +55572,10 @@
         <v>4.21999979019165</v>
       </c>
       <c r="BX132" t="n">
-        <v>0.888197919742589</v>
+        <v>0.8881979182066739</v>
       </c>
       <c r="BY132" t="n">
-        <v>0.9831240724150782</v>
+        <v>0.9831240707150123</v>
       </c>
       <c r="BZ132" t="inlineStr"/>
       <c r="CA132" t="inlineStr"/>
@@ -55584,13 +55584,13 @@
       <c r="CD132" t="inlineStr"/>
       <c r="CE132" t="inlineStr"/>
       <c r="CF132" t="n">
-        <v>0.9356609960788336</v>
+        <v>0.9356609944608432</v>
       </c>
       <c r="CG132" t="n">
-        <v>0.9356609960788336</v>
+        <v>0.9356609944608432</v>
       </c>
       <c r="CH132" t="n">
-        <v>0.8420948964709503</v>
+        <v>0.8420948950147589</v>
       </c>
       <c r="CI132" t="n">
         <v>2</v>
@@ -55602,10 +55602,10 @@
         <v>1.1</v>
       </c>
       <c r="CL132" t="n">
-        <v>-80.04514364128187</v>
+        <v>-80.04514367578878</v>
       </c>
       <c r="CM132" t="n">
-        <v>-77.82793737920208</v>
+        <v>-77.82793741754308</v>
       </c>
       <c r="CN132" t="inlineStr">
         <is>
@@ -55886,10 +55886,10 @@
         <v>1.220000028610229</v>
       </c>
       <c r="BX133" t="n">
-        <v>0.3579768033346697</v>
+        <v>0.3579768030146158</v>
       </c>
       <c r="BY133" t="n">
-        <v>0.6640469701858123</v>
+        <v>0.6640469695921123</v>
       </c>
       <c r="BZ133" t="inlineStr"/>
       <c r="CA133" t="inlineStr"/>
@@ -55898,13 +55898,13 @@
       <c r="CD133" t="inlineStr"/>
       <c r="CE133" t="inlineStr"/>
       <c r="CF133" t="n">
-        <v>0.511011886760241</v>
+        <v>0.511011886303364</v>
       </c>
       <c r="CG133" t="n">
-        <v>0.511011886760241</v>
+        <v>0.511011886303364</v>
       </c>
       <c r="CH133" t="n">
-        <v>0.4599106980842169</v>
+        <v>0.4599106976730276</v>
       </c>
       <c r="CI133" t="n">
         <v>2</v>
@@ -55916,10 +55916,10 @@
         <v>1.9</v>
       </c>
       <c r="CL133" t="n">
-        <v>-62.30240268042231</v>
+        <v>-62.30240271412634</v>
       </c>
       <c r="CM133" t="n">
-        <v>-58.11378075602479</v>
+        <v>-58.11378079347372</v>
       </c>
       <c r="CN133" t="inlineStr">
         <is>
@@ -56506,10 +56506,10 @@
         <v>5.460000038146973</v>
       </c>
       <c r="BX135" t="n">
-        <v>1.040556585576844</v>
+        <v>1.040556585573552</v>
       </c>
       <c r="BY135" t="n">
-        <v>1.930232466245046</v>
+        <v>1.930232466238939</v>
       </c>
       <c r="BZ135" t="inlineStr"/>
       <c r="CA135" t="inlineStr"/>
@@ -56520,13 +56520,13 @@
         <v>2.857508361672422</v>
       </c>
       <c r="CF135" t="n">
-        <v>1.942765804498104</v>
+        <v>1.942765804494971</v>
       </c>
       <c r="CG135" t="n">
-        <v>1.930232466245046</v>
+        <v>1.930232466238939</v>
       </c>
       <c r="CH135" t="n">
-        <v>1.737209219620541</v>
+        <v>1.737209219615045</v>
       </c>
       <c r="CI135" t="n">
         <v>3</v>
@@ -56538,10 +56538,10 @@
         <v>2.7</v>
       </c>
       <c r="CL135" t="n">
-        <v>-68.18298154792468</v>
+        <v>-68.18298154802535</v>
       </c>
       <c r="CM135" t="n">
-        <v>-64.41820895742256</v>
+        <v>-64.41820895747995</v>
       </c>
       <c r="CN135" t="inlineStr">
         <is>
@@ -56818,10 +56818,10 @@
         <v>37.15000152587891</v>
       </c>
       <c r="BX136" t="n">
-        <v>8.367448548552685</v>
+        <v>8.36744854177276</v>
       </c>
       <c r="BY136" t="n">
-        <v>12.18300508669271</v>
+        <v>12.18300507682114</v>
       </c>
       <c r="BZ136" t="n">
         <v>8.093004102830763</v>
@@ -57130,25 +57130,25 @@
         <v>4.840000152587891</v>
       </c>
       <c r="BX137" t="n">
-        <v>1.502502732837283</v>
+        <v>1.502502741599506</v>
       </c>
       <c r="BY137" t="n">
-        <v>1.672911394360608</v>
+        <v>1.672911402026541</v>
       </c>
       <c r="BZ137" t="n">
-        <v>2.547478597058078</v>
+        <v>2.547478593875357</v>
       </c>
       <c r="CA137" t="n">
         <v>7.892423639597566</v>
       </c>
       <c r="CB137" t="n">
-        <v>1.797906282310984</v>
+        <v>1.797906285902958</v>
       </c>
       <c r="CC137" t="n">
-        <v>1.783573756944044</v>
+        <v>1.783573756695152</v>
       </c>
       <c r="CD137" t="n">
-        <v>1.110767096376859</v>
+        <v>1.11076709353159</v>
       </c>
       <c r="CE137" t="n">
         <v>0.03519118999648198</v>
@@ -57442,10 +57442,10 @@
         <v>1.990000009536743</v>
       </c>
       <c r="BX138" t="n">
-        <v>0.5586583822132701</v>
+        <v>0.5586583794511485</v>
       </c>
       <c r="BY138" t="n">
-        <v>0.8134066045025214</v>
+        <v>0.8134066004808723</v>
       </c>
       <c r="BZ138" t="n">
         <v>0.3613128508935427</v>
@@ -57508,7 +57508,7 @@
         <v>-0.9950239314132636</v>
       </c>
       <c r="CZ138" t="n">
-        <v>-53.22526227613638</v>
+        <v>-53.22525700906506</v>
       </c>
       <c r="DA138" t="b">
         <v>0</v>
@@ -57750,10 +57750,10 @@
         <v>6.889999866485596</v>
       </c>
       <c r="BX139" t="n">
-        <v>1.890787841647547</v>
+        <v>1.890787835526199</v>
       </c>
       <c r="BY139" t="n">
-        <v>2.752987097438828</v>
+        <v>2.752987088526146</v>
       </c>
       <c r="BZ139" t="n">
         <v>1.758861036118071</v>
@@ -58922,25 +58922,25 @@
         <v>4.539999961853027</v>
       </c>
       <c r="BX143" t="n">
-        <v>0.7601321081395994</v>
+        <v>0.7601321063839337</v>
       </c>
       <c r="BY143" t="n">
-        <v>0.7672876014117518</v>
+        <v>0.7672875997377082</v>
       </c>
       <c r="BZ143" t="n">
-        <v>0.8975551705530024</v>
+        <v>0.897555170667815</v>
       </c>
       <c r="CA143" t="n">
         <v>6.621863553251451</v>
       </c>
       <c r="CB143" t="n">
-        <v>0.306070586641194</v>
+        <v>0.3060705861614106</v>
       </c>
       <c r="CC143" t="n">
-        <v>0.4177451123060008</v>
+        <v>0.4177451123125095</v>
       </c>
       <c r="CD143" t="n">
-        <v>0.3415268765811094</v>
+        <v>0.3415268767031632</v>
       </c>
       <c r="CE143" t="inlineStr"/>
       <c r="CF143" t="inlineStr"/>
@@ -59236,10 +59236,10 @@
         <v>18.30999946594238</v>
       </c>
       <c r="BX144" t="n">
-        <v>27.85107504987825</v>
+        <v>27.85107496589993</v>
       </c>
       <c r="BY144" t="n">
-        <v>37.25854928894824</v>
+        <v>37.25854917660391</v>
       </c>
       <c r="BZ144" t="n">
         <v>2.504827732555547</v>
@@ -59248,7 +59248,7 @@
         <v>6.943403056792157</v>
       </c>
       <c r="CB144" t="n">
-        <v>6.421002848809036</v>
+        <v>6.421002831977304</v>
       </c>
       <c r="CC144" t="n">
         <v>3.046690502845772</v>
@@ -59550,10 +59550,10 @@
         <v>3.75</v>
       </c>
       <c r="BX145" t="n">
-        <v>0.6782855620196929</v>
+        <v>0.6782855620059272</v>
       </c>
       <c r="BY145" t="n">
-        <v>1.25821971754653</v>
+        <v>1.258219717520995</v>
       </c>
       <c r="BZ145" t="inlineStr"/>
       <c r="CA145" t="inlineStr"/>
@@ -59564,13 +59564,13 @@
         <v>3.40392002364466</v>
       </c>
       <c r="CF145" t="n">
-        <v>0.9682526397831117</v>
+        <v>0.968252639763461</v>
       </c>
       <c r="CG145" t="n">
-        <v>0.9682526397831117</v>
+        <v>0.968252639763461</v>
       </c>
       <c r="CH145" t="n">
-        <v>0.8714273758048006</v>
+        <v>0.8714273757871149</v>
       </c>
       <c r="CI145" t="n">
         <v>2</v>
@@ -59582,10 +59582,10 @@
         <v>5</v>
       </c>
       <c r="CL145" t="n">
-        <v>-76.76193664520532</v>
+        <v>-76.76193664567693</v>
       </c>
       <c r="CM145" t="n">
-        <v>-74.17992960578368</v>
+        <v>-74.17992960630771</v>
       </c>
       <c r="CN145" t="inlineStr">
         <is>
@@ -59862,10 +59862,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX146" t="n">
-        <v>9.498030429469232</v>
+        <v>9.49803045923322</v>
       </c>
       <c r="BY146" t="n">
-        <v>13.8291323053072</v>
+        <v>13.82913234864357</v>
       </c>
       <c r="BZ146" t="n">
         <v>4.692896643862964</v>
@@ -60794,10 +60794,10 @@
         <v>10.71000003814697</v>
       </c>
       <c r="BX149" t="n">
-        <v>5.72237090499523</v>
+        <v>5.722370899696617</v>
       </c>
       <c r="BY149" t="n">
-        <v>10.47405815277275</v>
+        <v>10.47405814307433</v>
       </c>
       <c r="BZ149" t="inlineStr"/>
       <c r="CA149" t="inlineStr"/>
@@ -60808,13 +60808,13 @@
         <v>2.986819537882496</v>
       </c>
       <c r="CF149" t="n">
-        <v>6.394416198550158</v>
+        <v>6.394416193551147</v>
       </c>
       <c r="CG149" t="n">
-        <v>5.72237090499523</v>
+        <v>5.722370899696617</v>
       </c>
       <c r="CH149" t="n">
-        <v>5.150133814495707</v>
+        <v>5.150133809726956</v>
       </c>
       <c r="CI149" t="n">
         <v>3</v>
@@ -60826,10 +60826,10 @@
         <v>3.5</v>
       </c>
       <c r="CL149" t="n">
-        <v>-51.91284970913244</v>
+        <v>-51.9128497536586</v>
       </c>
       <c r="CM149" t="n">
-        <v>-40.29490031956611</v>
+        <v>-40.29490036624222</v>
       </c>
       <c r="CN149" t="inlineStr">
         <is>
@@ -61010,13 +61010,13 @@
         <v>1</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AS150" t="b">
         <v>1</v>
       </c>
       <c r="AT150" t="n">
-        <v>51254054912</v>
+        <v>51058106368</v>
       </c>
       <c r="AU150" t="n">
         <v>52.72</v>
@@ -61422,10 +61422,10 @@
         <v>15.35000038146973</v>
       </c>
       <c r="BX151" t="n">
-        <v>3.926670165568006</v>
+        <v>3.926670164688034</v>
       </c>
       <c r="BY151" t="n">
-        <v>5.717231761067017</v>
+        <v>5.717231759785779</v>
       </c>
       <c r="BZ151" t="inlineStr"/>
       <c r="CA151" t="inlineStr"/>
@@ -61436,7 +61436,7 @@
         <v>5.079183152512682</v>
       </c>
       <c r="CF151" t="n">
-        <v>4.907695026382568</v>
+        <v>4.907695025662165</v>
       </c>
       <c r="CG151" t="n">
         <v>5.079183152512682</v>
@@ -61457,7 +61457,7 @@
         <v>-70.21977378723865</v>
       </c>
       <c r="CM151" t="n">
-        <v>-68.0280462252818</v>
+        <v>-68.02804622997498</v>
       </c>
       <c r="CN151" t="inlineStr">
         <is>
